--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA221"/>
+  <dimension ref="A1:AA222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18419,76 +18419,76 @@
         <v>8</v>
       </c>
       <c r="D217" t="n">
-        <v>3376</v>
+        <v>3282</v>
       </c>
       <c r="E217" t="n">
-        <v>3180</v>
+        <v>3112</v>
       </c>
       <c r="F217" t="n">
-        <v>3074</v>
+        <v>3022</v>
       </c>
       <c r="G217" t="n">
-        <v>3024</v>
+        <v>2979</v>
       </c>
       <c r="H217" t="n">
-        <v>3017</v>
+        <v>2974</v>
       </c>
       <c r="I217" t="n">
-        <v>3112</v>
+        <v>3067</v>
       </c>
       <c r="J217" t="n">
-        <v>3386</v>
+        <v>3338</v>
       </c>
       <c r="K217" t="n">
-        <v>3666</v>
+        <v>3614</v>
       </c>
       <c r="L217" t="n">
-        <v>3976</v>
+        <v>3916</v>
       </c>
       <c r="M217" t="n">
-        <v>4144</v>
+        <v>4074</v>
       </c>
       <c r="N217" t="n">
-        <v>4222</v>
+        <v>4142</v>
       </c>
       <c r="O217" t="n">
-        <v>4329</v>
+        <v>4249</v>
       </c>
       <c r="P217" t="n">
+        <v>4316</v>
+      </c>
+      <c r="Q217" t="n">
+        <v>4466</v>
+      </c>
+      <c r="R217" t="n">
         <v>4397</v>
       </c>
-      <c r="Q217" t="n">
-        <v>4549</v>
-      </c>
-      <c r="R217" t="n">
-        <v>4502</v>
-      </c>
       <c r="S217" t="n">
-        <v>4484</v>
+        <v>4350</v>
       </c>
       <c r="T217" t="n">
-        <v>4420</v>
+        <v>4278</v>
       </c>
       <c r="U217" t="n">
-        <v>4387</v>
+        <v>4242</v>
       </c>
       <c r="V217" t="n">
-        <v>4712</v>
+        <v>4526</v>
       </c>
       <c r="W217" t="n">
-        <v>4683</v>
+        <v>4504</v>
       </c>
       <c r="X217" t="n">
-        <v>4682</v>
+        <v>4550</v>
       </c>
       <c r="Y217" t="n">
-        <v>4388</v>
+        <v>4244</v>
       </c>
       <c r="Z217" t="n">
-        <v>4018</v>
+        <v>3930</v>
       </c>
       <c r="AA217" t="n">
-        <v>3676</v>
+        <v>3636</v>
       </c>
     </row>
     <row r="218">
@@ -18502,76 +18502,76 @@
         <v>9</v>
       </c>
       <c r="D218" t="n">
-        <v>3366</v>
+        <v>3276</v>
       </c>
       <c r="E218" t="n">
-        <v>3173</v>
+        <v>3107</v>
       </c>
       <c r="F218" t="n">
-        <v>3069</v>
+        <v>3019</v>
       </c>
       <c r="G218" t="n">
-        <v>3019</v>
+        <v>2976</v>
       </c>
       <c r="H218" t="n">
-        <v>3012</v>
+        <v>2971</v>
       </c>
       <c r="I218" t="n">
-        <v>3106</v>
+        <v>3064</v>
       </c>
       <c r="J218" t="n">
-        <v>3377</v>
+        <v>3333</v>
       </c>
       <c r="K218" t="n">
-        <v>3655</v>
+        <v>3608</v>
       </c>
       <c r="L218" t="n">
-        <v>3962</v>
+        <v>3907</v>
       </c>
       <c r="M218" t="n">
-        <v>4129</v>
+        <v>4065</v>
       </c>
       <c r="N218" t="n">
-        <v>4206</v>
+        <v>4133</v>
       </c>
       <c r="O218" t="n">
-        <v>4312</v>
+        <v>4239</v>
       </c>
       <c r="P218" t="n">
-        <v>4380</v>
+        <v>4305</v>
       </c>
       <c r="Q218" t="n">
-        <v>4530</v>
+        <v>4455</v>
       </c>
       <c r="R218" t="n">
-        <v>4483</v>
+        <v>4385</v>
       </c>
       <c r="S218" t="n">
-        <v>4465</v>
+        <v>4339</v>
       </c>
       <c r="T218" t="n">
-        <v>4401</v>
+        <v>4267</v>
       </c>
       <c r="U218" t="n">
-        <v>4369</v>
+        <v>4231</v>
       </c>
       <c r="V218" t="n">
-        <v>4699</v>
+        <v>4519</v>
       </c>
       <c r="W218" t="n">
-        <v>4671</v>
+        <v>4496</v>
       </c>
       <c r="X218" t="n">
-        <v>4670</v>
+        <v>4497</v>
       </c>
       <c r="Y218" t="n">
-        <v>4377</v>
+        <v>4237</v>
       </c>
       <c r="Z218" t="n">
-        <v>4009</v>
+        <v>3924</v>
       </c>
       <c r="AA218" t="n">
-        <v>3669</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="219">
@@ -18585,76 +18585,76 @@
         <v>10</v>
       </c>
       <c r="D219" t="n">
-        <v>3372</v>
+        <v>3282</v>
       </c>
       <c r="E219" t="n">
-        <v>3177</v>
+        <v>3112</v>
       </c>
       <c r="F219" t="n">
-        <v>3072</v>
+        <v>3023</v>
       </c>
       <c r="G219" t="n">
-        <v>3023</v>
+        <v>2980</v>
       </c>
       <c r="H219" t="n">
-        <v>3015</v>
+        <v>2974</v>
       </c>
       <c r="I219" t="n">
-        <v>3110</v>
+        <v>3068</v>
       </c>
       <c r="J219" t="n">
-        <v>3383</v>
+        <v>3338</v>
       </c>
       <c r="K219" t="n">
-        <v>3662</v>
+        <v>3615</v>
       </c>
       <c r="L219" t="n">
-        <v>3970</v>
+        <v>3916</v>
       </c>
       <c r="M219" t="n">
-        <v>4139</v>
+        <v>4075</v>
       </c>
       <c r="N219" t="n">
-        <v>4216</v>
+        <v>4143</v>
       </c>
       <c r="O219" t="n">
-        <v>4322</v>
+        <v>4249</v>
       </c>
       <c r="P219" t="n">
-        <v>4391</v>
+        <v>4317</v>
       </c>
       <c r="Q219" t="n">
-        <v>4541</v>
+        <v>4467</v>
       </c>
       <c r="R219" t="n">
-        <v>4495</v>
+        <v>4397</v>
       </c>
       <c r="S219" t="n">
-        <v>4477</v>
+        <v>4351</v>
       </c>
       <c r="T219" t="n">
-        <v>4413</v>
+        <v>4278</v>
       </c>
       <c r="U219" t="n">
-        <v>4380</v>
+        <v>4242</v>
       </c>
       <c r="V219" t="n">
-        <v>4707</v>
+        <v>4526</v>
       </c>
       <c r="W219" t="n">
-        <v>4678</v>
+        <v>4504</v>
       </c>
       <c r="X219" t="n">
-        <v>4677</v>
+        <v>4504</v>
       </c>
       <c r="Y219" t="n">
-        <v>4384</v>
+        <v>4244</v>
       </c>
       <c r="Z219" t="n">
-        <v>4015</v>
+        <v>3930</v>
       </c>
       <c r="AA219" t="n">
-        <v>3673</v>
+        <v>3636</v>
       </c>
     </row>
     <row r="220">
@@ -18668,76 +18668,76 @@
         <v>11</v>
       </c>
       <c r="D220" t="n">
-        <v>3379</v>
+        <v>3291</v>
       </c>
       <c r="E220" t="n">
-        <v>3182</v>
+        <v>3118</v>
       </c>
       <c r="F220" t="n">
-        <v>3077</v>
+        <v>3028</v>
       </c>
       <c r="G220" t="n">
-        <v>3026</v>
+        <v>2984</v>
       </c>
       <c r="H220" t="n">
-        <v>3019</v>
+        <v>2978</v>
       </c>
       <c r="I220" t="n">
-        <v>3114</v>
+        <v>3073</v>
       </c>
       <c r="J220" t="n">
-        <v>3389</v>
+        <v>3346</v>
       </c>
       <c r="K220" t="n">
-        <v>3670</v>
+        <v>3624</v>
       </c>
       <c r="L220" t="n">
-        <v>3980</v>
+        <v>3928</v>
       </c>
       <c r="M220" t="n">
-        <v>4150</v>
+        <v>4089</v>
       </c>
       <c r="N220" t="n">
-        <v>4227</v>
+        <v>4157</v>
       </c>
       <c r="O220" t="n">
-        <v>4335</v>
+        <v>4265</v>
       </c>
       <c r="P220" t="n">
-        <v>4404</v>
+        <v>4332</v>
       </c>
       <c r="Q220" t="n">
-        <v>4555</v>
+        <v>4484</v>
       </c>
       <c r="R220" t="n">
-        <v>4509</v>
+        <v>4414</v>
       </c>
       <c r="S220" t="n">
-        <v>4491</v>
+        <v>4367</v>
       </c>
       <c r="T220" t="n">
-        <v>4426</v>
+        <v>4295</v>
       </c>
       <c r="U220" t="n">
-        <v>4394</v>
+        <v>4259</v>
       </c>
       <c r="V220" t="n">
-        <v>4636</v>
+        <v>4457</v>
       </c>
       <c r="W220" t="n">
-        <v>4608</v>
+        <v>4436</v>
       </c>
       <c r="X220" t="n">
-        <v>4607</v>
+        <v>4436</v>
       </c>
       <c r="Y220" t="n">
-        <v>4322</v>
+        <v>4184</v>
       </c>
       <c r="Z220" t="n">
-        <v>3962</v>
+        <v>3879</v>
       </c>
       <c r="AA220" t="n">
-        <v>3630</v>
+        <v>3594</v>
       </c>
     </row>
     <row r="221">
@@ -18751,76 +18751,159 @@
         <v>12</v>
       </c>
       <c r="D221" t="n">
-        <v>3368</v>
+        <v>3267</v>
       </c>
       <c r="E221" t="n">
-        <v>3157</v>
+        <v>3086</v>
       </c>
       <c r="F221" t="n">
-        <v>3051</v>
+        <v>3000</v>
       </c>
       <c r="G221" t="n">
-        <v>2982</v>
+        <v>2934</v>
       </c>
       <c r="H221" t="n">
-        <v>2948</v>
+        <v>2902</v>
       </c>
       <c r="I221" t="n">
-        <v>2975</v>
+        <v>2930</v>
       </c>
       <c r="J221" t="n">
-        <v>3072</v>
+        <v>3046</v>
       </c>
       <c r="K221" t="n">
-        <v>3247</v>
+        <v>3269</v>
       </c>
       <c r="L221" t="n">
-        <v>3562</v>
+        <v>3542</v>
       </c>
       <c r="M221" t="n">
-        <v>3803</v>
+        <v>3855</v>
       </c>
       <c r="N221" t="n">
-        <v>3968</v>
+        <v>4001</v>
       </c>
       <c r="O221" t="n">
-        <v>4086</v>
+        <v>4143</v>
       </c>
       <c r="P221" t="n">
-        <v>4178</v>
+        <v>4001</v>
       </c>
       <c r="Q221" t="n">
-        <v>4234</v>
+        <v>4001</v>
       </c>
       <c r="R221" t="n">
-        <v>4186</v>
+        <v>4001</v>
       </c>
       <c r="S221" t="n">
-        <v>4164</v>
+        <v>4012</v>
       </c>
       <c r="T221" t="n">
-        <v>4233</v>
+        <v>4128</v>
       </c>
       <c r="U221" t="n">
-        <v>4358</v>
+        <v>4224</v>
       </c>
       <c r="V221" t="n">
-        <v>4432</v>
+        <v>4239</v>
       </c>
       <c r="W221" t="n">
-        <v>4399</v>
+        <v>4169</v>
       </c>
       <c r="X221" t="n">
+        <v>4167</v>
+      </c>
+      <c r="Y221" t="n">
+        <v>4043</v>
+      </c>
+      <c r="Z221" t="n">
+        <v>3727</v>
+      </c>
+      <c r="AA221" t="n">
+        <v>3481</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B222" t="n">
+        <v>9</v>
+      </c>
+      <c r="C222" t="n">
+        <v>13</v>
+      </c>
+      <c r="D222" t="n">
+        <v>3198</v>
+      </c>
+      <c r="E222" t="n">
+        <v>3020</v>
+      </c>
+      <c r="F222" t="n">
+        <v>2918</v>
+      </c>
+      <c r="G222" t="n">
+        <v>2866</v>
+      </c>
+      <c r="H222" t="n">
+        <v>2845</v>
+      </c>
+      <c r="I222" t="n">
+        <v>2860</v>
+      </c>
+      <c r="J222" t="n">
+        <v>2929</v>
+      </c>
+      <c r="K222" t="n">
+        <v>3062</v>
+      </c>
+      <c r="L222" t="n">
+        <v>3363</v>
+      </c>
+      <c r="M222" t="n">
+        <v>3636</v>
+      </c>
+      <c r="N222" t="n">
+        <v>3822</v>
+      </c>
+      <c r="O222" t="n">
+        <v>4026</v>
+      </c>
+      <c r="P222" t="n">
+        <v>4115</v>
+      </c>
+      <c r="Q222" t="n">
+        <v>4080</v>
+      </c>
+      <c r="R222" t="n">
+        <v>4052</v>
+      </c>
+      <c r="S222" t="n">
+        <v>4029</v>
+      </c>
+      <c r="T222" t="n">
+        <v>4136</v>
+      </c>
+      <c r="U222" t="n">
+        <v>4239</v>
+      </c>
+      <c r="V222" t="n">
+        <v>4414</v>
+      </c>
+      <c r="W222" t="n">
         <v>4409</v>
       </c>
-      <c r="Y221" t="n">
-        <v>4124</v>
-      </c>
-      <c r="Z221" t="n">
-        <v>3784</v>
-      </c>
-      <c r="AA221" t="n">
-        <v>3526</v>
+      <c r="X222" t="n">
+        <v>4448</v>
+      </c>
+      <c r="Y222" t="n">
+        <v>4200</v>
+      </c>
+      <c r="Z222" t="n">
+        <v>3862</v>
+      </c>
+      <c r="AA222" t="n">
+        <v>3564</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA222"/>
+  <dimension ref="A1:AA223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18502,76 +18502,76 @@
         <v>9</v>
       </c>
       <c r="D218" t="n">
-        <v>3276</v>
+        <v>3315</v>
       </c>
       <c r="E218" t="n">
-        <v>3107</v>
+        <v>3163</v>
       </c>
       <c r="F218" t="n">
-        <v>3019</v>
+        <v>3084</v>
       </c>
       <c r="G218" t="n">
-        <v>2976</v>
+        <v>3052</v>
       </c>
       <c r="H218" t="n">
-        <v>2971</v>
+        <v>3043</v>
       </c>
       <c r="I218" t="n">
-        <v>3064</v>
+        <v>3134</v>
       </c>
       <c r="J218" t="n">
-        <v>3333</v>
+        <v>3390</v>
       </c>
       <c r="K218" t="n">
-        <v>3608</v>
+        <v>3646</v>
       </c>
       <c r="L218" t="n">
-        <v>3907</v>
+        <v>3911</v>
       </c>
       <c r="M218" t="n">
-        <v>4065</v>
+        <v>4037</v>
       </c>
       <c r="N218" t="n">
-        <v>4133</v>
+        <v>4086</v>
       </c>
       <c r="O218" t="n">
-        <v>4239</v>
+        <v>4179</v>
       </c>
       <c r="P218" t="n">
-        <v>4305</v>
+        <v>4245</v>
       </c>
       <c r="Q218" t="n">
-        <v>4455</v>
+        <v>4363</v>
       </c>
       <c r="R218" t="n">
-        <v>4385</v>
+        <v>4363</v>
       </c>
       <c r="S218" t="n">
-        <v>4339</v>
+        <v>4363</v>
       </c>
       <c r="T218" t="n">
-        <v>4267</v>
+        <v>4324</v>
       </c>
       <c r="U218" t="n">
-        <v>4231</v>
+        <v>4322</v>
       </c>
       <c r="V218" t="n">
-        <v>4519</v>
+        <v>4421</v>
       </c>
       <c r="W218" t="n">
-        <v>4496</v>
+        <v>4396</v>
       </c>
       <c r="X218" t="n">
-        <v>4497</v>
+        <v>4404</v>
       </c>
       <c r="Y218" t="n">
-        <v>4237</v>
+        <v>4161</v>
       </c>
       <c r="Z218" t="n">
-        <v>3924</v>
+        <v>3867</v>
       </c>
       <c r="AA218" t="n">
-        <v>3632</v>
+        <v>3586</v>
       </c>
     </row>
     <row r="219">
@@ -18585,76 +18585,76 @@
         <v>10</v>
       </c>
       <c r="D219" t="n">
-        <v>3282</v>
+        <v>3329</v>
       </c>
       <c r="E219" t="n">
-        <v>3112</v>
+        <v>3174</v>
       </c>
       <c r="F219" t="n">
-        <v>3023</v>
+        <v>3093</v>
       </c>
       <c r="G219" t="n">
-        <v>2980</v>
+        <v>3059</v>
       </c>
       <c r="H219" t="n">
-        <v>2974</v>
+        <v>3050</v>
       </c>
       <c r="I219" t="n">
-        <v>3068</v>
+        <v>3143</v>
       </c>
       <c r="J219" t="n">
-        <v>3338</v>
+        <v>3402</v>
       </c>
       <c r="K219" t="n">
-        <v>3615</v>
+        <v>3662</v>
       </c>
       <c r="L219" t="n">
-        <v>3916</v>
+        <v>3932</v>
       </c>
       <c r="M219" t="n">
-        <v>4075</v>
+        <v>4060</v>
       </c>
       <c r="N219" t="n">
-        <v>4143</v>
+        <v>4110</v>
       </c>
       <c r="O219" t="n">
-        <v>4249</v>
+        <v>4204</v>
       </c>
       <c r="P219" t="n">
-        <v>4317</v>
+        <v>4272</v>
       </c>
       <c r="Q219" t="n">
-        <v>4467</v>
+        <v>4391</v>
       </c>
       <c r="R219" t="n">
-        <v>4397</v>
+        <v>4391</v>
       </c>
       <c r="S219" t="n">
+        <v>4391</v>
+      </c>
+      <c r="T219" t="n">
         <v>4351</v>
       </c>
-      <c r="T219" t="n">
-        <v>4278</v>
-      </c>
       <c r="U219" t="n">
-        <v>4242</v>
+        <v>4349</v>
       </c>
       <c r="V219" t="n">
-        <v>4526</v>
+        <v>4439</v>
       </c>
       <c r="W219" t="n">
-        <v>4504</v>
+        <v>4414</v>
       </c>
       <c r="X219" t="n">
-        <v>4504</v>
+        <v>4422</v>
       </c>
       <c r="Y219" t="n">
-        <v>4244</v>
+        <v>4176</v>
       </c>
       <c r="Z219" t="n">
-        <v>3930</v>
+        <v>3880</v>
       </c>
       <c r="AA219" t="n">
-        <v>3636</v>
+        <v>3596</v>
       </c>
     </row>
     <row r="220">
@@ -18668,76 +18668,76 @@
         <v>11</v>
       </c>
       <c r="D220" t="n">
-        <v>3291</v>
+        <v>3346</v>
       </c>
       <c r="E220" t="n">
-        <v>3118</v>
+        <v>3186</v>
       </c>
       <c r="F220" t="n">
-        <v>3028</v>
+        <v>3102</v>
       </c>
       <c r="G220" t="n">
-        <v>2984</v>
+        <v>3068</v>
       </c>
       <c r="H220" t="n">
-        <v>2978</v>
+        <v>3059</v>
       </c>
       <c r="I220" t="n">
-        <v>3073</v>
+        <v>3153</v>
       </c>
       <c r="J220" t="n">
-        <v>3346</v>
+        <v>3417</v>
       </c>
       <c r="K220" t="n">
-        <v>3624</v>
+        <v>3682</v>
       </c>
       <c r="L220" t="n">
-        <v>3928</v>
+        <v>3956</v>
       </c>
       <c r="M220" t="n">
-        <v>4089</v>
+        <v>4086</v>
       </c>
       <c r="N220" t="n">
-        <v>4157</v>
+        <v>4137</v>
       </c>
       <c r="O220" t="n">
-        <v>4265</v>
+        <v>4232</v>
       </c>
       <c r="P220" t="n">
-        <v>4332</v>
+        <v>4301</v>
       </c>
       <c r="Q220" t="n">
-        <v>4484</v>
+        <v>4423</v>
       </c>
       <c r="R220" t="n">
-        <v>4414</v>
+        <v>4423</v>
       </c>
       <c r="S220" t="n">
-        <v>4367</v>
+        <v>4423</v>
       </c>
       <c r="T220" t="n">
-        <v>4295</v>
+        <v>4382</v>
       </c>
       <c r="U220" t="n">
-        <v>4259</v>
+        <v>4380</v>
       </c>
       <c r="V220" t="n">
-        <v>4457</v>
+        <v>4380</v>
       </c>
       <c r="W220" t="n">
-        <v>4436</v>
+        <v>4355</v>
       </c>
       <c r="X220" t="n">
-        <v>4436</v>
+        <v>4363</v>
       </c>
       <c r="Y220" t="n">
-        <v>4184</v>
+        <v>4124</v>
       </c>
       <c r="Z220" t="n">
-        <v>3879</v>
+        <v>3835</v>
       </c>
       <c r="AA220" t="n">
-        <v>3594</v>
+        <v>3559</v>
       </c>
     </row>
     <row r="221">
@@ -18751,76 +18751,76 @@
         <v>12</v>
       </c>
       <c r="D221" t="n">
-        <v>3267</v>
+        <v>3333</v>
       </c>
       <c r="E221" t="n">
-        <v>3086</v>
+        <v>3161</v>
       </c>
       <c r="F221" t="n">
-        <v>3000</v>
+        <v>3080</v>
       </c>
       <c r="G221" t="n">
-        <v>2934</v>
+        <v>3018</v>
       </c>
       <c r="H221" t="n">
-        <v>2902</v>
+        <v>2987</v>
       </c>
       <c r="I221" t="n">
-        <v>2930</v>
+        <v>3012</v>
       </c>
       <c r="J221" t="n">
-        <v>3046</v>
+        <v>3115</v>
       </c>
       <c r="K221" t="n">
-        <v>3269</v>
+        <v>3314</v>
       </c>
       <c r="L221" t="n">
-        <v>3542</v>
+        <v>3558</v>
       </c>
       <c r="M221" t="n">
-        <v>3855</v>
+        <v>3836</v>
       </c>
       <c r="N221" t="n">
-        <v>4001</v>
+        <v>3966</v>
       </c>
       <c r="O221" t="n">
-        <v>4143</v>
+        <v>4092</v>
       </c>
       <c r="P221" t="n">
-        <v>4001</v>
+        <v>4145</v>
       </c>
       <c r="Q221" t="n">
-        <v>4001</v>
+        <v>4145</v>
       </c>
       <c r="R221" t="n">
-        <v>4001</v>
+        <v>4145</v>
       </c>
       <c r="S221" t="n">
-        <v>4012</v>
+        <v>4146</v>
       </c>
       <c r="T221" t="n">
-        <v>4128</v>
+        <v>4161</v>
       </c>
       <c r="U221" t="n">
-        <v>4224</v>
+        <v>4172</v>
       </c>
       <c r="V221" t="n">
-        <v>4239</v>
+        <v>4174</v>
       </c>
       <c r="W221" t="n">
-        <v>4169</v>
+        <v>4107</v>
       </c>
       <c r="X221" t="n">
-        <v>4167</v>
+        <v>4106</v>
       </c>
       <c r="Y221" t="n">
-        <v>4043</v>
+        <v>3988</v>
       </c>
       <c r="Z221" t="n">
-        <v>3727</v>
+        <v>3688</v>
       </c>
       <c r="AA221" t="n">
-        <v>3481</v>
+        <v>3453</v>
       </c>
     </row>
     <row r="222">
@@ -18834,76 +18834,159 @@
         <v>13</v>
       </c>
       <c r="D222" t="n">
-        <v>3198</v>
+        <v>3268</v>
       </c>
       <c r="E222" t="n">
-        <v>3020</v>
+        <v>3101</v>
       </c>
       <c r="F222" t="n">
-        <v>2918</v>
+        <v>3017</v>
       </c>
       <c r="G222" t="n">
-        <v>2866</v>
+        <v>2959</v>
       </c>
       <c r="H222" t="n">
-        <v>2845</v>
+        <v>2933</v>
       </c>
       <c r="I222" t="n">
-        <v>2860</v>
+        <v>2953</v>
       </c>
       <c r="J222" t="n">
-        <v>2929</v>
+        <v>3043</v>
       </c>
       <c r="K222" t="n">
-        <v>3062</v>
+        <v>3222</v>
       </c>
       <c r="L222" t="n">
-        <v>3363</v>
+        <v>3466</v>
       </c>
       <c r="M222" t="n">
-        <v>3636</v>
+        <v>3761</v>
       </c>
       <c r="N222" t="n">
-        <v>3822</v>
+        <v>3904</v>
       </c>
       <c r="O222" t="n">
-        <v>4026</v>
+        <v>4074</v>
       </c>
       <c r="P222" t="n">
-        <v>4115</v>
+        <v>4186</v>
       </c>
       <c r="Q222" t="n">
-        <v>4080</v>
+        <v>4186</v>
       </c>
       <c r="R222" t="n">
-        <v>4052</v>
+        <v>4186</v>
       </c>
       <c r="S222" t="n">
-        <v>4029</v>
+        <v>4197</v>
       </c>
       <c r="T222" t="n">
-        <v>4136</v>
+        <v>4293</v>
       </c>
       <c r="U222" t="n">
-        <v>4239</v>
+        <v>4354</v>
       </c>
       <c r="V222" t="n">
-        <v>4414</v>
+        <v>4382</v>
       </c>
       <c r="W222" t="n">
-        <v>4409</v>
+        <v>4315</v>
       </c>
       <c r="X222" t="n">
-        <v>4448</v>
+        <v>4321</v>
       </c>
       <c r="Y222" t="n">
-        <v>4200</v>
+        <v>4195</v>
       </c>
       <c r="Z222" t="n">
-        <v>3862</v>
+        <v>3837</v>
       </c>
       <c r="AA222" t="n">
-        <v>3564</v>
+        <v>3539</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B223" t="n">
+        <v>9</v>
+      </c>
+      <c r="C223" t="n">
+        <v>14</v>
+      </c>
+      <c r="D223" t="n">
+        <v>3298</v>
+      </c>
+      <c r="E223" t="n">
+        <v>3139</v>
+      </c>
+      <c r="F223" t="n">
+        <v>3053</v>
+      </c>
+      <c r="G223" t="n">
+        <v>3013</v>
+      </c>
+      <c r="H223" t="n">
+        <v>3003</v>
+      </c>
+      <c r="I223" t="n">
+        <v>3073</v>
+      </c>
+      <c r="J223" t="n">
+        <v>3318</v>
+      </c>
+      <c r="K223" t="n">
+        <v>3631</v>
+      </c>
+      <c r="L223" t="n">
+        <v>3984</v>
+      </c>
+      <c r="M223" t="n">
+        <v>4234</v>
+      </c>
+      <c r="N223" t="n">
+        <v>4372</v>
+      </c>
+      <c r="O223" t="n">
+        <v>4451</v>
+      </c>
+      <c r="P223" t="n">
+        <v>4454</v>
+      </c>
+      <c r="Q223" t="n">
+        <v>4536</v>
+      </c>
+      <c r="R223" t="n">
+        <v>4498</v>
+      </c>
+      <c r="S223" t="n">
+        <v>4502</v>
+      </c>
+      <c r="T223" t="n">
+        <v>4540</v>
+      </c>
+      <c r="U223" t="n">
+        <v>4553</v>
+      </c>
+      <c r="V223" t="n">
+        <v>4568</v>
+      </c>
+      <c r="W223" t="n">
+        <v>4570</v>
+      </c>
+      <c r="X223" t="n">
+        <v>4592</v>
+      </c>
+      <c r="Y223" t="n">
+        <v>4353</v>
+      </c>
+      <c r="Z223" t="n">
+        <v>3967</v>
+      </c>
+      <c r="AA223" t="n">
+        <v>3694</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA223"/>
+  <dimension ref="A1:AA224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18585,76 +18585,76 @@
         <v>10</v>
       </c>
       <c r="D219" t="n">
-        <v>3329</v>
+        <v>3233</v>
       </c>
       <c r="E219" t="n">
-        <v>3174</v>
+        <v>3072</v>
       </c>
       <c r="F219" t="n">
-        <v>3093</v>
+        <v>2988</v>
       </c>
       <c r="G219" t="n">
-        <v>3059</v>
+        <v>2955</v>
       </c>
       <c r="H219" t="n">
-        <v>3050</v>
+        <v>2950</v>
       </c>
       <c r="I219" t="n">
-        <v>3143</v>
+        <v>3049</v>
       </c>
       <c r="J219" t="n">
-        <v>3402</v>
+        <v>3325</v>
       </c>
       <c r="K219" t="n">
-        <v>3662</v>
+        <v>3595</v>
       </c>
       <c r="L219" t="n">
-        <v>3932</v>
+        <v>3868</v>
       </c>
       <c r="M219" t="n">
-        <v>4060</v>
+        <v>3992</v>
       </c>
       <c r="N219" t="n">
-        <v>4110</v>
+        <v>4036</v>
       </c>
       <c r="O219" t="n">
-        <v>4204</v>
+        <v>4122</v>
       </c>
       <c r="P219" t="n">
-        <v>4272</v>
+        <v>4186</v>
       </c>
       <c r="Q219" t="n">
-        <v>4391</v>
+        <v>4310</v>
       </c>
       <c r="R219" t="n">
-        <v>4391</v>
+        <v>4310</v>
       </c>
       <c r="S219" t="n">
-        <v>4391</v>
+        <v>4310</v>
       </c>
       <c r="T219" t="n">
-        <v>4351</v>
+        <v>4244</v>
       </c>
       <c r="U219" t="n">
-        <v>4349</v>
+        <v>4263</v>
       </c>
       <c r="V219" t="n">
-        <v>4439</v>
+        <v>4329</v>
       </c>
       <c r="W219" t="n">
-        <v>4414</v>
+        <v>4292</v>
       </c>
       <c r="X219" t="n">
-        <v>4422</v>
+        <v>4392</v>
       </c>
       <c r="Y219" t="n">
-        <v>4176</v>
+        <v>4146</v>
       </c>
       <c r="Z219" t="n">
-        <v>3880</v>
+        <v>3846</v>
       </c>
       <c r="AA219" t="n">
-        <v>3596</v>
+        <v>3561</v>
       </c>
     </row>
     <row r="220">
@@ -18668,76 +18668,76 @@
         <v>11</v>
       </c>
       <c r="D220" t="n">
-        <v>3346</v>
+        <v>3253</v>
       </c>
       <c r="E220" t="n">
-        <v>3186</v>
+        <v>3086</v>
       </c>
       <c r="F220" t="n">
-        <v>3102</v>
+        <v>2999</v>
       </c>
       <c r="G220" t="n">
-        <v>3068</v>
+        <v>2965</v>
       </c>
       <c r="H220" t="n">
-        <v>3059</v>
+        <v>2959</v>
       </c>
       <c r="I220" t="n">
-        <v>3153</v>
+        <v>3060</v>
       </c>
       <c r="J220" t="n">
-        <v>3417</v>
+        <v>3342</v>
       </c>
       <c r="K220" t="n">
-        <v>3682</v>
+        <v>3618</v>
       </c>
       <c r="L220" t="n">
-        <v>3956</v>
+        <v>3896</v>
       </c>
       <c r="M220" t="n">
-        <v>4086</v>
+        <v>4022</v>
       </c>
       <c r="N220" t="n">
-        <v>4137</v>
+        <v>4067</v>
       </c>
       <c r="O220" t="n">
-        <v>4232</v>
+        <v>4154</v>
       </c>
       <c r="P220" t="n">
+        <v>4220</v>
+      </c>
+      <c r="Q220" t="n">
+        <v>4346</v>
+      </c>
+      <c r="R220" t="n">
+        <v>4346</v>
+      </c>
+      <c r="S220" t="n">
+        <v>4346</v>
+      </c>
+      <c r="T220" t="n">
+        <v>4290</v>
+      </c>
+      <c r="U220" t="n">
+        <v>4294</v>
+      </c>
+      <c r="V220" t="n">
+        <v>4309</v>
+      </c>
+      <c r="W220" t="n">
         <v>4301</v>
       </c>
-      <c r="Q220" t="n">
-        <v>4423</v>
-      </c>
-      <c r="R220" t="n">
-        <v>4423</v>
-      </c>
-      <c r="S220" t="n">
-        <v>4423</v>
-      </c>
-      <c r="T220" t="n">
-        <v>4382</v>
-      </c>
-      <c r="U220" t="n">
-        <v>4380</v>
-      </c>
-      <c r="V220" t="n">
-        <v>4380</v>
-      </c>
-      <c r="W220" t="n">
-        <v>4355</v>
-      </c>
       <c r="X220" t="n">
-        <v>4363</v>
+        <v>4323</v>
       </c>
       <c r="Y220" t="n">
-        <v>4124</v>
+        <v>4087</v>
       </c>
       <c r="Z220" t="n">
-        <v>3835</v>
+        <v>3800</v>
       </c>
       <c r="AA220" t="n">
-        <v>3559</v>
+        <v>3526</v>
       </c>
     </row>
     <row r="221">
@@ -18751,76 +18751,76 @@
         <v>12</v>
       </c>
       <c r="D221" t="n">
-        <v>3333</v>
+        <v>3228</v>
       </c>
       <c r="E221" t="n">
-        <v>3161</v>
+        <v>3060</v>
       </c>
       <c r="F221" t="n">
-        <v>3080</v>
+        <v>2970</v>
       </c>
       <c r="G221" t="n">
-        <v>3018</v>
+        <v>2915</v>
       </c>
       <c r="H221" t="n">
-        <v>2987</v>
+        <v>2882</v>
       </c>
       <c r="I221" t="n">
-        <v>3012</v>
+        <v>2906</v>
       </c>
       <c r="J221" t="n">
-        <v>3115</v>
+        <v>3022</v>
       </c>
       <c r="K221" t="n">
-        <v>3314</v>
+        <v>3178</v>
       </c>
       <c r="L221" t="n">
-        <v>3558</v>
+        <v>3444</v>
       </c>
       <c r="M221" t="n">
-        <v>3836</v>
+        <v>3619</v>
       </c>
       <c r="N221" t="n">
-        <v>3966</v>
+        <v>3759</v>
       </c>
       <c r="O221" t="n">
-        <v>4092</v>
+        <v>3844</v>
       </c>
       <c r="P221" t="n">
-        <v>4145</v>
+        <v>3937</v>
       </c>
       <c r="Q221" t="n">
-        <v>4145</v>
+        <v>4000</v>
       </c>
       <c r="R221" t="n">
-        <v>4145</v>
+        <v>4000</v>
       </c>
       <c r="S221" t="n">
-        <v>4146</v>
+        <v>4011</v>
       </c>
       <c r="T221" t="n">
-        <v>4161</v>
+        <v>4029</v>
       </c>
       <c r="U221" t="n">
-        <v>4172</v>
+        <v>4086</v>
       </c>
       <c r="V221" t="n">
-        <v>4174</v>
+        <v>4103</v>
       </c>
       <c r="W221" t="n">
-        <v>4107</v>
+        <v>4077</v>
       </c>
       <c r="X221" t="n">
-        <v>4106</v>
+        <v>4026</v>
       </c>
       <c r="Y221" t="n">
-        <v>3988</v>
+        <v>3818</v>
       </c>
       <c r="Z221" t="n">
-        <v>3688</v>
+        <v>3597</v>
       </c>
       <c r="AA221" t="n">
-        <v>3453</v>
+        <v>3413</v>
       </c>
     </row>
     <row r="222">
@@ -18834,76 +18834,76 @@
         <v>13</v>
       </c>
       <c r="D222" t="n">
-        <v>3268</v>
+        <v>3147</v>
       </c>
       <c r="E222" t="n">
-        <v>3101</v>
+        <v>2984</v>
       </c>
       <c r="F222" t="n">
-        <v>3017</v>
+        <v>2889</v>
       </c>
       <c r="G222" t="n">
-        <v>2959</v>
+        <v>2842</v>
       </c>
       <c r="H222" t="n">
-        <v>2933</v>
+        <v>2820</v>
       </c>
       <c r="I222" t="n">
-        <v>2953</v>
+        <v>2840</v>
       </c>
       <c r="J222" t="n">
-        <v>3043</v>
+        <v>2925</v>
       </c>
       <c r="K222" t="n">
-        <v>3222</v>
+        <v>3070</v>
       </c>
       <c r="L222" t="n">
-        <v>3466</v>
+        <v>3329</v>
       </c>
       <c r="M222" t="n">
-        <v>3761</v>
+        <v>3550</v>
       </c>
       <c r="N222" t="n">
-        <v>3904</v>
+        <v>3700</v>
       </c>
       <c r="O222" t="n">
-        <v>4074</v>
+        <v>3868</v>
       </c>
       <c r="P222" t="n">
-        <v>4186</v>
+        <v>3957</v>
       </c>
       <c r="Q222" t="n">
-        <v>4186</v>
+        <v>3976</v>
       </c>
       <c r="R222" t="n">
-        <v>4186</v>
+        <v>3994</v>
       </c>
       <c r="S222" t="n">
-        <v>4197</v>
+        <v>4030</v>
       </c>
       <c r="T222" t="n">
-        <v>4293</v>
+        <v>4082</v>
       </c>
       <c r="U222" t="n">
-        <v>4354</v>
+        <v>4164</v>
       </c>
       <c r="V222" t="n">
-        <v>4382</v>
+        <v>4237</v>
       </c>
       <c r="W222" t="n">
-        <v>4315</v>
+        <v>4260</v>
       </c>
       <c r="X222" t="n">
-        <v>4321</v>
+        <v>4306</v>
       </c>
       <c r="Y222" t="n">
-        <v>4195</v>
+        <v>4071</v>
       </c>
       <c r="Z222" t="n">
-        <v>3837</v>
+        <v>3773</v>
       </c>
       <c r="AA222" t="n">
-        <v>3539</v>
+        <v>3488</v>
       </c>
     </row>
     <row r="223">
@@ -18917,76 +18917,159 @@
         <v>14</v>
       </c>
       <c r="D223" t="n">
-        <v>3298</v>
+        <v>3170</v>
       </c>
       <c r="E223" t="n">
-        <v>3139</v>
+        <v>3014</v>
       </c>
       <c r="F223" t="n">
-        <v>3053</v>
+        <v>2932</v>
       </c>
       <c r="G223" t="n">
-        <v>3013</v>
+        <v>2893</v>
       </c>
       <c r="H223" t="n">
-        <v>3003</v>
+        <v>2886</v>
       </c>
       <c r="I223" t="n">
-        <v>3073</v>
+        <v>2959</v>
       </c>
       <c r="J223" t="n">
-        <v>3318</v>
+        <v>3191</v>
       </c>
       <c r="K223" t="n">
-        <v>3631</v>
+        <v>3460</v>
       </c>
       <c r="L223" t="n">
-        <v>3984</v>
+        <v>3787</v>
       </c>
       <c r="M223" t="n">
-        <v>4234</v>
+        <v>4028</v>
       </c>
       <c r="N223" t="n">
-        <v>4372</v>
+        <v>4138</v>
       </c>
       <c r="O223" t="n">
-        <v>4451</v>
+        <v>4232</v>
       </c>
       <c r="P223" t="n">
-        <v>4454</v>
+        <v>4315</v>
       </c>
       <c r="Q223" t="n">
-        <v>4536</v>
+        <v>4405</v>
       </c>
       <c r="R223" t="n">
-        <v>4498</v>
+        <v>4327</v>
       </c>
       <c r="S223" t="n">
-        <v>4502</v>
+        <v>4344</v>
       </c>
       <c r="T223" t="n">
-        <v>4540</v>
+        <v>4393</v>
       </c>
       <c r="U223" t="n">
-        <v>4553</v>
+        <v>4425</v>
       </c>
       <c r="V223" t="n">
-        <v>4568</v>
+        <v>4460</v>
       </c>
       <c r="W223" t="n">
-        <v>4570</v>
+        <v>4467</v>
       </c>
       <c r="X223" t="n">
-        <v>4592</v>
+        <v>4512</v>
       </c>
       <c r="Y223" t="n">
-        <v>4353</v>
+        <v>4250</v>
       </c>
       <c r="Z223" t="n">
-        <v>3967</v>
+        <v>3929</v>
       </c>
       <c r="AA223" t="n">
-        <v>3694</v>
+        <v>3638</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B224" t="n">
+        <v>9</v>
+      </c>
+      <c r="C224" t="n">
+        <v>15</v>
+      </c>
+      <c r="D224" t="n">
+        <v>3221</v>
+      </c>
+      <c r="E224" t="n">
+        <v>3074</v>
+      </c>
+      <c r="F224" t="n">
+        <v>2997</v>
+      </c>
+      <c r="G224" t="n">
+        <v>2967</v>
+      </c>
+      <c r="H224" t="n">
+        <v>2962</v>
+      </c>
+      <c r="I224" t="n">
+        <v>3066</v>
+      </c>
+      <c r="J224" t="n">
+        <v>3358</v>
+      </c>
+      <c r="K224" t="n">
+        <v>3642</v>
+      </c>
+      <c r="L224" t="n">
+        <v>3930</v>
+      </c>
+      <c r="M224" t="n">
+        <v>4061</v>
+      </c>
+      <c r="N224" t="n">
+        <v>4107</v>
+      </c>
+      <c r="O224" t="n">
+        <v>4198</v>
+      </c>
+      <c r="P224" t="n">
+        <v>4265</v>
+      </c>
+      <c r="Q224" t="n">
+        <v>4396</v>
+      </c>
+      <c r="R224" t="n">
+        <v>4396</v>
+      </c>
+      <c r="S224" t="n">
+        <v>4396</v>
+      </c>
+      <c r="T224" t="n">
+        <v>4314</v>
+      </c>
+      <c r="U224" t="n">
+        <v>4339</v>
+      </c>
+      <c r="V224" t="n">
+        <v>4426</v>
+      </c>
+      <c r="W224" t="n">
+        <v>4377</v>
+      </c>
+      <c r="X224" t="n">
+        <v>4509</v>
+      </c>
+      <c r="Y224" t="n">
+        <v>4250</v>
+      </c>
+      <c r="Z224" t="n">
+        <v>3935</v>
+      </c>
+      <c r="AA224" t="n">
+        <v>3635</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA224"/>
+  <dimension ref="A1:AA225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19072,6 +19072,89 @@
         <v>3635</v>
       </c>
     </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B225" t="n">
+        <v>9</v>
+      </c>
+      <c r="C225" t="n">
+        <v>16</v>
+      </c>
+      <c r="D225" t="n">
+        <v>3224</v>
+      </c>
+      <c r="E225" t="n">
+        <v>3076</v>
+      </c>
+      <c r="F225" t="n">
+        <v>2999</v>
+      </c>
+      <c r="G225" t="n">
+        <v>2968</v>
+      </c>
+      <c r="H225" t="n">
+        <v>2963</v>
+      </c>
+      <c r="I225" t="n">
+        <v>3068</v>
+      </c>
+      <c r="J225" t="n">
+        <v>3360</v>
+      </c>
+      <c r="K225" t="n">
+        <v>3646</v>
+      </c>
+      <c r="L225" t="n">
+        <v>3935</v>
+      </c>
+      <c r="M225" t="n">
+        <v>4066</v>
+      </c>
+      <c r="N225" t="n">
+        <v>4112</v>
+      </c>
+      <c r="O225" t="n">
+        <v>4203</v>
+      </c>
+      <c r="P225" t="n">
+        <v>4271</v>
+      </c>
+      <c r="Q225" t="n">
+        <v>4401</v>
+      </c>
+      <c r="R225" t="n">
+        <v>4401</v>
+      </c>
+      <c r="S225" t="n">
+        <v>4401</v>
+      </c>
+      <c r="T225" t="n">
+        <v>4322</v>
+      </c>
+      <c r="U225" t="n">
+        <v>4346</v>
+      </c>
+      <c r="V225" t="n">
+        <v>4430</v>
+      </c>
+      <c r="W225" t="n">
+        <v>4382</v>
+      </c>
+      <c r="X225" t="n">
+        <v>4511</v>
+      </c>
+      <c r="Y225" t="n">
+        <v>4252</v>
+      </c>
+      <c r="Z225" t="n">
+        <v>3937</v>
+      </c>
+      <c r="AA225" t="n">
+        <v>3637</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA225"/>
+  <dimension ref="A1:AA226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18751,76 +18751,76 @@
         <v>12</v>
       </c>
       <c r="D221" t="n">
-        <v>3228</v>
+        <v>3229</v>
       </c>
       <c r="E221" t="n">
-        <v>3060</v>
+        <v>3061</v>
       </c>
       <c r="F221" t="n">
-        <v>2970</v>
+        <v>2971</v>
       </c>
       <c r="G221" t="n">
         <v>2915</v>
       </c>
       <c r="H221" t="n">
-        <v>2882</v>
+        <v>2883</v>
       </c>
       <c r="I221" t="n">
-        <v>2906</v>
+        <v>2904</v>
       </c>
       <c r="J221" t="n">
-        <v>3022</v>
+        <v>3012</v>
       </c>
       <c r="K221" t="n">
-        <v>3178</v>
+        <v>3156</v>
       </c>
       <c r="L221" t="n">
-        <v>3444</v>
+        <v>3402</v>
       </c>
       <c r="M221" t="n">
-        <v>3619</v>
+        <v>3563</v>
       </c>
       <c r="N221" t="n">
-        <v>3759</v>
+        <v>3692</v>
       </c>
       <c r="O221" t="n">
-        <v>3844</v>
+        <v>3771</v>
       </c>
       <c r="P221" t="n">
-        <v>3937</v>
+        <v>3856</v>
       </c>
       <c r="Q221" t="n">
-        <v>4000</v>
+        <v>3915</v>
       </c>
       <c r="R221" t="n">
-        <v>4000</v>
+        <v>3915</v>
       </c>
       <c r="S221" t="n">
-        <v>4011</v>
+        <v>3942</v>
       </c>
       <c r="T221" t="n">
-        <v>4029</v>
+        <v>3983</v>
       </c>
       <c r="U221" t="n">
-        <v>4086</v>
+        <v>4116</v>
       </c>
       <c r="V221" t="n">
-        <v>4103</v>
+        <v>4156</v>
       </c>
       <c r="W221" t="n">
-        <v>4077</v>
+        <v>4132</v>
       </c>
       <c r="X221" t="n">
-        <v>4026</v>
+        <v>4084</v>
       </c>
       <c r="Y221" t="n">
-        <v>3818</v>
+        <v>3888</v>
       </c>
       <c r="Z221" t="n">
-        <v>3597</v>
+        <v>3680</v>
       </c>
       <c r="AA221" t="n">
-        <v>3413</v>
+        <v>3507</v>
       </c>
     </row>
     <row r="222">
@@ -18834,76 +18834,76 @@
         <v>13</v>
       </c>
       <c r="D222" t="n">
-        <v>3147</v>
+        <v>3135</v>
       </c>
       <c r="E222" t="n">
-        <v>2984</v>
+        <v>2977</v>
       </c>
       <c r="F222" t="n">
-        <v>2889</v>
+        <v>2883</v>
       </c>
       <c r="G222" t="n">
-        <v>2842</v>
+        <v>2838</v>
       </c>
       <c r="H222" t="n">
-        <v>2820</v>
+        <v>2814</v>
       </c>
       <c r="I222" t="n">
-        <v>2840</v>
+        <v>2838</v>
       </c>
       <c r="J222" t="n">
-        <v>2925</v>
+        <v>2938</v>
       </c>
       <c r="K222" t="n">
-        <v>3070</v>
+        <v>3096</v>
       </c>
       <c r="L222" t="n">
-        <v>3329</v>
+        <v>3325</v>
       </c>
       <c r="M222" t="n">
-        <v>3550</v>
+        <v>3503</v>
       </c>
       <c r="N222" t="n">
-        <v>3700</v>
+        <v>3623</v>
       </c>
       <c r="O222" t="n">
-        <v>3868</v>
+        <v>3764</v>
       </c>
       <c r="P222" t="n">
-        <v>3957</v>
+        <v>3853</v>
       </c>
       <c r="Q222" t="n">
-        <v>3976</v>
+        <v>3871</v>
       </c>
       <c r="R222" t="n">
-        <v>3994</v>
+        <v>3892</v>
       </c>
       <c r="S222" t="n">
-        <v>4030</v>
+        <v>3952</v>
       </c>
       <c r="T222" t="n">
-        <v>4082</v>
+        <v>3985</v>
       </c>
       <c r="U222" t="n">
-        <v>4164</v>
+        <v>4092</v>
       </c>
       <c r="V222" t="n">
-        <v>4237</v>
+        <v>4118</v>
       </c>
       <c r="W222" t="n">
-        <v>4260</v>
+        <v>4176</v>
       </c>
       <c r="X222" t="n">
-        <v>4306</v>
+        <v>4252</v>
       </c>
       <c r="Y222" t="n">
-        <v>4071</v>
+        <v>4040</v>
       </c>
       <c r="Z222" t="n">
-        <v>3773</v>
+        <v>3791</v>
       </c>
       <c r="AA222" t="n">
-        <v>3488</v>
+        <v>3533</v>
       </c>
     </row>
     <row r="223">
@@ -18917,76 +18917,76 @@
         <v>14</v>
       </c>
       <c r="D223" t="n">
-        <v>3170</v>
+        <v>3153</v>
       </c>
       <c r="E223" t="n">
-        <v>3014</v>
+        <v>3007</v>
       </c>
       <c r="F223" t="n">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="G223" t="n">
-        <v>2893</v>
+        <v>2889</v>
       </c>
       <c r="H223" t="n">
-        <v>2886</v>
+        <v>2877</v>
       </c>
       <c r="I223" t="n">
-        <v>2959</v>
+        <v>2908</v>
       </c>
       <c r="J223" t="n">
-        <v>3191</v>
+        <v>3084</v>
       </c>
       <c r="K223" t="n">
-        <v>3460</v>
+        <v>3312</v>
       </c>
       <c r="L223" t="n">
-        <v>3787</v>
+        <v>3643</v>
       </c>
       <c r="M223" t="n">
-        <v>4028</v>
+        <v>3895</v>
       </c>
       <c r="N223" t="n">
-        <v>4138</v>
+        <v>4022</v>
       </c>
       <c r="O223" t="n">
-        <v>4232</v>
+        <v>4098</v>
       </c>
       <c r="P223" t="n">
-        <v>4315</v>
+        <v>4132</v>
       </c>
       <c r="Q223" t="n">
-        <v>4405</v>
+        <v>4191</v>
       </c>
       <c r="R223" t="n">
-        <v>4327</v>
+        <v>4168</v>
       </c>
       <c r="S223" t="n">
-        <v>4344</v>
+        <v>4128</v>
       </c>
       <c r="T223" t="n">
-        <v>4393</v>
+        <v>4156</v>
       </c>
       <c r="U223" t="n">
-        <v>4425</v>
+        <v>4212</v>
       </c>
       <c r="V223" t="n">
-        <v>4460</v>
+        <v>4228</v>
       </c>
       <c r="W223" t="n">
-        <v>4467</v>
+        <v>4250</v>
       </c>
       <c r="X223" t="n">
-        <v>4512</v>
+        <v>4305</v>
       </c>
       <c r="Y223" t="n">
-        <v>4250</v>
+        <v>4087</v>
       </c>
       <c r="Z223" t="n">
-        <v>3929</v>
+        <v>3831</v>
       </c>
       <c r="AA223" t="n">
-        <v>3638</v>
+        <v>3579</v>
       </c>
     </row>
     <row r="224">
@@ -19000,76 +19000,76 @@
         <v>15</v>
       </c>
       <c r="D224" t="n">
-        <v>3221</v>
+        <v>3199</v>
       </c>
       <c r="E224" t="n">
-        <v>3074</v>
+        <v>3056</v>
       </c>
       <c r="F224" t="n">
-        <v>2997</v>
+        <v>2985</v>
       </c>
       <c r="G224" t="n">
-        <v>2967</v>
+        <v>2955</v>
       </c>
       <c r="H224" t="n">
-        <v>2962</v>
+        <v>2950</v>
       </c>
       <c r="I224" t="n">
-        <v>3066</v>
+        <v>3043</v>
       </c>
       <c r="J224" t="n">
-        <v>3358</v>
+        <v>3305</v>
       </c>
       <c r="K224" t="n">
-        <v>3642</v>
+        <v>3560</v>
       </c>
       <c r="L224" t="n">
-        <v>3930</v>
+        <v>3810</v>
       </c>
       <c r="M224" t="n">
-        <v>4061</v>
+        <v>3919</v>
       </c>
       <c r="N224" t="n">
-        <v>4107</v>
+        <v>3945</v>
       </c>
       <c r="O224" t="n">
-        <v>4198</v>
+        <v>4031</v>
       </c>
       <c r="P224" t="n">
-        <v>4265</v>
+        <v>4068</v>
       </c>
       <c r="Q224" t="n">
-        <v>4396</v>
+        <v>4173</v>
       </c>
       <c r="R224" t="n">
-        <v>4396</v>
+        <v>4105</v>
       </c>
       <c r="S224" t="n">
-        <v>4396</v>
+        <v>4105</v>
       </c>
       <c r="T224" t="n">
-        <v>4314</v>
+        <v>4105</v>
       </c>
       <c r="U224" t="n">
-        <v>4339</v>
+        <v>4134</v>
       </c>
       <c r="V224" t="n">
-        <v>4426</v>
+        <v>4176</v>
       </c>
       <c r="W224" t="n">
-        <v>4377</v>
+        <v>4237</v>
       </c>
       <c r="X224" t="n">
-        <v>4509</v>
+        <v>4299</v>
       </c>
       <c r="Y224" t="n">
-        <v>4250</v>
+        <v>4079</v>
       </c>
       <c r="Z224" t="n">
-        <v>3935</v>
+        <v>3821</v>
       </c>
       <c r="AA224" t="n">
-        <v>3635</v>
+        <v>3573</v>
       </c>
     </row>
     <row r="225">
@@ -19083,76 +19083,159 @@
         <v>16</v>
       </c>
       <c r="D225" t="n">
-        <v>3224</v>
+        <v>3202</v>
       </c>
       <c r="E225" t="n">
-        <v>3076</v>
+        <v>3058</v>
       </c>
       <c r="F225" t="n">
-        <v>2999</v>
+        <v>2986</v>
       </c>
       <c r="G225" t="n">
-        <v>2968</v>
+        <v>2957</v>
       </c>
       <c r="H225" t="n">
-        <v>2963</v>
+        <v>2952</v>
       </c>
       <c r="I225" t="n">
-        <v>3068</v>
+        <v>3045</v>
       </c>
       <c r="J225" t="n">
-        <v>3360</v>
+        <v>3308</v>
       </c>
       <c r="K225" t="n">
-        <v>3646</v>
+        <v>3563</v>
       </c>
       <c r="L225" t="n">
-        <v>3935</v>
+        <v>3814</v>
       </c>
       <c r="M225" t="n">
-        <v>4066</v>
+        <v>3924</v>
       </c>
       <c r="N225" t="n">
+        <v>3949</v>
+      </c>
+      <c r="O225" t="n">
+        <v>4036</v>
+      </c>
+      <c r="P225" t="n">
+        <v>4073</v>
+      </c>
+      <c r="Q225" t="n">
+        <v>4178</v>
+      </c>
+      <c r="R225" t="n">
         <v>4112</v>
       </c>
-      <c r="O225" t="n">
-        <v>4203</v>
-      </c>
-      <c r="P225" t="n">
-        <v>4271</v>
-      </c>
-      <c r="Q225" t="n">
-        <v>4401</v>
-      </c>
-      <c r="R225" t="n">
-        <v>4401</v>
-      </c>
       <c r="S225" t="n">
-        <v>4401</v>
+        <v>4112</v>
       </c>
       <c r="T225" t="n">
-        <v>4322</v>
+        <v>4112</v>
       </c>
       <c r="U225" t="n">
-        <v>4346</v>
+        <v>4140</v>
       </c>
       <c r="V225" t="n">
-        <v>4430</v>
+        <v>4181</v>
       </c>
       <c r="W225" t="n">
-        <v>4382</v>
+        <v>4240</v>
       </c>
       <c r="X225" t="n">
-        <v>4511</v>
+        <v>4301</v>
       </c>
       <c r="Y225" t="n">
-        <v>4252</v>
+        <v>4081</v>
       </c>
       <c r="Z225" t="n">
-        <v>3937</v>
+        <v>3823</v>
       </c>
       <c r="AA225" t="n">
-        <v>3637</v>
+        <v>3575</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B226" t="n">
+        <v>9</v>
+      </c>
+      <c r="C226" t="n">
+        <v>17</v>
+      </c>
+      <c r="D226" t="n">
+        <v>3207</v>
+      </c>
+      <c r="E226" t="n">
+        <v>3062</v>
+      </c>
+      <c r="F226" t="n">
+        <v>2989</v>
+      </c>
+      <c r="G226" t="n">
+        <v>2959</v>
+      </c>
+      <c r="H226" t="n">
+        <v>2954</v>
+      </c>
+      <c r="I226" t="n">
+        <v>3048</v>
+      </c>
+      <c r="J226" t="n">
+        <v>3312</v>
+      </c>
+      <c r="K226" t="n">
+        <v>3569</v>
+      </c>
+      <c r="L226" t="n">
+        <v>3821</v>
+      </c>
+      <c r="M226" t="n">
+        <v>3932</v>
+      </c>
+      <c r="N226" t="n">
+        <v>3957</v>
+      </c>
+      <c r="O226" t="n">
+        <v>4044</v>
+      </c>
+      <c r="P226" t="n">
+        <v>4081</v>
+      </c>
+      <c r="Q226" t="n">
+        <v>4187</v>
+      </c>
+      <c r="R226" t="n">
+        <v>4123</v>
+      </c>
+      <c r="S226" t="n">
+        <v>4123</v>
+      </c>
+      <c r="T226" t="n">
+        <v>4123</v>
+      </c>
+      <c r="U226" t="n">
+        <v>4150</v>
+      </c>
+      <c r="V226" t="n">
+        <v>4189</v>
+      </c>
+      <c r="W226" t="n">
+        <v>4246</v>
+      </c>
+      <c r="X226" t="n">
+        <v>4304</v>
+      </c>
+      <c r="Y226" t="n">
+        <v>4084</v>
+      </c>
+      <c r="Z226" t="n">
+        <v>3826</v>
+      </c>
+      <c r="AA226" t="n">
+        <v>3578</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA226"/>
+  <dimension ref="A1:AA227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18834,76 +18834,76 @@
         <v>13</v>
       </c>
       <c r="D222" t="n">
-        <v>3135</v>
+        <v>3150</v>
       </c>
       <c r="E222" t="n">
-        <v>2977</v>
+        <v>3024</v>
       </c>
       <c r="F222" t="n">
-        <v>2883</v>
+        <v>2949</v>
       </c>
       <c r="G222" t="n">
-        <v>2838</v>
+        <v>2913</v>
       </c>
       <c r="H222" t="n">
-        <v>2814</v>
+        <v>2894</v>
       </c>
       <c r="I222" t="n">
-        <v>2838</v>
+        <v>2917</v>
       </c>
       <c r="J222" t="n">
-        <v>2938</v>
+        <v>3011</v>
       </c>
       <c r="K222" t="n">
-        <v>3096</v>
+        <v>3163</v>
       </c>
       <c r="L222" t="n">
-        <v>3325</v>
+        <v>3381</v>
       </c>
       <c r="M222" t="n">
-        <v>3503</v>
+        <v>3551</v>
       </c>
       <c r="N222" t="n">
-        <v>3623</v>
+        <v>3665</v>
       </c>
       <c r="O222" t="n">
-        <v>3764</v>
+        <v>3800</v>
       </c>
       <c r="P222" t="n">
-        <v>3853</v>
+        <v>3885</v>
       </c>
       <c r="Q222" t="n">
-        <v>3871</v>
+        <v>3876</v>
       </c>
       <c r="R222" t="n">
-        <v>3892</v>
+        <v>3866</v>
       </c>
       <c r="S222" t="n">
-        <v>3952</v>
+        <v>3836</v>
       </c>
       <c r="T222" t="n">
-        <v>3985</v>
+        <v>3877</v>
       </c>
       <c r="U222" t="n">
-        <v>4092</v>
+        <v>4008</v>
       </c>
       <c r="V222" t="n">
-        <v>4118</v>
+        <v>4040</v>
       </c>
       <c r="W222" t="n">
-        <v>4176</v>
+        <v>4111</v>
       </c>
       <c r="X222" t="n">
-        <v>4252</v>
+        <v>4204</v>
       </c>
       <c r="Y222" t="n">
-        <v>4040</v>
+        <v>4010</v>
       </c>
       <c r="Z222" t="n">
-        <v>3791</v>
+        <v>3782</v>
       </c>
       <c r="AA222" t="n">
-        <v>3533</v>
+        <v>3545</v>
       </c>
     </row>
     <row r="223">
@@ -18917,76 +18917,76 @@
         <v>14</v>
       </c>
       <c r="D223" t="n">
-        <v>3153</v>
+        <v>3175</v>
       </c>
       <c r="E223" t="n">
-        <v>3007</v>
+        <v>3061</v>
       </c>
       <c r="F223" t="n">
-        <v>2931</v>
+        <v>3002</v>
       </c>
       <c r="G223" t="n">
-        <v>2889</v>
+        <v>2970</v>
       </c>
       <c r="H223" t="n">
-        <v>2877</v>
+        <v>2960</v>
       </c>
       <c r="I223" t="n">
-        <v>2908</v>
+        <v>2993</v>
       </c>
       <c r="J223" t="n">
-        <v>3084</v>
+        <v>3177</v>
       </c>
       <c r="K223" t="n">
-        <v>3312</v>
+        <v>3416</v>
       </c>
       <c r="L223" t="n">
-        <v>3643</v>
+        <v>3763</v>
       </c>
       <c r="M223" t="n">
-        <v>3895</v>
+        <v>4026</v>
       </c>
       <c r="N223" t="n">
-        <v>4022</v>
+        <v>4159</v>
       </c>
       <c r="O223" t="n">
-        <v>4098</v>
+        <v>4240</v>
       </c>
       <c r="P223" t="n">
-        <v>4132</v>
+        <v>4275</v>
       </c>
       <c r="Q223" t="n">
-        <v>4191</v>
+        <v>4337</v>
       </c>
       <c r="R223" t="n">
-        <v>4168</v>
+        <v>4262</v>
       </c>
       <c r="S223" t="n">
-        <v>4128</v>
+        <v>4131</v>
       </c>
       <c r="T223" t="n">
-        <v>4156</v>
+        <v>4175</v>
       </c>
       <c r="U223" t="n">
-        <v>4212</v>
+        <v>4264</v>
       </c>
       <c r="V223" t="n">
-        <v>4228</v>
+        <v>4290</v>
       </c>
       <c r="W223" t="n">
-        <v>4250</v>
+        <v>4324</v>
       </c>
       <c r="X223" t="n">
-        <v>4305</v>
+        <v>4411</v>
       </c>
       <c r="Y223" t="n">
-        <v>4087</v>
+        <v>4166</v>
       </c>
       <c r="Z223" t="n">
-        <v>3831</v>
+        <v>3879</v>
       </c>
       <c r="AA223" t="n">
-        <v>3579</v>
+        <v>3596</v>
       </c>
     </row>
     <row r="224">
@@ -19000,76 +19000,76 @@
         <v>15</v>
       </c>
       <c r="D224" t="n">
-        <v>3199</v>
+        <v>3217</v>
       </c>
       <c r="E224" t="n">
-        <v>3056</v>
+        <v>3066</v>
       </c>
       <c r="F224" t="n">
-        <v>2985</v>
+        <v>2990</v>
       </c>
       <c r="G224" t="n">
-        <v>2955</v>
+        <v>2956</v>
       </c>
       <c r="H224" t="n">
-        <v>2950</v>
+        <v>2952</v>
       </c>
       <c r="I224" t="n">
-        <v>3043</v>
+        <v>3060</v>
       </c>
       <c r="J224" t="n">
-        <v>3305</v>
+        <v>3352</v>
       </c>
       <c r="K224" t="n">
-        <v>3560</v>
+        <v>3633</v>
       </c>
       <c r="L224" t="n">
-        <v>3810</v>
+        <v>3899</v>
       </c>
       <c r="M224" t="n">
-        <v>3919</v>
+        <v>4011</v>
       </c>
       <c r="N224" t="n">
-        <v>3945</v>
+        <v>4053</v>
       </c>
       <c r="O224" t="n">
-        <v>4031</v>
+        <v>4114</v>
       </c>
       <c r="P224" t="n">
-        <v>4068</v>
+        <v>4149</v>
       </c>
       <c r="Q224" t="n">
-        <v>4173</v>
+        <v>4260</v>
       </c>
       <c r="R224" t="n">
-        <v>4105</v>
+        <v>3948</v>
       </c>
       <c r="S224" t="n">
-        <v>4105</v>
+        <v>3948</v>
       </c>
       <c r="T224" t="n">
-        <v>4105</v>
+        <v>3948</v>
       </c>
       <c r="U224" t="n">
-        <v>4134</v>
+        <v>3987</v>
       </c>
       <c r="V224" t="n">
-        <v>4176</v>
+        <v>4081</v>
       </c>
       <c r="W224" t="n">
-        <v>4237</v>
+        <v>4228</v>
       </c>
       <c r="X224" t="n">
-        <v>4299</v>
+        <v>4303</v>
       </c>
       <c r="Y224" t="n">
-        <v>4079</v>
+        <v>4077</v>
       </c>
       <c r="Z224" t="n">
-        <v>3821</v>
+        <v>3828</v>
       </c>
       <c r="AA224" t="n">
-        <v>3573</v>
+        <v>3587</v>
       </c>
     </row>
     <row r="225">
@@ -19083,76 +19083,76 @@
         <v>16</v>
       </c>
       <c r="D225" t="n">
-        <v>3202</v>
+        <v>3223</v>
       </c>
       <c r="E225" t="n">
-        <v>3058</v>
+        <v>3070</v>
       </c>
       <c r="F225" t="n">
-        <v>2986</v>
+        <v>2993</v>
       </c>
       <c r="G225" t="n">
-        <v>2957</v>
+        <v>2960</v>
       </c>
       <c r="H225" t="n">
-        <v>2952</v>
+        <v>2955</v>
       </c>
       <c r="I225" t="n">
-        <v>3045</v>
+        <v>3064</v>
       </c>
       <c r="J225" t="n">
-        <v>3308</v>
+        <v>3358</v>
       </c>
       <c r="K225" t="n">
-        <v>3563</v>
+        <v>3641</v>
       </c>
       <c r="L225" t="n">
-        <v>3814</v>
+        <v>3909</v>
       </c>
       <c r="M225" t="n">
-        <v>3924</v>
+        <v>4021</v>
       </c>
       <c r="N225" t="n">
-        <v>3949</v>
+        <v>4063</v>
       </c>
       <c r="O225" t="n">
-        <v>4036</v>
+        <v>4124</v>
       </c>
       <c r="P225" t="n">
-        <v>4073</v>
+        <v>4160</v>
       </c>
       <c r="Q225" t="n">
-        <v>4178</v>
+        <v>4272</v>
       </c>
       <c r="R225" t="n">
-        <v>4112</v>
+        <v>3962</v>
       </c>
       <c r="S225" t="n">
-        <v>4112</v>
+        <v>3962</v>
       </c>
       <c r="T225" t="n">
-        <v>4112</v>
+        <v>3962</v>
       </c>
       <c r="U225" t="n">
-        <v>4140</v>
+        <v>4001</v>
       </c>
       <c r="V225" t="n">
-        <v>4181</v>
+        <v>4091</v>
       </c>
       <c r="W225" t="n">
-        <v>4240</v>
+        <v>4234</v>
       </c>
       <c r="X225" t="n">
-        <v>4301</v>
+        <v>4306</v>
       </c>
       <c r="Y225" t="n">
         <v>4081</v>
       </c>
       <c r="Z225" t="n">
-        <v>3823</v>
+        <v>3832</v>
       </c>
       <c r="AA225" t="n">
-        <v>3575</v>
+        <v>3591</v>
       </c>
     </row>
     <row r="226">
@@ -19166,76 +19166,159 @@
         <v>17</v>
       </c>
       <c r="D226" t="n">
-        <v>3207</v>
+        <v>3233</v>
       </c>
       <c r="E226" t="n">
-        <v>3062</v>
+        <v>3077</v>
       </c>
       <c r="F226" t="n">
-        <v>2989</v>
+        <v>2999</v>
       </c>
       <c r="G226" t="n">
-        <v>2959</v>
+        <v>2965</v>
       </c>
       <c r="H226" t="n">
-        <v>2954</v>
+        <v>2960</v>
       </c>
       <c r="I226" t="n">
-        <v>3048</v>
+        <v>3070</v>
       </c>
       <c r="J226" t="n">
-        <v>3312</v>
+        <v>3367</v>
       </c>
       <c r="K226" t="n">
-        <v>3569</v>
+        <v>3653</v>
       </c>
       <c r="L226" t="n">
-        <v>3821</v>
+        <v>3924</v>
       </c>
       <c r="M226" t="n">
-        <v>3932</v>
+        <v>4037</v>
       </c>
       <c r="N226" t="n">
-        <v>3957</v>
+        <v>4080</v>
       </c>
       <c r="O226" t="n">
-        <v>4044</v>
+        <v>4142</v>
       </c>
       <c r="P226" t="n">
-        <v>4081</v>
+        <v>4178</v>
       </c>
       <c r="Q226" t="n">
+        <v>4291</v>
+      </c>
+      <c r="R226" t="n">
+        <v>3986</v>
+      </c>
+      <c r="S226" t="n">
+        <v>3986</v>
+      </c>
+      <c r="T226" t="n">
+        <v>3986</v>
+      </c>
+      <c r="U226" t="n">
+        <v>4023</v>
+      </c>
+      <c r="V226" t="n">
+        <v>4108</v>
+      </c>
+      <c r="W226" t="n">
+        <v>4243</v>
+      </c>
+      <c r="X226" t="n">
+        <v>4312</v>
+      </c>
+      <c r="Y226" t="n">
+        <v>4086</v>
+      </c>
+      <c r="Z226" t="n">
+        <v>3839</v>
+      </c>
+      <c r="AA226" t="n">
+        <v>3598</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B227" t="n">
+        <v>9</v>
+      </c>
+      <c r="C227" t="n">
+        <v>18</v>
+      </c>
+      <c r="D227" t="n">
+        <v>3241</v>
+      </c>
+      <c r="E227" t="n">
+        <v>3083</v>
+      </c>
+      <c r="F227" t="n">
+        <v>3003</v>
+      </c>
+      <c r="G227" t="n">
+        <v>2969</v>
+      </c>
+      <c r="H227" t="n">
+        <v>2964</v>
+      </c>
+      <c r="I227" t="n">
+        <v>3075</v>
+      </c>
+      <c r="J227" t="n">
+        <v>3374</v>
+      </c>
+      <c r="K227" t="n">
+        <v>3663</v>
+      </c>
+      <c r="L227" t="n">
+        <v>3936</v>
+      </c>
+      <c r="M227" t="n">
+        <v>4050</v>
+      </c>
+      <c r="N227" t="n">
+        <v>4093</v>
+      </c>
+      <c r="O227" t="n">
+        <v>4155</v>
+      </c>
+      <c r="P227" t="n">
+        <v>4192</v>
+      </c>
+      <c r="Q227" t="n">
+        <v>4306</v>
+      </c>
+      <c r="R227" t="n">
+        <v>4005</v>
+      </c>
+      <c r="S227" t="n">
+        <v>4005</v>
+      </c>
+      <c r="T227" t="n">
+        <v>4005</v>
+      </c>
+      <c r="U227" t="n">
+        <v>4031</v>
+      </c>
+      <c r="V227" t="n">
+        <v>4092</v>
+      </c>
+      <c r="W227" t="n">
         <v>4187</v>
       </c>
-      <c r="R226" t="n">
-        <v>4123</v>
-      </c>
-      <c r="S226" t="n">
-        <v>4123</v>
-      </c>
-      <c r="T226" t="n">
-        <v>4123</v>
-      </c>
-      <c r="U226" t="n">
-        <v>4150</v>
-      </c>
-      <c r="V226" t="n">
-        <v>4189</v>
-      </c>
-      <c r="W226" t="n">
-        <v>4246</v>
-      </c>
-      <c r="X226" t="n">
-        <v>4304</v>
-      </c>
-      <c r="Y226" t="n">
-        <v>4084</v>
-      </c>
-      <c r="Z226" t="n">
-        <v>3826</v>
-      </c>
-      <c r="AA226" t="n">
-        <v>3578</v>
+      <c r="X227" t="n">
+        <v>4236</v>
+      </c>
+      <c r="Y227" t="n">
+        <v>4021</v>
+      </c>
+      <c r="Z227" t="n">
+        <v>3785</v>
+      </c>
+      <c r="AA227" t="n">
+        <v>3555</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA227"/>
+  <dimension ref="A1:AA228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18917,76 +18917,76 @@
         <v>14</v>
       </c>
       <c r="D223" t="n">
-        <v>3175</v>
+        <v>3173</v>
       </c>
       <c r="E223" t="n">
-        <v>3061</v>
+        <v>2992</v>
       </c>
       <c r="F223" t="n">
-        <v>3002</v>
+        <v>2898</v>
       </c>
       <c r="G223" t="n">
-        <v>2970</v>
+        <v>2846</v>
       </c>
       <c r="H223" t="n">
-        <v>2960</v>
+        <v>2832</v>
       </c>
       <c r="I223" t="n">
-        <v>2993</v>
+        <v>2864</v>
       </c>
       <c r="J223" t="n">
-        <v>3177</v>
+        <v>3051</v>
       </c>
       <c r="K223" t="n">
-        <v>3416</v>
+        <v>3294</v>
       </c>
       <c r="L223" t="n">
-        <v>3763</v>
+        <v>3646</v>
       </c>
       <c r="M223" t="n">
-        <v>4026</v>
+        <v>3914</v>
       </c>
       <c r="N223" t="n">
-        <v>4159</v>
+        <v>4049</v>
       </c>
       <c r="O223" t="n">
-        <v>4240</v>
+        <v>4131</v>
       </c>
       <c r="P223" t="n">
-        <v>4275</v>
+        <v>4167</v>
       </c>
       <c r="Q223" t="n">
-        <v>4337</v>
+        <v>4229</v>
       </c>
       <c r="R223" t="n">
-        <v>4262</v>
+        <v>4150</v>
       </c>
       <c r="S223" t="n">
-        <v>4131</v>
+        <v>4010</v>
       </c>
       <c r="T223" t="n">
-        <v>4175</v>
+        <v>4039</v>
       </c>
       <c r="U223" t="n">
-        <v>4264</v>
+        <v>4097</v>
       </c>
       <c r="V223" t="n">
-        <v>4290</v>
+        <v>4114</v>
       </c>
       <c r="W223" t="n">
-        <v>4324</v>
+        <v>4136</v>
       </c>
       <c r="X223" t="n">
-        <v>4411</v>
+        <v>4193</v>
       </c>
       <c r="Y223" t="n">
-        <v>4166</v>
+        <v>4012</v>
       </c>
       <c r="Z223" t="n">
-        <v>3879</v>
+        <v>3800</v>
       </c>
       <c r="AA223" t="n">
-        <v>3596</v>
+        <v>3591</v>
       </c>
     </row>
     <row r="224">
@@ -19000,76 +19000,76 @@
         <v>15</v>
       </c>
       <c r="D224" t="n">
-        <v>3217</v>
+        <v>3215</v>
       </c>
       <c r="E224" t="n">
-        <v>3066</v>
+        <v>3037</v>
       </c>
       <c r="F224" t="n">
-        <v>2990</v>
+        <v>2947</v>
       </c>
       <c r="G224" t="n">
-        <v>2956</v>
+        <v>2908</v>
       </c>
       <c r="H224" t="n">
-        <v>2952</v>
+        <v>2902</v>
       </c>
       <c r="I224" t="n">
-        <v>3060</v>
+        <v>3015</v>
       </c>
       <c r="J224" t="n">
-        <v>3352</v>
+        <v>3314</v>
       </c>
       <c r="K224" t="n">
-        <v>3633</v>
+        <v>3600</v>
       </c>
       <c r="L224" t="n">
-        <v>3899</v>
+        <v>3866</v>
       </c>
       <c r="M224" t="n">
+        <v>3975</v>
+      </c>
+      <c r="N224" t="n">
+        <v>4009</v>
+      </c>
+      <c r="O224" t="n">
+        <v>4064</v>
+      </c>
+      <c r="P224" t="n">
+        <v>4094</v>
+      </c>
+      <c r="Q224" t="n">
+        <v>4202</v>
+      </c>
+      <c r="R224" t="n">
+        <v>3980</v>
+      </c>
+      <c r="S224" t="n">
+        <v>3995</v>
+      </c>
+      <c r="T224" t="n">
+        <v>3990</v>
+      </c>
+      <c r="U224" t="n">
         <v>4011</v>
       </c>
-      <c r="N224" t="n">
-        <v>4053</v>
-      </c>
-      <c r="O224" t="n">
-        <v>4114</v>
-      </c>
-      <c r="P224" t="n">
-        <v>4149</v>
-      </c>
-      <c r="Q224" t="n">
-        <v>4260</v>
-      </c>
-      <c r="R224" t="n">
-        <v>3948</v>
-      </c>
-      <c r="S224" t="n">
-        <v>3948</v>
-      </c>
-      <c r="T224" t="n">
-        <v>3948</v>
-      </c>
-      <c r="U224" t="n">
-        <v>3987</v>
-      </c>
       <c r="V224" t="n">
-        <v>4081</v>
+        <v>4058</v>
       </c>
       <c r="W224" t="n">
-        <v>4228</v>
+        <v>4142</v>
       </c>
       <c r="X224" t="n">
-        <v>4303</v>
+        <v>4185</v>
       </c>
       <c r="Y224" t="n">
-        <v>4077</v>
+        <v>3991</v>
       </c>
       <c r="Z224" t="n">
-        <v>3828</v>
+        <v>3784</v>
       </c>
       <c r="AA224" t="n">
-        <v>3587</v>
+        <v>3581</v>
       </c>
     </row>
     <row r="225">
@@ -19083,76 +19083,76 @@
         <v>16</v>
       </c>
       <c r="D225" t="n">
-        <v>3223</v>
+        <v>3227</v>
       </c>
       <c r="E225" t="n">
-        <v>3070</v>
+        <v>3045</v>
       </c>
       <c r="F225" t="n">
-        <v>2993</v>
+        <v>2954</v>
       </c>
       <c r="G225" t="n">
-        <v>2960</v>
+        <v>2914</v>
       </c>
       <c r="H225" t="n">
-        <v>2955</v>
+        <v>2908</v>
       </c>
       <c r="I225" t="n">
-        <v>3064</v>
+        <v>3022</v>
       </c>
       <c r="J225" t="n">
-        <v>3358</v>
+        <v>3325</v>
       </c>
       <c r="K225" t="n">
-        <v>3641</v>
+        <v>3614</v>
       </c>
       <c r="L225" t="n">
-        <v>3909</v>
+        <v>3884</v>
       </c>
       <c r="M225" t="n">
-        <v>4021</v>
+        <v>3994</v>
       </c>
       <c r="N225" t="n">
-        <v>4063</v>
+        <v>4029</v>
       </c>
       <c r="O225" t="n">
-        <v>4124</v>
+        <v>4084</v>
       </c>
       <c r="P225" t="n">
-        <v>4160</v>
+        <v>4115</v>
       </c>
       <c r="Q225" t="n">
-        <v>4272</v>
+        <v>4224</v>
       </c>
       <c r="R225" t="n">
-        <v>3962</v>
+        <v>4005</v>
       </c>
       <c r="S225" t="n">
-        <v>3962</v>
+        <v>4019</v>
       </c>
       <c r="T225" t="n">
-        <v>3962</v>
+        <v>4015</v>
       </c>
       <c r="U225" t="n">
-        <v>4001</v>
+        <v>4034</v>
       </c>
       <c r="V225" t="n">
-        <v>4091</v>
+        <v>4076</v>
       </c>
       <c r="W225" t="n">
-        <v>4234</v>
+        <v>4152</v>
       </c>
       <c r="X225" t="n">
-        <v>4306</v>
+        <v>4191</v>
       </c>
       <c r="Y225" t="n">
-        <v>4081</v>
+        <v>3998</v>
       </c>
       <c r="Z225" t="n">
-        <v>3832</v>
+        <v>3791</v>
       </c>
       <c r="AA225" t="n">
-        <v>3591</v>
+        <v>3589</v>
       </c>
     </row>
     <row r="226">
@@ -19169,73 +19169,73 @@
         <v>3233</v>
       </c>
       <c r="E226" t="n">
-        <v>3077</v>
+        <v>3050</v>
       </c>
       <c r="F226" t="n">
-        <v>2999</v>
+        <v>2957</v>
       </c>
       <c r="G226" t="n">
-        <v>2965</v>
+        <v>2917</v>
       </c>
       <c r="H226" t="n">
-        <v>2960</v>
+        <v>2911</v>
       </c>
       <c r="I226" t="n">
-        <v>3070</v>
+        <v>3025</v>
       </c>
       <c r="J226" t="n">
-        <v>3367</v>
+        <v>3331</v>
       </c>
       <c r="K226" t="n">
-        <v>3653</v>
+        <v>3622</v>
       </c>
       <c r="L226" t="n">
-        <v>3924</v>
+        <v>3893</v>
       </c>
       <c r="M226" t="n">
-        <v>4037</v>
+        <v>4004</v>
       </c>
       <c r="N226" t="n">
-        <v>4080</v>
+        <v>4039</v>
       </c>
       <c r="O226" t="n">
-        <v>4142</v>
+        <v>4094</v>
       </c>
       <c r="P226" t="n">
-        <v>4178</v>
+        <v>4126</v>
       </c>
       <c r="Q226" t="n">
-        <v>4291</v>
+        <v>4236</v>
       </c>
       <c r="R226" t="n">
-        <v>3986</v>
+        <v>4018</v>
       </c>
       <c r="S226" t="n">
-        <v>3986</v>
+        <v>4031</v>
       </c>
       <c r="T226" t="n">
-        <v>3986</v>
+        <v>4027</v>
       </c>
       <c r="U226" t="n">
-        <v>4023</v>
+        <v>4045</v>
       </c>
       <c r="V226" t="n">
-        <v>4108</v>
+        <v>4085</v>
       </c>
       <c r="W226" t="n">
-        <v>4243</v>
+        <v>4157</v>
       </c>
       <c r="X226" t="n">
-        <v>4312</v>
+        <v>4194</v>
       </c>
       <c r="Y226" t="n">
-        <v>4086</v>
+        <v>4001</v>
       </c>
       <c r="Z226" t="n">
-        <v>3839</v>
+        <v>3795</v>
       </c>
       <c r="AA226" t="n">
-        <v>3598</v>
+        <v>3593</v>
       </c>
     </row>
     <row r="227">
@@ -19249,76 +19249,159 @@
         <v>18</v>
       </c>
       <c r="D227" t="n">
-        <v>3241</v>
+        <v>3244</v>
       </c>
       <c r="E227" t="n">
-        <v>3083</v>
+        <v>3058</v>
       </c>
       <c r="F227" t="n">
-        <v>3003</v>
+        <v>2964</v>
       </c>
       <c r="G227" t="n">
-        <v>2969</v>
+        <v>2923</v>
       </c>
       <c r="H227" t="n">
-        <v>2964</v>
+        <v>2917</v>
       </c>
       <c r="I227" t="n">
-        <v>3075</v>
+        <v>3032</v>
       </c>
       <c r="J227" t="n">
-        <v>3374</v>
+        <v>3341</v>
       </c>
       <c r="K227" t="n">
-        <v>3663</v>
+        <v>3636</v>
       </c>
       <c r="L227" t="n">
-        <v>3936</v>
+        <v>3910</v>
       </c>
       <c r="M227" t="n">
-        <v>4050</v>
+        <v>4022</v>
       </c>
       <c r="N227" t="n">
-        <v>4093</v>
+        <v>4058</v>
       </c>
       <c r="O227" t="n">
-        <v>4155</v>
+        <v>4114</v>
       </c>
       <c r="P227" t="n">
-        <v>4192</v>
+        <v>4146</v>
       </c>
       <c r="Q227" t="n">
-        <v>4306</v>
+        <v>4257</v>
       </c>
       <c r="R227" t="n">
-        <v>4005</v>
+        <v>4042</v>
       </c>
       <c r="S227" t="n">
-        <v>4005</v>
+        <v>4048</v>
       </c>
       <c r="T227" t="n">
-        <v>4005</v>
+        <v>4046</v>
       </c>
       <c r="U227" t="n">
-        <v>4031</v>
+        <v>4054</v>
       </c>
       <c r="V227" t="n">
-        <v>4092</v>
+        <v>4072</v>
       </c>
       <c r="W227" t="n">
-        <v>4187</v>
+        <v>4104</v>
       </c>
       <c r="X227" t="n">
-        <v>4236</v>
+        <v>4121</v>
       </c>
       <c r="Y227" t="n">
-        <v>4021</v>
+        <v>3938</v>
       </c>
       <c r="Z227" t="n">
-        <v>3785</v>
+        <v>3743</v>
       </c>
       <c r="AA227" t="n">
-        <v>3555</v>
+        <v>3552</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B228" t="n">
+        <v>9</v>
+      </c>
+      <c r="C228" t="n">
+        <v>19</v>
+      </c>
+      <c r="D228" t="n">
+        <v>3237</v>
+      </c>
+      <c r="E228" t="n">
+        <v>3058</v>
+      </c>
+      <c r="F228" t="n">
+        <v>2954</v>
+      </c>
+      <c r="G228" t="n">
+        <v>2888</v>
+      </c>
+      <c r="H228" t="n">
+        <v>2849</v>
+      </c>
+      <c r="I228" t="n">
+        <v>2875</v>
+      </c>
+      <c r="J228" t="n">
+        <v>3004</v>
+      </c>
+      <c r="K228" t="n">
+        <v>3173</v>
+      </c>
+      <c r="L228" t="n">
+        <v>3402</v>
+      </c>
+      <c r="M228" t="n">
+        <v>3580</v>
+      </c>
+      <c r="N228" t="n">
+        <v>3719</v>
+      </c>
+      <c r="O228" t="n">
+        <v>3747</v>
+      </c>
+      <c r="P228" t="n">
+        <v>3851</v>
+      </c>
+      <c r="Q228" t="n">
+        <v>3946</v>
+      </c>
+      <c r="R228" t="n">
+        <v>3843</v>
+      </c>
+      <c r="S228" t="n">
+        <v>3878</v>
+      </c>
+      <c r="T228" t="n">
+        <v>3825</v>
+      </c>
+      <c r="U228" t="n">
+        <v>3840</v>
+      </c>
+      <c r="V228" t="n">
+        <v>3867</v>
+      </c>
+      <c r="W228" t="n">
+        <v>3904</v>
+      </c>
+      <c r="X228" t="n">
+        <v>3889</v>
+      </c>
+      <c r="Y228" t="n">
+        <v>3747</v>
+      </c>
+      <c r="Z228" t="n">
+        <v>3592</v>
+      </c>
+      <c r="AA228" t="n">
+        <v>3451</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA228"/>
+  <dimension ref="A1:AA229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19000,76 +19000,76 @@
         <v>15</v>
       </c>
       <c r="D224" t="n">
-        <v>3215</v>
+        <v>3191</v>
       </c>
       <c r="E224" t="n">
-        <v>3037</v>
+        <v>3014</v>
       </c>
       <c r="F224" t="n">
-        <v>2947</v>
+        <v>2927</v>
       </c>
       <c r="G224" t="n">
-        <v>2908</v>
+        <v>2890</v>
       </c>
       <c r="H224" t="n">
-        <v>2902</v>
+        <v>2887</v>
       </c>
       <c r="I224" t="n">
-        <v>3015</v>
+        <v>2995</v>
       </c>
       <c r="J224" t="n">
-        <v>3314</v>
+        <v>3289</v>
       </c>
       <c r="K224" t="n">
-        <v>3600</v>
+        <v>3561</v>
       </c>
       <c r="L224" t="n">
-        <v>3866</v>
+        <v>3806</v>
       </c>
       <c r="M224" t="n">
-        <v>3975</v>
+        <v>3898</v>
       </c>
       <c r="N224" t="n">
-        <v>4009</v>
+        <v>3915</v>
       </c>
       <c r="O224" t="n">
-        <v>4064</v>
+        <v>3976</v>
       </c>
       <c r="P224" t="n">
-        <v>4094</v>
+        <v>3994</v>
       </c>
       <c r="Q224" t="n">
-        <v>4202</v>
+        <v>4101</v>
       </c>
       <c r="R224" t="n">
-        <v>3980</v>
+        <v>3861</v>
       </c>
       <c r="S224" t="n">
-        <v>3995</v>
+        <v>3944</v>
       </c>
       <c r="T224" t="n">
-        <v>3990</v>
+        <v>3930</v>
       </c>
       <c r="U224" t="n">
-        <v>4011</v>
+        <v>4006</v>
       </c>
       <c r="V224" t="n">
-        <v>4058</v>
+        <v>4117</v>
       </c>
       <c r="W224" t="n">
-        <v>4142</v>
+        <v>4304</v>
       </c>
       <c r="X224" t="n">
-        <v>4185</v>
+        <v>4374</v>
       </c>
       <c r="Y224" t="n">
-        <v>3991</v>
+        <v>4096</v>
       </c>
       <c r="Z224" t="n">
-        <v>3784</v>
+        <v>3787</v>
       </c>
       <c r="AA224" t="n">
-        <v>3581</v>
+        <v>3498</v>
       </c>
     </row>
     <row r="225">
@@ -19083,76 +19083,76 @@
         <v>16</v>
       </c>
       <c r="D225" t="n">
-        <v>3227</v>
+        <v>3205</v>
       </c>
       <c r="E225" t="n">
-        <v>3045</v>
+        <v>3024</v>
       </c>
       <c r="F225" t="n">
-        <v>2954</v>
+        <v>2935</v>
       </c>
       <c r="G225" t="n">
-        <v>2914</v>
+        <v>2897</v>
       </c>
       <c r="H225" t="n">
-        <v>2908</v>
+        <v>2893</v>
       </c>
       <c r="I225" t="n">
-        <v>3022</v>
+        <v>3004</v>
       </c>
       <c r="J225" t="n">
-        <v>3325</v>
+        <v>3302</v>
       </c>
       <c r="K225" t="n">
-        <v>3614</v>
+        <v>3578</v>
       </c>
       <c r="L225" t="n">
-        <v>3884</v>
+        <v>3828</v>
       </c>
       <c r="M225" t="n">
-        <v>3994</v>
+        <v>3920</v>
       </c>
       <c r="N225" t="n">
-        <v>4029</v>
+        <v>3938</v>
       </c>
       <c r="O225" t="n">
-        <v>4084</v>
+        <v>4000</v>
       </c>
       <c r="P225" t="n">
-        <v>4115</v>
+        <v>4019</v>
       </c>
       <c r="Q225" t="n">
-        <v>4224</v>
+        <v>4127</v>
       </c>
       <c r="R225" t="n">
-        <v>4005</v>
+        <v>3891</v>
       </c>
       <c r="S225" t="n">
-        <v>4019</v>
+        <v>3970</v>
       </c>
       <c r="T225" t="n">
-        <v>4015</v>
+        <v>3957</v>
       </c>
       <c r="U225" t="n">
-        <v>4034</v>
+        <v>4030</v>
       </c>
       <c r="V225" t="n">
-        <v>4076</v>
+        <v>4136</v>
       </c>
       <c r="W225" t="n">
-        <v>4152</v>
+        <v>4315</v>
       </c>
       <c r="X225" t="n">
-        <v>4191</v>
+        <v>4382</v>
       </c>
       <c r="Y225" t="n">
-        <v>3998</v>
+        <v>4105</v>
       </c>
       <c r="Z225" t="n">
-        <v>3791</v>
+        <v>3796</v>
       </c>
       <c r="AA225" t="n">
-        <v>3589</v>
+        <v>3508</v>
       </c>
     </row>
     <row r="226">
@@ -19166,76 +19166,76 @@
         <v>17</v>
       </c>
       <c r="D226" t="n">
-        <v>3233</v>
+        <v>3217</v>
       </c>
       <c r="E226" t="n">
-        <v>3050</v>
+        <v>3033</v>
       </c>
       <c r="F226" t="n">
-        <v>2957</v>
+        <v>2942</v>
       </c>
       <c r="G226" t="n">
-        <v>2917</v>
+        <v>2903</v>
       </c>
       <c r="H226" t="n">
-        <v>2911</v>
+        <v>2900</v>
       </c>
       <c r="I226" t="n">
-        <v>3025</v>
+        <v>3012</v>
       </c>
       <c r="J226" t="n">
-        <v>3331</v>
+        <v>3314</v>
       </c>
       <c r="K226" t="n">
-        <v>3622</v>
+        <v>3594</v>
       </c>
       <c r="L226" t="n">
-        <v>3893</v>
+        <v>3847</v>
       </c>
       <c r="M226" t="n">
-        <v>4004</v>
+        <v>3941</v>
       </c>
       <c r="N226" t="n">
-        <v>4039</v>
+        <v>3958</v>
       </c>
       <c r="O226" t="n">
-        <v>4094</v>
+        <v>4022</v>
       </c>
       <c r="P226" t="n">
-        <v>4126</v>
+        <v>4040</v>
       </c>
       <c r="Q226" t="n">
-        <v>4236</v>
+        <v>4150</v>
       </c>
       <c r="R226" t="n">
-        <v>4018</v>
+        <v>3917</v>
       </c>
       <c r="S226" t="n">
-        <v>4031</v>
+        <v>3993</v>
       </c>
       <c r="T226" t="n">
-        <v>4027</v>
+        <v>3980</v>
       </c>
       <c r="U226" t="n">
-        <v>4045</v>
+        <v>4051</v>
       </c>
       <c r="V226" t="n">
-        <v>4085</v>
+        <v>4153</v>
       </c>
       <c r="W226" t="n">
-        <v>4157</v>
+        <v>4324</v>
       </c>
       <c r="X226" t="n">
-        <v>4194</v>
+        <v>4388</v>
       </c>
       <c r="Y226" t="n">
-        <v>4001</v>
+        <v>4112</v>
       </c>
       <c r="Z226" t="n">
-        <v>3795</v>
+        <v>3803</v>
       </c>
       <c r="AA226" t="n">
-        <v>3593</v>
+        <v>3516</v>
       </c>
     </row>
     <row r="227">
@@ -19249,76 +19249,76 @@
         <v>18</v>
       </c>
       <c r="D227" t="n">
-        <v>3244</v>
+        <v>3228</v>
       </c>
       <c r="E227" t="n">
-        <v>3058</v>
+        <v>3040</v>
       </c>
       <c r="F227" t="n">
-        <v>2964</v>
+        <v>2948</v>
       </c>
       <c r="G227" t="n">
-        <v>2923</v>
+        <v>2908</v>
       </c>
       <c r="H227" t="n">
-        <v>2917</v>
+        <v>2905</v>
       </c>
       <c r="I227" t="n">
-        <v>3032</v>
+        <v>3018</v>
       </c>
       <c r="J227" t="n">
-        <v>3341</v>
+        <v>3324</v>
       </c>
       <c r="K227" t="n">
-        <v>3636</v>
+        <v>3607</v>
       </c>
       <c r="L227" t="n">
-        <v>3910</v>
+        <v>3863</v>
       </c>
       <c r="M227" t="n">
-        <v>4022</v>
+        <v>3958</v>
       </c>
       <c r="N227" t="n">
-        <v>4058</v>
+        <v>3976</v>
       </c>
       <c r="O227" t="n">
-        <v>4114</v>
+        <v>4040</v>
       </c>
       <c r="P227" t="n">
-        <v>4146</v>
+        <v>4059</v>
       </c>
       <c r="Q227" t="n">
-        <v>4257</v>
+        <v>4170</v>
       </c>
       <c r="R227" t="n">
-        <v>4042</v>
+        <v>3940</v>
       </c>
       <c r="S227" t="n">
+        <v>4000</v>
+      </c>
+      <c r="T227" t="n">
+        <v>3990</v>
+      </c>
+      <c r="U227" t="n">
+        <v>4046</v>
+      </c>
+      <c r="V227" t="n">
+        <v>4127</v>
+      </c>
+      <c r="W227" t="n">
+        <v>4263</v>
+      </c>
+      <c r="X227" t="n">
+        <v>4314</v>
+      </c>
+      <c r="Y227" t="n">
         <v>4048</v>
       </c>
-      <c r="T227" t="n">
-        <v>4046</v>
-      </c>
-      <c r="U227" t="n">
-        <v>4054</v>
-      </c>
-      <c r="V227" t="n">
-        <v>4072</v>
-      </c>
-      <c r="W227" t="n">
-        <v>4104</v>
-      </c>
-      <c r="X227" t="n">
-        <v>4121</v>
-      </c>
-      <c r="Y227" t="n">
-        <v>3938</v>
-      </c>
       <c r="Z227" t="n">
-        <v>3743</v>
+        <v>3751</v>
       </c>
       <c r="AA227" t="n">
-        <v>3552</v>
+        <v>3475</v>
       </c>
     </row>
     <row r="228">
@@ -19332,76 +19332,159 @@
         <v>19</v>
       </c>
       <c r="D228" t="n">
-        <v>3237</v>
+        <v>3220</v>
       </c>
       <c r="E228" t="n">
-        <v>3058</v>
+        <v>3033</v>
       </c>
       <c r="F228" t="n">
-        <v>2954</v>
+        <v>2930</v>
       </c>
       <c r="G228" t="n">
-        <v>2888</v>
+        <v>2871</v>
       </c>
       <c r="H228" t="n">
-        <v>2849</v>
+        <v>2836</v>
       </c>
       <c r="I228" t="n">
-        <v>2875</v>
+        <v>2861</v>
       </c>
       <c r="J228" t="n">
-        <v>3004</v>
+        <v>2982</v>
       </c>
       <c r="K228" t="n">
-        <v>3173</v>
+        <v>3131</v>
       </c>
       <c r="L228" t="n">
-        <v>3402</v>
+        <v>3364</v>
       </c>
       <c r="M228" t="n">
-        <v>3580</v>
+        <v>3536</v>
       </c>
       <c r="N228" t="n">
-        <v>3719</v>
+        <v>3650</v>
       </c>
       <c r="O228" t="n">
-        <v>3747</v>
+        <v>3726</v>
       </c>
       <c r="P228" t="n">
-        <v>3851</v>
+        <v>3809</v>
       </c>
       <c r="Q228" t="n">
-        <v>3946</v>
+        <v>3857</v>
       </c>
       <c r="R228" t="n">
-        <v>3843</v>
+        <v>3829</v>
       </c>
       <c r="S228" t="n">
-        <v>3878</v>
+        <v>3780</v>
       </c>
       <c r="T228" t="n">
+        <v>3720</v>
+      </c>
+      <c r="U228" t="n">
+        <v>3930</v>
+      </c>
+      <c r="V228" t="n">
+        <v>4071</v>
+      </c>
+      <c r="W228" t="n">
+        <v>4098</v>
+      </c>
+      <c r="X228" t="n">
+        <v>4044</v>
+      </c>
+      <c r="Y228" t="n">
+        <v>3777</v>
+      </c>
+      <c r="Z228" t="n">
+        <v>3552</v>
+      </c>
+      <c r="AA228" t="n">
+        <v>3373</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B229" t="n">
+        <v>9</v>
+      </c>
+      <c r="C229" t="n">
+        <v>20</v>
+      </c>
+      <c r="D229" t="n">
+        <v>3172</v>
+      </c>
+      <c r="E229" t="n">
+        <v>2992</v>
+      </c>
+      <c r="F229" t="n">
+        <v>2873</v>
+      </c>
+      <c r="G229" t="n">
+        <v>2821</v>
+      </c>
+      <c r="H229" t="n">
+        <v>2790</v>
+      </c>
+      <c r="I229" t="n">
+        <v>2808</v>
+      </c>
+      <c r="J229" t="n">
+        <v>2935</v>
+      </c>
+      <c r="K229" t="n">
+        <v>3120</v>
+      </c>
+      <c r="L229" t="n">
+        <v>3405</v>
+      </c>
+      <c r="M229" t="n">
+        <v>3616</v>
+      </c>
+      <c r="N229" t="n">
+        <v>3732</v>
+      </c>
+      <c r="O229" t="n">
+        <v>3803</v>
+      </c>
+      <c r="P229" t="n">
+        <v>3859</v>
+      </c>
+      <c r="Q229" t="n">
+        <v>3841</v>
+      </c>
+      <c r="R229" t="n">
         <v>3825</v>
       </c>
-      <c r="U228" t="n">
-        <v>3840</v>
-      </c>
-      <c r="V228" t="n">
-        <v>3867</v>
-      </c>
-      <c r="W228" t="n">
-        <v>3904</v>
-      </c>
-      <c r="X228" t="n">
-        <v>3889</v>
-      </c>
-      <c r="Y228" t="n">
-        <v>3747</v>
-      </c>
-      <c r="Z228" t="n">
-        <v>3592</v>
-      </c>
-      <c r="AA228" t="n">
-        <v>3451</v>
+      <c r="S229" t="n">
+        <v>3801</v>
+      </c>
+      <c r="T229" t="n">
+        <v>3902</v>
+      </c>
+      <c r="U229" t="n">
+        <v>4037</v>
+      </c>
+      <c r="V229" t="n">
+        <v>4107</v>
+      </c>
+      <c r="W229" t="n">
+        <v>4232</v>
+      </c>
+      <c r="X229" t="n">
+        <v>4319</v>
+      </c>
+      <c r="Y229" t="n">
+        <v>4128</v>
+      </c>
+      <c r="Z229" t="n">
+        <v>3772</v>
+      </c>
+      <c r="AA229" t="n">
+        <v>3470</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA229"/>
+  <dimension ref="A1:AA230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19083,76 +19083,76 @@
         <v>16</v>
       </c>
       <c r="D225" t="n">
-        <v>3205</v>
+        <v>3130</v>
       </c>
       <c r="E225" t="n">
-        <v>3024</v>
+        <v>2987</v>
       </c>
       <c r="F225" t="n">
-        <v>2935</v>
+        <v>2918</v>
       </c>
       <c r="G225" t="n">
-        <v>2897</v>
+        <v>2889</v>
       </c>
       <c r="H225" t="n">
-        <v>2893</v>
+        <v>2891</v>
       </c>
       <c r="I225" t="n">
-        <v>3004</v>
+        <v>3007</v>
       </c>
       <c r="J225" t="n">
-        <v>3302</v>
+        <v>3324</v>
       </c>
       <c r="K225" t="n">
-        <v>3578</v>
+        <v>3615</v>
       </c>
       <c r="L225" t="n">
-        <v>3828</v>
+        <v>3865</v>
       </c>
       <c r="M225" t="n">
-        <v>3920</v>
+        <v>3957</v>
       </c>
       <c r="N225" t="n">
-        <v>3938</v>
+        <v>3967</v>
       </c>
       <c r="O225" t="n">
-        <v>4000</v>
+        <v>4024</v>
       </c>
       <c r="P225" t="n">
-        <v>4019</v>
+        <v>4038</v>
       </c>
       <c r="Q225" t="n">
-        <v>4127</v>
+        <v>4146</v>
       </c>
       <c r="R225" t="n">
-        <v>3891</v>
+        <v>4130</v>
       </c>
       <c r="S225" t="n">
-        <v>3970</v>
+        <v>4173</v>
       </c>
       <c r="T225" t="n">
-        <v>3957</v>
+        <v>4183</v>
       </c>
       <c r="U225" t="n">
-        <v>4030</v>
+        <v>4210</v>
       </c>
       <c r="V225" t="n">
-        <v>4136</v>
+        <v>4258</v>
       </c>
       <c r="W225" t="n">
-        <v>4315</v>
+        <v>4354</v>
       </c>
       <c r="X225" t="n">
-        <v>4382</v>
+        <v>4386</v>
       </c>
       <c r="Y225" t="n">
-        <v>4105</v>
+        <v>4125</v>
       </c>
       <c r="Z225" t="n">
-        <v>3796</v>
+        <v>3830</v>
       </c>
       <c r="AA225" t="n">
-        <v>3508</v>
+        <v>3557</v>
       </c>
     </row>
     <row r="226">
@@ -19166,76 +19166,76 @@
         <v>17</v>
       </c>
       <c r="D226" t="n">
-        <v>3217</v>
+        <v>3135</v>
       </c>
       <c r="E226" t="n">
-        <v>3033</v>
+        <v>2990</v>
       </c>
       <c r="F226" t="n">
-        <v>2942</v>
+        <v>2921</v>
       </c>
       <c r="G226" t="n">
-        <v>2903</v>
+        <v>2891</v>
       </c>
       <c r="H226" t="n">
-        <v>2900</v>
+        <v>2893</v>
       </c>
       <c r="I226" t="n">
-        <v>3012</v>
+        <v>3010</v>
       </c>
       <c r="J226" t="n">
-        <v>3314</v>
+        <v>3329</v>
       </c>
       <c r="K226" t="n">
-        <v>3594</v>
+        <v>3621</v>
       </c>
       <c r="L226" t="n">
-        <v>3847</v>
+        <v>3873</v>
       </c>
       <c r="M226" t="n">
-        <v>3941</v>
+        <v>3966</v>
       </c>
       <c r="N226" t="n">
-        <v>3958</v>
+        <v>3975</v>
       </c>
       <c r="O226" t="n">
-        <v>4022</v>
+        <v>4033</v>
       </c>
       <c r="P226" t="n">
-        <v>4040</v>
+        <v>4047</v>
       </c>
       <c r="Q226" t="n">
-        <v>4150</v>
+        <v>4155</v>
       </c>
       <c r="R226" t="n">
-        <v>3917</v>
+        <v>4141</v>
       </c>
       <c r="S226" t="n">
-        <v>3993</v>
+        <v>4182</v>
       </c>
       <c r="T226" t="n">
-        <v>3980</v>
+        <v>4192</v>
       </c>
       <c r="U226" t="n">
-        <v>4051</v>
+        <v>4219</v>
       </c>
       <c r="V226" t="n">
-        <v>4153</v>
+        <v>4264</v>
       </c>
       <c r="W226" t="n">
-        <v>4324</v>
+        <v>4358</v>
       </c>
       <c r="X226" t="n">
-        <v>4388</v>
+        <v>4389</v>
       </c>
       <c r="Y226" t="n">
-        <v>4112</v>
+        <v>4128</v>
       </c>
       <c r="Z226" t="n">
-        <v>3803</v>
+        <v>3833</v>
       </c>
       <c r="AA226" t="n">
-        <v>3516</v>
+        <v>3561</v>
       </c>
     </row>
     <row r="227">
@@ -19249,76 +19249,76 @@
         <v>18</v>
       </c>
       <c r="D227" t="n">
-        <v>3228</v>
+        <v>3140</v>
       </c>
       <c r="E227" t="n">
-        <v>3040</v>
+        <v>2994</v>
       </c>
       <c r="F227" t="n">
-        <v>2948</v>
+        <v>2924</v>
       </c>
       <c r="G227" t="n">
-        <v>2908</v>
+        <v>2894</v>
       </c>
       <c r="H227" t="n">
-        <v>2905</v>
+        <v>2896</v>
       </c>
       <c r="I227" t="n">
-        <v>3018</v>
+        <v>3014</v>
       </c>
       <c r="J227" t="n">
-        <v>3324</v>
+        <v>3334</v>
       </c>
       <c r="K227" t="n">
-        <v>3607</v>
+        <v>3629</v>
       </c>
       <c r="L227" t="n">
-        <v>3863</v>
+        <v>3882</v>
       </c>
       <c r="M227" t="n">
-        <v>3958</v>
+        <v>3975</v>
       </c>
       <c r="N227" t="n">
-        <v>3976</v>
+        <v>3985</v>
       </c>
       <c r="O227" t="n">
-        <v>4040</v>
+        <v>4043</v>
       </c>
       <c r="P227" t="n">
-        <v>4059</v>
+        <v>4057</v>
       </c>
       <c r="Q227" t="n">
-        <v>4170</v>
+        <v>4166</v>
       </c>
       <c r="R227" t="n">
-        <v>3940</v>
+        <v>4154</v>
       </c>
       <c r="S227" t="n">
-        <v>4000</v>
+        <v>4180</v>
       </c>
       <c r="T227" t="n">
-        <v>3990</v>
+        <v>4186</v>
       </c>
       <c r="U227" t="n">
-        <v>4046</v>
+        <v>4203</v>
       </c>
       <c r="V227" t="n">
-        <v>4127</v>
+        <v>4232</v>
       </c>
       <c r="W227" t="n">
-        <v>4263</v>
+        <v>4292</v>
       </c>
       <c r="X227" t="n">
-        <v>4314</v>
+        <v>4312</v>
       </c>
       <c r="Y227" t="n">
-        <v>4048</v>
+        <v>4062</v>
       </c>
       <c r="Z227" t="n">
-        <v>3751</v>
+        <v>3778</v>
       </c>
       <c r="AA227" t="n">
-        <v>3475</v>
+        <v>3516</v>
       </c>
     </row>
     <row r="228">
@@ -19332,76 +19332,76 @@
         <v>19</v>
       </c>
       <c r="D228" t="n">
-        <v>3220</v>
+        <v>3129</v>
       </c>
       <c r="E228" t="n">
-        <v>3033</v>
+        <v>2980</v>
       </c>
       <c r="F228" t="n">
-        <v>2930</v>
+        <v>2898</v>
       </c>
       <c r="G228" t="n">
-        <v>2871</v>
+        <v>2851</v>
       </c>
       <c r="H228" t="n">
-        <v>2836</v>
+        <v>2824</v>
       </c>
       <c r="I228" t="n">
-        <v>2861</v>
+        <v>2849</v>
       </c>
       <c r="J228" t="n">
-        <v>2982</v>
+        <v>2970</v>
       </c>
       <c r="K228" t="n">
-        <v>3131</v>
+        <v>3119</v>
       </c>
       <c r="L228" t="n">
-        <v>3364</v>
+        <v>3352</v>
       </c>
       <c r="M228" t="n">
-        <v>3536</v>
+        <v>3524</v>
       </c>
       <c r="N228" t="n">
-        <v>3650</v>
+        <v>3638</v>
       </c>
       <c r="O228" t="n">
-        <v>3726</v>
+        <v>3714</v>
       </c>
       <c r="P228" t="n">
-        <v>3809</v>
+        <v>3798</v>
       </c>
       <c r="Q228" t="n">
-        <v>3857</v>
+        <v>3846</v>
       </c>
       <c r="R228" t="n">
-        <v>3829</v>
+        <v>3862</v>
       </c>
       <c r="S228" t="n">
-        <v>3780</v>
+        <v>3890</v>
       </c>
       <c r="T228" t="n">
-        <v>3720</v>
+        <v>3925</v>
       </c>
       <c r="U228" t="n">
-        <v>3930</v>
+        <v>4020</v>
       </c>
       <c r="V228" t="n">
-        <v>4071</v>
+        <v>4084</v>
       </c>
       <c r="W228" t="n">
-        <v>4098</v>
+        <v>4096</v>
       </c>
       <c r="X228" t="n">
-        <v>4044</v>
+        <v>4045</v>
       </c>
       <c r="Y228" t="n">
-        <v>3777</v>
+        <v>3793</v>
       </c>
       <c r="Z228" t="n">
-        <v>3552</v>
+        <v>3581</v>
       </c>
       <c r="AA228" t="n">
-        <v>3373</v>
+        <v>3412</v>
       </c>
     </row>
     <row r="229">
@@ -19415,76 +19415,159 @@
         <v>20</v>
       </c>
       <c r="D229" t="n">
-        <v>3172</v>
+        <v>3079</v>
       </c>
       <c r="E229" t="n">
-        <v>2992</v>
+        <v>2933</v>
       </c>
       <c r="F229" t="n">
-        <v>2873</v>
+        <v>2842</v>
       </c>
       <c r="G229" t="n">
-        <v>2821</v>
+        <v>2804</v>
       </c>
       <c r="H229" t="n">
-        <v>2790</v>
+        <v>2777</v>
       </c>
       <c r="I229" t="n">
-        <v>2808</v>
+        <v>2800</v>
       </c>
       <c r="J229" t="n">
-        <v>2935</v>
+        <v>2913</v>
       </c>
       <c r="K229" t="n">
-        <v>3120</v>
+        <v>3068</v>
       </c>
       <c r="L229" t="n">
-        <v>3405</v>
+        <v>3323</v>
       </c>
       <c r="M229" t="n">
-        <v>3616</v>
+        <v>3525</v>
       </c>
       <c r="N229" t="n">
-        <v>3732</v>
+        <v>3647</v>
       </c>
       <c r="O229" t="n">
-        <v>3803</v>
+        <v>3781</v>
       </c>
       <c r="P229" t="n">
-        <v>3859</v>
+        <v>3845</v>
       </c>
       <c r="Q229" t="n">
-        <v>3841</v>
+        <v>3903</v>
       </c>
       <c r="R229" t="n">
-        <v>3825</v>
+        <v>3947</v>
       </c>
       <c r="S229" t="n">
-        <v>3801</v>
+        <v>4001</v>
       </c>
       <c r="T229" t="n">
-        <v>3902</v>
+        <v>4016</v>
       </c>
       <c r="U229" t="n">
-        <v>4037</v>
+        <v>4095</v>
       </c>
       <c r="V229" t="n">
-        <v>4107</v>
+        <v>4146</v>
       </c>
       <c r="W229" t="n">
-        <v>4232</v>
+        <v>4239</v>
       </c>
       <c r="X229" t="n">
-        <v>4319</v>
+        <v>4316</v>
       </c>
       <c r="Y229" t="n">
-        <v>4128</v>
+        <v>4067</v>
       </c>
       <c r="Z229" t="n">
-        <v>3772</v>
+        <v>3777</v>
       </c>
       <c r="AA229" t="n">
-        <v>3470</v>
+        <v>3508</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B230" t="n">
+        <v>9</v>
+      </c>
+      <c r="C230" t="n">
+        <v>21</v>
+      </c>
+      <c r="D230" t="n">
+        <v>3122</v>
+      </c>
+      <c r="E230" t="n">
+        <v>2965</v>
+      </c>
+      <c r="F230" t="n">
+        <v>2924</v>
+      </c>
+      <c r="G230" t="n">
+        <v>2886</v>
+      </c>
+      <c r="H230" t="n">
+        <v>2853</v>
+      </c>
+      <c r="I230" t="n">
+        <v>2969</v>
+      </c>
+      <c r="J230" t="n">
+        <v>3187</v>
+      </c>
+      <c r="K230" t="n">
+        <v>3514</v>
+      </c>
+      <c r="L230" t="n">
+        <v>3839</v>
+      </c>
+      <c r="M230" t="n">
+        <v>4057</v>
+      </c>
+      <c r="N230" t="n">
+        <v>4190</v>
+      </c>
+      <c r="O230" t="n">
+        <v>4223</v>
+      </c>
+      <c r="P230" t="n">
+        <v>4240</v>
+      </c>
+      <c r="Q230" t="n">
+        <v>4331</v>
+      </c>
+      <c r="R230" t="n">
+        <v>4340</v>
+      </c>
+      <c r="S230" t="n">
+        <v>4341</v>
+      </c>
+      <c r="T230" t="n">
+        <v>4360</v>
+      </c>
+      <c r="U230" t="n">
+        <v>4393</v>
+      </c>
+      <c r="V230" t="n">
+        <v>4420</v>
+      </c>
+      <c r="W230" t="n">
+        <v>4450</v>
+      </c>
+      <c r="X230" t="n">
+        <v>4533</v>
+      </c>
+      <c r="Y230" t="n">
+        <v>4282</v>
+      </c>
+      <c r="Z230" t="n">
+        <v>3955</v>
+      </c>
+      <c r="AA230" t="n">
+        <v>3671</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA230"/>
+  <dimension ref="A1:AA231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19570,6 +19570,89 @@
         <v>3671</v>
       </c>
     </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B231" t="n">
+        <v>9</v>
+      </c>
+      <c r="C231" t="n">
+        <v>22</v>
+      </c>
+      <c r="D231" t="n">
+        <v>3161</v>
+      </c>
+      <c r="E231" t="n">
+        <v>3019</v>
+      </c>
+      <c r="F231" t="n">
+        <v>2952</v>
+      </c>
+      <c r="G231" t="n">
+        <v>2923</v>
+      </c>
+      <c r="H231" t="n">
+        <v>2925</v>
+      </c>
+      <c r="I231" t="n">
+        <v>3052</v>
+      </c>
+      <c r="J231" t="n">
+        <v>3399</v>
+      </c>
+      <c r="K231" t="n">
+        <v>3718</v>
+      </c>
+      <c r="L231" t="n">
+        <v>3992</v>
+      </c>
+      <c r="M231" t="n">
+        <v>4093</v>
+      </c>
+      <c r="N231" t="n">
+        <v>4103</v>
+      </c>
+      <c r="O231" t="n">
+        <v>4166</v>
+      </c>
+      <c r="P231" t="n">
+        <v>4181</v>
+      </c>
+      <c r="Q231" t="n">
+        <v>4299</v>
+      </c>
+      <c r="R231" t="n">
+        <v>4304</v>
+      </c>
+      <c r="S231" t="n">
+        <v>4341</v>
+      </c>
+      <c r="T231" t="n">
+        <v>4349</v>
+      </c>
+      <c r="U231" t="n">
+        <v>4373</v>
+      </c>
+      <c r="V231" t="n">
+        <v>4413</v>
+      </c>
+      <c r="W231" t="n">
+        <v>4497</v>
+      </c>
+      <c r="X231" t="n">
+        <v>4524</v>
+      </c>
+      <c r="Y231" t="n">
+        <v>4252</v>
+      </c>
+      <c r="Z231" t="n">
+        <v>3945</v>
+      </c>
+      <c r="AA231" t="n">
+        <v>3660</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA231"/>
+  <dimension ref="A1:AA232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19249,76 +19249,76 @@
         <v>18</v>
       </c>
       <c r="D227" t="n">
-        <v>3140</v>
+        <v>3210</v>
       </c>
       <c r="E227" t="n">
-        <v>2994</v>
+        <v>3003</v>
       </c>
       <c r="F227" t="n">
-        <v>2924</v>
+        <v>2913</v>
       </c>
       <c r="G227" t="n">
-        <v>2894</v>
+        <v>2870</v>
       </c>
       <c r="H227" t="n">
-        <v>2896</v>
+        <v>2889</v>
       </c>
       <c r="I227" t="n">
-        <v>3014</v>
+        <v>3049</v>
       </c>
       <c r="J227" t="n">
-        <v>3334</v>
+        <v>3354</v>
       </c>
       <c r="K227" t="n">
-        <v>3629</v>
+        <v>3612</v>
       </c>
       <c r="L227" t="n">
-        <v>3882</v>
+        <v>3833</v>
       </c>
       <c r="M227" t="n">
-        <v>3975</v>
+        <v>3895</v>
       </c>
       <c r="N227" t="n">
-        <v>3985</v>
+        <v>3879</v>
       </c>
       <c r="O227" t="n">
-        <v>4043</v>
+        <v>3917</v>
       </c>
       <c r="P227" t="n">
+        <v>3936</v>
+      </c>
+      <c r="Q227" t="n">
+        <v>4023</v>
+      </c>
+      <c r="R227" t="n">
+        <v>3886</v>
+      </c>
+      <c r="S227" t="n">
+        <v>3886</v>
+      </c>
+      <c r="T227" t="n">
+        <v>3886</v>
+      </c>
+      <c r="U227" t="n">
+        <v>3921</v>
+      </c>
+      <c r="V227" t="n">
         <v>4057</v>
       </c>
-      <c r="Q227" t="n">
-        <v>4166</v>
-      </c>
-      <c r="R227" t="n">
-        <v>4154</v>
-      </c>
-      <c r="S227" t="n">
-        <v>4180</v>
-      </c>
-      <c r="T227" t="n">
-        <v>4186</v>
-      </c>
-      <c r="U227" t="n">
-        <v>4203</v>
-      </c>
-      <c r="V227" t="n">
-        <v>4232</v>
-      </c>
       <c r="W227" t="n">
-        <v>4292</v>
+        <v>4241</v>
       </c>
       <c r="X227" t="n">
-        <v>4312</v>
+        <v>4200</v>
       </c>
       <c r="Y227" t="n">
-        <v>4062</v>
+        <v>3993</v>
       </c>
       <c r="Z227" t="n">
-        <v>3778</v>
+        <v>3697</v>
       </c>
       <c r="AA227" t="n">
-        <v>3516</v>
+        <v>3460</v>
       </c>
     </row>
     <row r="228">
@@ -19332,76 +19332,76 @@
         <v>19</v>
       </c>
       <c r="D228" t="n">
-        <v>3129</v>
+        <v>3205</v>
       </c>
       <c r="E228" t="n">
-        <v>2980</v>
+        <v>3008</v>
       </c>
       <c r="F228" t="n">
-        <v>2898</v>
+        <v>2897</v>
       </c>
       <c r="G228" t="n">
-        <v>2851</v>
+        <v>2838</v>
       </c>
       <c r="H228" t="n">
-        <v>2824</v>
+        <v>2803</v>
       </c>
       <c r="I228" t="n">
-        <v>2849</v>
+        <v>2829</v>
       </c>
       <c r="J228" t="n">
-        <v>2970</v>
+        <v>2950</v>
       </c>
       <c r="K228" t="n">
-        <v>3119</v>
+        <v>3091</v>
       </c>
       <c r="L228" t="n">
-        <v>3352</v>
+        <v>3288</v>
       </c>
       <c r="M228" t="n">
-        <v>3524</v>
+        <v>3454</v>
       </c>
       <c r="N228" t="n">
-        <v>3638</v>
+        <v>3542</v>
       </c>
       <c r="O228" t="n">
-        <v>3714</v>
+        <v>3608</v>
       </c>
       <c r="P228" t="n">
-        <v>3798</v>
+        <v>3682</v>
       </c>
       <c r="Q228" t="n">
-        <v>3846</v>
+        <v>3715</v>
       </c>
       <c r="R228" t="n">
-        <v>3862</v>
+        <v>3703</v>
       </c>
       <c r="S228" t="n">
-        <v>3890</v>
+        <v>3690</v>
       </c>
       <c r="T228" t="n">
-        <v>3925</v>
+        <v>3673</v>
       </c>
       <c r="U228" t="n">
-        <v>4020</v>
+        <v>3767</v>
       </c>
       <c r="V228" t="n">
-        <v>4084</v>
+        <v>3913</v>
       </c>
       <c r="W228" t="n">
-        <v>4096</v>
+        <v>4025</v>
       </c>
       <c r="X228" t="n">
-        <v>4045</v>
+        <v>3973</v>
       </c>
       <c r="Y228" t="n">
-        <v>3793</v>
+        <v>3750</v>
       </c>
       <c r="Z228" t="n">
-        <v>3581</v>
+        <v>3550</v>
       </c>
       <c r="AA228" t="n">
-        <v>3412</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="229">
@@ -19415,76 +19415,76 @@
         <v>20</v>
       </c>
       <c r="D229" t="n">
-        <v>3079</v>
+        <v>3157</v>
       </c>
       <c r="E229" t="n">
-        <v>2933</v>
+        <v>2969</v>
       </c>
       <c r="F229" t="n">
-        <v>2842</v>
+        <v>2845</v>
       </c>
       <c r="G229" t="n">
-        <v>2804</v>
+        <v>2799</v>
       </c>
       <c r="H229" t="n">
-        <v>2777</v>
+        <v>2757</v>
       </c>
       <c r="I229" t="n">
-        <v>2800</v>
+        <v>2776</v>
       </c>
       <c r="J229" t="n">
-        <v>2913</v>
+        <v>2887</v>
       </c>
       <c r="K229" t="n">
-        <v>3068</v>
+        <v>3020</v>
       </c>
       <c r="L229" t="n">
-        <v>3323</v>
+        <v>3268</v>
       </c>
       <c r="M229" t="n">
-        <v>3525</v>
+        <v>3466</v>
       </c>
       <c r="N229" t="n">
-        <v>3647</v>
+        <v>3575</v>
       </c>
       <c r="O229" t="n">
-        <v>3781</v>
+        <v>3686</v>
       </c>
       <c r="P229" t="n">
-        <v>3845</v>
+        <v>3717</v>
       </c>
       <c r="Q229" t="n">
-        <v>3903</v>
+        <v>3734</v>
       </c>
       <c r="R229" t="n">
-        <v>3947</v>
+        <v>3746</v>
       </c>
       <c r="S229" t="n">
-        <v>4001</v>
+        <v>3755</v>
       </c>
       <c r="T229" t="n">
-        <v>4016</v>
+        <v>3763</v>
       </c>
       <c r="U229" t="n">
-        <v>4095</v>
+        <v>3860</v>
       </c>
       <c r="V229" t="n">
-        <v>4146</v>
+        <v>3956</v>
       </c>
       <c r="W229" t="n">
-        <v>4239</v>
+        <v>4127</v>
       </c>
       <c r="X229" t="n">
-        <v>4316</v>
+        <v>4246</v>
       </c>
       <c r="Y229" t="n">
-        <v>4067</v>
+        <v>3991</v>
       </c>
       <c r="Z229" t="n">
-        <v>3777</v>
+        <v>3700</v>
       </c>
       <c r="AA229" t="n">
-        <v>3508</v>
+        <v>3458</v>
       </c>
     </row>
     <row r="230">
@@ -19498,76 +19498,76 @@
         <v>21</v>
       </c>
       <c r="D230" t="n">
-        <v>3122</v>
+        <v>3202</v>
       </c>
       <c r="E230" t="n">
-        <v>2965</v>
+        <v>2992</v>
       </c>
       <c r="F230" t="n">
-        <v>2924</v>
+        <v>2886</v>
       </c>
       <c r="G230" t="n">
-        <v>2886</v>
+        <v>2837</v>
       </c>
       <c r="H230" t="n">
-        <v>2853</v>
+        <v>2834</v>
       </c>
       <c r="I230" t="n">
-        <v>2969</v>
+        <v>2922</v>
       </c>
       <c r="J230" t="n">
-        <v>3187</v>
+        <v>3235</v>
       </c>
       <c r="K230" t="n">
-        <v>3514</v>
+        <v>3527</v>
       </c>
       <c r="L230" t="n">
-        <v>3839</v>
+        <v>3838</v>
       </c>
       <c r="M230" t="n">
-        <v>4057</v>
+        <v>4029</v>
       </c>
       <c r="N230" t="n">
-        <v>4190</v>
+        <v>4088</v>
       </c>
       <c r="O230" t="n">
-        <v>4223</v>
+        <v>4146</v>
       </c>
       <c r="P230" t="n">
-        <v>4240</v>
+        <v>4149</v>
       </c>
       <c r="Q230" t="n">
-        <v>4331</v>
+        <v>4206</v>
       </c>
       <c r="R230" t="n">
-        <v>4340</v>
+        <v>4097</v>
       </c>
       <c r="S230" t="n">
-        <v>4341</v>
+        <v>4100</v>
       </c>
       <c r="T230" t="n">
-        <v>4360</v>
+        <v>4132</v>
       </c>
       <c r="U230" t="n">
-        <v>4393</v>
+        <v>4185</v>
       </c>
       <c r="V230" t="n">
-        <v>4420</v>
+        <v>4251</v>
       </c>
       <c r="W230" t="n">
-        <v>4450</v>
+        <v>4361</v>
       </c>
       <c r="X230" t="n">
-        <v>4533</v>
+        <v>4464</v>
       </c>
       <c r="Y230" t="n">
-        <v>4282</v>
+        <v>4206</v>
       </c>
       <c r="Z230" t="n">
-        <v>3955</v>
+        <v>3912</v>
       </c>
       <c r="AA230" t="n">
-        <v>3671</v>
+        <v>3622</v>
       </c>
     </row>
     <row r="231">
@@ -19581,76 +19581,159 @@
         <v>22</v>
       </c>
       <c r="D231" t="n">
-        <v>3161</v>
+        <v>3211</v>
       </c>
       <c r="E231" t="n">
-        <v>3019</v>
+        <v>3015</v>
       </c>
       <c r="F231" t="n">
-        <v>2952</v>
+        <v>2930</v>
       </c>
       <c r="G231" t="n">
-        <v>2923</v>
+        <v>2889</v>
       </c>
       <c r="H231" t="n">
-        <v>2925</v>
+        <v>2908</v>
       </c>
       <c r="I231" t="n">
-        <v>3052</v>
+        <v>3079</v>
       </c>
       <c r="J231" t="n">
-        <v>3399</v>
+        <v>3405</v>
       </c>
       <c r="K231" t="n">
-        <v>3718</v>
+        <v>3679</v>
       </c>
       <c r="L231" t="n">
-        <v>3992</v>
+        <v>3915</v>
       </c>
       <c r="M231" t="n">
-        <v>4093</v>
+        <v>3981</v>
       </c>
       <c r="N231" t="n">
-        <v>4103</v>
+        <v>3964</v>
       </c>
       <c r="O231" t="n">
-        <v>4166</v>
+        <v>4004</v>
       </c>
       <c r="P231" t="n">
-        <v>4181</v>
+        <v>4025</v>
       </c>
       <c r="Q231" t="n">
-        <v>4299</v>
+        <v>4118</v>
       </c>
       <c r="R231" t="n">
-        <v>4304</v>
+        <v>3985</v>
       </c>
       <c r="S231" t="n">
-        <v>4341</v>
+        <v>3985</v>
       </c>
       <c r="T231" t="n">
-        <v>4349</v>
+        <v>3985</v>
       </c>
       <c r="U231" t="n">
-        <v>4373</v>
+        <v>4032</v>
       </c>
       <c r="V231" t="n">
-        <v>4413</v>
+        <v>4219</v>
       </c>
       <c r="W231" t="n">
-        <v>4497</v>
+        <v>4472</v>
       </c>
       <c r="X231" t="n">
-        <v>4524</v>
+        <v>4424</v>
       </c>
       <c r="Y231" t="n">
-        <v>4252</v>
+        <v>4192</v>
       </c>
       <c r="Z231" t="n">
-        <v>3945</v>
+        <v>3857</v>
       </c>
       <c r="AA231" t="n">
-        <v>3660</v>
+        <v>3591</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B232" t="n">
+        <v>9</v>
+      </c>
+      <c r="C232" t="n">
+        <v>23</v>
+      </c>
+      <c r="D232" t="n">
+        <v>3170</v>
+      </c>
+      <c r="E232" t="n">
+        <v>2986</v>
+      </c>
+      <c r="F232" t="n">
+        <v>2907</v>
+      </c>
+      <c r="G232" t="n">
+        <v>2868</v>
+      </c>
+      <c r="H232" t="n">
+        <v>2887</v>
+      </c>
+      <c r="I232" t="n">
+        <v>3050</v>
+      </c>
+      <c r="J232" t="n">
+        <v>3361</v>
+      </c>
+      <c r="K232" t="n">
+        <v>3623</v>
+      </c>
+      <c r="L232" t="n">
+        <v>3848</v>
+      </c>
+      <c r="M232" t="n">
+        <v>3911</v>
+      </c>
+      <c r="N232" t="n">
+        <v>3894</v>
+      </c>
+      <c r="O232" t="n">
+        <v>3933</v>
+      </c>
+      <c r="P232" t="n">
+        <v>3953</v>
+      </c>
+      <c r="Q232" t="n">
+        <v>4041</v>
+      </c>
+      <c r="R232" t="n">
+        <v>3889</v>
+      </c>
+      <c r="S232" t="n">
+        <v>3889</v>
+      </c>
+      <c r="T232" t="n">
+        <v>3889</v>
+      </c>
+      <c r="U232" t="n">
+        <v>3946</v>
+      </c>
+      <c r="V232" t="n">
+        <v>4172</v>
+      </c>
+      <c r="W232" t="n">
+        <v>4478</v>
+      </c>
+      <c r="X232" t="n">
+        <v>4429</v>
+      </c>
+      <c r="Y232" t="n">
+        <v>4188</v>
+      </c>
+      <c r="Z232" t="n">
+        <v>3841</v>
+      </c>
+      <c r="AA232" t="n">
+        <v>3564</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA232"/>
+  <dimension ref="A1:AA233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19332,16 +19332,16 @@
         <v>19</v>
       </c>
       <c r="D228" t="n">
-        <v>3205</v>
+        <v>3193</v>
       </c>
       <c r="E228" t="n">
-        <v>3008</v>
+        <v>3003</v>
       </c>
       <c r="F228" t="n">
-        <v>2897</v>
+        <v>2895</v>
       </c>
       <c r="G228" t="n">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="H228" t="n">
         <v>2803</v>
@@ -19350,58 +19350,58 @@
         <v>2829</v>
       </c>
       <c r="J228" t="n">
-        <v>2950</v>
+        <v>2952</v>
       </c>
       <c r="K228" t="n">
-        <v>3091</v>
+        <v>3093</v>
       </c>
       <c r="L228" t="n">
-        <v>3288</v>
+        <v>3291</v>
       </c>
       <c r="M228" t="n">
-        <v>3454</v>
+        <v>3458</v>
       </c>
       <c r="N228" t="n">
-        <v>3542</v>
+        <v>3546</v>
       </c>
       <c r="O228" t="n">
-        <v>3608</v>
+        <v>3613</v>
       </c>
       <c r="P228" t="n">
-        <v>3682</v>
+        <v>3687</v>
       </c>
       <c r="Q228" t="n">
-        <v>3715</v>
+        <v>3720</v>
       </c>
       <c r="R228" t="n">
-        <v>3703</v>
+        <v>3731</v>
       </c>
       <c r="S228" t="n">
-        <v>3690</v>
+        <v>3744</v>
       </c>
       <c r="T228" t="n">
-        <v>3673</v>
+        <v>3760</v>
       </c>
       <c r="U228" t="n">
-        <v>3767</v>
+        <v>3820</v>
       </c>
       <c r="V228" t="n">
         <v>3913</v>
       </c>
       <c r="W228" t="n">
-        <v>4025</v>
+        <v>3984</v>
       </c>
       <c r="X228" t="n">
-        <v>3973</v>
+        <v>3935</v>
       </c>
       <c r="Y228" t="n">
-        <v>3750</v>
+        <v>3723</v>
       </c>
       <c r="Z228" t="n">
-        <v>3550</v>
+        <v>3533</v>
       </c>
       <c r="AA228" t="n">
-        <v>3360</v>
+        <v>3354</v>
       </c>
     </row>
     <row r="229">
@@ -19415,76 +19415,76 @@
         <v>20</v>
       </c>
       <c r="D229" t="n">
-        <v>3157</v>
+        <v>3145</v>
       </c>
       <c r="E229" t="n">
-        <v>2969</v>
+        <v>2964</v>
       </c>
       <c r="F229" t="n">
-        <v>2845</v>
+        <v>2843</v>
       </c>
       <c r="G229" t="n">
         <v>2799</v>
       </c>
       <c r="H229" t="n">
-        <v>2757</v>
+        <v>2758</v>
       </c>
       <c r="I229" t="n">
-        <v>2776</v>
+        <v>2777</v>
       </c>
       <c r="J229" t="n">
-        <v>2887</v>
+        <v>2888</v>
       </c>
       <c r="K229" t="n">
-        <v>3020</v>
+        <v>3022</v>
       </c>
       <c r="L229" t="n">
-        <v>3268</v>
+        <v>3271</v>
       </c>
       <c r="M229" t="n">
-        <v>3466</v>
+        <v>3471</v>
       </c>
       <c r="N229" t="n">
-        <v>3575</v>
+        <v>3580</v>
       </c>
       <c r="O229" t="n">
-        <v>3686</v>
+        <v>3691</v>
       </c>
       <c r="P229" t="n">
-        <v>3717</v>
+        <v>3723</v>
       </c>
       <c r="Q229" t="n">
-        <v>3734</v>
+        <v>3778</v>
       </c>
       <c r="R229" t="n">
-        <v>3746</v>
+        <v>3815</v>
       </c>
       <c r="S229" t="n">
-        <v>3755</v>
+        <v>3842</v>
       </c>
       <c r="T229" t="n">
-        <v>3763</v>
+        <v>3848</v>
       </c>
       <c r="U229" t="n">
-        <v>3860</v>
+        <v>3920</v>
       </c>
       <c r="V229" t="n">
-        <v>3956</v>
+        <v>3991</v>
       </c>
       <c r="W229" t="n">
-        <v>4127</v>
+        <v>4117</v>
       </c>
       <c r="X229" t="n">
-        <v>4246</v>
+        <v>4205</v>
       </c>
       <c r="Y229" t="n">
-        <v>3991</v>
+        <v>3962</v>
       </c>
       <c r="Z229" t="n">
-        <v>3700</v>
+        <v>3682</v>
       </c>
       <c r="AA229" t="n">
-        <v>3458</v>
+        <v>3451</v>
       </c>
     </row>
     <row r="230">
@@ -19498,76 +19498,76 @@
         <v>21</v>
       </c>
       <c r="D230" t="n">
-        <v>3202</v>
+        <v>3190</v>
       </c>
       <c r="E230" t="n">
-        <v>2992</v>
+        <v>2988</v>
       </c>
       <c r="F230" t="n">
-        <v>2886</v>
+        <v>2885</v>
       </c>
       <c r="G230" t="n">
-        <v>2837</v>
+        <v>2838</v>
       </c>
       <c r="H230" t="n">
-        <v>2834</v>
+        <v>2835</v>
       </c>
       <c r="I230" t="n">
-        <v>2922</v>
+        <v>2923</v>
       </c>
       <c r="J230" t="n">
-        <v>3235</v>
+        <v>3238</v>
       </c>
       <c r="K230" t="n">
-        <v>3527</v>
+        <v>3530</v>
       </c>
       <c r="L230" t="n">
-        <v>3838</v>
+        <v>3843</v>
       </c>
       <c r="M230" t="n">
-        <v>4029</v>
+        <v>4034</v>
       </c>
       <c r="N230" t="n">
-        <v>4088</v>
+        <v>4093</v>
       </c>
       <c r="O230" t="n">
-        <v>4146</v>
+        <v>4152</v>
       </c>
       <c r="P230" t="n">
-        <v>4149</v>
+        <v>4155</v>
       </c>
       <c r="Q230" t="n">
-        <v>4206</v>
+        <v>4211</v>
       </c>
       <c r="R230" t="n">
-        <v>4097</v>
+        <v>4184</v>
       </c>
       <c r="S230" t="n">
-        <v>4100</v>
+        <v>4186</v>
       </c>
       <c r="T230" t="n">
-        <v>4132</v>
+        <v>4207</v>
       </c>
       <c r="U230" t="n">
-        <v>4185</v>
+        <v>4242</v>
       </c>
       <c r="V230" t="n">
-        <v>4251</v>
+        <v>4284</v>
       </c>
       <c r="W230" t="n">
-        <v>4361</v>
+        <v>4356</v>
       </c>
       <c r="X230" t="n">
-        <v>4464</v>
+        <v>4423</v>
       </c>
       <c r="Y230" t="n">
-        <v>4206</v>
+        <v>4176</v>
       </c>
       <c r="Z230" t="n">
-        <v>3912</v>
+        <v>3893</v>
       </c>
       <c r="AA230" t="n">
-        <v>3622</v>
+        <v>3615</v>
       </c>
     </row>
     <row r="231">
@@ -19581,76 +19581,76 @@
         <v>22</v>
       </c>
       <c r="D231" t="n">
-        <v>3211</v>
+        <v>3199</v>
       </c>
       <c r="E231" t="n">
         <v>3015</v>
       </c>
       <c r="F231" t="n">
-        <v>2930</v>
+        <v>2929</v>
       </c>
       <c r="G231" t="n">
         <v>2889</v>
       </c>
       <c r="H231" t="n">
-        <v>2908</v>
+        <v>2895</v>
       </c>
       <c r="I231" t="n">
-        <v>3079</v>
+        <v>3012</v>
       </c>
       <c r="J231" t="n">
-        <v>3405</v>
+        <v>3363</v>
       </c>
       <c r="K231" t="n">
-        <v>3679</v>
+        <v>3663</v>
       </c>
       <c r="L231" t="n">
-        <v>3915</v>
+        <v>3901</v>
       </c>
       <c r="M231" t="n">
-        <v>3981</v>
+        <v>3970</v>
       </c>
       <c r="N231" t="n">
-        <v>3964</v>
+        <v>3962</v>
       </c>
       <c r="O231" t="n">
-        <v>4004</v>
+        <v>4010</v>
       </c>
       <c r="P231" t="n">
-        <v>4025</v>
+        <v>4026</v>
       </c>
       <c r="Q231" t="n">
-        <v>4118</v>
+        <v>4123</v>
       </c>
       <c r="R231" t="n">
-        <v>3985</v>
+        <v>4083</v>
       </c>
       <c r="S231" t="n">
-        <v>3985</v>
+        <v>4100</v>
       </c>
       <c r="T231" t="n">
-        <v>3985</v>
+        <v>4092</v>
       </c>
       <c r="U231" t="n">
-        <v>4032</v>
+        <v>4106</v>
       </c>
       <c r="V231" t="n">
-        <v>4219</v>
+        <v>4181</v>
       </c>
       <c r="W231" t="n">
-        <v>4472</v>
+        <v>4354</v>
       </c>
       <c r="X231" t="n">
-        <v>4424</v>
+        <v>4397</v>
       </c>
       <c r="Y231" t="n">
-        <v>4192</v>
+        <v>4141</v>
       </c>
       <c r="Z231" t="n">
         <v>3857</v>
       </c>
       <c r="AA231" t="n">
-        <v>3591</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="232">
@@ -19664,76 +19664,159 @@
         <v>23</v>
       </c>
       <c r="D232" t="n">
-        <v>3170</v>
+        <v>3159</v>
       </c>
       <c r="E232" t="n">
         <v>2986</v>
       </c>
       <c r="F232" t="n">
-        <v>2907</v>
+        <v>2906</v>
       </c>
       <c r="G232" t="n">
-        <v>2868</v>
+        <v>2869</v>
       </c>
       <c r="H232" t="n">
-        <v>2887</v>
+        <v>2874</v>
       </c>
       <c r="I232" t="n">
-        <v>3050</v>
+        <v>2986</v>
       </c>
       <c r="J232" t="n">
-        <v>3361</v>
+        <v>3321</v>
       </c>
       <c r="K232" t="n">
-        <v>3623</v>
+        <v>3608</v>
       </c>
       <c r="L232" t="n">
-        <v>3848</v>
+        <v>3835</v>
       </c>
       <c r="M232" t="n">
-        <v>3911</v>
+        <v>3900</v>
       </c>
       <c r="N232" t="n">
-        <v>3894</v>
+        <v>3893</v>
       </c>
       <c r="O232" t="n">
-        <v>3933</v>
+        <v>3938</v>
       </c>
       <c r="P232" t="n">
-        <v>3953</v>
+        <v>3954</v>
       </c>
       <c r="Q232" t="n">
-        <v>4041</v>
+        <v>4047</v>
       </c>
       <c r="R232" t="n">
-        <v>3889</v>
+        <v>3995</v>
       </c>
       <c r="S232" t="n">
-        <v>3889</v>
+        <v>4015</v>
       </c>
       <c r="T232" t="n">
-        <v>3889</v>
+        <v>4006</v>
       </c>
       <c r="U232" t="n">
-        <v>3946</v>
+        <v>4023</v>
       </c>
       <c r="V232" t="n">
-        <v>4172</v>
+        <v>4114</v>
       </c>
       <c r="W232" t="n">
-        <v>4478</v>
+        <v>4323</v>
       </c>
       <c r="X232" t="n">
-        <v>4429</v>
+        <v>4375</v>
       </c>
       <c r="Y232" t="n">
-        <v>4188</v>
+        <v>4117</v>
       </c>
       <c r="Z232" t="n">
-        <v>3841</v>
+        <v>3832</v>
       </c>
       <c r="AA232" t="n">
-        <v>3564</v>
+        <v>3557</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B233" t="n">
+        <v>9</v>
+      </c>
+      <c r="C233" t="n">
+        <v>24</v>
+      </c>
+      <c r="D233" t="n">
+        <v>3142</v>
+      </c>
+      <c r="E233" t="n">
+        <v>2975</v>
+      </c>
+      <c r="F233" t="n">
+        <v>2897</v>
+      </c>
+      <c r="G233" t="n">
+        <v>2861</v>
+      </c>
+      <c r="H233" t="n">
+        <v>2866</v>
+      </c>
+      <c r="I233" t="n">
+        <v>2976</v>
+      </c>
+      <c r="J233" t="n">
+        <v>3304</v>
+      </c>
+      <c r="K233" t="n">
+        <v>3585</v>
+      </c>
+      <c r="L233" t="n">
+        <v>3808</v>
+      </c>
+      <c r="M233" t="n">
+        <v>3872</v>
+      </c>
+      <c r="N233" t="n">
+        <v>3865</v>
+      </c>
+      <c r="O233" t="n">
+        <v>3909</v>
+      </c>
+      <c r="P233" t="n">
+        <v>3925</v>
+      </c>
+      <c r="Q233" t="n">
+        <v>4016</v>
+      </c>
+      <c r="R233" t="n">
+        <v>3960</v>
+      </c>
+      <c r="S233" t="n">
+        <v>3981</v>
+      </c>
+      <c r="T233" t="n">
+        <v>3971</v>
+      </c>
+      <c r="U233" t="n">
+        <v>3990</v>
+      </c>
+      <c r="V233" t="n">
+        <v>4087</v>
+      </c>
+      <c r="W233" t="n">
+        <v>4310</v>
+      </c>
+      <c r="X233" t="n">
+        <v>4365</v>
+      </c>
+      <c r="Y233" t="n">
+        <v>4107</v>
+      </c>
+      <c r="Z233" t="n">
+        <v>3821</v>
+      </c>
+      <c r="AA233" t="n">
+        <v>3546</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA233"/>
+  <dimension ref="A1:AA234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19415,76 +19415,76 @@
         <v>20</v>
       </c>
       <c r="D229" t="n">
-        <v>3145</v>
+        <v>3168</v>
       </c>
       <c r="E229" t="n">
-        <v>2964</v>
+        <v>2986</v>
       </c>
       <c r="F229" t="n">
-        <v>2843</v>
+        <v>2865</v>
       </c>
       <c r="G229" t="n">
-        <v>2799</v>
+        <v>2821</v>
       </c>
       <c r="H229" t="n">
-        <v>2758</v>
+        <v>2780</v>
       </c>
       <c r="I229" t="n">
-        <v>2777</v>
+        <v>2798</v>
       </c>
       <c r="J229" t="n">
-        <v>2888</v>
+        <v>2903</v>
       </c>
       <c r="K229" t="n">
-        <v>3022</v>
+        <v>3030</v>
       </c>
       <c r="L229" t="n">
-        <v>3271</v>
+        <v>3266</v>
       </c>
       <c r="M229" t="n">
-        <v>3471</v>
+        <v>3455</v>
       </c>
       <c r="N229" t="n">
-        <v>3580</v>
+        <v>3559</v>
       </c>
       <c r="O229" t="n">
-        <v>3691</v>
+        <v>3665</v>
       </c>
       <c r="P229" t="n">
-        <v>3723</v>
+        <v>3694</v>
       </c>
       <c r="Q229" t="n">
-        <v>3778</v>
+        <v>3758</v>
       </c>
       <c r="R229" t="n">
-        <v>3815</v>
+        <v>3801</v>
       </c>
       <c r="S229" t="n">
-        <v>3842</v>
+        <v>3832</v>
       </c>
       <c r="T229" t="n">
-        <v>3848</v>
+        <v>3838</v>
       </c>
       <c r="U229" t="n">
-        <v>3920</v>
+        <v>3906</v>
       </c>
       <c r="V229" t="n">
-        <v>3991</v>
+        <v>3975</v>
       </c>
       <c r="W229" t="n">
-        <v>4117</v>
+        <v>4095</v>
       </c>
       <c r="X229" t="n">
-        <v>4205</v>
+        <v>4179</v>
       </c>
       <c r="Y229" t="n">
-        <v>3962</v>
+        <v>3936</v>
       </c>
       <c r="Z229" t="n">
-        <v>3682</v>
+        <v>3658</v>
       </c>
       <c r="AA229" t="n">
-        <v>3451</v>
+        <v>3427</v>
       </c>
     </row>
     <row r="230">
@@ -19498,76 +19498,76 @@
         <v>21</v>
       </c>
       <c r="D230" t="n">
-        <v>3190</v>
+        <v>3211</v>
       </c>
       <c r="E230" t="n">
-        <v>2988</v>
+        <v>3000</v>
       </c>
       <c r="F230" t="n">
-        <v>2885</v>
+        <v>2895</v>
       </c>
       <c r="G230" t="n">
-        <v>2838</v>
+        <v>2856</v>
       </c>
       <c r="H230" t="n">
-        <v>2835</v>
+        <v>2868</v>
       </c>
       <c r="I230" t="n">
-        <v>2923</v>
+        <v>3010</v>
       </c>
       <c r="J230" t="n">
-        <v>3238</v>
+        <v>3440</v>
       </c>
       <c r="K230" t="n">
-        <v>3530</v>
+        <v>3772</v>
       </c>
       <c r="L230" t="n">
-        <v>3843</v>
+        <v>4036</v>
       </c>
       <c r="M230" t="n">
-        <v>4034</v>
+        <v>4145</v>
       </c>
       <c r="N230" t="n">
-        <v>4093</v>
+        <v>4127</v>
       </c>
       <c r="O230" t="n">
-        <v>4152</v>
+        <v>4161</v>
       </c>
       <c r="P230" t="n">
-        <v>4155</v>
+        <v>4131</v>
       </c>
       <c r="Q230" t="n">
-        <v>4211</v>
+        <v>4180</v>
       </c>
       <c r="R230" t="n">
-        <v>4184</v>
+        <v>4171</v>
       </c>
       <c r="S230" t="n">
-        <v>4186</v>
+        <v>4174</v>
       </c>
       <c r="T230" t="n">
-        <v>4207</v>
+        <v>4185</v>
       </c>
       <c r="U230" t="n">
-        <v>4242</v>
+        <v>4196</v>
       </c>
       <c r="V230" t="n">
-        <v>4284</v>
+        <v>4247</v>
       </c>
       <c r="W230" t="n">
-        <v>4356</v>
+        <v>4336</v>
       </c>
       <c r="X230" t="n">
-        <v>4423</v>
+        <v>4396</v>
       </c>
       <c r="Y230" t="n">
-        <v>4176</v>
+        <v>4145</v>
       </c>
       <c r="Z230" t="n">
-        <v>3893</v>
+        <v>3866</v>
       </c>
       <c r="AA230" t="n">
-        <v>3615</v>
+        <v>3590</v>
       </c>
     </row>
     <row r="231">
@@ -19581,76 +19581,76 @@
         <v>22</v>
       </c>
       <c r="D231" t="n">
-        <v>3199</v>
+        <v>3226</v>
       </c>
       <c r="E231" t="n">
-        <v>3015</v>
+        <v>3039</v>
       </c>
       <c r="F231" t="n">
-        <v>2929</v>
+        <v>2952</v>
       </c>
       <c r="G231" t="n">
-        <v>2889</v>
+        <v>2913</v>
       </c>
       <c r="H231" t="n">
-        <v>2895</v>
+        <v>2918</v>
       </c>
       <c r="I231" t="n">
-        <v>3012</v>
+        <v>3034</v>
       </c>
       <c r="J231" t="n">
-        <v>3363</v>
+        <v>3390</v>
       </c>
       <c r="K231" t="n">
-        <v>3663</v>
+        <v>3684</v>
       </c>
       <c r="L231" t="n">
-        <v>3901</v>
+        <v>3913</v>
       </c>
       <c r="M231" t="n">
-        <v>3970</v>
+        <v>3976</v>
       </c>
       <c r="N231" t="n">
-        <v>3962</v>
+        <v>3963</v>
       </c>
       <c r="O231" t="n">
-        <v>4010</v>
+        <v>4003</v>
       </c>
       <c r="P231" t="n">
-        <v>4026</v>
+        <v>4015</v>
       </c>
       <c r="Q231" t="n">
-        <v>4123</v>
+        <v>4102</v>
       </c>
       <c r="R231" t="n">
-        <v>4083</v>
+        <v>4081</v>
       </c>
       <c r="S231" t="n">
-        <v>4100</v>
+        <v>4086</v>
       </c>
       <c r="T231" t="n">
-        <v>4092</v>
+        <v>4081</v>
       </c>
       <c r="U231" t="n">
-        <v>4106</v>
+        <v>4098</v>
       </c>
       <c r="V231" t="n">
-        <v>4181</v>
+        <v>4169</v>
       </c>
       <c r="W231" t="n">
-        <v>4354</v>
+        <v>4333</v>
       </c>
       <c r="X231" t="n">
-        <v>4397</v>
+        <v>4373</v>
       </c>
       <c r="Y231" t="n">
-        <v>4141</v>
+        <v>4118</v>
       </c>
       <c r="Z231" t="n">
-        <v>3857</v>
+        <v>3836</v>
       </c>
       <c r="AA231" t="n">
-        <v>3584</v>
+        <v>3563</v>
       </c>
     </row>
     <row r="232">
@@ -19664,76 +19664,76 @@
         <v>23</v>
       </c>
       <c r="D232" t="n">
-        <v>3159</v>
+        <v>3179</v>
       </c>
       <c r="E232" t="n">
-        <v>2986</v>
+        <v>3007</v>
       </c>
       <c r="F232" t="n">
-        <v>2906</v>
+        <v>2926</v>
       </c>
       <c r="G232" t="n">
-        <v>2869</v>
+        <v>2890</v>
       </c>
       <c r="H232" t="n">
-        <v>2874</v>
+        <v>2894</v>
       </c>
       <c r="I232" t="n">
-        <v>2986</v>
+        <v>3004</v>
       </c>
       <c r="J232" t="n">
-        <v>3321</v>
+        <v>3342</v>
       </c>
       <c r="K232" t="n">
-        <v>3608</v>
+        <v>3619</v>
       </c>
       <c r="L232" t="n">
-        <v>3835</v>
+        <v>3836</v>
       </c>
       <c r="M232" t="n">
-        <v>3900</v>
+        <v>3896</v>
       </c>
       <c r="N232" t="n">
-        <v>3893</v>
+        <v>3883</v>
       </c>
       <c r="O232" t="n">
-        <v>3938</v>
+        <v>3921</v>
       </c>
       <c r="P232" t="n">
-        <v>3954</v>
+        <v>3933</v>
       </c>
       <c r="Q232" t="n">
-        <v>4047</v>
+        <v>4014</v>
       </c>
       <c r="R232" t="n">
-        <v>3995</v>
+        <v>3981</v>
       </c>
       <c r="S232" t="n">
-        <v>4015</v>
+        <v>3988</v>
       </c>
       <c r="T232" t="n">
-        <v>4006</v>
+        <v>3981</v>
       </c>
       <c r="U232" t="n">
-        <v>4023</v>
+        <v>4002</v>
       </c>
       <c r="V232" t="n">
-        <v>4114</v>
+        <v>4091</v>
       </c>
       <c r="W232" t="n">
-        <v>4323</v>
+        <v>4297</v>
       </c>
       <c r="X232" t="n">
-        <v>4375</v>
+        <v>4347</v>
       </c>
       <c r="Y232" t="n">
-        <v>4117</v>
+        <v>4091</v>
       </c>
       <c r="Z232" t="n">
-        <v>3832</v>
+        <v>3807</v>
       </c>
       <c r="AA232" t="n">
-        <v>3557</v>
+        <v>3532</v>
       </c>
     </row>
     <row r="233">
@@ -19747,76 +19747,159 @@
         <v>24</v>
       </c>
       <c r="D233" t="n">
-        <v>3142</v>
+        <v>3162</v>
       </c>
       <c r="E233" t="n">
-        <v>2975</v>
+        <v>2994</v>
       </c>
       <c r="F233" t="n">
-        <v>2897</v>
+        <v>2916</v>
       </c>
       <c r="G233" t="n">
-        <v>2861</v>
+        <v>2881</v>
       </c>
       <c r="H233" t="n">
-        <v>2866</v>
+        <v>2885</v>
       </c>
       <c r="I233" t="n">
-        <v>2976</v>
+        <v>2993</v>
       </c>
       <c r="J233" t="n">
-        <v>3304</v>
+        <v>3323</v>
       </c>
       <c r="K233" t="n">
-        <v>3585</v>
+        <v>3594</v>
       </c>
       <c r="L233" t="n">
-        <v>3808</v>
+        <v>3806</v>
       </c>
       <c r="M233" t="n">
-        <v>3872</v>
+        <v>3864</v>
       </c>
       <c r="N233" t="n">
+        <v>3852</v>
+      </c>
+      <c r="O233" t="n">
+        <v>3889</v>
+      </c>
+      <c r="P233" t="n">
+        <v>3900</v>
+      </c>
+      <c r="Q233" t="n">
+        <v>3981</v>
+      </c>
+      <c r="R233" t="n">
+        <v>3942</v>
+      </c>
+      <c r="S233" t="n">
+        <v>3949</v>
+      </c>
+      <c r="T233" t="n">
+        <v>3943</v>
+      </c>
+      <c r="U233" t="n">
+        <v>3965</v>
+      </c>
+      <c r="V233" t="n">
+        <v>4061</v>
+      </c>
+      <c r="W233" t="n">
+        <v>4283</v>
+      </c>
+      <c r="X233" t="n">
+        <v>4337</v>
+      </c>
+      <c r="Y233" t="n">
+        <v>4080</v>
+      </c>
+      <c r="Z233" t="n">
+        <v>3796</v>
+      </c>
+      <c r="AA233" t="n">
+        <v>3520</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B234" t="n">
+        <v>9</v>
+      </c>
+      <c r="C234" t="n">
+        <v>25</v>
+      </c>
+      <c r="D234" t="n">
+        <v>3169</v>
+      </c>
+      <c r="E234" t="n">
+        <v>2999</v>
+      </c>
+      <c r="F234" t="n">
+        <v>2920</v>
+      </c>
+      <c r="G234" t="n">
+        <v>2885</v>
+      </c>
+      <c r="H234" t="n">
+        <v>2889</v>
+      </c>
+      <c r="I234" t="n">
+        <v>2998</v>
+      </c>
+      <c r="J234" t="n">
+        <v>3330</v>
+      </c>
+      <c r="K234" t="n">
+        <v>3604</v>
+      </c>
+      <c r="L234" t="n">
+        <v>3818</v>
+      </c>
+      <c r="M234" t="n">
+        <v>3877</v>
+      </c>
+      <c r="N234" t="n">
         <v>3865</v>
       </c>
-      <c r="O233" t="n">
-        <v>3909</v>
-      </c>
-      <c r="P233" t="n">
-        <v>3925</v>
-      </c>
-      <c r="Q233" t="n">
-        <v>4016</v>
-      </c>
-      <c r="R233" t="n">
-        <v>3960</v>
-      </c>
-      <c r="S233" t="n">
-        <v>3981</v>
-      </c>
-      <c r="T233" t="n">
-        <v>3971</v>
-      </c>
-      <c r="U233" t="n">
-        <v>3990</v>
-      </c>
-      <c r="V233" t="n">
-        <v>4087</v>
-      </c>
-      <c r="W233" t="n">
-        <v>4310</v>
-      </c>
-      <c r="X233" t="n">
-        <v>4365</v>
-      </c>
-      <c r="Y233" t="n">
-        <v>4107</v>
-      </c>
-      <c r="Z233" t="n">
-        <v>3821</v>
-      </c>
-      <c r="AA233" t="n">
-        <v>3546</v>
+      <c r="O234" t="n">
+        <v>3902</v>
+      </c>
+      <c r="P234" t="n">
+        <v>3913</v>
+      </c>
+      <c r="Q234" t="n">
+        <v>3994</v>
+      </c>
+      <c r="R234" t="n">
+        <v>3958</v>
+      </c>
+      <c r="S234" t="n">
+        <v>3963</v>
+      </c>
+      <c r="T234" t="n">
+        <v>3958</v>
+      </c>
+      <c r="U234" t="n">
+        <v>3976</v>
+      </c>
+      <c r="V234" t="n">
+        <v>4049</v>
+      </c>
+      <c r="W234" t="n">
+        <v>4220</v>
+      </c>
+      <c r="X234" t="n">
+        <v>4261</v>
+      </c>
+      <c r="Y234" t="n">
+        <v>4014</v>
+      </c>
+      <c r="Z234" t="n">
+        <v>3741</v>
+      </c>
+      <c r="AA234" t="n">
+        <v>3477</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA234"/>
+  <dimension ref="A1:AA235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19498,76 +19498,76 @@
         <v>21</v>
       </c>
       <c r="D230" t="n">
-        <v>3211</v>
+        <v>3170</v>
       </c>
       <c r="E230" t="n">
-        <v>3000</v>
+        <v>2963</v>
       </c>
       <c r="F230" t="n">
-        <v>2895</v>
+        <v>2861</v>
       </c>
       <c r="G230" t="n">
-        <v>2856</v>
+        <v>2823</v>
       </c>
       <c r="H230" t="n">
-        <v>2868</v>
+        <v>2833</v>
       </c>
       <c r="I230" t="n">
-        <v>3010</v>
+        <v>2960</v>
       </c>
       <c r="J230" t="n">
-        <v>3440</v>
+        <v>3347</v>
       </c>
       <c r="K230" t="n">
-        <v>3772</v>
+        <v>3644</v>
       </c>
       <c r="L230" t="n">
-        <v>4036</v>
+        <v>3881</v>
       </c>
       <c r="M230" t="n">
-        <v>4145</v>
+        <v>3978</v>
       </c>
       <c r="N230" t="n">
-        <v>4127</v>
+        <v>3962</v>
       </c>
       <c r="O230" t="n">
-        <v>4161</v>
+        <v>3993</v>
       </c>
       <c r="P230" t="n">
-        <v>4131</v>
+        <v>3966</v>
       </c>
       <c r="Q230" t="n">
-        <v>4180</v>
+        <v>4010</v>
       </c>
       <c r="R230" t="n">
+        <v>3900</v>
+      </c>
+      <c r="S230" t="n">
+        <v>3903</v>
+      </c>
+      <c r="T230" t="n">
+        <v>3917</v>
+      </c>
+      <c r="U230" t="n">
+        <v>3929</v>
+      </c>
+      <c r="V230" t="n">
+        <v>3991</v>
+      </c>
+      <c r="W230" t="n">
+        <v>4099</v>
+      </c>
+      <c r="X230" t="n">
         <v>4171</v>
       </c>
-      <c r="S230" t="n">
-        <v>4174</v>
-      </c>
-      <c r="T230" t="n">
-        <v>4185</v>
-      </c>
-      <c r="U230" t="n">
-        <v>4196</v>
-      </c>
-      <c r="V230" t="n">
-        <v>4247</v>
-      </c>
-      <c r="W230" t="n">
-        <v>4336</v>
-      </c>
-      <c r="X230" t="n">
-        <v>4396</v>
-      </c>
       <c r="Y230" t="n">
-        <v>4145</v>
+        <v>3961</v>
       </c>
       <c r="Z230" t="n">
-        <v>3866</v>
+        <v>3728</v>
       </c>
       <c r="AA230" t="n">
-        <v>3590</v>
+        <v>3497</v>
       </c>
     </row>
     <row r="231">
@@ -19581,76 +19581,76 @@
         <v>22</v>
       </c>
       <c r="D231" t="n">
-        <v>3226</v>
+        <v>3175</v>
       </c>
       <c r="E231" t="n">
-        <v>3039</v>
+        <v>2998</v>
       </c>
       <c r="F231" t="n">
-        <v>2952</v>
+        <v>2914</v>
       </c>
       <c r="G231" t="n">
-        <v>2913</v>
+        <v>2875</v>
       </c>
       <c r="H231" t="n">
-        <v>2918</v>
+        <v>2876</v>
       </c>
       <c r="I231" t="n">
-        <v>3034</v>
+        <v>2982</v>
       </c>
       <c r="J231" t="n">
-        <v>3390</v>
+        <v>3324</v>
       </c>
       <c r="K231" t="n">
-        <v>3684</v>
+        <v>3595</v>
       </c>
       <c r="L231" t="n">
+        <v>3788</v>
+      </c>
+      <c r="M231" t="n">
+        <v>3842</v>
+      </c>
+      <c r="N231" t="n">
+        <v>3823</v>
+      </c>
+      <c r="O231" t="n">
+        <v>3854</v>
+      </c>
+      <c r="P231" t="n">
+        <v>3851</v>
+      </c>
+      <c r="Q231" t="n">
         <v>3913</v>
       </c>
-      <c r="M231" t="n">
-        <v>3976</v>
-      </c>
-      <c r="N231" t="n">
-        <v>3963</v>
-      </c>
-      <c r="O231" t="n">
-        <v>4003</v>
-      </c>
-      <c r="P231" t="n">
-        <v>4015</v>
-      </c>
-      <c r="Q231" t="n">
-        <v>4102</v>
-      </c>
       <c r="R231" t="n">
-        <v>4081</v>
+        <v>3788</v>
       </c>
       <c r="S231" t="n">
-        <v>4086</v>
+        <v>3800</v>
       </c>
       <c r="T231" t="n">
-        <v>4081</v>
+        <v>3797</v>
       </c>
       <c r="U231" t="n">
-        <v>4098</v>
+        <v>3821</v>
       </c>
       <c r="V231" t="n">
-        <v>4169</v>
+        <v>3928</v>
       </c>
       <c r="W231" t="n">
-        <v>4333</v>
+        <v>4136</v>
       </c>
       <c r="X231" t="n">
-        <v>4373</v>
+        <v>4143</v>
       </c>
       <c r="Y231" t="n">
-        <v>4118</v>
+        <v>3919</v>
       </c>
       <c r="Z231" t="n">
-        <v>3836</v>
+        <v>3693</v>
       </c>
       <c r="AA231" t="n">
-        <v>3563</v>
+        <v>3463</v>
       </c>
     </row>
     <row r="232">
@@ -19664,76 +19664,76 @@
         <v>23</v>
       </c>
       <c r="D232" t="n">
-        <v>3179</v>
+        <v>3130</v>
       </c>
       <c r="E232" t="n">
-        <v>3007</v>
+        <v>2966</v>
       </c>
       <c r="F232" t="n">
-        <v>2926</v>
+        <v>2889</v>
       </c>
       <c r="G232" t="n">
-        <v>2890</v>
+        <v>2853</v>
       </c>
       <c r="H232" t="n">
-        <v>2894</v>
+        <v>2854</v>
       </c>
       <c r="I232" t="n">
-        <v>3004</v>
+        <v>2954</v>
       </c>
       <c r="J232" t="n">
-        <v>3342</v>
+        <v>3275</v>
       </c>
       <c r="K232" t="n">
-        <v>3619</v>
+        <v>3530</v>
       </c>
       <c r="L232" t="n">
-        <v>3836</v>
+        <v>3711</v>
       </c>
       <c r="M232" t="n">
-        <v>3896</v>
+        <v>3762</v>
       </c>
       <c r="N232" t="n">
-        <v>3883</v>
+        <v>3745</v>
       </c>
       <c r="O232" t="n">
-        <v>3921</v>
+        <v>3774</v>
       </c>
       <c r="P232" t="n">
-        <v>3933</v>
+        <v>3771</v>
       </c>
       <c r="Q232" t="n">
-        <v>4014</v>
+        <v>3829</v>
       </c>
       <c r="R232" t="n">
-        <v>3981</v>
+        <v>3692</v>
       </c>
       <c r="S232" t="n">
-        <v>3988</v>
+        <v>3707</v>
       </c>
       <c r="T232" t="n">
-        <v>3981</v>
+        <v>3703</v>
       </c>
       <c r="U232" t="n">
-        <v>4002</v>
+        <v>3731</v>
       </c>
       <c r="V232" t="n">
-        <v>4091</v>
+        <v>3859</v>
       </c>
       <c r="W232" t="n">
-        <v>4297</v>
+        <v>4110</v>
       </c>
       <c r="X232" t="n">
-        <v>4347</v>
+        <v>4118</v>
       </c>
       <c r="Y232" t="n">
-        <v>4091</v>
+        <v>3893</v>
       </c>
       <c r="Z232" t="n">
-        <v>3807</v>
+        <v>3665</v>
       </c>
       <c r="AA232" t="n">
-        <v>3532</v>
+        <v>3433</v>
       </c>
     </row>
     <row r="233">
@@ -19747,76 +19747,76 @@
         <v>24</v>
       </c>
       <c r="D233" t="n">
-        <v>3162</v>
+        <v>3110</v>
       </c>
       <c r="E233" t="n">
-        <v>2994</v>
+        <v>2952</v>
       </c>
       <c r="F233" t="n">
-        <v>2916</v>
+        <v>2878</v>
       </c>
       <c r="G233" t="n">
-        <v>2881</v>
+        <v>2843</v>
       </c>
       <c r="H233" t="n">
-        <v>2885</v>
+        <v>2844</v>
       </c>
       <c r="I233" t="n">
-        <v>2993</v>
+        <v>2941</v>
       </c>
       <c r="J233" t="n">
-        <v>3323</v>
+        <v>3253</v>
       </c>
       <c r="K233" t="n">
-        <v>3594</v>
+        <v>3501</v>
       </c>
       <c r="L233" t="n">
-        <v>3806</v>
+        <v>3677</v>
       </c>
       <c r="M233" t="n">
-        <v>3864</v>
+        <v>3727</v>
       </c>
       <c r="N233" t="n">
-        <v>3852</v>
+        <v>3710</v>
       </c>
       <c r="O233" t="n">
-        <v>3889</v>
+        <v>3738</v>
       </c>
       <c r="P233" t="n">
-        <v>3900</v>
+        <v>3735</v>
       </c>
       <c r="Q233" t="n">
-        <v>3981</v>
+        <v>3792</v>
       </c>
       <c r="R233" t="n">
-        <v>3942</v>
+        <v>3649</v>
       </c>
       <c r="S233" t="n">
-        <v>3949</v>
+        <v>3665</v>
       </c>
       <c r="T233" t="n">
-        <v>3943</v>
+        <v>3661</v>
       </c>
       <c r="U233" t="n">
-        <v>3965</v>
+        <v>3691</v>
       </c>
       <c r="V233" t="n">
-        <v>4061</v>
+        <v>3829</v>
       </c>
       <c r="W233" t="n">
-        <v>4283</v>
+        <v>4099</v>
       </c>
       <c r="X233" t="n">
-        <v>4337</v>
+        <v>4107</v>
       </c>
       <c r="Y233" t="n">
-        <v>4080</v>
+        <v>3881</v>
       </c>
       <c r="Z233" t="n">
-        <v>3796</v>
+        <v>3652</v>
       </c>
       <c r="AA233" t="n">
-        <v>3520</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="234">
@@ -19830,76 +19830,159 @@
         <v>25</v>
       </c>
       <c r="D234" t="n">
-        <v>3169</v>
+        <v>3116</v>
       </c>
       <c r="E234" t="n">
-        <v>2999</v>
+        <v>2956</v>
       </c>
       <c r="F234" t="n">
-        <v>2920</v>
+        <v>2881</v>
       </c>
       <c r="G234" t="n">
-        <v>2885</v>
+        <v>2846</v>
       </c>
       <c r="H234" t="n">
-        <v>2889</v>
+        <v>2847</v>
       </c>
       <c r="I234" t="n">
-        <v>2998</v>
+        <v>2944</v>
       </c>
       <c r="J234" t="n">
-        <v>3330</v>
+        <v>3259</v>
       </c>
       <c r="K234" t="n">
-        <v>3604</v>
+        <v>3510</v>
       </c>
       <c r="L234" t="n">
-        <v>3818</v>
+        <v>3687</v>
       </c>
       <c r="M234" t="n">
-        <v>3877</v>
+        <v>3737</v>
       </c>
       <c r="N234" t="n">
-        <v>3865</v>
+        <v>3720</v>
       </c>
       <c r="O234" t="n">
-        <v>3902</v>
+        <v>3748</v>
       </c>
       <c r="P234" t="n">
-        <v>3913</v>
+        <v>3745</v>
       </c>
       <c r="Q234" t="n">
-        <v>3994</v>
+        <v>3802</v>
       </c>
       <c r="R234" t="n">
-        <v>3958</v>
+        <v>3661</v>
       </c>
       <c r="S234" t="n">
-        <v>3963</v>
+        <v>3674</v>
       </c>
       <c r="T234" t="n">
-        <v>3958</v>
+        <v>3671</v>
       </c>
       <c r="U234" t="n">
-        <v>3976</v>
+        <v>3695</v>
       </c>
       <c r="V234" t="n">
-        <v>4049</v>
+        <v>3806</v>
       </c>
       <c r="W234" t="n">
-        <v>4220</v>
+        <v>4024</v>
       </c>
       <c r="X234" t="n">
-        <v>4261</v>
+        <v>4030</v>
       </c>
       <c r="Y234" t="n">
-        <v>4014</v>
+        <v>3815</v>
       </c>
       <c r="Z234" t="n">
-        <v>3741</v>
+        <v>3597</v>
       </c>
       <c r="AA234" t="n">
-        <v>3477</v>
+        <v>3376</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B235" t="n">
+        <v>9</v>
+      </c>
+      <c r="C235" t="n">
+        <v>26</v>
+      </c>
+      <c r="D235" t="n">
+        <v>3112</v>
+      </c>
+      <c r="E235" t="n">
+        <v>2949</v>
+      </c>
+      <c r="F235" t="n">
+        <v>2856</v>
+      </c>
+      <c r="G235" t="n">
+        <v>2807</v>
+      </c>
+      <c r="H235" t="n">
+        <v>2779</v>
+      </c>
+      <c r="I235" t="n">
+        <v>2799</v>
+      </c>
+      <c r="J235" t="n">
+        <v>2894</v>
+      </c>
+      <c r="K235" t="n">
+        <v>3005</v>
+      </c>
+      <c r="L235" t="n">
+        <v>3160</v>
+      </c>
+      <c r="M235" t="n">
+        <v>3290</v>
+      </c>
+      <c r="N235" t="n">
+        <v>3359</v>
+      </c>
+      <c r="O235" t="n">
+        <v>3411</v>
+      </c>
+      <c r="P235" t="n">
+        <v>3469</v>
+      </c>
+      <c r="Q235" t="n">
+        <v>3495</v>
+      </c>
+      <c r="R235" t="n">
+        <v>3483</v>
+      </c>
+      <c r="S235" t="n">
+        <v>3468</v>
+      </c>
+      <c r="T235" t="n">
+        <v>3449</v>
+      </c>
+      <c r="U235" t="n">
+        <v>3547</v>
+      </c>
+      <c r="V235" t="n">
+        <v>3698</v>
+      </c>
+      <c r="W235" t="n">
+        <v>3813</v>
+      </c>
+      <c r="X235" t="n">
+        <v>3772</v>
+      </c>
+      <c r="Y235" t="n">
+        <v>3591</v>
+      </c>
+      <c r="Z235" t="n">
+        <v>3429</v>
+      </c>
+      <c r="AA235" t="n">
+        <v>3276</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA235"/>
+  <dimension ref="A1:AA236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19581,76 +19581,76 @@
         <v>22</v>
       </c>
       <c r="D231" t="n">
-        <v>3175</v>
+        <v>3069</v>
       </c>
       <c r="E231" t="n">
-        <v>2998</v>
+        <v>2925</v>
       </c>
       <c r="F231" t="n">
-        <v>2914</v>
+        <v>2856</v>
       </c>
       <c r="G231" t="n">
-        <v>2875</v>
+        <v>2724</v>
       </c>
       <c r="H231" t="n">
-        <v>2876</v>
+        <v>2728</v>
       </c>
       <c r="I231" t="n">
-        <v>2982</v>
+        <v>2717</v>
       </c>
       <c r="J231" t="n">
-        <v>3324</v>
+        <v>2925</v>
       </c>
       <c r="K231" t="n">
-        <v>3595</v>
+        <v>3058</v>
       </c>
       <c r="L231" t="n">
-        <v>3788</v>
+        <v>3313</v>
       </c>
       <c r="M231" t="n">
-        <v>3842</v>
+        <v>3555</v>
       </c>
       <c r="N231" t="n">
-        <v>3823</v>
+        <v>3636</v>
       </c>
       <c r="O231" t="n">
-        <v>3854</v>
+        <v>3656</v>
       </c>
       <c r="P231" t="n">
-        <v>3851</v>
+        <v>3749</v>
       </c>
       <c r="Q231" t="n">
-        <v>3913</v>
+        <v>3795</v>
       </c>
       <c r="R231" t="n">
-        <v>3788</v>
+        <v>3797</v>
       </c>
       <c r="S231" t="n">
-        <v>3800</v>
+        <v>3700</v>
       </c>
       <c r="T231" t="n">
-        <v>3797</v>
+        <v>3705</v>
       </c>
       <c r="U231" t="n">
-        <v>3821</v>
+        <v>3719</v>
       </c>
       <c r="V231" t="n">
-        <v>3928</v>
+        <v>3865</v>
       </c>
       <c r="W231" t="n">
-        <v>4136</v>
+        <v>4155</v>
       </c>
       <c r="X231" t="n">
-        <v>4143</v>
+        <v>4153</v>
       </c>
       <c r="Y231" t="n">
-        <v>3919</v>
+        <v>3899</v>
       </c>
       <c r="Z231" t="n">
-        <v>3693</v>
+        <v>3651</v>
       </c>
       <c r="AA231" t="n">
-        <v>3463</v>
+        <v>3393</v>
       </c>
     </row>
     <row r="232">
@@ -19664,76 +19664,76 @@
         <v>23</v>
       </c>
       <c r="D232" t="n">
-        <v>3130</v>
+        <v>3030</v>
       </c>
       <c r="E232" t="n">
-        <v>2966</v>
+        <v>2898</v>
       </c>
       <c r="F232" t="n">
-        <v>2889</v>
+        <v>2835</v>
       </c>
       <c r="G232" t="n">
-        <v>2853</v>
+        <v>2805</v>
       </c>
       <c r="H232" t="n">
-        <v>2854</v>
+        <v>2808</v>
       </c>
       <c r="I232" t="n">
-        <v>2954</v>
+        <v>2892</v>
       </c>
       <c r="J232" t="n">
-        <v>3275</v>
+        <v>3182</v>
       </c>
       <c r="K232" t="n">
-        <v>3530</v>
+        <v>3400</v>
       </c>
       <c r="L232" t="n">
-        <v>3711</v>
+        <v>3545</v>
       </c>
       <c r="M232" t="n">
-        <v>3762</v>
+        <v>3585</v>
       </c>
       <c r="N232" t="n">
-        <v>3745</v>
+        <v>3567</v>
       </c>
       <c r="O232" t="n">
-        <v>3774</v>
+        <v>3586</v>
       </c>
       <c r="P232" t="n">
-        <v>3771</v>
+        <v>3579</v>
       </c>
       <c r="Q232" t="n">
-        <v>3829</v>
+        <v>3622</v>
       </c>
       <c r="R232" t="n">
-        <v>3692</v>
+        <v>3621</v>
       </c>
       <c r="S232" t="n">
-        <v>3707</v>
+        <v>3617</v>
       </c>
       <c r="T232" t="n">
-        <v>3703</v>
+        <v>3613</v>
       </c>
       <c r="U232" t="n">
-        <v>3731</v>
+        <v>3630</v>
       </c>
       <c r="V232" t="n">
-        <v>3859</v>
+        <v>3808</v>
       </c>
       <c r="W232" t="n">
-        <v>4110</v>
+        <v>4161</v>
       </c>
       <c r="X232" t="n">
-        <v>4118</v>
+        <v>4159</v>
       </c>
       <c r="Y232" t="n">
-        <v>3893</v>
+        <v>3894</v>
       </c>
       <c r="Z232" t="n">
-        <v>3665</v>
+        <v>3637</v>
       </c>
       <c r="AA232" t="n">
-        <v>3433</v>
+        <v>3368</v>
       </c>
     </row>
     <row r="233">
@@ -19747,76 +19747,76 @@
         <v>24</v>
       </c>
       <c r="D233" t="n">
-        <v>3110</v>
+        <v>3019</v>
       </c>
       <c r="E233" t="n">
-        <v>2952</v>
+        <v>2890</v>
       </c>
       <c r="F233" t="n">
-        <v>2878</v>
+        <v>2828</v>
       </c>
       <c r="G233" t="n">
-        <v>2843</v>
+        <v>2799</v>
       </c>
       <c r="H233" t="n">
-        <v>2844</v>
+        <v>2803</v>
       </c>
       <c r="I233" t="n">
-        <v>2941</v>
+        <v>2885</v>
       </c>
       <c r="J233" t="n">
-        <v>3253</v>
+        <v>3168</v>
       </c>
       <c r="K233" t="n">
-        <v>3501</v>
+        <v>3382</v>
       </c>
       <c r="L233" t="n">
-        <v>3677</v>
+        <v>3525</v>
       </c>
       <c r="M233" t="n">
-        <v>3727</v>
+        <v>3564</v>
       </c>
       <c r="N233" t="n">
-        <v>3710</v>
+        <v>3546</v>
       </c>
       <c r="O233" t="n">
-        <v>3738</v>
+        <v>3565</v>
       </c>
       <c r="P233" t="n">
-        <v>3735</v>
+        <v>3558</v>
       </c>
       <c r="Q233" t="n">
-        <v>3792</v>
+        <v>3600</v>
       </c>
       <c r="R233" t="n">
-        <v>3649</v>
+        <v>3598</v>
       </c>
       <c r="S233" t="n">
-        <v>3665</v>
+        <v>3592</v>
       </c>
       <c r="T233" t="n">
-        <v>3661</v>
+        <v>3585</v>
       </c>
       <c r="U233" t="n">
-        <v>3691</v>
+        <v>3603</v>
       </c>
       <c r="V233" t="n">
-        <v>3829</v>
+        <v>3791</v>
       </c>
       <c r="W233" t="n">
-        <v>4099</v>
+        <v>4163</v>
       </c>
       <c r="X233" t="n">
-        <v>4107</v>
+        <v>4161</v>
       </c>
       <c r="Y233" t="n">
-        <v>3881</v>
+        <v>3893</v>
       </c>
       <c r="Z233" t="n">
-        <v>3652</v>
+        <v>3632</v>
       </c>
       <c r="AA233" t="n">
-        <v>3420</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="234">
@@ -19830,76 +19830,76 @@
         <v>25</v>
       </c>
       <c r="D234" t="n">
-        <v>3116</v>
+        <v>3021</v>
       </c>
       <c r="E234" t="n">
-        <v>2956</v>
+        <v>2892</v>
       </c>
       <c r="F234" t="n">
-        <v>2881</v>
+        <v>2829</v>
       </c>
       <c r="G234" t="n">
-        <v>2846</v>
+        <v>2801</v>
       </c>
       <c r="H234" t="n">
-        <v>2847</v>
+        <v>2804</v>
       </c>
       <c r="I234" t="n">
-        <v>2944</v>
+        <v>2886</v>
       </c>
       <c r="J234" t="n">
-        <v>3259</v>
+        <v>3171</v>
       </c>
       <c r="K234" t="n">
-        <v>3510</v>
+        <v>3386</v>
       </c>
       <c r="L234" t="n">
-        <v>3687</v>
+        <v>3528</v>
       </c>
       <c r="M234" t="n">
-        <v>3737</v>
+        <v>3568</v>
       </c>
       <c r="N234" t="n">
-        <v>3720</v>
+        <v>3550</v>
       </c>
       <c r="O234" t="n">
-        <v>3748</v>
+        <v>3569</v>
       </c>
       <c r="P234" t="n">
-        <v>3745</v>
+        <v>3562</v>
       </c>
       <c r="Q234" t="n">
-        <v>3802</v>
+        <v>3604</v>
       </c>
       <c r="R234" t="n">
-        <v>3661</v>
+        <v>3602</v>
       </c>
       <c r="S234" t="n">
-        <v>3674</v>
+        <v>3597</v>
       </c>
       <c r="T234" t="n">
-        <v>3671</v>
+        <v>3590</v>
       </c>
       <c r="U234" t="n">
-        <v>3695</v>
+        <v>3605</v>
       </c>
       <c r="V234" t="n">
-        <v>3806</v>
+        <v>3765</v>
       </c>
       <c r="W234" t="n">
-        <v>4024</v>
+        <v>4083</v>
       </c>
       <c r="X234" t="n">
-        <v>4030</v>
+        <v>4081</v>
       </c>
       <c r="Y234" t="n">
-        <v>3815</v>
+        <v>3824</v>
       </c>
       <c r="Z234" t="n">
-        <v>3597</v>
+        <v>3574</v>
       </c>
       <c r="AA234" t="n">
-        <v>3376</v>
+        <v>3313</v>
       </c>
     </row>
     <row r="235">
@@ -19913,76 +19913,159 @@
         <v>26</v>
       </c>
       <c r="D235" t="n">
-        <v>3112</v>
+        <v>3020</v>
       </c>
       <c r="E235" t="n">
-        <v>2949</v>
+        <v>2876</v>
       </c>
       <c r="F235" t="n">
-        <v>2856</v>
+        <v>2799</v>
       </c>
       <c r="G235" t="n">
-        <v>2807</v>
+        <v>2758</v>
       </c>
       <c r="H235" t="n">
-        <v>2779</v>
+        <v>2735</v>
       </c>
       <c r="I235" t="n">
-        <v>2799</v>
+        <v>2751</v>
       </c>
       <c r="J235" t="n">
-        <v>2894</v>
+        <v>2845</v>
       </c>
       <c r="K235" t="n">
-        <v>3005</v>
+        <v>2935</v>
       </c>
       <c r="L235" t="n">
-        <v>3160</v>
+        <v>3064</v>
       </c>
       <c r="M235" t="n">
-        <v>3290</v>
+        <v>3161</v>
       </c>
       <c r="N235" t="n">
-        <v>3359</v>
+        <v>3230</v>
       </c>
       <c r="O235" t="n">
-        <v>3411</v>
+        <v>3241</v>
       </c>
       <c r="P235" t="n">
-        <v>3469</v>
+        <v>3287</v>
       </c>
       <c r="Q235" t="n">
-        <v>3495</v>
+        <v>3304</v>
       </c>
       <c r="R235" t="n">
-        <v>3483</v>
+        <v>3315</v>
       </c>
       <c r="S235" t="n">
-        <v>3468</v>
+        <v>3344</v>
       </c>
       <c r="T235" t="n">
-        <v>3449</v>
+        <v>3387</v>
       </c>
       <c r="U235" t="n">
-        <v>3547</v>
+        <v>3509</v>
       </c>
       <c r="V235" t="n">
-        <v>3698</v>
+        <v>3603</v>
       </c>
       <c r="W235" t="n">
-        <v>3813</v>
+        <v>3866</v>
       </c>
       <c r="X235" t="n">
-        <v>3772</v>
+        <v>3832</v>
       </c>
       <c r="Y235" t="n">
-        <v>3591</v>
+        <v>3622</v>
       </c>
       <c r="Z235" t="n">
-        <v>3429</v>
+        <v>3431</v>
       </c>
       <c r="AA235" t="n">
-        <v>3276</v>
+        <v>3216</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B236" t="n">
+        <v>9</v>
+      </c>
+      <c r="C236" t="n">
+        <v>27</v>
+      </c>
+      <c r="D236" t="n">
+        <v>2971</v>
+      </c>
+      <c r="E236" t="n">
+        <v>2842</v>
+      </c>
+      <c r="F236" t="n">
+        <v>2758</v>
+      </c>
+      <c r="G236" t="n">
+        <v>2717</v>
+      </c>
+      <c r="H236" t="n">
+        <v>2689</v>
+      </c>
+      <c r="I236" t="n">
+        <v>2697</v>
+      </c>
+      <c r="J236" t="n">
+        <v>2781</v>
+      </c>
+      <c r="K236" t="n">
+        <v>2867</v>
+      </c>
+      <c r="L236" t="n">
+        <v>3014</v>
+      </c>
+      <c r="M236" t="n">
+        <v>3133</v>
+      </c>
+      <c r="N236" t="n">
+        <v>3203</v>
+      </c>
+      <c r="O236" t="n">
+        <v>3262</v>
+      </c>
+      <c r="P236" t="n">
+        <v>3305</v>
+      </c>
+      <c r="Q236" t="n">
+        <v>3351</v>
+      </c>
+      <c r="R236" t="n">
+        <v>3383</v>
+      </c>
+      <c r="S236" t="n">
+        <v>3425</v>
+      </c>
+      <c r="T236" t="n">
+        <v>3465</v>
+      </c>
+      <c r="U236" t="n">
+        <v>3489</v>
+      </c>
+      <c r="V236" t="n">
+        <v>3668</v>
+      </c>
+      <c r="W236" t="n">
+        <v>3984</v>
+      </c>
+      <c r="X236" t="n">
+        <v>4086</v>
+      </c>
+      <c r="Y236" t="n">
+        <v>3838</v>
+      </c>
+      <c r="Z236" t="n">
+        <v>3572</v>
+      </c>
+      <c r="AA236" t="n">
+        <v>3313</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA236"/>
+  <dimension ref="A1:AA237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19664,76 +19664,76 @@
         <v>23</v>
       </c>
       <c r="D232" t="n">
-        <v>3030</v>
+        <v>3048</v>
       </c>
       <c r="E232" t="n">
-        <v>2898</v>
+        <v>2885</v>
       </c>
       <c r="F232" t="n">
-        <v>2835</v>
+        <v>2807</v>
       </c>
       <c r="G232" t="n">
-        <v>2805</v>
+        <v>2773</v>
       </c>
       <c r="H232" t="n">
-        <v>2808</v>
+        <v>2778</v>
       </c>
       <c r="I232" t="n">
-        <v>2892</v>
+        <v>2875</v>
       </c>
       <c r="J232" t="n">
-        <v>3182</v>
+        <v>3202</v>
       </c>
       <c r="K232" t="n">
-        <v>3400</v>
+        <v>3449</v>
       </c>
       <c r="L232" t="n">
-        <v>3545</v>
+        <v>3625</v>
       </c>
       <c r="M232" t="n">
-        <v>3585</v>
+        <v>3666</v>
       </c>
       <c r="N232" t="n">
-        <v>3567</v>
+        <v>3646</v>
       </c>
       <c r="O232" t="n">
-        <v>3586</v>
+        <v>3672</v>
       </c>
       <c r="P232" t="n">
-        <v>3579</v>
+        <v>3670</v>
       </c>
       <c r="Q232" t="n">
-        <v>3622</v>
+        <v>3727</v>
       </c>
       <c r="R232" t="n">
-        <v>3621</v>
+        <v>3721</v>
       </c>
       <c r="S232" t="n">
-        <v>3617</v>
+        <v>3675</v>
       </c>
       <c r="T232" t="n">
-        <v>3613</v>
+        <v>3620</v>
       </c>
       <c r="U232" t="n">
-        <v>3630</v>
+        <v>3627</v>
       </c>
       <c r="V232" t="n">
-        <v>3808</v>
+        <v>3742</v>
       </c>
       <c r="W232" t="n">
-        <v>4161</v>
+        <v>4013</v>
       </c>
       <c r="X232" t="n">
-        <v>4159</v>
+        <v>4037</v>
       </c>
       <c r="Y232" t="n">
-        <v>3894</v>
+        <v>3828</v>
       </c>
       <c r="Z232" t="n">
-        <v>3637</v>
+        <v>3615</v>
       </c>
       <c r="AA232" t="n">
-        <v>3368</v>
+        <v>3407</v>
       </c>
     </row>
     <row r="233">
@@ -19747,76 +19747,76 @@
         <v>24</v>
       </c>
       <c r="D233" t="n">
-        <v>3019</v>
+        <v>3037</v>
       </c>
       <c r="E233" t="n">
-        <v>2890</v>
+        <v>2876</v>
       </c>
       <c r="F233" t="n">
-        <v>2828</v>
+        <v>2800</v>
       </c>
       <c r="G233" t="n">
-        <v>2799</v>
+        <v>2767</v>
       </c>
       <c r="H233" t="n">
-        <v>2803</v>
+        <v>2772</v>
       </c>
       <c r="I233" t="n">
-        <v>2885</v>
+        <v>2867</v>
       </c>
       <c r="J233" t="n">
-        <v>3168</v>
+        <v>3189</v>
       </c>
       <c r="K233" t="n">
-        <v>3382</v>
+        <v>3432</v>
       </c>
       <c r="L233" t="n">
-        <v>3525</v>
+        <v>3605</v>
       </c>
       <c r="M233" t="n">
-        <v>3564</v>
+        <v>3645</v>
       </c>
       <c r="N233" t="n">
-        <v>3546</v>
+        <v>3625</v>
       </c>
       <c r="O233" t="n">
-        <v>3565</v>
+        <v>3651</v>
       </c>
       <c r="P233" t="n">
-        <v>3558</v>
+        <v>3649</v>
       </c>
       <c r="Q233" t="n">
+        <v>3705</v>
+      </c>
+      <c r="R233" t="n">
+        <v>3698</v>
+      </c>
+      <c r="S233" t="n">
+        <v>3651</v>
+      </c>
+      <c r="T233" t="n">
+        <v>3593</v>
+      </c>
+      <c r="U233" t="n">
         <v>3600</v>
       </c>
-      <c r="R233" t="n">
-        <v>3598</v>
-      </c>
-      <c r="S233" t="n">
-        <v>3592</v>
-      </c>
-      <c r="T233" t="n">
-        <v>3585</v>
-      </c>
-      <c r="U233" t="n">
-        <v>3603</v>
-      </c>
       <c r="V233" t="n">
-        <v>3791</v>
+        <v>3721</v>
       </c>
       <c r="W233" t="n">
-        <v>4163</v>
+        <v>4006</v>
       </c>
       <c r="X233" t="n">
-        <v>4161</v>
+        <v>4031</v>
       </c>
       <c r="Y233" t="n">
-        <v>3893</v>
+        <v>3821</v>
       </c>
       <c r="Z233" t="n">
-        <v>3632</v>
+        <v>3608</v>
       </c>
       <c r="AA233" t="n">
-        <v>3360</v>
+        <v>3399</v>
       </c>
     </row>
     <row r="234">
@@ -19830,76 +19830,76 @@
         <v>25</v>
       </c>
       <c r="D234" t="n">
-        <v>3021</v>
+        <v>3039</v>
       </c>
       <c r="E234" t="n">
-        <v>2892</v>
+        <v>2878</v>
       </c>
       <c r="F234" t="n">
-        <v>2829</v>
+        <v>2802</v>
       </c>
       <c r="G234" t="n">
-        <v>2801</v>
+        <v>2768</v>
       </c>
       <c r="H234" t="n">
-        <v>2804</v>
+        <v>2773</v>
       </c>
       <c r="I234" t="n">
-        <v>2886</v>
+        <v>2868</v>
       </c>
       <c r="J234" t="n">
-        <v>3171</v>
+        <v>3191</v>
       </c>
       <c r="K234" t="n">
-        <v>3386</v>
+        <v>3435</v>
       </c>
       <c r="L234" t="n">
-        <v>3528</v>
+        <v>3609</v>
       </c>
       <c r="M234" t="n">
-        <v>3568</v>
+        <v>3649</v>
       </c>
       <c r="N234" t="n">
-        <v>3550</v>
+        <v>3629</v>
       </c>
       <c r="O234" t="n">
-        <v>3569</v>
+        <v>3654</v>
       </c>
       <c r="P234" t="n">
-        <v>3562</v>
+        <v>3652</v>
       </c>
       <c r="Q234" t="n">
+        <v>3709</v>
+      </c>
+      <c r="R234" t="n">
+        <v>3702</v>
+      </c>
+      <c r="S234" t="n">
+        <v>3655</v>
+      </c>
+      <c r="T234" t="n">
+        <v>3598</v>
+      </c>
+      <c r="U234" t="n">
         <v>3604</v>
       </c>
-      <c r="R234" t="n">
-        <v>3602</v>
-      </c>
-      <c r="S234" t="n">
-        <v>3597</v>
-      </c>
-      <c r="T234" t="n">
-        <v>3590</v>
-      </c>
-      <c r="U234" t="n">
-        <v>3605</v>
-      </c>
       <c r="V234" t="n">
-        <v>3765</v>
+        <v>3701</v>
       </c>
       <c r="W234" t="n">
-        <v>4083</v>
+        <v>3932</v>
       </c>
       <c r="X234" t="n">
-        <v>4081</v>
+        <v>3952</v>
       </c>
       <c r="Y234" t="n">
-        <v>3824</v>
+        <v>3753</v>
       </c>
       <c r="Z234" t="n">
-        <v>3574</v>
+        <v>3551</v>
       </c>
       <c r="AA234" t="n">
-        <v>3313</v>
+        <v>3353</v>
       </c>
     </row>
     <row r="235">
@@ -19913,76 +19913,76 @@
         <v>26</v>
       </c>
       <c r="D235" t="n">
-        <v>3020</v>
+        <v>3038</v>
       </c>
       <c r="E235" t="n">
-        <v>2876</v>
+        <v>2869</v>
       </c>
       <c r="F235" t="n">
-        <v>2799</v>
+        <v>2775</v>
       </c>
       <c r="G235" t="n">
-        <v>2758</v>
+        <v>2725</v>
       </c>
       <c r="H235" t="n">
-        <v>2735</v>
+        <v>2703</v>
       </c>
       <c r="I235" t="n">
-        <v>2751</v>
+        <v>2728</v>
       </c>
       <c r="J235" t="n">
-        <v>2845</v>
+        <v>2832</v>
       </c>
       <c r="K235" t="n">
-        <v>2935</v>
+        <v>2940</v>
       </c>
       <c r="L235" t="n">
-        <v>3064</v>
+        <v>3110</v>
       </c>
       <c r="M235" t="n">
-        <v>3161</v>
+        <v>3233</v>
       </c>
       <c r="N235" t="n">
-        <v>3230</v>
+        <v>3291</v>
       </c>
       <c r="O235" t="n">
-        <v>3241</v>
+        <v>3328</v>
       </c>
       <c r="P235" t="n">
-        <v>3287</v>
+        <v>3401</v>
       </c>
       <c r="Q235" t="n">
-        <v>3304</v>
+        <v>3409</v>
       </c>
       <c r="R235" t="n">
-        <v>3315</v>
+        <v>3404</v>
       </c>
       <c r="S235" t="n">
-        <v>3344</v>
+        <v>3400</v>
       </c>
       <c r="T235" t="n">
-        <v>3387</v>
+        <v>3394</v>
       </c>
       <c r="U235" t="n">
-        <v>3509</v>
+        <v>3507</v>
       </c>
       <c r="V235" t="n">
-        <v>3603</v>
+        <v>3586</v>
       </c>
       <c r="W235" t="n">
-        <v>3866</v>
+        <v>3735</v>
       </c>
       <c r="X235" t="n">
-        <v>3832</v>
+        <v>3706</v>
       </c>
       <c r="Y235" t="n">
-        <v>3622</v>
+        <v>3536</v>
       </c>
       <c r="Z235" t="n">
-        <v>3431</v>
+        <v>3400</v>
       </c>
       <c r="AA235" t="n">
-        <v>3216</v>
+        <v>3256</v>
       </c>
     </row>
     <row r="236">
@@ -19996,76 +19996,159 @@
         <v>27</v>
       </c>
       <c r="D236" t="n">
-        <v>2971</v>
+        <v>2989</v>
       </c>
       <c r="E236" t="n">
-        <v>2842</v>
+        <v>2828</v>
       </c>
       <c r="F236" t="n">
-        <v>2758</v>
+        <v>2729</v>
       </c>
       <c r="G236" t="n">
-        <v>2717</v>
+        <v>2682</v>
       </c>
       <c r="H236" t="n">
-        <v>2689</v>
+        <v>2657</v>
       </c>
       <c r="I236" t="n">
-        <v>2697</v>
+        <v>2674</v>
       </c>
       <c r="J236" t="n">
-        <v>2781</v>
+        <v>2763</v>
       </c>
       <c r="K236" t="n">
-        <v>2867</v>
+        <v>2861</v>
       </c>
       <c r="L236" t="n">
-        <v>3014</v>
+        <v>3045</v>
       </c>
       <c r="M236" t="n">
-        <v>3133</v>
+        <v>3191</v>
       </c>
       <c r="N236" t="n">
-        <v>3203</v>
+        <v>3275</v>
       </c>
       <c r="O236" t="n">
-        <v>3262</v>
+        <v>3346</v>
       </c>
       <c r="P236" t="n">
-        <v>3305</v>
+        <v>3410</v>
       </c>
       <c r="Q236" t="n">
-        <v>3351</v>
+        <v>3427</v>
       </c>
       <c r="R236" t="n">
-        <v>3383</v>
+        <v>3453</v>
       </c>
       <c r="S236" t="n">
-        <v>3425</v>
+        <v>3470</v>
       </c>
       <c r="T236" t="n">
-        <v>3465</v>
+        <v>3473</v>
       </c>
       <c r="U236" t="n">
-        <v>3489</v>
+        <v>3571</v>
       </c>
       <c r="V236" t="n">
-        <v>3668</v>
+        <v>3660</v>
       </c>
       <c r="W236" t="n">
-        <v>3984</v>
+        <v>3863</v>
       </c>
       <c r="X236" t="n">
-        <v>4086</v>
+        <v>3955</v>
       </c>
       <c r="Y236" t="n">
-        <v>3838</v>
+        <v>3757</v>
       </c>
       <c r="Z236" t="n">
-        <v>3572</v>
+        <v>3541</v>
       </c>
       <c r="AA236" t="n">
-        <v>3313</v>
+        <v>3352</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B237" t="n">
+        <v>9</v>
+      </c>
+      <c r="C237" t="n">
+        <v>28</v>
+      </c>
+      <c r="D237" t="n">
+        <v>3039</v>
+      </c>
+      <c r="E237" t="n">
+        <v>2859</v>
+      </c>
+      <c r="F237" t="n">
+        <v>2769</v>
+      </c>
+      <c r="G237" t="n">
+        <v>2736</v>
+      </c>
+      <c r="H237" t="n">
+        <v>2747</v>
+      </c>
+      <c r="I237" t="n">
+        <v>2872</v>
+      </c>
+      <c r="J237" t="n">
+        <v>3253</v>
+      </c>
+      <c r="K237" t="n">
+        <v>3547</v>
+      </c>
+      <c r="L237" t="n">
+        <v>3781</v>
+      </c>
+      <c r="M237" t="n">
+        <v>3877</v>
+      </c>
+      <c r="N237" t="n">
+        <v>3861</v>
+      </c>
+      <c r="O237" t="n">
+        <v>3891</v>
+      </c>
+      <c r="P237" t="n">
+        <v>3865</v>
+      </c>
+      <c r="Q237" t="n">
+        <v>3909</v>
+      </c>
+      <c r="R237" t="n">
+        <v>3827</v>
+      </c>
+      <c r="S237" t="n">
+        <v>3831</v>
+      </c>
+      <c r="T237" t="n">
+        <v>3848</v>
+      </c>
+      <c r="U237" t="n">
+        <v>3864</v>
+      </c>
+      <c r="V237" t="n">
+        <v>3944</v>
+      </c>
+      <c r="W237" t="n">
+        <v>4083</v>
+      </c>
+      <c r="X237" t="n">
+        <v>4176</v>
+      </c>
+      <c r="Y237" t="n">
+        <v>3972</v>
+      </c>
+      <c r="Z237" t="n">
+        <v>3744</v>
+      </c>
+      <c r="AA237" t="n">
+        <v>3520</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA237"/>
+  <dimension ref="A1:AA238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19747,76 +19747,76 @@
         <v>24</v>
       </c>
       <c r="D233" t="n">
-        <v>3037</v>
+        <v>3072</v>
       </c>
       <c r="E233" t="n">
-        <v>2876</v>
+        <v>2881</v>
       </c>
       <c r="F233" t="n">
-        <v>2800</v>
+        <v>2792</v>
       </c>
       <c r="G233" t="n">
-        <v>2767</v>
+        <v>2753</v>
       </c>
       <c r="H233" t="n">
-        <v>2772</v>
+        <v>2761</v>
       </c>
       <c r="I233" t="n">
-        <v>2867</v>
+        <v>2883</v>
       </c>
       <c r="J233" t="n">
-        <v>3189</v>
+        <v>3318</v>
       </c>
       <c r="K233" t="n">
-        <v>3432</v>
+        <v>3633</v>
       </c>
       <c r="L233" t="n">
+        <v>3842</v>
+      </c>
+      <c r="M233" t="n">
+        <v>3874</v>
+      </c>
+      <c r="N233" t="n">
+        <v>3829</v>
+      </c>
+      <c r="O233" t="n">
+        <v>3849</v>
+      </c>
+      <c r="P233" t="n">
+        <v>3848</v>
+      </c>
+      <c r="Q233" t="n">
+        <v>3908</v>
+      </c>
+      <c r="R233" t="n">
+        <v>3878</v>
+      </c>
+      <c r="S233" t="n">
+        <v>3776</v>
+      </c>
+      <c r="T233" t="n">
+        <v>3696</v>
+      </c>
+      <c r="U233" t="n">
+        <v>3713</v>
+      </c>
+      <c r="V233" t="n">
+        <v>3840</v>
+      </c>
+      <c r="W233" t="n">
+        <v>4138</v>
+      </c>
+      <c r="X233" t="n">
+        <v>4173</v>
+      </c>
+      <c r="Y233" t="n">
+        <v>3890</v>
+      </c>
+      <c r="Z233" t="n">
         <v>3605</v>
       </c>
-      <c r="M233" t="n">
-        <v>3645</v>
-      </c>
-      <c r="N233" t="n">
-        <v>3625</v>
-      </c>
-      <c r="O233" t="n">
-        <v>3651</v>
-      </c>
-      <c r="P233" t="n">
-        <v>3649</v>
-      </c>
-      <c r="Q233" t="n">
-        <v>3705</v>
-      </c>
-      <c r="R233" t="n">
-        <v>3698</v>
-      </c>
-      <c r="S233" t="n">
-        <v>3651</v>
-      </c>
-      <c r="T233" t="n">
-        <v>3593</v>
-      </c>
-      <c r="U233" t="n">
-        <v>3600</v>
-      </c>
-      <c r="V233" t="n">
-        <v>3721</v>
-      </c>
-      <c r="W233" t="n">
-        <v>4006</v>
-      </c>
-      <c r="X233" t="n">
-        <v>4031</v>
-      </c>
-      <c r="Y233" t="n">
-        <v>3821</v>
-      </c>
-      <c r="Z233" t="n">
-        <v>3608</v>
-      </c>
       <c r="AA233" t="n">
-        <v>3399</v>
+        <v>3317</v>
       </c>
     </row>
     <row r="234">
@@ -19830,76 +19830,76 @@
         <v>25</v>
       </c>
       <c r="D234" t="n">
-        <v>3039</v>
+        <v>3068</v>
       </c>
       <c r="E234" t="n">
-        <v>2878</v>
+        <v>2879</v>
       </c>
       <c r="F234" t="n">
-        <v>2802</v>
+        <v>2790</v>
       </c>
       <c r="G234" t="n">
-        <v>2768</v>
+        <v>2751</v>
       </c>
       <c r="H234" t="n">
-        <v>2773</v>
+        <v>2759</v>
       </c>
       <c r="I234" t="n">
-        <v>2868</v>
+        <v>2881</v>
       </c>
       <c r="J234" t="n">
-        <v>3191</v>
+        <v>3314</v>
       </c>
       <c r="K234" t="n">
-        <v>3435</v>
+        <v>3627</v>
       </c>
       <c r="L234" t="n">
-        <v>3609</v>
+        <v>3835</v>
       </c>
       <c r="M234" t="n">
-        <v>3649</v>
+        <v>3867</v>
       </c>
       <c r="N234" t="n">
-        <v>3629</v>
+        <v>3823</v>
       </c>
       <c r="O234" t="n">
-        <v>3654</v>
+        <v>3842</v>
       </c>
       <c r="P234" t="n">
-        <v>3652</v>
+        <v>3842</v>
       </c>
       <c r="Q234" t="n">
-        <v>3709</v>
+        <v>3901</v>
       </c>
       <c r="R234" t="n">
+        <v>3871</v>
+      </c>
+      <c r="S234" t="n">
+        <v>3768</v>
+      </c>
+      <c r="T234" t="n">
+        <v>3688</v>
+      </c>
+      <c r="U234" t="n">
         <v>3702</v>
       </c>
-      <c r="S234" t="n">
-        <v>3655</v>
-      </c>
-      <c r="T234" t="n">
-        <v>3598</v>
-      </c>
-      <c r="U234" t="n">
-        <v>3604</v>
-      </c>
       <c r="V234" t="n">
-        <v>3701</v>
+        <v>3809</v>
       </c>
       <c r="W234" t="n">
-        <v>3932</v>
+        <v>4061</v>
       </c>
       <c r="X234" t="n">
-        <v>3952</v>
+        <v>4091</v>
       </c>
       <c r="Y234" t="n">
-        <v>3753</v>
+        <v>3818</v>
       </c>
       <c r="Z234" t="n">
-        <v>3551</v>
+        <v>3544</v>
       </c>
       <c r="AA234" t="n">
-        <v>3353</v>
+        <v>3267</v>
       </c>
     </row>
     <row r="235">
@@ -19913,76 +19913,76 @@
         <v>26</v>
       </c>
       <c r="D235" t="n">
-        <v>3038</v>
+        <v>3067</v>
       </c>
       <c r="E235" t="n">
-        <v>2869</v>
+        <v>2874</v>
       </c>
       <c r="F235" t="n">
-        <v>2775</v>
+        <v>2768</v>
       </c>
       <c r="G235" t="n">
-        <v>2725</v>
+        <v>2711</v>
       </c>
       <c r="H235" t="n">
-        <v>2703</v>
+        <v>2685</v>
       </c>
       <c r="I235" t="n">
-        <v>2728</v>
+        <v>2717</v>
       </c>
       <c r="J235" t="n">
-        <v>2832</v>
+        <v>2853</v>
       </c>
       <c r="K235" t="n">
-        <v>2940</v>
+        <v>2992</v>
       </c>
       <c r="L235" t="n">
-        <v>3110</v>
+        <v>3213</v>
       </c>
       <c r="M235" t="n">
-        <v>3233</v>
+        <v>3371</v>
       </c>
       <c r="N235" t="n">
-        <v>3291</v>
+        <v>3446</v>
       </c>
       <c r="O235" t="n">
-        <v>3328</v>
+        <v>3494</v>
       </c>
       <c r="P235" t="n">
-        <v>3401</v>
+        <v>3589</v>
       </c>
       <c r="Q235" t="n">
-        <v>3409</v>
+        <v>3599</v>
       </c>
       <c r="R235" t="n">
-        <v>3404</v>
+        <v>3555</v>
       </c>
       <c r="S235" t="n">
-        <v>3400</v>
+        <v>3526</v>
       </c>
       <c r="T235" t="n">
-        <v>3394</v>
+        <v>3482</v>
       </c>
       <c r="U235" t="n">
-        <v>3507</v>
+        <v>3612</v>
       </c>
       <c r="V235" t="n">
-        <v>3586</v>
+        <v>3703</v>
       </c>
       <c r="W235" t="n">
-        <v>3735</v>
+        <v>3873</v>
       </c>
       <c r="X235" t="n">
-        <v>3706</v>
+        <v>3831</v>
       </c>
       <c r="Y235" t="n">
-        <v>3536</v>
+        <v>3582</v>
       </c>
       <c r="Z235" t="n">
-        <v>3400</v>
+        <v>3381</v>
       </c>
       <c r="AA235" t="n">
-        <v>3256</v>
+        <v>3169</v>
       </c>
     </row>
     <row r="236">
@@ -19996,76 +19996,76 @@
         <v>27</v>
       </c>
       <c r="D236" t="n">
-        <v>2989</v>
+        <v>3021</v>
       </c>
       <c r="E236" t="n">
-        <v>2828</v>
+        <v>2837</v>
       </c>
       <c r="F236" t="n">
-        <v>2729</v>
+        <v>2724</v>
       </c>
       <c r="G236" t="n">
-        <v>2682</v>
+        <v>2670</v>
       </c>
       <c r="H236" t="n">
-        <v>2657</v>
+        <v>2641</v>
       </c>
       <c r="I236" t="n">
-        <v>2674</v>
+        <v>2663</v>
       </c>
       <c r="J236" t="n">
-        <v>2763</v>
+        <v>2777</v>
       </c>
       <c r="K236" t="n">
-        <v>2861</v>
+        <v>2902</v>
       </c>
       <c r="L236" t="n">
-        <v>3045</v>
+        <v>3137</v>
       </c>
       <c r="M236" t="n">
-        <v>3191</v>
+        <v>3325</v>
       </c>
       <c r="N236" t="n">
-        <v>3275</v>
+        <v>3432</v>
       </c>
       <c r="O236" t="n">
-        <v>3346</v>
+        <v>3523</v>
       </c>
       <c r="P236" t="n">
-        <v>3410</v>
+        <v>3604</v>
       </c>
       <c r="Q236" t="n">
-        <v>3427</v>
+        <v>3594</v>
       </c>
       <c r="R236" t="n">
-        <v>3453</v>
+        <v>3579</v>
       </c>
       <c r="S236" t="n">
-        <v>3470</v>
+        <v>3569</v>
       </c>
       <c r="T236" t="n">
-        <v>3473</v>
+        <v>3568</v>
       </c>
       <c r="U236" t="n">
-        <v>3571</v>
+        <v>3676</v>
       </c>
       <c r="V236" t="n">
-        <v>3660</v>
+        <v>3773</v>
       </c>
       <c r="W236" t="n">
-        <v>3863</v>
+        <v>3995</v>
       </c>
       <c r="X236" t="n">
-        <v>3955</v>
+        <v>4096</v>
       </c>
       <c r="Y236" t="n">
-        <v>3757</v>
+        <v>3824</v>
       </c>
       <c r="Z236" t="n">
-        <v>3541</v>
+        <v>3526</v>
       </c>
       <c r="AA236" t="n">
-        <v>3352</v>
+        <v>3268</v>
       </c>
     </row>
     <row r="237">
@@ -20079,76 +20079,159 @@
         <v>28</v>
       </c>
       <c r="D237" t="n">
-        <v>3039</v>
+        <v>3072</v>
       </c>
       <c r="E237" t="n">
-        <v>2859</v>
+        <v>2874</v>
       </c>
       <c r="F237" t="n">
         <v>2769</v>
       </c>
       <c r="G237" t="n">
-        <v>2736</v>
+        <v>2722</v>
       </c>
       <c r="H237" t="n">
-        <v>2747</v>
+        <v>2721</v>
       </c>
       <c r="I237" t="n">
-        <v>2872</v>
+        <v>2836</v>
       </c>
       <c r="J237" t="n">
-        <v>3253</v>
+        <v>3260</v>
       </c>
       <c r="K237" t="n">
-        <v>3547</v>
+        <v>3583</v>
       </c>
       <c r="L237" t="n">
-        <v>3781</v>
+        <v>3838</v>
       </c>
       <c r="M237" t="n">
-        <v>3877</v>
+        <v>3961</v>
       </c>
       <c r="N237" t="n">
-        <v>3861</v>
+        <v>3975</v>
       </c>
       <c r="O237" t="n">
-        <v>3891</v>
+        <v>3961</v>
       </c>
       <c r="P237" t="n">
-        <v>3865</v>
+        <v>3953</v>
       </c>
       <c r="Q237" t="n">
-        <v>3909</v>
+        <v>4106</v>
       </c>
       <c r="R237" t="n">
-        <v>3827</v>
+        <v>4057</v>
       </c>
       <c r="S237" t="n">
-        <v>3831</v>
+        <v>3936</v>
       </c>
       <c r="T237" t="n">
-        <v>3848</v>
+        <v>3926</v>
       </c>
       <c r="U237" t="n">
-        <v>3864</v>
+        <v>3923</v>
       </c>
       <c r="V237" t="n">
-        <v>3944</v>
+        <v>4015</v>
       </c>
       <c r="W237" t="n">
-        <v>4083</v>
+        <v>4260</v>
       </c>
       <c r="X237" t="n">
-        <v>4176</v>
+        <v>4317</v>
       </c>
       <c r="Y237" t="n">
-        <v>3972</v>
+        <v>4027</v>
       </c>
       <c r="Z237" t="n">
-        <v>3744</v>
+        <v>3710</v>
       </c>
       <c r="AA237" t="n">
-        <v>3520</v>
+        <v>3436</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B238" t="n">
+        <v>9</v>
+      </c>
+      <c r="C238" t="n">
+        <v>29</v>
+      </c>
+      <c r="D238" t="n">
+        <v>3135</v>
+      </c>
+      <c r="E238" t="n">
+        <v>2937</v>
+      </c>
+      <c r="F238" t="n">
+        <v>2843</v>
+      </c>
+      <c r="G238" t="n">
+        <v>2802</v>
+      </c>
+      <c r="H238" t="n">
+        <v>2811</v>
+      </c>
+      <c r="I238" t="n">
+        <v>2952</v>
+      </c>
+      <c r="J238" t="n">
+        <v>3447</v>
+      </c>
+      <c r="K238" t="n">
+        <v>3806</v>
+      </c>
+      <c r="L238" t="n">
+        <v>4044</v>
+      </c>
+      <c r="M238" t="n">
+        <v>4081</v>
+      </c>
+      <c r="N238" t="n">
+        <v>4030</v>
+      </c>
+      <c r="O238" t="n">
+        <v>4052</v>
+      </c>
+      <c r="P238" t="n">
+        <v>4052</v>
+      </c>
+      <c r="Q238" t="n">
+        <v>4120</v>
+      </c>
+      <c r="R238" t="n">
+        <v>4094</v>
+      </c>
+      <c r="S238" t="n">
+        <v>4007</v>
+      </c>
+      <c r="T238" t="n">
+        <v>3939</v>
+      </c>
+      <c r="U238" t="n">
+        <v>3953</v>
+      </c>
+      <c r="V238" t="n">
+        <v>4055</v>
+      </c>
+      <c r="W238" t="n">
+        <v>4293</v>
+      </c>
+      <c r="X238" t="n">
+        <v>4321</v>
+      </c>
+      <c r="Y238" t="n">
+        <v>4031</v>
+      </c>
+      <c r="Z238" t="n">
+        <v>3738</v>
+      </c>
+      <c r="AA238" t="n">
+        <v>3441</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA238"/>
+  <dimension ref="A1:AA239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19830,76 +19830,76 @@
         <v>25</v>
       </c>
       <c r="D234" t="n">
-        <v>3068</v>
+        <v>3048</v>
       </c>
       <c r="E234" t="n">
-        <v>2879</v>
+        <v>2808</v>
       </c>
       <c r="F234" t="n">
+        <v>2695</v>
+      </c>
+      <c r="G234" t="n">
+        <v>2657</v>
+      </c>
+      <c r="H234" t="n">
+        <v>2654</v>
+      </c>
+      <c r="I234" t="n">
         <v>2790</v>
       </c>
-      <c r="G234" t="n">
-        <v>2751</v>
-      </c>
-      <c r="H234" t="n">
-        <v>2759</v>
-      </c>
-      <c r="I234" t="n">
-        <v>2881</v>
-      </c>
       <c r="J234" t="n">
-        <v>3314</v>
+        <v>3327</v>
       </c>
       <c r="K234" t="n">
-        <v>3627</v>
+        <v>3742</v>
       </c>
       <c r="L234" t="n">
-        <v>3835</v>
+        <v>4082</v>
       </c>
       <c r="M234" t="n">
-        <v>3867</v>
+        <v>4137</v>
       </c>
       <c r="N234" t="n">
-        <v>3823</v>
+        <v>4108</v>
       </c>
       <c r="O234" t="n">
-        <v>3842</v>
+        <v>4171</v>
       </c>
       <c r="P234" t="n">
-        <v>3842</v>
+        <v>4250</v>
       </c>
       <c r="Q234" t="n">
-        <v>3901</v>
+        <v>4331</v>
       </c>
       <c r="R234" t="n">
-        <v>3871</v>
+        <v>4353</v>
       </c>
       <c r="S234" t="n">
-        <v>3768</v>
+        <v>4112</v>
       </c>
       <c r="T234" t="n">
-        <v>3688</v>
+        <v>3954</v>
       </c>
       <c r="U234" t="n">
-        <v>3702</v>
+        <v>3922</v>
       </c>
       <c r="V234" t="n">
-        <v>3809</v>
+        <v>4060</v>
       </c>
       <c r="W234" t="n">
-        <v>4061</v>
+        <v>4403</v>
       </c>
       <c r="X234" t="n">
-        <v>4091</v>
+        <v>4405</v>
       </c>
       <c r="Y234" t="n">
-        <v>3818</v>
+        <v>4103</v>
       </c>
       <c r="Z234" t="n">
-        <v>3544</v>
+        <v>3784</v>
       </c>
       <c r="AA234" t="n">
-        <v>3267</v>
+        <v>3436</v>
       </c>
     </row>
     <row r="235">
@@ -19913,76 +19913,76 @@
         <v>26</v>
       </c>
       <c r="D235" t="n">
-        <v>3067</v>
+        <v>3037</v>
       </c>
       <c r="E235" t="n">
-        <v>2874</v>
+        <v>2799</v>
       </c>
       <c r="F235" t="n">
-        <v>2768</v>
+        <v>2672</v>
       </c>
       <c r="G235" t="n">
-        <v>2711</v>
+        <v>2603</v>
       </c>
       <c r="H235" t="n">
-        <v>2685</v>
+        <v>2583</v>
       </c>
       <c r="I235" t="n">
-        <v>2717</v>
+        <v>2642</v>
       </c>
       <c r="J235" t="n">
-        <v>2853</v>
+        <v>2871</v>
       </c>
       <c r="K235" t="n">
-        <v>2992</v>
+        <v>3083</v>
       </c>
       <c r="L235" t="n">
-        <v>3213</v>
+        <v>3458</v>
       </c>
       <c r="M235" t="n">
-        <v>3371</v>
+        <v>3688</v>
       </c>
       <c r="N235" t="n">
-        <v>3446</v>
+        <v>3782</v>
       </c>
       <c r="O235" t="n">
-        <v>3494</v>
+        <v>3830</v>
       </c>
       <c r="P235" t="n">
-        <v>3589</v>
+        <v>4006</v>
       </c>
       <c r="Q235" t="n">
-        <v>3599</v>
+        <v>3983</v>
       </c>
       <c r="R235" t="n">
-        <v>3555</v>
+        <v>3852</v>
       </c>
       <c r="S235" t="n">
-        <v>3526</v>
+        <v>3793</v>
       </c>
       <c r="T235" t="n">
-        <v>3482</v>
+        <v>3693</v>
       </c>
       <c r="U235" t="n">
-        <v>3612</v>
+        <v>3883</v>
       </c>
       <c r="V235" t="n">
-        <v>3703</v>
+        <v>3927</v>
       </c>
       <c r="W235" t="n">
-        <v>3873</v>
+        <v>4190</v>
       </c>
       <c r="X235" t="n">
-        <v>3831</v>
+        <v>4154</v>
       </c>
       <c r="Y235" t="n">
-        <v>3582</v>
+        <v>3834</v>
       </c>
       <c r="Z235" t="n">
-        <v>3381</v>
+        <v>3604</v>
       </c>
       <c r="AA235" t="n">
-        <v>3169</v>
+        <v>3332</v>
       </c>
     </row>
     <row r="236">
@@ -19996,76 +19996,76 @@
         <v>27</v>
       </c>
       <c r="D236" t="n">
-        <v>3021</v>
+        <v>2996</v>
       </c>
       <c r="E236" t="n">
-        <v>2837</v>
+        <v>2768</v>
       </c>
       <c r="F236" t="n">
-        <v>2724</v>
+        <v>2640</v>
       </c>
       <c r="G236" t="n">
-        <v>2670</v>
+        <v>2563</v>
       </c>
       <c r="H236" t="n">
-        <v>2641</v>
+        <v>2541</v>
       </c>
       <c r="I236" t="n">
-        <v>2663</v>
+        <v>2580</v>
       </c>
       <c r="J236" t="n">
-        <v>2777</v>
+        <v>2758</v>
       </c>
       <c r="K236" t="n">
-        <v>2902</v>
+        <v>2938</v>
       </c>
       <c r="L236" t="n">
-        <v>3137</v>
+        <v>3279</v>
       </c>
       <c r="M236" t="n">
-        <v>3325</v>
+        <v>3549</v>
       </c>
       <c r="N236" t="n">
-        <v>3432</v>
+        <v>3713</v>
       </c>
       <c r="O236" t="n">
-        <v>3523</v>
+        <v>3822</v>
       </c>
       <c r="P236" t="n">
-        <v>3604</v>
+        <v>4018</v>
       </c>
       <c r="Q236" t="n">
-        <v>3594</v>
+        <v>4013</v>
       </c>
       <c r="R236" t="n">
-        <v>3579</v>
+        <v>3893</v>
       </c>
       <c r="S236" t="n">
-        <v>3569</v>
+        <v>3817</v>
       </c>
       <c r="T236" t="n">
-        <v>3568</v>
+        <v>3791</v>
       </c>
       <c r="U236" t="n">
-        <v>3676</v>
+        <v>3921</v>
       </c>
       <c r="V236" t="n">
-        <v>3773</v>
+        <v>4024</v>
       </c>
       <c r="W236" t="n">
-        <v>3995</v>
+        <v>4339</v>
       </c>
       <c r="X236" t="n">
-        <v>4096</v>
+        <v>4415</v>
       </c>
       <c r="Y236" t="n">
-        <v>3824</v>
+        <v>4089</v>
       </c>
       <c r="Z236" t="n">
-        <v>3526</v>
+        <v>3745</v>
       </c>
       <c r="AA236" t="n">
-        <v>3268</v>
+        <v>3434</v>
       </c>
     </row>
     <row r="237">
@@ -20079,76 +20079,76 @@
         <v>28</v>
       </c>
       <c r="D237" t="n">
-        <v>3072</v>
+        <v>3046</v>
       </c>
       <c r="E237" t="n">
-        <v>2874</v>
+        <v>2793</v>
       </c>
       <c r="F237" t="n">
-        <v>2769</v>
+        <v>2672</v>
       </c>
       <c r="G237" t="n">
-        <v>2722</v>
+        <v>2621</v>
       </c>
       <c r="H237" t="n">
-        <v>2721</v>
+        <v>2628</v>
       </c>
       <c r="I237" t="n">
-        <v>2836</v>
+        <v>2810</v>
       </c>
       <c r="J237" t="n">
-        <v>3260</v>
+        <v>3382</v>
       </c>
       <c r="K237" t="n">
-        <v>3583</v>
+        <v>3820</v>
       </c>
       <c r="L237" t="n">
-        <v>3838</v>
+        <v>4165</v>
       </c>
       <c r="M237" t="n">
-        <v>3961</v>
+        <v>4316</v>
       </c>
       <c r="N237" t="n">
-        <v>3975</v>
+        <v>4324</v>
       </c>
       <c r="O237" t="n">
-        <v>3961</v>
+        <v>4396</v>
       </c>
       <c r="P237" t="n">
-        <v>3953</v>
+        <v>4455</v>
       </c>
       <c r="Q237" t="n">
-        <v>4106</v>
+        <v>4517</v>
       </c>
       <c r="R237" t="n">
-        <v>4057</v>
+        <v>4501</v>
       </c>
       <c r="S237" t="n">
-        <v>3936</v>
+        <v>4325</v>
       </c>
       <c r="T237" t="n">
-        <v>3926</v>
+        <v>4147</v>
       </c>
       <c r="U237" t="n">
-        <v>3923</v>
+        <v>4151</v>
       </c>
       <c r="V237" t="n">
-        <v>4015</v>
+        <v>4280</v>
       </c>
       <c r="W237" t="n">
-        <v>4260</v>
+        <v>4597</v>
       </c>
       <c r="X237" t="n">
-        <v>4317</v>
+        <v>4635</v>
       </c>
       <c r="Y237" t="n">
-        <v>4027</v>
+        <v>4268</v>
       </c>
       <c r="Z237" t="n">
-        <v>3710</v>
+        <v>3943</v>
       </c>
       <c r="AA237" t="n">
-        <v>3436</v>
+        <v>3602</v>
       </c>
     </row>
     <row r="238">
@@ -20162,76 +20162,159 @@
         <v>29</v>
       </c>
       <c r="D238" t="n">
-        <v>3135</v>
+        <v>3101</v>
       </c>
       <c r="E238" t="n">
-        <v>2937</v>
+        <v>2856</v>
       </c>
       <c r="F238" t="n">
-        <v>2843</v>
+        <v>2740</v>
       </c>
       <c r="G238" t="n">
-        <v>2802</v>
+        <v>2701</v>
       </c>
       <c r="H238" t="n">
-        <v>2811</v>
+        <v>2698</v>
       </c>
       <c r="I238" t="n">
-        <v>2952</v>
+        <v>2846</v>
       </c>
       <c r="J238" t="n">
-        <v>3447</v>
+        <v>3428</v>
       </c>
       <c r="K238" t="n">
-        <v>3806</v>
+        <v>3877</v>
       </c>
       <c r="L238" t="n">
-        <v>4044</v>
+        <v>4246</v>
       </c>
       <c r="M238" t="n">
-        <v>4081</v>
+        <v>4306</v>
       </c>
       <c r="N238" t="n">
-        <v>4030</v>
+        <v>4274</v>
       </c>
       <c r="O238" t="n">
-        <v>4052</v>
+        <v>4343</v>
       </c>
       <c r="P238" t="n">
-        <v>4052</v>
+        <v>4428</v>
       </c>
       <c r="Q238" t="n">
-        <v>4120</v>
+        <v>4516</v>
       </c>
       <c r="R238" t="n">
-        <v>4094</v>
+        <v>4536</v>
       </c>
       <c r="S238" t="n">
-        <v>4007</v>
+        <v>4317</v>
       </c>
       <c r="T238" t="n">
-        <v>3939</v>
+        <v>4174</v>
       </c>
       <c r="U238" t="n">
-        <v>3953</v>
+        <v>4145</v>
       </c>
       <c r="V238" t="n">
-        <v>4055</v>
+        <v>4285</v>
       </c>
       <c r="W238" t="n">
-        <v>4293</v>
+        <v>4633</v>
       </c>
       <c r="X238" t="n">
-        <v>4321</v>
+        <v>4635</v>
       </c>
       <c r="Y238" t="n">
-        <v>4031</v>
+        <v>4313</v>
       </c>
       <c r="Z238" t="n">
-        <v>3738</v>
+        <v>3972</v>
       </c>
       <c r="AA238" t="n">
-        <v>3441</v>
+        <v>3601</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B239" t="n">
+        <v>9</v>
+      </c>
+      <c r="C239" t="n">
+        <v>30</v>
+      </c>
+      <c r="D239" t="n">
+        <v>3108</v>
+      </c>
+      <c r="E239" t="n">
+        <v>2861</v>
+      </c>
+      <c r="F239" t="n">
+        <v>2744</v>
+      </c>
+      <c r="G239" t="n">
+        <v>2704</v>
+      </c>
+      <c r="H239" t="n">
+        <v>2702</v>
+      </c>
+      <c r="I239" t="n">
+        <v>2850</v>
+      </c>
+      <c r="J239" t="n">
+        <v>3436</v>
+      </c>
+      <c r="K239" t="n">
+        <v>3887</v>
+      </c>
+      <c r="L239" t="n">
+        <v>4257</v>
+      </c>
+      <c r="M239" t="n">
+        <v>4317</v>
+      </c>
+      <c r="N239" t="n">
+        <v>4286</v>
+      </c>
+      <c r="O239" t="n">
+        <v>4354</v>
+      </c>
+      <c r="P239" t="n">
+        <v>4441</v>
+      </c>
+      <c r="Q239" t="n">
+        <v>4528</v>
+      </c>
+      <c r="R239" t="n">
+        <v>4549</v>
+      </c>
+      <c r="S239" t="n">
+        <v>4330</v>
+      </c>
+      <c r="T239" t="n">
+        <v>4187</v>
+      </c>
+      <c r="U239" t="n">
+        <v>4158</v>
+      </c>
+      <c r="V239" t="n">
+        <v>4295</v>
+      </c>
+      <c r="W239" t="n">
+        <v>4637</v>
+      </c>
+      <c r="X239" t="n">
+        <v>4639</v>
+      </c>
+      <c r="Y239" t="n">
+        <v>4317</v>
+      </c>
+      <c r="Z239" t="n">
+        <v>3976</v>
+      </c>
+      <c r="AA239" t="n">
+        <v>3606</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA239"/>
+  <dimension ref="A1:AA240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19913,76 +19913,76 @@
         <v>26</v>
       </c>
       <c r="D235" t="n">
-        <v>3037</v>
+        <v>3141</v>
       </c>
       <c r="E235" t="n">
+        <v>2918</v>
+      </c>
+      <c r="F235" t="n">
         <v>2799</v>
       </c>
-      <c r="F235" t="n">
-        <v>2672</v>
-      </c>
       <c r="G235" t="n">
-        <v>2603</v>
+        <v>2735</v>
       </c>
       <c r="H235" t="n">
-        <v>2583</v>
+        <v>2716</v>
       </c>
       <c r="I235" t="n">
-        <v>2642</v>
+        <v>2756</v>
       </c>
       <c r="J235" t="n">
-        <v>2871</v>
+        <v>2911</v>
       </c>
       <c r="K235" t="n">
-        <v>3083</v>
+        <v>3055</v>
       </c>
       <c r="L235" t="n">
-        <v>3458</v>
+        <v>3309</v>
       </c>
       <c r="M235" t="n">
-        <v>3688</v>
+        <v>3465</v>
       </c>
       <c r="N235" t="n">
-        <v>3782</v>
+        <v>3529</v>
       </c>
       <c r="O235" t="n">
-        <v>3830</v>
+        <v>3561</v>
       </c>
       <c r="P235" t="n">
-        <v>4006</v>
+        <v>3681</v>
       </c>
       <c r="Q235" t="n">
-        <v>3983</v>
+        <v>3681</v>
       </c>
       <c r="R235" t="n">
-        <v>3852</v>
+        <v>3682</v>
       </c>
       <c r="S235" t="n">
-        <v>3793</v>
+        <v>3683</v>
       </c>
       <c r="T235" t="n">
-        <v>3693</v>
+        <v>3684</v>
       </c>
       <c r="U235" t="n">
-        <v>3883</v>
+        <v>3860</v>
       </c>
       <c r="V235" t="n">
-        <v>3927</v>
+        <v>3900</v>
       </c>
       <c r="W235" t="n">
-        <v>4190</v>
+        <v>4144</v>
       </c>
       <c r="X235" t="n">
-        <v>4154</v>
+        <v>4112</v>
       </c>
       <c r="Y235" t="n">
-        <v>3834</v>
+        <v>3826</v>
       </c>
       <c r="Z235" t="n">
-        <v>3604</v>
+        <v>3620</v>
       </c>
       <c r="AA235" t="n">
-        <v>3332</v>
+        <v>3377</v>
       </c>
     </row>
     <row r="236">
@@ -19996,76 +19996,76 @@
         <v>27</v>
       </c>
       <c r="D236" t="n">
-        <v>2996</v>
+        <v>3100</v>
       </c>
       <c r="E236" t="n">
-        <v>2768</v>
+        <v>2887</v>
       </c>
       <c r="F236" t="n">
-        <v>2640</v>
+        <v>2767</v>
       </c>
       <c r="G236" t="n">
-        <v>2563</v>
+        <v>2694</v>
       </c>
       <c r="H236" t="n">
-        <v>2541</v>
+        <v>2674</v>
       </c>
       <c r="I236" t="n">
-        <v>2580</v>
+        <v>2701</v>
       </c>
       <c r="J236" t="n">
-        <v>2758</v>
+        <v>2824</v>
       </c>
       <c r="K236" t="n">
-        <v>2938</v>
+        <v>2948</v>
       </c>
       <c r="L236" t="n">
-        <v>3279</v>
+        <v>3183</v>
       </c>
       <c r="M236" t="n">
-        <v>3549</v>
+        <v>3370</v>
       </c>
       <c r="N236" t="n">
-        <v>3713</v>
+        <v>3482</v>
       </c>
       <c r="O236" t="n">
-        <v>3822</v>
+        <v>3558</v>
       </c>
       <c r="P236" t="n">
-        <v>4018</v>
+        <v>3693</v>
       </c>
       <c r="Q236" t="n">
-        <v>4013</v>
+        <v>3694</v>
       </c>
       <c r="R236" t="n">
-        <v>3893</v>
+        <v>3742</v>
       </c>
       <c r="S236" t="n">
-        <v>3817</v>
+        <v>3772</v>
       </c>
       <c r="T236" t="n">
-        <v>3791</v>
+        <v>3782</v>
       </c>
       <c r="U236" t="n">
-        <v>3921</v>
+        <v>3904</v>
       </c>
       <c r="V236" t="n">
-        <v>4024</v>
+        <v>4001</v>
       </c>
       <c r="W236" t="n">
-        <v>4339</v>
+        <v>4298</v>
       </c>
       <c r="X236" t="n">
-        <v>4415</v>
+        <v>4369</v>
       </c>
       <c r="Y236" t="n">
-        <v>4089</v>
+        <v>4073</v>
       </c>
       <c r="Z236" t="n">
-        <v>3745</v>
+        <v>3761</v>
       </c>
       <c r="AA236" t="n">
-        <v>3434</v>
+        <v>3478</v>
       </c>
     </row>
     <row r="237">
@@ -20079,76 +20079,76 @@
         <v>28</v>
       </c>
       <c r="D237" t="n">
-        <v>3046</v>
+        <v>3150</v>
       </c>
       <c r="E237" t="n">
-        <v>2793</v>
+        <v>2914</v>
       </c>
       <c r="F237" t="n">
-        <v>2672</v>
+        <v>2801</v>
       </c>
       <c r="G237" t="n">
-        <v>2621</v>
+        <v>2753</v>
       </c>
       <c r="H237" t="n">
-        <v>2628</v>
+        <v>2759</v>
       </c>
       <c r="I237" t="n">
-        <v>2810</v>
+        <v>2897</v>
       </c>
       <c r="J237" t="n">
-        <v>3382</v>
+        <v>3331</v>
       </c>
       <c r="K237" t="n">
-        <v>3820</v>
+        <v>3664</v>
       </c>
       <c r="L237" t="n">
-        <v>4165</v>
+        <v>3925</v>
       </c>
       <c r="M237" t="n">
-        <v>4316</v>
+        <v>4040</v>
       </c>
       <c r="N237" t="n">
-        <v>4324</v>
+        <v>4045</v>
       </c>
       <c r="O237" t="n">
-        <v>4396</v>
+        <v>4100</v>
       </c>
       <c r="P237" t="n">
-        <v>4455</v>
+        <v>4145</v>
       </c>
       <c r="Q237" t="n">
-        <v>4517</v>
+        <v>4192</v>
       </c>
       <c r="R237" t="n">
-        <v>4501</v>
+        <v>4190</v>
       </c>
       <c r="S237" t="n">
-        <v>4325</v>
+        <v>4164</v>
       </c>
       <c r="T237" t="n">
-        <v>4147</v>
+        <v>4137</v>
       </c>
       <c r="U237" t="n">
-        <v>4151</v>
+        <v>4141</v>
       </c>
       <c r="V237" t="n">
-        <v>4280</v>
+        <v>4261</v>
       </c>
       <c r="W237" t="n">
-        <v>4597</v>
+        <v>4554</v>
       </c>
       <c r="X237" t="n">
-        <v>4635</v>
+        <v>4590</v>
       </c>
       <c r="Y237" t="n">
-        <v>4268</v>
+        <v>4255</v>
       </c>
       <c r="Z237" t="n">
-        <v>3943</v>
+        <v>3958</v>
       </c>
       <c r="AA237" t="n">
-        <v>3602</v>
+        <v>3646</v>
       </c>
     </row>
     <row r="238">
@@ -20162,76 +20162,76 @@
         <v>29</v>
       </c>
       <c r="D238" t="n">
-        <v>3101</v>
+        <v>3205</v>
       </c>
       <c r="E238" t="n">
-        <v>2856</v>
+        <v>2984</v>
       </c>
       <c r="F238" t="n">
-        <v>2740</v>
+        <v>2875</v>
       </c>
       <c r="G238" t="n">
-        <v>2701</v>
+        <v>2831</v>
       </c>
       <c r="H238" t="n">
-        <v>2698</v>
+        <v>2836</v>
       </c>
       <c r="I238" t="n">
-        <v>2846</v>
+        <v>2961</v>
       </c>
       <c r="J238" t="n">
-        <v>3428</v>
+        <v>3424</v>
       </c>
       <c r="K238" t="n">
-        <v>3877</v>
+        <v>3779</v>
       </c>
       <c r="L238" t="n">
-        <v>4246</v>
+        <v>4065</v>
       </c>
       <c r="M238" t="n">
-        <v>4306</v>
+        <v>4141</v>
       </c>
       <c r="N238" t="n">
-        <v>4274</v>
+        <v>4106</v>
       </c>
       <c r="O238" t="n">
-        <v>4343</v>
+        <v>4114</v>
       </c>
       <c r="P238" t="n">
-        <v>4428</v>
+        <v>4122</v>
       </c>
       <c r="Q238" t="n">
-        <v>4516</v>
+        <v>4191</v>
       </c>
       <c r="R238" t="n">
-        <v>4536</v>
+        <v>4181</v>
       </c>
       <c r="S238" t="n">
-        <v>4317</v>
+        <v>4158</v>
       </c>
       <c r="T238" t="n">
-        <v>4174</v>
+        <v>4136</v>
       </c>
       <c r="U238" t="n">
-        <v>4145</v>
+        <v>4155</v>
       </c>
       <c r="V238" t="n">
-        <v>4285</v>
+        <v>4286</v>
       </c>
       <c r="W238" t="n">
-        <v>4633</v>
+        <v>4577</v>
       </c>
       <c r="X238" t="n">
-        <v>4635</v>
+        <v>4589</v>
       </c>
       <c r="Y238" t="n">
-        <v>4313</v>
+        <v>4280</v>
       </c>
       <c r="Z238" t="n">
-        <v>3972</v>
+        <v>3966</v>
       </c>
       <c r="AA238" t="n">
-        <v>3601</v>
+        <v>3646</v>
       </c>
     </row>
     <row r="239">
@@ -20245,76 +20245,159 @@
         <v>30</v>
       </c>
       <c r="D239" t="n">
-        <v>3108</v>
+        <v>3212</v>
       </c>
       <c r="E239" t="n">
-        <v>2861</v>
+        <v>2989</v>
       </c>
       <c r="F239" t="n">
-        <v>2744</v>
+        <v>2879</v>
       </c>
       <c r="G239" t="n">
-        <v>2704</v>
+        <v>2834</v>
       </c>
       <c r="H239" t="n">
-        <v>2702</v>
+        <v>2839</v>
       </c>
       <c r="I239" t="n">
-        <v>2850</v>
+        <v>2965</v>
       </c>
       <c r="J239" t="n">
-        <v>3436</v>
+        <v>3432</v>
       </c>
       <c r="K239" t="n">
-        <v>3887</v>
+        <v>3789</v>
       </c>
       <c r="L239" t="n">
-        <v>4257</v>
+        <v>4077</v>
       </c>
       <c r="M239" t="n">
-        <v>4317</v>
+        <v>4153</v>
       </c>
       <c r="N239" t="n">
-        <v>4286</v>
+        <v>4118</v>
       </c>
       <c r="O239" t="n">
-        <v>4354</v>
+        <v>4126</v>
       </c>
       <c r="P239" t="n">
-        <v>4441</v>
+        <v>4135</v>
       </c>
       <c r="Q239" t="n">
-        <v>4528</v>
+        <v>4203</v>
       </c>
       <c r="R239" t="n">
-        <v>4549</v>
+        <v>4194</v>
       </c>
       <c r="S239" t="n">
-        <v>4330</v>
+        <v>4173</v>
       </c>
       <c r="T239" t="n">
-        <v>4187</v>
+        <v>4152</v>
       </c>
       <c r="U239" t="n">
-        <v>4158</v>
+        <v>4171</v>
       </c>
       <c r="V239" t="n">
-        <v>4295</v>
+        <v>4298</v>
       </c>
       <c r="W239" t="n">
-        <v>4637</v>
+        <v>4581</v>
       </c>
       <c r="X239" t="n">
-        <v>4639</v>
+        <v>4593</v>
       </c>
       <c r="Y239" t="n">
-        <v>4317</v>
+        <v>4284</v>
       </c>
       <c r="Z239" t="n">
-        <v>3976</v>
+        <v>3970</v>
       </c>
       <c r="AA239" t="n">
-        <v>3606</v>
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B240" t="n">
+        <v>10</v>
+      </c>
+      <c r="C240" t="n">
+        <v>1</v>
+      </c>
+      <c r="D240" t="n">
+        <v>3202</v>
+      </c>
+      <c r="E240" t="n">
+        <v>2978</v>
+      </c>
+      <c r="F240" t="n">
+        <v>2867</v>
+      </c>
+      <c r="G240" t="n">
+        <v>2822</v>
+      </c>
+      <c r="H240" t="n">
+        <v>2827</v>
+      </c>
+      <c r="I240" t="n">
+        <v>2952</v>
+      </c>
+      <c r="J240" t="n">
+        <v>3417</v>
+      </c>
+      <c r="K240" t="n">
+        <v>3772</v>
+      </c>
+      <c r="L240" t="n">
+        <v>4059</v>
+      </c>
+      <c r="M240" t="n">
+        <v>4135</v>
+      </c>
+      <c r="N240" t="n">
+        <v>4100</v>
+      </c>
+      <c r="O240" t="n">
+        <v>4108</v>
+      </c>
+      <c r="P240" t="n">
+        <v>4116</v>
+      </c>
+      <c r="Q240" t="n">
+        <v>4185</v>
+      </c>
+      <c r="R240" t="n">
+        <v>4175</v>
+      </c>
+      <c r="S240" t="n">
+        <v>4153</v>
+      </c>
+      <c r="T240" t="n">
+        <v>4130</v>
+      </c>
+      <c r="U240" t="n">
+        <v>4150</v>
+      </c>
+      <c r="V240" t="n">
+        <v>4278</v>
+      </c>
+      <c r="W240" t="n">
+        <v>4563</v>
+      </c>
+      <c r="X240" t="n">
+        <v>4575</v>
+      </c>
+      <c r="Y240" t="n">
+        <v>4268</v>
+      </c>
+      <c r="Z240" t="n">
+        <v>3956</v>
+      </c>
+      <c r="AA240" t="n">
+        <v>3638</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA240"/>
+  <dimension ref="A1:AA241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19996,76 +19996,76 @@
         <v>27</v>
       </c>
       <c r="D236" t="n">
-        <v>3100</v>
+        <v>3224</v>
       </c>
       <c r="E236" t="n">
-        <v>2887</v>
+        <v>3070</v>
       </c>
       <c r="F236" t="n">
-        <v>2767</v>
+        <v>2983</v>
       </c>
       <c r="G236" t="n">
-        <v>2694</v>
+        <v>2930</v>
       </c>
       <c r="H236" t="n">
-        <v>2674</v>
+        <v>2916</v>
       </c>
       <c r="I236" t="n">
-        <v>2701</v>
+        <v>2941</v>
       </c>
       <c r="J236" t="n">
-        <v>2824</v>
+        <v>3056</v>
       </c>
       <c r="K236" t="n">
-        <v>2948</v>
+        <v>3172</v>
       </c>
       <c r="L236" t="n">
-        <v>3183</v>
+        <v>3392</v>
       </c>
       <c r="M236" t="n">
-        <v>3370</v>
+        <v>3567</v>
       </c>
       <c r="N236" t="n">
-        <v>3482</v>
+        <v>3673</v>
       </c>
       <c r="O236" t="n">
-        <v>3558</v>
+        <v>3743</v>
       </c>
       <c r="P236" t="n">
-        <v>3693</v>
+        <v>3870</v>
       </c>
       <c r="Q236" t="n">
-        <v>3694</v>
+        <v>3868</v>
       </c>
       <c r="R236" t="n">
-        <v>3742</v>
+        <v>3838</v>
       </c>
       <c r="S236" t="n">
-        <v>3772</v>
+        <v>3820</v>
       </c>
       <c r="T236" t="n">
-        <v>3782</v>
+        <v>3813</v>
       </c>
       <c r="U236" t="n">
-        <v>3904</v>
+        <v>3925</v>
       </c>
       <c r="V236" t="n">
-        <v>4001</v>
+        <v>4014</v>
       </c>
       <c r="W236" t="n">
-        <v>4298</v>
+        <v>4286</v>
       </c>
       <c r="X236" t="n">
-        <v>4369</v>
+        <v>4351</v>
       </c>
       <c r="Y236" t="n">
-        <v>4073</v>
+        <v>4089</v>
       </c>
       <c r="Z236" t="n">
-        <v>3761</v>
+        <v>3811</v>
       </c>
       <c r="AA236" t="n">
-        <v>3478</v>
+        <v>3561</v>
       </c>
     </row>
     <row r="237">
@@ -20079,76 +20079,76 @@
         <v>28</v>
       </c>
       <c r="D237" t="n">
-        <v>3150</v>
+        <v>3271</v>
       </c>
       <c r="E237" t="n">
-        <v>2914</v>
+        <v>3107</v>
       </c>
       <c r="F237" t="n">
-        <v>2801</v>
+        <v>3031</v>
       </c>
       <c r="G237" t="n">
-        <v>2753</v>
+        <v>2995</v>
       </c>
       <c r="H237" t="n">
-        <v>2759</v>
+        <v>2994</v>
       </c>
       <c r="I237" t="n">
-        <v>2897</v>
+        <v>3111</v>
       </c>
       <c r="J237" t="n">
-        <v>3331</v>
+        <v>3495</v>
       </c>
       <c r="K237" t="n">
-        <v>3664</v>
+        <v>3785</v>
       </c>
       <c r="L237" t="n">
-        <v>3925</v>
+        <v>4012</v>
       </c>
       <c r="M237" t="n">
-        <v>4040</v>
+        <v>4118</v>
       </c>
       <c r="N237" t="n">
-        <v>4045</v>
+        <v>4145</v>
       </c>
       <c r="O237" t="n">
-        <v>4100</v>
+        <v>4213</v>
       </c>
       <c r="P237" t="n">
-        <v>4145</v>
+        <v>4325</v>
       </c>
       <c r="Q237" t="n">
-        <v>4192</v>
+        <v>4364</v>
       </c>
       <c r="R237" t="n">
-        <v>4190</v>
+        <v>4391</v>
       </c>
       <c r="S237" t="n">
-        <v>4164</v>
+        <v>4296</v>
       </c>
       <c r="T237" t="n">
-        <v>4137</v>
+        <v>4180</v>
       </c>
       <c r="U237" t="n">
-        <v>4141</v>
+        <v>4160</v>
       </c>
       <c r="V237" t="n">
-        <v>4261</v>
+        <v>4248</v>
       </c>
       <c r="W237" t="n">
-        <v>4554</v>
+        <v>4568</v>
       </c>
       <c r="X237" t="n">
-        <v>4590</v>
+        <v>4492</v>
       </c>
       <c r="Y237" t="n">
-        <v>4255</v>
+        <v>4160</v>
       </c>
       <c r="Z237" t="n">
-        <v>3958</v>
+        <v>3934</v>
       </c>
       <c r="AA237" t="n">
-        <v>3646</v>
+        <v>3676</v>
       </c>
     </row>
     <row r="238">
@@ -20162,76 +20162,76 @@
         <v>29</v>
       </c>
       <c r="D238" t="n">
-        <v>3205</v>
+        <v>3325</v>
       </c>
       <c r="E238" t="n">
-        <v>2984</v>
+        <v>3167</v>
       </c>
       <c r="F238" t="n">
-        <v>2875</v>
+        <v>3089</v>
       </c>
       <c r="G238" t="n">
-        <v>2831</v>
+        <v>3071</v>
       </c>
       <c r="H238" t="n">
-        <v>2836</v>
+        <v>3075</v>
       </c>
       <c r="I238" t="n">
-        <v>2961</v>
+        <v>3189</v>
       </c>
       <c r="J238" t="n">
-        <v>3424</v>
+        <v>3644</v>
       </c>
       <c r="K238" t="n">
-        <v>3779</v>
+        <v>3981</v>
       </c>
       <c r="L238" t="n">
-        <v>4065</v>
+        <v>4259</v>
       </c>
       <c r="M238" t="n">
-        <v>4141</v>
+        <v>4338</v>
       </c>
       <c r="N238" t="n">
-        <v>4106</v>
+        <v>4299</v>
       </c>
       <c r="O238" t="n">
-        <v>4114</v>
+        <v>4284</v>
       </c>
       <c r="P238" t="n">
-        <v>4122</v>
+        <v>4292</v>
       </c>
       <c r="Q238" t="n">
-        <v>4191</v>
+        <v>4359</v>
       </c>
       <c r="R238" t="n">
-        <v>4181</v>
+        <v>4340</v>
       </c>
       <c r="S238" t="n">
-        <v>4158</v>
+        <v>4250</v>
       </c>
       <c r="T238" t="n">
-        <v>4136</v>
+        <v>4154</v>
       </c>
       <c r="U238" t="n">
-        <v>4155</v>
+        <v>4166</v>
       </c>
       <c r="V238" t="n">
-        <v>4286</v>
+        <v>4304</v>
       </c>
       <c r="W238" t="n">
-        <v>4577</v>
+        <v>4552</v>
       </c>
       <c r="X238" t="n">
-        <v>4589</v>
+        <v>4566</v>
       </c>
       <c r="Y238" t="n">
-        <v>4280</v>
+        <v>4262</v>
       </c>
       <c r="Z238" t="n">
-        <v>3966</v>
+        <v>3940</v>
       </c>
       <c r="AA238" t="n">
-        <v>3646</v>
+        <v>3595</v>
       </c>
     </row>
     <row r="239">
@@ -20245,76 +20245,76 @@
         <v>30</v>
       </c>
       <c r="D239" t="n">
-        <v>3212</v>
+        <v>3318</v>
       </c>
       <c r="E239" t="n">
-        <v>2989</v>
+        <v>3162</v>
       </c>
       <c r="F239" t="n">
-        <v>2879</v>
+        <v>3086</v>
       </c>
       <c r="G239" t="n">
-        <v>2834</v>
+        <v>3067</v>
       </c>
       <c r="H239" t="n">
-        <v>2839</v>
+        <v>3072</v>
       </c>
       <c r="I239" t="n">
-        <v>2965</v>
+        <v>3185</v>
       </c>
       <c r="J239" t="n">
-        <v>3432</v>
+        <v>3637</v>
       </c>
       <c r="K239" t="n">
-        <v>3789</v>
+        <v>3971</v>
       </c>
       <c r="L239" t="n">
-        <v>4077</v>
+        <v>4248</v>
       </c>
       <c r="M239" t="n">
-        <v>4153</v>
+        <v>4326</v>
       </c>
       <c r="N239" t="n">
-        <v>4118</v>
+        <v>4287</v>
       </c>
       <c r="O239" t="n">
-        <v>4126</v>
+        <v>4272</v>
       </c>
       <c r="P239" t="n">
-        <v>4135</v>
+        <v>4280</v>
       </c>
       <c r="Q239" t="n">
-        <v>4203</v>
+        <v>4347</v>
       </c>
       <c r="R239" t="n">
-        <v>4194</v>
+        <v>4327</v>
       </c>
       <c r="S239" t="n">
-        <v>4173</v>
+        <v>4235</v>
       </c>
       <c r="T239" t="n">
-        <v>4152</v>
+        <v>4139</v>
       </c>
       <c r="U239" t="n">
-        <v>4171</v>
+        <v>4151</v>
       </c>
       <c r="V239" t="n">
-        <v>4298</v>
+        <v>4293</v>
       </c>
       <c r="W239" t="n">
-        <v>4581</v>
+        <v>4548</v>
       </c>
       <c r="X239" t="n">
-        <v>4593</v>
+        <v>4563</v>
       </c>
       <c r="Y239" t="n">
-        <v>4284</v>
+        <v>4258</v>
       </c>
       <c r="Z239" t="n">
-        <v>3970</v>
+        <v>3936</v>
       </c>
       <c r="AA239" t="n">
-        <v>3650</v>
+        <v>3591</v>
       </c>
     </row>
     <row r="240">
@@ -20328,76 +20328,159 @@
         <v>1</v>
       </c>
       <c r="D240" t="n">
-        <v>3202</v>
+        <v>3328</v>
       </c>
       <c r="E240" t="n">
-        <v>2978</v>
+        <v>3173</v>
       </c>
       <c r="F240" t="n">
-        <v>2867</v>
+        <v>3097</v>
       </c>
       <c r="G240" t="n">
-        <v>2822</v>
+        <v>3079</v>
       </c>
       <c r="H240" t="n">
-        <v>2827</v>
+        <v>3083</v>
       </c>
       <c r="I240" t="n">
-        <v>2952</v>
+        <v>3197</v>
       </c>
       <c r="J240" t="n">
-        <v>3417</v>
+        <v>3652</v>
       </c>
       <c r="K240" t="n">
-        <v>3772</v>
+        <v>3988</v>
       </c>
       <c r="L240" t="n">
-        <v>4059</v>
+        <v>4265</v>
       </c>
       <c r="M240" t="n">
-        <v>4135</v>
+        <v>4343</v>
       </c>
       <c r="N240" t="n">
-        <v>4100</v>
+        <v>4305</v>
       </c>
       <c r="O240" t="n">
-        <v>4108</v>
+        <v>4289</v>
       </c>
       <c r="P240" t="n">
-        <v>4116</v>
+        <v>4298</v>
       </c>
       <c r="Q240" t="n">
-        <v>4185</v>
+        <v>4365</v>
       </c>
       <c r="R240" t="n">
-        <v>4175</v>
+        <v>4345</v>
       </c>
       <c r="S240" t="n">
-        <v>4153</v>
+        <v>4255</v>
       </c>
       <c r="T240" t="n">
-        <v>4130</v>
+        <v>4159</v>
       </c>
       <c r="U240" t="n">
-        <v>4150</v>
+        <v>4171</v>
       </c>
       <c r="V240" t="n">
-        <v>4278</v>
+        <v>4312</v>
       </c>
       <c r="W240" t="n">
-        <v>4563</v>
+        <v>4565</v>
       </c>
       <c r="X240" t="n">
-        <v>4575</v>
+        <v>4580</v>
       </c>
       <c r="Y240" t="n">
-        <v>4268</v>
+        <v>4273</v>
       </c>
       <c r="Z240" t="n">
-        <v>3956</v>
+        <v>3949</v>
       </c>
       <c r="AA240" t="n">
-        <v>3638</v>
+        <v>3602</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B241" t="n">
+        <v>10</v>
+      </c>
+      <c r="C241" t="n">
+        <v>2</v>
+      </c>
+      <c r="D241" t="n">
+        <v>3342</v>
+      </c>
+      <c r="E241" t="n">
+        <v>3189</v>
+      </c>
+      <c r="F241" t="n">
+        <v>3115</v>
+      </c>
+      <c r="G241" t="n">
+        <v>3097</v>
+      </c>
+      <c r="H241" t="n">
+        <v>3101</v>
+      </c>
+      <c r="I241" t="n">
+        <v>3216</v>
+      </c>
+      <c r="J241" t="n">
+        <v>3673</v>
+      </c>
+      <c r="K241" t="n">
+        <v>4012</v>
+      </c>
+      <c r="L241" t="n">
+        <v>4291</v>
+      </c>
+      <c r="M241" t="n">
+        <v>4370</v>
+      </c>
+      <c r="N241" t="n">
+        <v>4331</v>
+      </c>
+      <c r="O241" t="n">
+        <v>4316</v>
+      </c>
+      <c r="P241" t="n">
+        <v>4324</v>
+      </c>
+      <c r="Q241" t="n">
+        <v>4392</v>
+      </c>
+      <c r="R241" t="n">
+        <v>4373</v>
+      </c>
+      <c r="S241" t="n">
+        <v>4284</v>
+      </c>
+      <c r="T241" t="n">
+        <v>4190</v>
+      </c>
+      <c r="U241" t="n">
+        <v>4200</v>
+      </c>
+      <c r="V241" t="n">
+        <v>4312</v>
+      </c>
+      <c r="W241" t="n">
+        <v>4514</v>
+      </c>
+      <c r="X241" t="n">
+        <v>4525</v>
+      </c>
+      <c r="Y241" t="n">
+        <v>4226</v>
+      </c>
+      <c r="Z241" t="n">
+        <v>3910</v>
+      </c>
+      <c r="AA241" t="n">
+        <v>3572</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA241"/>
+  <dimension ref="A1:AA242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20079,76 +20079,76 @@
         <v>28</v>
       </c>
       <c r="D237" t="n">
-        <v>3271</v>
+        <v>3304</v>
       </c>
       <c r="E237" t="n">
-        <v>3107</v>
+        <v>3088</v>
       </c>
       <c r="F237" t="n">
-        <v>3031</v>
+        <v>2988</v>
       </c>
       <c r="G237" t="n">
-        <v>2995</v>
+        <v>2940</v>
       </c>
       <c r="H237" t="n">
-        <v>2994</v>
+        <v>2938</v>
       </c>
       <c r="I237" t="n">
-        <v>3111</v>
+        <v>3056</v>
       </c>
       <c r="J237" t="n">
-        <v>3495</v>
+        <v>3438</v>
       </c>
       <c r="K237" t="n">
-        <v>3785</v>
+        <v>3728</v>
       </c>
       <c r="L237" t="n">
-        <v>4012</v>
+        <v>3954</v>
       </c>
       <c r="M237" t="n">
-        <v>4118</v>
+        <v>4060</v>
       </c>
       <c r="N237" t="n">
-        <v>4145</v>
+        <v>4087</v>
       </c>
       <c r="O237" t="n">
-        <v>4213</v>
+        <v>4155</v>
       </c>
       <c r="P237" t="n">
-        <v>4325</v>
+        <v>4267</v>
       </c>
       <c r="Q237" t="n">
-        <v>4364</v>
+        <v>4305</v>
       </c>
       <c r="R237" t="n">
-        <v>4391</v>
+        <v>4294</v>
       </c>
       <c r="S237" t="n">
-        <v>4296</v>
+        <v>4333</v>
       </c>
       <c r="T237" t="n">
-        <v>4180</v>
+        <v>4382</v>
       </c>
       <c r="U237" t="n">
-        <v>4160</v>
+        <v>4390</v>
       </c>
       <c r="V237" t="n">
-        <v>4248</v>
+        <v>4398</v>
       </c>
       <c r="W237" t="n">
-        <v>4568</v>
+        <v>4427</v>
       </c>
       <c r="X237" t="n">
-        <v>4492</v>
+        <v>4361</v>
       </c>
       <c r="Y237" t="n">
-        <v>4160</v>
+        <v>4067</v>
       </c>
       <c r="Z237" t="n">
-        <v>3934</v>
+        <v>3868</v>
       </c>
       <c r="AA237" t="n">
-        <v>3676</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="238">
@@ -20162,76 +20162,76 @@
         <v>29</v>
       </c>
       <c r="D238" t="n">
-        <v>3325</v>
+        <v>3354</v>
       </c>
       <c r="E238" t="n">
-        <v>3167</v>
+        <v>3141</v>
       </c>
       <c r="F238" t="n">
-        <v>3089</v>
+        <v>3039</v>
       </c>
       <c r="G238" t="n">
-        <v>3071</v>
+        <v>3013</v>
       </c>
       <c r="H238" t="n">
-        <v>3075</v>
+        <v>3014</v>
       </c>
       <c r="I238" t="n">
-        <v>3189</v>
+        <v>3123</v>
       </c>
       <c r="J238" t="n">
-        <v>3644</v>
+        <v>3571</v>
       </c>
       <c r="K238" t="n">
-        <v>3981</v>
+        <v>3906</v>
       </c>
       <c r="L238" t="n">
-        <v>4259</v>
+        <v>4197</v>
       </c>
       <c r="M238" t="n">
+        <v>4279</v>
+      </c>
+      <c r="N238" t="n">
+        <v>4238</v>
+      </c>
+      <c r="O238" t="n">
+        <v>4219</v>
+      </c>
+      <c r="P238" t="n">
+        <v>4227</v>
+      </c>
+      <c r="Q238" t="n">
+        <v>4294</v>
+      </c>
+      <c r="R238" t="n">
+        <v>4301</v>
+      </c>
+      <c r="S238" t="n">
         <v>4338</v>
       </c>
-      <c r="N238" t="n">
-        <v>4299</v>
-      </c>
-      <c r="O238" t="n">
-        <v>4284</v>
-      </c>
-      <c r="P238" t="n">
-        <v>4292</v>
-      </c>
-      <c r="Q238" t="n">
-        <v>4359</v>
-      </c>
-      <c r="R238" t="n">
-        <v>4340</v>
-      </c>
-      <c r="S238" t="n">
-        <v>4250</v>
-      </c>
       <c r="T238" t="n">
-        <v>4154</v>
+        <v>4376</v>
       </c>
       <c r="U238" t="n">
-        <v>4166</v>
+        <v>4378</v>
       </c>
       <c r="V238" t="n">
-        <v>4304</v>
+        <v>4394</v>
       </c>
       <c r="W238" t="n">
-        <v>4552</v>
+        <v>4423</v>
       </c>
       <c r="X238" t="n">
-        <v>4566</v>
+        <v>4424</v>
       </c>
       <c r="Y238" t="n">
-        <v>4262</v>
+        <v>4172</v>
       </c>
       <c r="Z238" t="n">
-        <v>3940</v>
+        <v>3903</v>
       </c>
       <c r="AA238" t="n">
-        <v>3595</v>
+        <v>3616</v>
       </c>
     </row>
     <row r="239">
@@ -20245,76 +20245,76 @@
         <v>30</v>
       </c>
       <c r="D239" t="n">
-        <v>3318</v>
+        <v>3356</v>
       </c>
       <c r="E239" t="n">
-        <v>3162</v>
+        <v>3142</v>
       </c>
       <c r="F239" t="n">
-        <v>3086</v>
+        <v>3040</v>
       </c>
       <c r="G239" t="n">
-        <v>3067</v>
+        <v>3014</v>
       </c>
       <c r="H239" t="n">
-        <v>3072</v>
+        <v>3015</v>
       </c>
       <c r="I239" t="n">
-        <v>3185</v>
+        <v>3124</v>
       </c>
       <c r="J239" t="n">
-        <v>3637</v>
+        <v>3573</v>
       </c>
       <c r="K239" t="n">
-        <v>3971</v>
+        <v>3909</v>
       </c>
       <c r="L239" t="n">
-        <v>4248</v>
+        <v>4200</v>
       </c>
       <c r="M239" t="n">
-        <v>4326</v>
+        <v>4282</v>
       </c>
       <c r="N239" t="n">
-        <v>4287</v>
+        <v>4241</v>
       </c>
       <c r="O239" t="n">
-        <v>4272</v>
+        <v>4222</v>
       </c>
       <c r="P239" t="n">
-        <v>4280</v>
+        <v>4230</v>
       </c>
       <c r="Q239" t="n">
-        <v>4347</v>
+        <v>4297</v>
       </c>
       <c r="R239" t="n">
-        <v>4327</v>
+        <v>4304</v>
       </c>
       <c r="S239" t="n">
-        <v>4235</v>
+        <v>4342</v>
       </c>
       <c r="T239" t="n">
-        <v>4139</v>
+        <v>4380</v>
       </c>
       <c r="U239" t="n">
-        <v>4151</v>
+        <v>4382</v>
       </c>
       <c r="V239" t="n">
-        <v>4293</v>
+        <v>4397</v>
       </c>
       <c r="W239" t="n">
-        <v>4548</v>
+        <v>4424</v>
       </c>
       <c r="X239" t="n">
-        <v>4563</v>
+        <v>4425</v>
       </c>
       <c r="Y239" t="n">
-        <v>4258</v>
+        <v>4173</v>
       </c>
       <c r="Z239" t="n">
-        <v>3936</v>
+        <v>3904</v>
       </c>
       <c r="AA239" t="n">
-        <v>3591</v>
+        <v>3617</v>
       </c>
     </row>
     <row r="240">
@@ -20328,76 +20328,76 @@
         <v>1</v>
       </c>
       <c r="D240" t="n">
-        <v>3328</v>
+        <v>3398</v>
       </c>
       <c r="E240" t="n">
-        <v>3173</v>
+        <v>3190</v>
       </c>
       <c r="F240" t="n">
-        <v>3097</v>
+        <v>3091</v>
       </c>
       <c r="G240" t="n">
-        <v>3079</v>
+        <v>3066</v>
       </c>
       <c r="H240" t="n">
-        <v>3083</v>
+        <v>3067</v>
       </c>
       <c r="I240" t="n">
-        <v>3197</v>
+        <v>3179</v>
       </c>
       <c r="J240" t="n">
-        <v>3652</v>
+        <v>3637</v>
       </c>
       <c r="K240" t="n">
-        <v>3988</v>
+        <v>3980</v>
       </c>
       <c r="L240" t="n">
-        <v>4265</v>
+        <v>4277</v>
       </c>
       <c r="M240" t="n">
-        <v>4343</v>
+        <v>4361</v>
       </c>
       <c r="N240" t="n">
-        <v>4305</v>
+        <v>4319</v>
       </c>
       <c r="O240" t="n">
-        <v>4289</v>
+        <v>4300</v>
       </c>
       <c r="P240" t="n">
-        <v>4298</v>
+        <v>4309</v>
       </c>
       <c r="Q240" t="n">
-        <v>4365</v>
+        <v>4377</v>
       </c>
       <c r="R240" t="n">
-        <v>4345</v>
+        <v>4385</v>
       </c>
       <c r="S240" t="n">
-        <v>4255</v>
+        <v>4428</v>
       </c>
       <c r="T240" t="n">
-        <v>4159</v>
+        <v>4471</v>
       </c>
       <c r="U240" t="n">
-        <v>4171</v>
+        <v>4472</v>
       </c>
       <c r="V240" t="n">
-        <v>4312</v>
+        <v>4482</v>
       </c>
       <c r="W240" t="n">
-        <v>4565</v>
+        <v>4500</v>
       </c>
       <c r="X240" t="n">
-        <v>4580</v>
+        <v>4500</v>
       </c>
       <c r="Y240" t="n">
-        <v>4273</v>
+        <v>4241</v>
       </c>
       <c r="Z240" t="n">
-        <v>3949</v>
+        <v>3965</v>
       </c>
       <c r="AA240" t="n">
-        <v>3602</v>
+        <v>3669</v>
       </c>
     </row>
     <row r="241">
@@ -20411,76 +20411,159 @@
         <v>2</v>
       </c>
       <c r="D241" t="n">
-        <v>3342</v>
+        <v>3427</v>
       </c>
       <c r="E241" t="n">
-        <v>3189</v>
+        <v>3224</v>
       </c>
       <c r="F241" t="n">
-        <v>3115</v>
+        <v>3126</v>
       </c>
       <c r="G241" t="n">
-        <v>3097</v>
+        <v>3102</v>
       </c>
       <c r="H241" t="n">
-        <v>3101</v>
+        <v>3103</v>
       </c>
       <c r="I241" t="n">
         <v>3216</v>
       </c>
       <c r="J241" t="n">
-        <v>3673</v>
+        <v>3681</v>
       </c>
       <c r="K241" t="n">
-        <v>4012</v>
+        <v>4029</v>
       </c>
       <c r="L241" t="n">
-        <v>4291</v>
+        <v>4331</v>
       </c>
       <c r="M241" t="n">
-        <v>4370</v>
+        <v>4416</v>
       </c>
       <c r="N241" t="n">
-        <v>4331</v>
+        <v>4373</v>
       </c>
       <c r="O241" t="n">
-        <v>4316</v>
+        <v>4354</v>
       </c>
       <c r="P241" t="n">
-        <v>4324</v>
+        <v>4362</v>
       </c>
       <c r="Q241" t="n">
-        <v>4392</v>
+        <v>4432</v>
       </c>
       <c r="R241" t="n">
-        <v>4373</v>
+        <v>4441</v>
       </c>
       <c r="S241" t="n">
-        <v>4284</v>
+        <v>4487</v>
       </c>
       <c r="T241" t="n">
-        <v>4190</v>
+        <v>4534</v>
       </c>
       <c r="U241" t="n">
-        <v>4200</v>
+        <v>4535</v>
       </c>
       <c r="V241" t="n">
-        <v>4312</v>
+        <v>4549</v>
       </c>
       <c r="W241" t="n">
-        <v>4514</v>
+        <v>4572</v>
       </c>
       <c r="X241" t="n">
-        <v>4525</v>
+        <v>4572</v>
       </c>
       <c r="Y241" t="n">
-        <v>4226</v>
+        <v>4287</v>
       </c>
       <c r="Z241" t="n">
+        <v>3982</v>
+      </c>
+      <c r="AA241" t="n">
+        <v>3657</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B242" t="n">
+        <v>10</v>
+      </c>
+      <c r="C242" t="n">
+        <v>3</v>
+      </c>
+      <c r="D242" t="n">
+        <v>3406</v>
+      </c>
+      <c r="E242" t="n">
+        <v>3211</v>
+      </c>
+      <c r="F242" t="n">
+        <v>3100</v>
+      </c>
+      <c r="G242" t="n">
+        <v>3046</v>
+      </c>
+      <c r="H242" t="n">
+        <v>3025</v>
+      </c>
+      <c r="I242" t="n">
+        <v>3068</v>
+      </c>
+      <c r="J242" t="n">
+        <v>3249</v>
+      </c>
+      <c r="K242" t="n">
+        <v>3458</v>
+      </c>
+      <c r="L242" t="n">
+        <v>3741</v>
+      </c>
+      <c r="M242" t="n">
         <v>3910</v>
       </c>
-      <c r="AA241" t="n">
-        <v>3572</v>
+      <c r="N242" t="n">
+        <v>3966</v>
+      </c>
+      <c r="O242" t="n">
+        <v>4016</v>
+      </c>
+      <c r="P242" t="n">
+        <v>4092</v>
+      </c>
+      <c r="Q242" t="n">
+        <v>4232</v>
+      </c>
+      <c r="R242" t="n">
+        <v>4281</v>
+      </c>
+      <c r="S242" t="n">
+        <v>4345</v>
+      </c>
+      <c r="T242" t="n">
+        <v>4315</v>
+      </c>
+      <c r="U242" t="n">
+        <v>4313</v>
+      </c>
+      <c r="V242" t="n">
+        <v>4315</v>
+      </c>
+      <c r="W242" t="n">
+        <v>4356</v>
+      </c>
+      <c r="X242" t="n">
+        <v>4257</v>
+      </c>
+      <c r="Y242" t="n">
+        <v>4107</v>
+      </c>
+      <c r="Z242" t="n">
+        <v>3810</v>
+      </c>
+      <c r="AA242" t="n">
+        <v>3546</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA242"/>
+  <dimension ref="A1:AA243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20162,76 +20162,76 @@
         <v>29</v>
       </c>
       <c r="D238" t="n">
-        <v>3354</v>
+        <v>3188</v>
       </c>
       <c r="E238" t="n">
-        <v>3141</v>
+        <v>3002</v>
       </c>
       <c r="F238" t="n">
-        <v>3039</v>
+        <v>2913</v>
       </c>
       <c r="G238" t="n">
-        <v>3013</v>
+        <v>2893</v>
       </c>
       <c r="H238" t="n">
-        <v>3014</v>
+        <v>2894</v>
       </c>
       <c r="I238" t="n">
-        <v>3123</v>
+        <v>3003</v>
       </c>
       <c r="J238" t="n">
-        <v>3571</v>
+        <v>3474</v>
       </c>
       <c r="K238" t="n">
-        <v>3906</v>
+        <v>3836</v>
       </c>
       <c r="L238" t="n">
-        <v>4197</v>
+        <v>4160</v>
       </c>
       <c r="M238" t="n">
-        <v>4279</v>
+        <v>4258</v>
       </c>
       <c r="N238" t="n">
-        <v>4238</v>
+        <v>4216</v>
       </c>
       <c r="O238" t="n">
-        <v>4219</v>
+        <v>4192</v>
       </c>
       <c r="P238" t="n">
-        <v>4227</v>
+        <v>4206</v>
       </c>
       <c r="Q238" t="n">
-        <v>4294</v>
+        <v>4284</v>
       </c>
       <c r="R238" t="n">
-        <v>4301</v>
+        <v>4253</v>
       </c>
       <c r="S238" t="n">
-        <v>4338</v>
+        <v>4140</v>
       </c>
       <c r="T238" t="n">
-        <v>4376</v>
+        <v>4008</v>
       </c>
       <c r="U238" t="n">
-        <v>4378</v>
+        <v>4017</v>
       </c>
       <c r="V238" t="n">
-        <v>4394</v>
+        <v>4133</v>
       </c>
       <c r="W238" t="n">
-        <v>4423</v>
+        <v>4323</v>
       </c>
       <c r="X238" t="n">
-        <v>4424</v>
+        <v>4322</v>
       </c>
       <c r="Y238" t="n">
-        <v>4172</v>
+        <v>4089</v>
       </c>
       <c r="Z238" t="n">
-        <v>3903</v>
+        <v>3842</v>
       </c>
       <c r="AA238" t="n">
-        <v>3616</v>
+        <v>3574</v>
       </c>
     </row>
     <row r="239">
@@ -20245,76 +20245,76 @@
         <v>30</v>
       </c>
       <c r="D239" t="n">
-        <v>3356</v>
+        <v>3192</v>
       </c>
       <c r="E239" t="n">
-        <v>3142</v>
+        <v>3005</v>
       </c>
       <c r="F239" t="n">
-        <v>3040</v>
+        <v>2915</v>
       </c>
       <c r="G239" t="n">
-        <v>3014</v>
+        <v>2895</v>
       </c>
       <c r="H239" t="n">
-        <v>3015</v>
+        <v>2896</v>
       </c>
       <c r="I239" t="n">
-        <v>3124</v>
+        <v>3006</v>
       </c>
       <c r="J239" t="n">
-        <v>3573</v>
+        <v>3478</v>
       </c>
       <c r="K239" t="n">
-        <v>3909</v>
+        <v>3841</v>
       </c>
       <c r="L239" t="n">
-        <v>4200</v>
+        <v>4167</v>
       </c>
       <c r="M239" t="n">
-        <v>4282</v>
+        <v>4265</v>
       </c>
       <c r="N239" t="n">
-        <v>4241</v>
+        <v>4223</v>
       </c>
       <c r="O239" t="n">
-        <v>4222</v>
+        <v>4199</v>
       </c>
       <c r="P239" t="n">
-        <v>4230</v>
+        <v>4213</v>
       </c>
       <c r="Q239" t="n">
-        <v>4297</v>
+        <v>4291</v>
       </c>
       <c r="R239" t="n">
-        <v>4304</v>
+        <v>4260</v>
       </c>
       <c r="S239" t="n">
-        <v>4342</v>
+        <v>4148</v>
       </c>
       <c r="T239" t="n">
-        <v>4380</v>
+        <v>4017</v>
       </c>
       <c r="U239" t="n">
-        <v>4382</v>
+        <v>4026</v>
       </c>
       <c r="V239" t="n">
-        <v>4397</v>
+        <v>4138</v>
       </c>
       <c r="W239" t="n">
-        <v>4424</v>
+        <v>4322</v>
       </c>
       <c r="X239" t="n">
-        <v>4425</v>
+        <v>4322</v>
       </c>
       <c r="Y239" t="n">
-        <v>4173</v>
+        <v>4089</v>
       </c>
       <c r="Z239" t="n">
-        <v>3904</v>
+        <v>3843</v>
       </c>
       <c r="AA239" t="n">
-        <v>3617</v>
+        <v>3576</v>
       </c>
     </row>
     <row r="240">
@@ -20328,76 +20328,76 @@
         <v>1</v>
       </c>
       <c r="D240" t="n">
-        <v>3398</v>
+        <v>3240</v>
       </c>
       <c r="E240" t="n">
-        <v>3190</v>
+        <v>3060</v>
       </c>
       <c r="F240" t="n">
-        <v>3091</v>
+        <v>2973</v>
       </c>
       <c r="G240" t="n">
-        <v>3066</v>
+        <v>2954</v>
       </c>
       <c r="H240" t="n">
+        <v>2955</v>
+      </c>
+      <c r="I240" t="n">
         <v>3067</v>
       </c>
-      <c r="I240" t="n">
-        <v>3179</v>
-      </c>
       <c r="J240" t="n">
-        <v>3637</v>
+        <v>3550</v>
       </c>
       <c r="K240" t="n">
-        <v>3980</v>
+        <v>3922</v>
       </c>
       <c r="L240" t="n">
-        <v>4277</v>
+        <v>4255</v>
       </c>
       <c r="M240" t="n">
-        <v>4361</v>
+        <v>4355</v>
       </c>
       <c r="N240" t="n">
-        <v>4319</v>
+        <v>4312</v>
       </c>
       <c r="O240" t="n">
-        <v>4300</v>
+        <v>4287</v>
       </c>
       <c r="P240" t="n">
-        <v>4309</v>
+        <v>4302</v>
       </c>
       <c r="Q240" t="n">
-        <v>4377</v>
+        <v>4382</v>
       </c>
       <c r="R240" t="n">
-        <v>4385</v>
+        <v>4352</v>
       </c>
       <c r="S240" t="n">
-        <v>4428</v>
+        <v>4245</v>
       </c>
       <c r="T240" t="n">
-        <v>4471</v>
+        <v>4121</v>
       </c>
       <c r="U240" t="n">
-        <v>4472</v>
+        <v>4129</v>
       </c>
       <c r="V240" t="n">
-        <v>4482</v>
+        <v>4235</v>
       </c>
       <c r="W240" t="n">
-        <v>4500</v>
+        <v>4409</v>
       </c>
       <c r="X240" t="n">
-        <v>4500</v>
+        <v>4408</v>
       </c>
       <c r="Y240" t="n">
-        <v>4241</v>
+        <v>4167</v>
       </c>
       <c r="Z240" t="n">
-        <v>3965</v>
+        <v>3912</v>
       </c>
       <c r="AA240" t="n">
-        <v>3669</v>
+        <v>3635</v>
       </c>
     </row>
     <row r="241">
@@ -20411,76 +20411,76 @@
         <v>2</v>
       </c>
       <c r="D241" t="n">
-        <v>3427</v>
+        <v>3271</v>
       </c>
       <c r="E241" t="n">
-        <v>3224</v>
+        <v>3095</v>
       </c>
       <c r="F241" t="n">
-        <v>3126</v>
+        <v>3011</v>
       </c>
       <c r="G241" t="n">
-        <v>3102</v>
+        <v>2992</v>
       </c>
       <c r="H241" t="n">
-        <v>3103</v>
+        <v>2993</v>
       </c>
       <c r="I241" t="n">
-        <v>3216</v>
+        <v>3107</v>
       </c>
       <c r="J241" t="n">
-        <v>3681</v>
+        <v>3597</v>
       </c>
       <c r="K241" t="n">
-        <v>4029</v>
+        <v>3973</v>
       </c>
       <c r="L241" t="n">
-        <v>4331</v>
+        <v>4311</v>
       </c>
       <c r="M241" t="n">
-        <v>4416</v>
+        <v>4413</v>
       </c>
       <c r="N241" t="n">
-        <v>4373</v>
+        <v>4369</v>
       </c>
       <c r="O241" t="n">
-        <v>4354</v>
+        <v>4344</v>
       </c>
       <c r="P241" t="n">
-        <v>4362</v>
+        <v>4359</v>
       </c>
       <c r="Q241" t="n">
-        <v>4432</v>
+        <v>4440</v>
       </c>
       <c r="R241" t="n">
-        <v>4441</v>
+        <v>4411</v>
       </c>
       <c r="S241" t="n">
-        <v>4487</v>
+        <v>4308</v>
       </c>
       <c r="T241" t="n">
-        <v>4534</v>
+        <v>4188</v>
       </c>
       <c r="U241" t="n">
-        <v>4535</v>
+        <v>4193</v>
       </c>
       <c r="V241" t="n">
-        <v>4549</v>
+        <v>4266</v>
       </c>
       <c r="W241" t="n">
-        <v>4572</v>
+        <v>4385</v>
       </c>
       <c r="X241" t="n">
-        <v>4572</v>
+        <v>4384</v>
       </c>
       <c r="Y241" t="n">
-        <v>4287</v>
+        <v>4147</v>
       </c>
       <c r="Z241" t="n">
-        <v>3982</v>
+        <v>3897</v>
       </c>
       <c r="AA241" t="n">
-        <v>3657</v>
+        <v>3625</v>
       </c>
     </row>
     <row r="242">
@@ -20494,76 +20494,159 @@
         <v>3</v>
       </c>
       <c r="D242" t="n">
-        <v>3406</v>
+        <v>3265</v>
       </c>
       <c r="E242" t="n">
-        <v>3211</v>
+        <v>3097</v>
       </c>
       <c r="F242" t="n">
-        <v>3100</v>
+        <v>3000</v>
       </c>
       <c r="G242" t="n">
-        <v>3046</v>
+        <v>2953</v>
       </c>
       <c r="H242" t="n">
-        <v>3025</v>
+        <v>2935</v>
       </c>
       <c r="I242" t="n">
-        <v>3068</v>
+        <v>2983</v>
       </c>
       <c r="J242" t="n">
-        <v>3249</v>
+        <v>3185</v>
       </c>
       <c r="K242" t="n">
-        <v>3458</v>
+        <v>3420</v>
       </c>
       <c r="L242" t="n">
-        <v>3741</v>
+        <v>3736</v>
       </c>
       <c r="M242" t="n">
-        <v>3910</v>
+        <v>3925</v>
       </c>
       <c r="N242" t="n">
-        <v>3966</v>
+        <v>3988</v>
       </c>
       <c r="O242" t="n">
-        <v>4016</v>
+        <v>4044</v>
       </c>
       <c r="P242" t="n">
-        <v>4092</v>
+        <v>4129</v>
       </c>
       <c r="Q242" t="n">
-        <v>4232</v>
+        <v>4007</v>
       </c>
       <c r="R242" t="n">
-        <v>4281</v>
+        <v>3964</v>
       </c>
       <c r="S242" t="n">
-        <v>4345</v>
+        <v>4165</v>
       </c>
       <c r="T242" t="n">
-        <v>4315</v>
+        <v>4069</v>
       </c>
       <c r="U242" t="n">
-        <v>4313</v>
+        <v>4063</v>
       </c>
       <c r="V242" t="n">
-        <v>4315</v>
+        <v>4070</v>
       </c>
       <c r="W242" t="n">
-        <v>4356</v>
+        <v>4197</v>
       </c>
       <c r="X242" t="n">
-        <v>4257</v>
+        <v>4116</v>
       </c>
       <c r="Y242" t="n">
-        <v>4107</v>
+        <v>3993</v>
       </c>
       <c r="Z242" t="n">
-        <v>3810</v>
+        <v>3750</v>
       </c>
       <c r="AA242" t="n">
-        <v>3546</v>
+        <v>3533</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B243" t="n">
+        <v>10</v>
+      </c>
+      <c r="C243" t="n">
+        <v>4</v>
+      </c>
+      <c r="D243" t="n">
+        <v>3219</v>
+      </c>
+      <c r="E243" t="n">
+        <v>3072</v>
+      </c>
+      <c r="F243" t="n">
+        <v>2979</v>
+      </c>
+      <c r="G243" t="n">
+        <v>2930</v>
+      </c>
+      <c r="H243" t="n">
+        <v>2899</v>
+      </c>
+      <c r="I243" t="n">
+        <v>2907</v>
+      </c>
+      <c r="J243" t="n">
+        <v>3094</v>
+      </c>
+      <c r="K243" t="n">
+        <v>3306</v>
+      </c>
+      <c r="L243" t="n">
+        <v>3585</v>
+      </c>
+      <c r="M243" t="n">
+        <v>3787</v>
+      </c>
+      <c r="N243" t="n">
+        <v>3914</v>
+      </c>
+      <c r="O243" t="n">
+        <v>3960</v>
+      </c>
+      <c r="P243" t="n">
+        <v>4128</v>
+      </c>
+      <c r="Q243" t="n">
+        <v>4139</v>
+      </c>
+      <c r="R243" t="n">
+        <v>4106</v>
+      </c>
+      <c r="S243" t="n">
+        <v>4078</v>
+      </c>
+      <c r="T243" t="n">
+        <v>4045</v>
+      </c>
+      <c r="U243" t="n">
+        <v>4064</v>
+      </c>
+      <c r="V243" t="n">
+        <v>4170</v>
+      </c>
+      <c r="W243" t="n">
+        <v>4434</v>
+      </c>
+      <c r="X243" t="n">
+        <v>4396</v>
+      </c>
+      <c r="Y243" t="n">
+        <v>4242</v>
+      </c>
+      <c r="Z243" t="n">
+        <v>3917</v>
+      </c>
+      <c r="AA243" t="n">
+        <v>3638</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA243"/>
+  <dimension ref="A1:AA244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20245,76 +20245,76 @@
         <v>30</v>
       </c>
       <c r="D239" t="n">
-        <v>3192</v>
+        <v>3231</v>
       </c>
       <c r="E239" t="n">
-        <v>3005</v>
+        <v>3028</v>
       </c>
       <c r="F239" t="n">
-        <v>2915</v>
+        <v>2933</v>
       </c>
       <c r="G239" t="n">
-        <v>2895</v>
+        <v>2909</v>
       </c>
       <c r="H239" t="n">
-        <v>2896</v>
+        <v>2916</v>
       </c>
       <c r="I239" t="n">
-        <v>3006</v>
+        <v>3009</v>
       </c>
       <c r="J239" t="n">
-        <v>3478</v>
+        <v>3386</v>
       </c>
       <c r="K239" t="n">
-        <v>3841</v>
+        <v>3690</v>
       </c>
       <c r="L239" t="n">
-        <v>4167</v>
+        <v>3983</v>
       </c>
       <c r="M239" t="n">
-        <v>4265</v>
+        <v>4086</v>
       </c>
       <c r="N239" t="n">
-        <v>4223</v>
+        <v>4061</v>
       </c>
       <c r="O239" t="n">
-        <v>4199</v>
+        <v>4055</v>
       </c>
       <c r="P239" t="n">
-        <v>4213</v>
+        <v>4077</v>
       </c>
       <c r="Q239" t="n">
-        <v>4291</v>
+        <v>4123</v>
       </c>
       <c r="R239" t="n">
-        <v>4260</v>
+        <v>3990</v>
       </c>
       <c r="S239" t="n">
-        <v>4148</v>
+        <v>3886</v>
       </c>
       <c r="T239" t="n">
-        <v>4017</v>
+        <v>3733</v>
       </c>
       <c r="U239" t="n">
-        <v>4026</v>
+        <v>3761</v>
       </c>
       <c r="V239" t="n">
-        <v>4138</v>
+        <v>3937</v>
       </c>
       <c r="W239" t="n">
-        <v>4322</v>
+        <v>4324</v>
       </c>
       <c r="X239" t="n">
-        <v>4322</v>
+        <v>4306</v>
       </c>
       <c r="Y239" t="n">
-        <v>4089</v>
+        <v>4098</v>
       </c>
       <c r="Z239" t="n">
-        <v>3843</v>
+        <v>3873</v>
       </c>
       <c r="AA239" t="n">
-        <v>3576</v>
+        <v>3645</v>
       </c>
     </row>
     <row r="240">
@@ -20328,76 +20328,76 @@
         <v>1</v>
       </c>
       <c r="D240" t="n">
-        <v>3240</v>
+        <v>3276</v>
       </c>
       <c r="E240" t="n">
-        <v>3060</v>
+        <v>3079</v>
       </c>
       <c r="F240" t="n">
-        <v>2973</v>
+        <v>2986</v>
       </c>
       <c r="G240" t="n">
-        <v>2954</v>
+        <v>2963</v>
       </c>
       <c r="H240" t="n">
-        <v>2955</v>
+        <v>2970</v>
       </c>
       <c r="I240" t="n">
-        <v>3067</v>
+        <v>3066</v>
       </c>
       <c r="J240" t="n">
-        <v>3550</v>
+        <v>3452</v>
       </c>
       <c r="K240" t="n">
-        <v>3922</v>
+        <v>3764</v>
       </c>
       <c r="L240" t="n">
-        <v>4255</v>
+        <v>4063</v>
       </c>
       <c r="M240" t="n">
-        <v>4355</v>
+        <v>4168</v>
       </c>
       <c r="N240" t="n">
-        <v>4312</v>
+        <v>4143</v>
       </c>
       <c r="O240" t="n">
-        <v>4287</v>
+        <v>4137</v>
       </c>
       <c r="P240" t="n">
-        <v>4302</v>
+        <v>4160</v>
       </c>
       <c r="Q240" t="n">
-        <v>4382</v>
+        <v>4207</v>
       </c>
       <c r="R240" t="n">
-        <v>4352</v>
+        <v>4078</v>
       </c>
       <c r="S240" t="n">
-        <v>4245</v>
+        <v>3977</v>
       </c>
       <c r="T240" t="n">
-        <v>4121</v>
+        <v>3829</v>
       </c>
       <c r="U240" t="n">
-        <v>4129</v>
+        <v>3856</v>
       </c>
       <c r="V240" t="n">
-        <v>4235</v>
+        <v>4028</v>
       </c>
       <c r="W240" t="n">
-        <v>4409</v>
+        <v>4404</v>
       </c>
       <c r="X240" t="n">
-        <v>4408</v>
+        <v>4386</v>
       </c>
       <c r="Y240" t="n">
-        <v>4167</v>
+        <v>4170</v>
       </c>
       <c r="Z240" t="n">
-        <v>3912</v>
+        <v>3936</v>
       </c>
       <c r="AA240" t="n">
-        <v>3635</v>
+        <v>3699</v>
       </c>
     </row>
     <row r="241">
@@ -20411,76 +20411,76 @@
         <v>2</v>
       </c>
       <c r="D241" t="n">
-        <v>3271</v>
+        <v>3303</v>
       </c>
       <c r="E241" t="n">
-        <v>3095</v>
+        <v>3110</v>
       </c>
       <c r="F241" t="n">
-        <v>3011</v>
+        <v>3019</v>
       </c>
       <c r="G241" t="n">
-        <v>2992</v>
+        <v>2996</v>
       </c>
       <c r="H241" t="n">
-        <v>2993</v>
+        <v>3004</v>
       </c>
       <c r="I241" t="n">
-        <v>3107</v>
+        <v>3100</v>
       </c>
       <c r="J241" t="n">
-        <v>3597</v>
+        <v>3492</v>
       </c>
       <c r="K241" t="n">
-        <v>3973</v>
+        <v>3808</v>
       </c>
       <c r="L241" t="n">
-        <v>4311</v>
+        <v>4112</v>
       </c>
       <c r="M241" t="n">
-        <v>4413</v>
+        <v>4219</v>
       </c>
       <c r="N241" t="n">
-        <v>4369</v>
+        <v>4193</v>
       </c>
       <c r="O241" t="n">
-        <v>4344</v>
+        <v>4187</v>
       </c>
       <c r="P241" t="n">
-        <v>4359</v>
+        <v>4210</v>
       </c>
       <c r="Q241" t="n">
-        <v>4440</v>
+        <v>4258</v>
       </c>
       <c r="R241" t="n">
-        <v>4411</v>
+        <v>4132</v>
       </c>
       <c r="S241" t="n">
-        <v>4308</v>
+        <v>4032</v>
       </c>
       <c r="T241" t="n">
-        <v>4188</v>
+        <v>3887</v>
       </c>
       <c r="U241" t="n">
-        <v>4193</v>
+        <v>3910</v>
       </c>
       <c r="V241" t="n">
-        <v>4266</v>
+        <v>4055</v>
       </c>
       <c r="W241" t="n">
-        <v>4385</v>
+        <v>4373</v>
       </c>
       <c r="X241" t="n">
-        <v>4384</v>
+        <v>4355</v>
       </c>
       <c r="Y241" t="n">
-        <v>4147</v>
+        <v>4144</v>
       </c>
       <c r="Z241" t="n">
-        <v>3897</v>
+        <v>3916</v>
       </c>
       <c r="AA241" t="n">
-        <v>3625</v>
+        <v>3684</v>
       </c>
     </row>
     <row r="242">
@@ -20494,76 +20494,76 @@
         <v>3</v>
       </c>
       <c r="D242" t="n">
-        <v>3265</v>
+        <v>3296</v>
       </c>
       <c r="E242" t="n">
-        <v>3097</v>
+        <v>3107</v>
       </c>
       <c r="F242" t="n">
-        <v>3000</v>
+        <v>3005</v>
       </c>
       <c r="G242" t="n">
-        <v>2953</v>
+        <v>2957</v>
       </c>
       <c r="H242" t="n">
-        <v>2935</v>
+        <v>2939</v>
       </c>
       <c r="I242" t="n">
-        <v>2983</v>
+        <v>2979</v>
       </c>
       <c r="J242" t="n">
-        <v>3185</v>
+        <v>3126</v>
       </c>
       <c r="K242" t="n">
-        <v>3420</v>
+        <v>3286</v>
       </c>
       <c r="L242" t="n">
-        <v>3736</v>
+        <v>3538</v>
       </c>
       <c r="M242" t="n">
-        <v>3925</v>
+        <v>3709</v>
       </c>
       <c r="N242" t="n">
-        <v>3988</v>
+        <v>3782</v>
       </c>
       <c r="O242" t="n">
-        <v>4044</v>
+        <v>3822</v>
       </c>
       <c r="P242" t="n">
-        <v>4129</v>
+        <v>3946</v>
       </c>
       <c r="Q242" t="n">
-        <v>4007</v>
+        <v>3930</v>
       </c>
       <c r="R242" t="n">
-        <v>3964</v>
+        <v>3784</v>
       </c>
       <c r="S242" t="n">
-        <v>4165</v>
+        <v>3772</v>
       </c>
       <c r="T242" t="n">
-        <v>4069</v>
+        <v>3666</v>
       </c>
       <c r="U242" t="n">
-        <v>4063</v>
+        <v>3729</v>
       </c>
       <c r="V242" t="n">
-        <v>4070</v>
+        <v>3791</v>
       </c>
       <c r="W242" t="n">
-        <v>4197</v>
+        <v>4183</v>
       </c>
       <c r="X242" t="n">
-        <v>4116</v>
+        <v>4119</v>
       </c>
       <c r="Y242" t="n">
-        <v>3993</v>
+        <v>3913</v>
       </c>
       <c r="Z242" t="n">
-        <v>3750</v>
+        <v>3756</v>
       </c>
       <c r="AA242" t="n">
-        <v>3533</v>
+        <v>3591</v>
       </c>
     </row>
     <row r="243">
@@ -20577,76 +20577,159 @@
         <v>4</v>
       </c>
       <c r="D243" t="n">
-        <v>3219</v>
+        <v>3254</v>
       </c>
       <c r="E243" t="n">
-        <v>3072</v>
+        <v>3082</v>
       </c>
       <c r="F243" t="n">
-        <v>2979</v>
+        <v>2982</v>
       </c>
       <c r="G243" t="n">
-        <v>2930</v>
+        <v>2928</v>
       </c>
       <c r="H243" t="n">
-        <v>2899</v>
+        <v>2909</v>
       </c>
       <c r="I243" t="n">
-        <v>2907</v>
+        <v>2933</v>
       </c>
       <c r="J243" t="n">
-        <v>3094</v>
+        <v>3070</v>
       </c>
       <c r="K243" t="n">
-        <v>3306</v>
+        <v>3212</v>
       </c>
       <c r="L243" t="n">
-        <v>3585</v>
+        <v>3463</v>
       </c>
       <c r="M243" t="n">
-        <v>3787</v>
+        <v>3659</v>
       </c>
       <c r="N243" t="n">
-        <v>3914</v>
+        <v>3774</v>
       </c>
       <c r="O243" t="n">
-        <v>3960</v>
+        <v>3819</v>
       </c>
       <c r="P243" t="n">
-        <v>4128</v>
+        <v>3964</v>
       </c>
       <c r="Q243" t="n">
-        <v>4139</v>
+        <v>3950</v>
       </c>
       <c r="R243" t="n">
-        <v>4106</v>
+        <v>3860</v>
       </c>
       <c r="S243" t="n">
-        <v>4078</v>
+        <v>3804</v>
       </c>
       <c r="T243" t="n">
-        <v>4045</v>
+        <v>3757</v>
       </c>
       <c r="U243" t="n">
-        <v>4064</v>
+        <v>3863</v>
       </c>
       <c r="V243" t="n">
-        <v>4170</v>
+        <v>3983</v>
       </c>
       <c r="W243" t="n">
-        <v>4434</v>
+        <v>4389</v>
       </c>
       <c r="X243" t="n">
-        <v>4396</v>
+        <v>4428</v>
       </c>
       <c r="Y243" t="n">
-        <v>4242</v>
+        <v>4187</v>
       </c>
       <c r="Z243" t="n">
-        <v>3917</v>
+        <v>3934</v>
       </c>
       <c r="AA243" t="n">
-        <v>3638</v>
+        <v>3702</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B244" t="n">
+        <v>10</v>
+      </c>
+      <c r="C244" t="n">
+        <v>5</v>
+      </c>
+      <c r="D244" t="n">
+        <v>3294</v>
+      </c>
+      <c r="E244" t="n">
+        <v>3102</v>
+      </c>
+      <c r="F244" t="n">
+        <v>3011</v>
+      </c>
+      <c r="G244" t="n">
+        <v>2981</v>
+      </c>
+      <c r="H244" t="n">
+        <v>2996</v>
+      </c>
+      <c r="I244" t="n">
+        <v>3136</v>
+      </c>
+      <c r="J244" t="n">
+        <v>3664</v>
+      </c>
+      <c r="K244" t="n">
+        <v>4038</v>
+      </c>
+      <c r="L244" t="n">
+        <v>4287</v>
+      </c>
+      <c r="M244" t="n">
+        <v>4383</v>
+      </c>
+      <c r="N244" t="n">
+        <v>4382</v>
+      </c>
+      <c r="O244" t="n">
+        <v>4411</v>
+      </c>
+      <c r="P244" t="n">
+        <v>4427</v>
+      </c>
+      <c r="Q244" t="n">
+        <v>4444</v>
+      </c>
+      <c r="R244" t="n">
+        <v>4444</v>
+      </c>
+      <c r="S244" t="n">
+        <v>4313</v>
+      </c>
+      <c r="T244" t="n">
+        <v>4096</v>
+      </c>
+      <c r="U244" t="n">
+        <v>4088</v>
+      </c>
+      <c r="V244" t="n">
+        <v>4300</v>
+      </c>
+      <c r="W244" t="n">
+        <v>4639</v>
+      </c>
+      <c r="X244" t="n">
+        <v>4478</v>
+      </c>
+      <c r="Y244" t="n">
+        <v>4269</v>
+      </c>
+      <c r="Z244" t="n">
+        <v>4077</v>
+      </c>
+      <c r="AA244" t="n">
+        <v>3860</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA244"/>
+  <dimension ref="A1:AA245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20328,76 +20328,76 @@
         <v>1</v>
       </c>
       <c r="D240" t="n">
-        <v>3276</v>
+        <v>3288</v>
       </c>
       <c r="E240" t="n">
-        <v>3079</v>
+        <v>3110</v>
       </c>
       <c r="F240" t="n">
-        <v>2986</v>
+        <v>3027</v>
       </c>
       <c r="G240" t="n">
-        <v>2963</v>
+        <v>3006</v>
       </c>
       <c r="H240" t="n">
-        <v>2970</v>
+        <v>3014</v>
       </c>
       <c r="I240" t="n">
-        <v>3066</v>
+        <v>3122</v>
       </c>
       <c r="J240" t="n">
-        <v>3452</v>
+        <v>3562</v>
       </c>
       <c r="K240" t="n">
-        <v>3764</v>
+        <v>3917</v>
       </c>
       <c r="L240" t="n">
-        <v>4063</v>
+        <v>4258</v>
       </c>
       <c r="M240" t="n">
-        <v>4168</v>
+        <v>4378</v>
       </c>
       <c r="N240" t="n">
-        <v>4143</v>
+        <v>4349</v>
       </c>
       <c r="O240" t="n">
-        <v>4137</v>
+        <v>4342</v>
       </c>
       <c r="P240" t="n">
-        <v>4160</v>
+        <v>4369</v>
       </c>
       <c r="Q240" t="n">
-        <v>4207</v>
+        <v>4422</v>
       </c>
       <c r="R240" t="n">
-        <v>4078</v>
+        <v>4326</v>
       </c>
       <c r="S240" t="n">
-        <v>3977</v>
+        <v>4250</v>
       </c>
       <c r="T240" t="n">
-        <v>3829</v>
+        <v>4138</v>
       </c>
       <c r="U240" t="n">
-        <v>3856</v>
+        <v>4158</v>
       </c>
       <c r="V240" t="n">
-        <v>4028</v>
+        <v>4285</v>
       </c>
       <c r="W240" t="n">
-        <v>4404</v>
+        <v>4561</v>
       </c>
       <c r="X240" t="n">
-        <v>4386</v>
+        <v>4538</v>
       </c>
       <c r="Y240" t="n">
-        <v>4170</v>
+        <v>4263</v>
       </c>
       <c r="Z240" t="n">
-        <v>3936</v>
+        <v>3966</v>
       </c>
       <c r="AA240" t="n">
-        <v>3699</v>
+        <v>3664</v>
       </c>
     </row>
     <row r="241">
@@ -20411,76 +20411,76 @@
         <v>2</v>
       </c>
       <c r="D241" t="n">
-        <v>3303</v>
+        <v>3315</v>
       </c>
       <c r="E241" t="n">
-        <v>3110</v>
+        <v>3141</v>
       </c>
       <c r="F241" t="n">
-        <v>3019</v>
+        <v>3059</v>
       </c>
       <c r="G241" t="n">
-        <v>2996</v>
+        <v>3039</v>
       </c>
       <c r="H241" t="n">
-        <v>3004</v>
+        <v>3047</v>
       </c>
       <c r="I241" t="n">
-        <v>3100</v>
+        <v>3157</v>
       </c>
       <c r="J241" t="n">
-        <v>3492</v>
+        <v>3602</v>
       </c>
       <c r="K241" t="n">
-        <v>3808</v>
+        <v>3962</v>
       </c>
       <c r="L241" t="n">
-        <v>4112</v>
+        <v>4307</v>
       </c>
       <c r="M241" t="n">
-        <v>4219</v>
+        <v>4428</v>
       </c>
       <c r="N241" t="n">
-        <v>4193</v>
+        <v>4399</v>
       </c>
       <c r="O241" t="n">
-        <v>4187</v>
+        <v>4392</v>
       </c>
       <c r="P241" t="n">
-        <v>4210</v>
+        <v>4419</v>
       </c>
       <c r="Q241" t="n">
-        <v>4258</v>
+        <v>4473</v>
       </c>
       <c r="R241" t="n">
-        <v>4132</v>
+        <v>4379</v>
       </c>
       <c r="S241" t="n">
-        <v>4032</v>
+        <v>4305</v>
       </c>
       <c r="T241" t="n">
-        <v>3887</v>
+        <v>4197</v>
       </c>
       <c r="U241" t="n">
-        <v>3910</v>
+        <v>4212</v>
       </c>
       <c r="V241" t="n">
-        <v>4055</v>
+        <v>4312</v>
       </c>
       <c r="W241" t="n">
-        <v>4373</v>
+        <v>4530</v>
       </c>
       <c r="X241" t="n">
-        <v>4355</v>
+        <v>4507</v>
       </c>
       <c r="Y241" t="n">
-        <v>4144</v>
+        <v>4238</v>
       </c>
       <c r="Z241" t="n">
-        <v>3916</v>
+        <v>3945</v>
       </c>
       <c r="AA241" t="n">
-        <v>3684</v>
+        <v>3649</v>
       </c>
     </row>
     <row r="242">
@@ -20494,76 +20494,76 @@
         <v>3</v>
       </c>
       <c r="D242" t="n">
-        <v>3296</v>
+        <v>3309</v>
       </c>
       <c r="E242" t="n">
-        <v>3107</v>
+        <v>3135</v>
       </c>
       <c r="F242" t="n">
-        <v>3005</v>
+        <v>3042</v>
       </c>
       <c r="G242" t="n">
-        <v>2957</v>
+        <v>2998</v>
       </c>
       <c r="H242" t="n">
-        <v>2939</v>
+        <v>2981</v>
       </c>
       <c r="I242" t="n">
-        <v>2979</v>
+        <v>3029</v>
       </c>
       <c r="J242" t="n">
-        <v>3126</v>
+        <v>3201</v>
       </c>
       <c r="K242" t="n">
-        <v>3286</v>
+        <v>3388</v>
       </c>
       <c r="L242" t="n">
-        <v>3538</v>
+        <v>3684</v>
       </c>
       <c r="M242" t="n">
-        <v>3709</v>
+        <v>3884</v>
       </c>
       <c r="N242" t="n">
-        <v>3782</v>
+        <v>3970</v>
       </c>
       <c r="O242" t="n">
-        <v>3822</v>
+        <v>4016</v>
       </c>
       <c r="P242" t="n">
-        <v>3946</v>
+        <v>4161</v>
       </c>
       <c r="Q242" t="n">
-        <v>3930</v>
+        <v>4151</v>
       </c>
       <c r="R242" t="n">
-        <v>3784</v>
+        <v>4054</v>
       </c>
       <c r="S242" t="n">
-        <v>3772</v>
+        <v>4046</v>
       </c>
       <c r="T242" t="n">
-        <v>3666</v>
+        <v>3976</v>
       </c>
       <c r="U242" t="n">
-        <v>3729</v>
+        <v>4021</v>
       </c>
       <c r="V242" t="n">
-        <v>3791</v>
+        <v>4064</v>
       </c>
       <c r="W242" t="n">
-        <v>4183</v>
+        <v>4340</v>
       </c>
       <c r="X242" t="n">
-        <v>4119</v>
+        <v>4255</v>
       </c>
       <c r="Y242" t="n">
-        <v>3913</v>
+        <v>3982</v>
       </c>
       <c r="Z242" t="n">
-        <v>3756</v>
+        <v>3775</v>
       </c>
       <c r="AA242" t="n">
-        <v>3591</v>
+        <v>3556</v>
       </c>
     </row>
     <row r="243">
@@ -20577,76 +20577,76 @@
         <v>4</v>
       </c>
       <c r="D243" t="n">
-        <v>3254</v>
+        <v>3266</v>
       </c>
       <c r="E243" t="n">
-        <v>3082</v>
+        <v>3109</v>
       </c>
       <c r="F243" t="n">
-        <v>2982</v>
+        <v>3018</v>
       </c>
       <c r="G243" t="n">
-        <v>2928</v>
+        <v>2969</v>
       </c>
       <c r="H243" t="n">
-        <v>2909</v>
+        <v>2952</v>
       </c>
       <c r="I243" t="n">
-        <v>2933</v>
+        <v>2979</v>
       </c>
       <c r="J243" t="n">
-        <v>3070</v>
+        <v>3138</v>
       </c>
       <c r="K243" t="n">
-        <v>3212</v>
+        <v>3304</v>
       </c>
       <c r="L243" t="n">
-        <v>3463</v>
+        <v>3596</v>
       </c>
       <c r="M243" t="n">
-        <v>3659</v>
+        <v>3825</v>
       </c>
       <c r="N243" t="n">
-        <v>3774</v>
+        <v>3959</v>
       </c>
       <c r="O243" t="n">
-        <v>3819</v>
+        <v>4010</v>
       </c>
       <c r="P243" t="n">
-        <v>3964</v>
+        <v>4179</v>
       </c>
       <c r="Q243" t="n">
-        <v>3950</v>
+        <v>4172</v>
       </c>
       <c r="R243" t="n">
-        <v>3860</v>
+        <v>4123</v>
       </c>
       <c r="S243" t="n">
-        <v>3804</v>
+        <v>4093</v>
       </c>
       <c r="T243" t="n">
-        <v>3757</v>
+        <v>4067</v>
       </c>
       <c r="U243" t="n">
-        <v>3863</v>
+        <v>4148</v>
       </c>
       <c r="V243" t="n">
-        <v>3983</v>
+        <v>4241</v>
       </c>
       <c r="W243" t="n">
-        <v>4389</v>
+        <v>4555</v>
       </c>
       <c r="X243" t="n">
-        <v>4428</v>
+        <v>4585</v>
       </c>
       <c r="Y243" t="n">
-        <v>4187</v>
+        <v>4280</v>
       </c>
       <c r="Z243" t="n">
-        <v>3934</v>
+        <v>3960</v>
       </c>
       <c r="AA243" t="n">
-        <v>3702</v>
+        <v>3666</v>
       </c>
     </row>
     <row r="244">
@@ -20660,76 +20660,159 @@
         <v>5</v>
       </c>
       <c r="D244" t="n">
-        <v>3294</v>
+        <v>3306</v>
       </c>
       <c r="E244" t="n">
-        <v>3102</v>
+        <v>3137</v>
       </c>
       <c r="F244" t="n">
-        <v>3011</v>
+        <v>3056</v>
       </c>
       <c r="G244" t="n">
-        <v>2981</v>
+        <v>3024</v>
       </c>
       <c r="H244" t="n">
-        <v>2996</v>
+        <v>3037</v>
       </c>
       <c r="I244" t="n">
-        <v>3136</v>
+        <v>3210</v>
       </c>
       <c r="J244" t="n">
-        <v>3664</v>
+        <v>3772</v>
       </c>
       <c r="K244" t="n">
-        <v>4038</v>
+        <v>4177</v>
       </c>
       <c r="L244" t="n">
-        <v>4287</v>
+        <v>4453</v>
       </c>
       <c r="M244" t="n">
+        <v>4547</v>
+      </c>
+      <c r="N244" t="n">
+        <v>4498</v>
+      </c>
+      <c r="O244" t="n">
+        <v>4532</v>
+      </c>
+      <c r="P244" t="n">
+        <v>4638</v>
+      </c>
+      <c r="Q244" t="n">
+        <v>4659</v>
+      </c>
+      <c r="R244" t="n">
+        <v>4630</v>
+      </c>
+      <c r="S244" t="n">
+        <v>4517</v>
+      </c>
+      <c r="T244" t="n">
+        <v>4399</v>
+      </c>
+      <c r="U244" t="n">
+        <v>4400</v>
+      </c>
+      <c r="V244" t="n">
+        <v>4534</v>
+      </c>
+      <c r="W244" t="n">
+        <v>4796</v>
+      </c>
+      <c r="X244" t="n">
+        <v>4731</v>
+      </c>
+      <c r="Y244" t="n">
         <v>4383</v>
       </c>
-      <c r="N244" t="n">
-        <v>4382</v>
-      </c>
-      <c r="O244" t="n">
-        <v>4411</v>
-      </c>
-      <c r="P244" t="n">
-        <v>4427</v>
-      </c>
-      <c r="Q244" t="n">
-        <v>4444</v>
-      </c>
-      <c r="R244" t="n">
-        <v>4444</v>
-      </c>
-      <c r="S244" t="n">
-        <v>4313</v>
-      </c>
-      <c r="T244" t="n">
-        <v>4096</v>
-      </c>
-      <c r="U244" t="n">
-        <v>4088</v>
-      </c>
-      <c r="V244" t="n">
-        <v>4300</v>
-      </c>
-      <c r="W244" t="n">
-        <v>4639</v>
-      </c>
-      <c r="X244" t="n">
-        <v>4478</v>
-      </c>
-      <c r="Y244" t="n">
-        <v>4269</v>
-      </c>
       <c r="Z244" t="n">
-        <v>4077</v>
+        <v>4121</v>
       </c>
       <c r="AA244" t="n">
-        <v>3860</v>
+        <v>3825</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B245" t="n">
+        <v>10</v>
+      </c>
+      <c r="C245" t="n">
+        <v>6</v>
+      </c>
+      <c r="D245" t="n">
+        <v>3344</v>
+      </c>
+      <c r="E245" t="n">
+        <v>3177</v>
+      </c>
+      <c r="F245" t="n">
+        <v>3099</v>
+      </c>
+      <c r="G245" t="n">
+        <v>3079</v>
+      </c>
+      <c r="H245" t="n">
+        <v>3088</v>
+      </c>
+      <c r="I245" t="n">
+        <v>3207</v>
+      </c>
+      <c r="J245" t="n">
+        <v>3687</v>
+      </c>
+      <c r="K245" t="n">
+        <v>4074</v>
+      </c>
+      <c r="L245" t="n">
+        <v>4446</v>
+      </c>
+      <c r="M245" t="n">
+        <v>4577</v>
+      </c>
+      <c r="N245" t="n">
+        <v>4545</v>
+      </c>
+      <c r="O245" t="n">
+        <v>4538</v>
+      </c>
+      <c r="P245" t="n">
+        <v>4567</v>
+      </c>
+      <c r="Q245" t="n">
+        <v>4625</v>
+      </c>
+      <c r="R245" t="n">
+        <v>4535</v>
+      </c>
+      <c r="S245" t="n">
+        <v>4464</v>
+      </c>
+      <c r="T245" t="n">
+        <v>4360</v>
+      </c>
+      <c r="U245" t="n">
+        <v>4379</v>
+      </c>
+      <c r="V245" t="n">
+        <v>4500</v>
+      </c>
+      <c r="W245" t="n">
+        <v>4763</v>
+      </c>
+      <c r="X245" t="n">
+        <v>4739</v>
+      </c>
+      <c r="Y245" t="n">
+        <v>4445</v>
+      </c>
+      <c r="Z245" t="n">
+        <v>4126</v>
+      </c>
+      <c r="AA245" t="n">
+        <v>3803</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA245"/>
+  <dimension ref="A1:AA246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20411,76 +20411,76 @@
         <v>2</v>
       </c>
       <c r="D241" t="n">
-        <v>3315</v>
+        <v>3332</v>
       </c>
       <c r="E241" t="n">
-        <v>3141</v>
+        <v>3185</v>
       </c>
       <c r="F241" t="n">
-        <v>3059</v>
+        <v>3117</v>
       </c>
       <c r="G241" t="n">
-        <v>3039</v>
+        <v>3098</v>
       </c>
       <c r="H241" t="n">
-        <v>3047</v>
+        <v>3115</v>
       </c>
       <c r="I241" t="n">
-        <v>3157</v>
+        <v>3215</v>
       </c>
       <c r="J241" t="n">
-        <v>3602</v>
+        <v>3638</v>
       </c>
       <c r="K241" t="n">
-        <v>3962</v>
+        <v>4000</v>
       </c>
       <c r="L241" t="n">
-        <v>4307</v>
+        <v>4335</v>
       </c>
       <c r="M241" t="n">
-        <v>4428</v>
+        <v>4449</v>
       </c>
       <c r="N241" t="n">
-        <v>4399</v>
+        <v>4405</v>
       </c>
       <c r="O241" t="n">
-        <v>4392</v>
+        <v>4397</v>
       </c>
       <c r="P241" t="n">
-        <v>4419</v>
+        <v>4411</v>
       </c>
       <c r="Q241" t="n">
-        <v>4473</v>
+        <v>4482</v>
       </c>
       <c r="R241" t="n">
-        <v>4379</v>
+        <v>4415</v>
       </c>
       <c r="S241" t="n">
-        <v>4305</v>
+        <v>4334</v>
       </c>
       <c r="T241" t="n">
-        <v>4197</v>
+        <v>4174</v>
       </c>
       <c r="U241" t="n">
-        <v>4212</v>
+        <v>4174</v>
       </c>
       <c r="V241" t="n">
-        <v>4312</v>
+        <v>4295</v>
       </c>
       <c r="W241" t="n">
-        <v>4530</v>
+        <v>4525</v>
       </c>
       <c r="X241" t="n">
-        <v>4507</v>
+        <v>4467</v>
       </c>
       <c r="Y241" t="n">
-        <v>4238</v>
+        <v>4233</v>
       </c>
       <c r="Z241" t="n">
-        <v>3945</v>
+        <v>3916</v>
       </c>
       <c r="AA241" t="n">
-        <v>3649</v>
+        <v>3641</v>
       </c>
     </row>
     <row r="242">
@@ -20494,76 +20494,76 @@
         <v>3</v>
       </c>
       <c r="D242" t="n">
-        <v>3309</v>
+        <v>3326</v>
       </c>
       <c r="E242" t="n">
-        <v>3135</v>
+        <v>3174</v>
       </c>
       <c r="F242" t="n">
+        <v>3091</v>
+      </c>
+      <c r="G242" t="n">
+        <v>3057</v>
+      </c>
+      <c r="H242" t="n">
         <v>3042</v>
       </c>
-      <c r="G242" t="n">
-        <v>2998</v>
-      </c>
-      <c r="H242" t="n">
-        <v>2981</v>
-      </c>
       <c r="I242" t="n">
-        <v>3029</v>
+        <v>3086</v>
       </c>
       <c r="J242" t="n">
-        <v>3201</v>
+        <v>3237</v>
       </c>
       <c r="K242" t="n">
-        <v>3388</v>
+        <v>3425</v>
       </c>
       <c r="L242" t="n">
-        <v>3684</v>
+        <v>3696</v>
       </c>
       <c r="M242" t="n">
-        <v>3884</v>
+        <v>3895</v>
       </c>
       <c r="N242" t="n">
-        <v>3970</v>
+        <v>3983</v>
       </c>
       <c r="O242" t="n">
-        <v>4016</v>
+        <v>4034</v>
       </c>
       <c r="P242" t="n">
-        <v>4161</v>
+        <v>4171</v>
       </c>
       <c r="Q242" t="n">
-        <v>4151</v>
+        <v>4168</v>
       </c>
       <c r="R242" t="n">
-        <v>4054</v>
+        <v>4052</v>
       </c>
       <c r="S242" t="n">
-        <v>4046</v>
+        <v>4089</v>
       </c>
       <c r="T242" t="n">
-        <v>3976</v>
+        <v>4009</v>
       </c>
       <c r="U242" t="n">
-        <v>4021</v>
+        <v>3959</v>
       </c>
       <c r="V242" t="n">
-        <v>4064</v>
+        <v>4008</v>
       </c>
       <c r="W242" t="n">
-        <v>4340</v>
+        <v>4337</v>
       </c>
       <c r="X242" t="n">
-        <v>4255</v>
+        <v>4209</v>
       </c>
       <c r="Y242" t="n">
-        <v>3982</v>
+        <v>3949</v>
       </c>
       <c r="Z242" t="n">
-        <v>3775</v>
+        <v>3744</v>
       </c>
       <c r="AA242" t="n">
-        <v>3556</v>
+        <v>3549</v>
       </c>
     </row>
     <row r="243">
@@ -20577,76 +20577,76 @@
         <v>4</v>
       </c>
       <c r="D243" t="n">
-        <v>3266</v>
+        <v>3280</v>
       </c>
       <c r="E243" t="n">
-        <v>3109</v>
+        <v>3143</v>
       </c>
       <c r="F243" t="n">
-        <v>3018</v>
+        <v>3064</v>
       </c>
       <c r="G243" t="n">
-        <v>2969</v>
+        <v>3022</v>
       </c>
       <c r="H243" t="n">
-        <v>2952</v>
+        <v>3007</v>
       </c>
       <c r="I243" t="n">
-        <v>2979</v>
+        <v>3033</v>
       </c>
       <c r="J243" t="n">
-        <v>3138</v>
+        <v>3185</v>
       </c>
       <c r="K243" t="n">
-        <v>3304</v>
+        <v>3344</v>
       </c>
       <c r="L243" t="n">
-        <v>3596</v>
+        <v>3624</v>
       </c>
       <c r="M243" t="n">
-        <v>3825</v>
+        <v>3843</v>
       </c>
       <c r="N243" t="n">
-        <v>3959</v>
+        <v>3971</v>
       </c>
       <c r="O243" t="n">
-        <v>4010</v>
+        <v>4020</v>
       </c>
       <c r="P243" t="n">
-        <v>4179</v>
+        <v>4182</v>
       </c>
       <c r="Q243" t="n">
-        <v>4172</v>
+        <v>4173</v>
       </c>
       <c r="R243" t="n">
-        <v>4123</v>
+        <v>4112</v>
       </c>
       <c r="S243" t="n">
-        <v>4093</v>
+        <v>4074</v>
       </c>
       <c r="T243" t="n">
-        <v>4067</v>
+        <v>4042</v>
       </c>
       <c r="U243" t="n">
-        <v>4148</v>
+        <v>4126</v>
       </c>
       <c r="V243" t="n">
-        <v>4241</v>
+        <v>4221</v>
       </c>
       <c r="W243" t="n">
-        <v>4555</v>
+        <v>4544</v>
       </c>
       <c r="X243" t="n">
-        <v>4585</v>
+        <v>4575</v>
       </c>
       <c r="Y243" t="n">
-        <v>4280</v>
+        <v>4270</v>
       </c>
       <c r="Z243" t="n">
-        <v>3960</v>
+        <v>3948</v>
       </c>
       <c r="AA243" t="n">
-        <v>3666</v>
+        <v>3654</v>
       </c>
     </row>
     <row r="244">
@@ -20660,76 +20660,76 @@
         <v>5</v>
       </c>
       <c r="D244" t="n">
-        <v>3306</v>
+        <v>3310</v>
       </c>
       <c r="E244" t="n">
-        <v>3137</v>
+        <v>3165</v>
       </c>
       <c r="F244" t="n">
-        <v>3056</v>
+        <v>3095</v>
       </c>
       <c r="G244" t="n">
-        <v>3024</v>
+        <v>3067</v>
       </c>
       <c r="H244" t="n">
-        <v>3037</v>
+        <v>3080</v>
       </c>
       <c r="I244" t="n">
-        <v>3210</v>
+        <v>3247</v>
       </c>
       <c r="J244" t="n">
-        <v>3772</v>
+        <v>3789</v>
       </c>
       <c r="K244" t="n">
-        <v>4177</v>
+        <v>4179</v>
       </c>
       <c r="L244" t="n">
-        <v>4453</v>
+        <v>4445</v>
       </c>
       <c r="M244" t="n">
-        <v>4547</v>
+        <v>4535</v>
       </c>
       <c r="N244" t="n">
-        <v>4498</v>
+        <v>4488</v>
       </c>
       <c r="O244" t="n">
-        <v>4532</v>
+        <v>4521</v>
       </c>
       <c r="P244" t="n">
-        <v>4638</v>
+        <v>4623</v>
       </c>
       <c r="Q244" t="n">
-        <v>4659</v>
+        <v>4644</v>
       </c>
       <c r="R244" t="n">
-        <v>4630</v>
+        <v>4611</v>
       </c>
       <c r="S244" t="n">
-        <v>4517</v>
+        <v>4485</v>
       </c>
       <c r="T244" t="n">
-        <v>4399</v>
+        <v>4353</v>
       </c>
       <c r="U244" t="n">
-        <v>4400</v>
+        <v>4353</v>
       </c>
       <c r="V244" t="n">
-        <v>4534</v>
+        <v>4494</v>
       </c>
       <c r="W244" t="n">
-        <v>4796</v>
+        <v>4768</v>
       </c>
       <c r="X244" t="n">
-        <v>4731</v>
+        <v>4703</v>
       </c>
       <c r="Y244" t="n">
-        <v>4383</v>
+        <v>4357</v>
       </c>
       <c r="Z244" t="n">
-        <v>4121</v>
+        <v>4095</v>
       </c>
       <c r="AA244" t="n">
-        <v>3825</v>
+        <v>3801</v>
       </c>
     </row>
     <row r="245">
@@ -20743,76 +20743,159 @@
         <v>6</v>
       </c>
       <c r="D245" t="n">
-        <v>3344</v>
+        <v>3351</v>
       </c>
       <c r="E245" t="n">
-        <v>3177</v>
+        <v>3211</v>
       </c>
       <c r="F245" t="n">
-        <v>3099</v>
+        <v>3145</v>
       </c>
       <c r="G245" t="n">
-        <v>3079</v>
+        <v>3127</v>
       </c>
       <c r="H245" t="n">
-        <v>3088</v>
+        <v>3145</v>
       </c>
       <c r="I245" t="n">
-        <v>3207</v>
+        <v>3252</v>
       </c>
       <c r="J245" t="n">
-        <v>3687</v>
+        <v>3708</v>
       </c>
       <c r="K245" t="n">
-        <v>4074</v>
+        <v>4098</v>
       </c>
       <c r="L245" t="n">
-        <v>4446</v>
+        <v>4458</v>
       </c>
       <c r="M245" t="n">
-        <v>4577</v>
+        <v>4581</v>
       </c>
       <c r="N245" t="n">
-        <v>4545</v>
+        <v>4534</v>
       </c>
       <c r="O245" t="n">
-        <v>4538</v>
+        <v>4526</v>
       </c>
       <c r="P245" t="n">
-        <v>4567</v>
+        <v>4540</v>
       </c>
       <c r="Q245" t="n">
-        <v>4625</v>
+        <v>4616</v>
       </c>
       <c r="R245" t="n">
-        <v>4535</v>
+        <v>4553</v>
       </c>
       <c r="S245" t="n">
-        <v>4464</v>
+        <v>4475</v>
       </c>
       <c r="T245" t="n">
+        <v>4322</v>
+      </c>
+      <c r="U245" t="n">
+        <v>4322</v>
+      </c>
+      <c r="V245" t="n">
+        <v>4467</v>
+      </c>
+      <c r="W245" t="n">
+        <v>4742</v>
+      </c>
+      <c r="X245" t="n">
+        <v>4679</v>
+      </c>
+      <c r="Y245" t="n">
+        <v>4425</v>
+      </c>
+      <c r="Z245" t="n">
+        <v>4081</v>
+      </c>
+      <c r="AA245" t="n">
+        <v>3783</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B246" t="n">
+        <v>10</v>
+      </c>
+      <c r="C246" t="n">
+        <v>7</v>
+      </c>
+      <c r="D246" t="n">
+        <v>3311</v>
+      </c>
+      <c r="E246" t="n">
+        <v>3165</v>
+      </c>
+      <c r="F246" t="n">
+        <v>3097</v>
+      </c>
+      <c r="G246" t="n">
+        <v>3078</v>
+      </c>
+      <c r="H246" t="n">
+        <v>3096</v>
+      </c>
+      <c r="I246" t="n">
+        <v>3201</v>
+      </c>
+      <c r="J246" t="n">
+        <v>3648</v>
+      </c>
+      <c r="K246" t="n">
+        <v>4031</v>
+      </c>
+      <c r="L246" t="n">
+        <v>4385</v>
+      </c>
+      <c r="M246" t="n">
+        <v>4507</v>
+      </c>
+      <c r="N246" t="n">
+        <v>4460</v>
+      </c>
+      <c r="O246" t="n">
+        <v>4452</v>
+      </c>
+      <c r="P246" t="n">
+        <v>4466</v>
+      </c>
+      <c r="Q246" t="n">
+        <v>4541</v>
+      </c>
+      <c r="R246" t="n">
+        <v>4475</v>
+      </c>
+      <c r="S246" t="n">
+        <v>4394</v>
+      </c>
+      <c r="T246" t="n">
+        <v>4235</v>
+      </c>
+      <c r="U246" t="n">
+        <v>4236</v>
+      </c>
+      <c r="V246" t="n">
+        <v>4385</v>
+      </c>
+      <c r="W246" t="n">
+        <v>4670</v>
+      </c>
+      <c r="X246" t="n">
+        <v>4608</v>
+      </c>
+      <c r="Y246" t="n">
         <v>4360</v>
       </c>
-      <c r="U245" t="n">
-        <v>4379</v>
-      </c>
-      <c r="V245" t="n">
-        <v>4500</v>
-      </c>
-      <c r="W245" t="n">
-        <v>4763</v>
-      </c>
-      <c r="X245" t="n">
-        <v>4739</v>
-      </c>
-      <c r="Y245" t="n">
-        <v>4445</v>
-      </c>
-      <c r="Z245" t="n">
-        <v>4126</v>
-      </c>
-      <c r="AA245" t="n">
-        <v>3803</v>
+      <c r="Z246" t="n">
+        <v>4025</v>
+      </c>
+      <c r="AA246" t="n">
+        <v>3734</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA246"/>
+  <dimension ref="A1:AA247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20494,76 +20494,76 @@
         <v>3</v>
       </c>
       <c r="D242" t="n">
-        <v>3326</v>
+        <v>3427</v>
       </c>
       <c r="E242" t="n">
-        <v>3174</v>
+        <v>3230</v>
       </c>
       <c r="F242" t="n">
-        <v>3091</v>
+        <v>3122</v>
       </c>
       <c r="G242" t="n">
+        <v>3078</v>
+      </c>
+      <c r="H242" t="n">
         <v>3057</v>
       </c>
-      <c r="H242" t="n">
-        <v>3042</v>
-      </c>
       <c r="I242" t="n">
-        <v>3086</v>
+        <v>3098</v>
       </c>
       <c r="J242" t="n">
-        <v>3237</v>
+        <v>3233</v>
       </c>
       <c r="K242" t="n">
-        <v>3425</v>
+        <v>3401</v>
       </c>
       <c r="L242" t="n">
-        <v>3696</v>
+        <v>3644</v>
       </c>
       <c r="M242" t="n">
-        <v>3895</v>
+        <v>3823</v>
       </c>
       <c r="N242" t="n">
-        <v>3983</v>
+        <v>3902</v>
       </c>
       <c r="O242" t="n">
-        <v>4034</v>
+        <v>3948</v>
       </c>
       <c r="P242" t="n">
-        <v>4171</v>
+        <v>4071</v>
       </c>
       <c r="Q242" t="n">
-        <v>4168</v>
+        <v>4067</v>
       </c>
       <c r="R242" t="n">
-        <v>4052</v>
+        <v>3912</v>
       </c>
       <c r="S242" t="n">
-        <v>4089</v>
+        <v>3961</v>
       </c>
       <c r="T242" t="n">
-        <v>4009</v>
+        <v>3854</v>
       </c>
       <c r="U242" t="n">
-        <v>3959</v>
+        <v>3789</v>
       </c>
       <c r="V242" t="n">
-        <v>4008</v>
+        <v>3853</v>
       </c>
       <c r="W242" t="n">
-        <v>4337</v>
+        <v>4282</v>
       </c>
       <c r="X242" t="n">
-        <v>4209</v>
+        <v>4157</v>
       </c>
       <c r="Y242" t="n">
-        <v>3949</v>
+        <v>3905</v>
       </c>
       <c r="Z242" t="n">
-        <v>3744</v>
+        <v>3706</v>
       </c>
       <c r="AA242" t="n">
-        <v>3549</v>
+        <v>3515</v>
       </c>
     </row>
     <row r="243">
@@ -20577,76 +20577,76 @@
         <v>4</v>
       </c>
       <c r="D243" t="n">
-        <v>3280</v>
+        <v>3357</v>
       </c>
       <c r="E243" t="n">
-        <v>3143</v>
+        <v>3176</v>
       </c>
       <c r="F243" t="n">
-        <v>3064</v>
+        <v>3067</v>
       </c>
       <c r="G243" t="n">
-        <v>3022</v>
+        <v>3015</v>
       </c>
       <c r="H243" t="n">
-        <v>3007</v>
+        <v>2993</v>
       </c>
       <c r="I243" t="n">
-        <v>3033</v>
+        <v>3012</v>
       </c>
       <c r="J243" t="n">
-        <v>3185</v>
+        <v>3157</v>
       </c>
       <c r="K243" t="n">
-        <v>3344</v>
+        <v>3312</v>
       </c>
       <c r="L243" t="n">
-        <v>3624</v>
+        <v>3568</v>
       </c>
       <c r="M243" t="n">
-        <v>3843</v>
+        <v>3766</v>
       </c>
       <c r="N243" t="n">
-        <v>3971</v>
+        <v>3878</v>
       </c>
       <c r="O243" t="n">
-        <v>4020</v>
+        <v>3889</v>
       </c>
       <c r="P243" t="n">
-        <v>4182</v>
+        <v>4039</v>
       </c>
       <c r="Q243" t="n">
-        <v>4173</v>
+        <v>4016</v>
       </c>
       <c r="R243" t="n">
-        <v>4112</v>
+        <v>3936</v>
       </c>
       <c r="S243" t="n">
-        <v>4074</v>
+        <v>3888</v>
       </c>
       <c r="T243" t="n">
-        <v>4042</v>
+        <v>3821</v>
       </c>
       <c r="U243" t="n">
-        <v>4126</v>
+        <v>3902</v>
       </c>
       <c r="V243" t="n">
-        <v>4221</v>
+        <v>4026</v>
       </c>
       <c r="W243" t="n">
-        <v>4544</v>
+        <v>4468</v>
       </c>
       <c r="X243" t="n">
-        <v>4575</v>
+        <v>4478</v>
       </c>
       <c r="Y243" t="n">
-        <v>4270</v>
+        <v>4185</v>
       </c>
       <c r="Z243" t="n">
-        <v>3948</v>
+        <v>3877</v>
       </c>
       <c r="AA243" t="n">
-        <v>3654</v>
+        <v>3592</v>
       </c>
     </row>
     <row r="244">
@@ -20660,76 +20660,76 @@
         <v>5</v>
       </c>
       <c r="D244" t="n">
-        <v>3310</v>
+        <v>3388</v>
       </c>
       <c r="E244" t="n">
-        <v>3165</v>
+        <v>3186</v>
       </c>
       <c r="F244" t="n">
-        <v>3095</v>
+        <v>3088</v>
       </c>
       <c r="G244" t="n">
-        <v>3067</v>
+        <v>3053</v>
       </c>
       <c r="H244" t="n">
-        <v>3080</v>
+        <v>3078</v>
       </c>
       <c r="I244" t="n">
-        <v>3247</v>
+        <v>3253</v>
       </c>
       <c r="J244" t="n">
-        <v>3789</v>
+        <v>3816</v>
       </c>
       <c r="K244" t="n">
-        <v>4179</v>
+        <v>4209</v>
       </c>
       <c r="L244" t="n">
-        <v>4445</v>
+        <v>4447</v>
       </c>
       <c r="M244" t="n">
-        <v>4535</v>
+        <v>4498</v>
       </c>
       <c r="N244" t="n">
-        <v>4488</v>
+        <v>4354</v>
       </c>
       <c r="O244" t="n">
-        <v>4521</v>
+        <v>4340</v>
       </c>
       <c r="P244" t="n">
-        <v>4623</v>
+        <v>4427</v>
       </c>
       <c r="Q244" t="n">
-        <v>4644</v>
+        <v>4422</v>
       </c>
       <c r="R244" t="n">
-        <v>4611</v>
+        <v>4341</v>
       </c>
       <c r="S244" t="n">
-        <v>4485</v>
+        <v>4230</v>
       </c>
       <c r="T244" t="n">
-        <v>4353</v>
+        <v>4133</v>
       </c>
       <c r="U244" t="n">
-        <v>4353</v>
+        <v>4147</v>
       </c>
       <c r="V244" t="n">
-        <v>4494</v>
+        <v>4355</v>
       </c>
       <c r="W244" t="n">
-        <v>4768</v>
+        <v>4673</v>
       </c>
       <c r="X244" t="n">
-        <v>4703</v>
+        <v>4625</v>
       </c>
       <c r="Y244" t="n">
-        <v>4357</v>
+        <v>4304</v>
       </c>
       <c r="Z244" t="n">
-        <v>4095</v>
+        <v>4036</v>
       </c>
       <c r="AA244" t="n">
-        <v>3801</v>
+        <v>3739</v>
       </c>
     </row>
     <row r="245">
@@ -20743,76 +20743,76 @@
         <v>6</v>
       </c>
       <c r="D245" t="n">
-        <v>3351</v>
+        <v>3432</v>
       </c>
       <c r="E245" t="n">
-        <v>3211</v>
+        <v>3242</v>
       </c>
       <c r="F245" t="n">
-        <v>3145</v>
+        <v>3151</v>
       </c>
       <c r="G245" t="n">
-        <v>3127</v>
+        <v>3118</v>
       </c>
       <c r="H245" t="n">
-        <v>3145</v>
+        <v>3134</v>
       </c>
       <c r="I245" t="n">
         <v>3252</v>
       </c>
       <c r="J245" t="n">
-        <v>3708</v>
+        <v>3680</v>
       </c>
       <c r="K245" t="n">
-        <v>4098</v>
+        <v>4006</v>
       </c>
       <c r="L245" t="n">
-        <v>4458</v>
+        <v>4312</v>
       </c>
       <c r="M245" t="n">
-        <v>4581</v>
+        <v>4439</v>
       </c>
       <c r="N245" t="n">
-        <v>4534</v>
+        <v>4384</v>
       </c>
       <c r="O245" t="n">
-        <v>4526</v>
+        <v>4392</v>
       </c>
       <c r="P245" t="n">
-        <v>4540</v>
+        <v>4412</v>
       </c>
       <c r="Q245" t="n">
-        <v>4616</v>
+        <v>4477</v>
       </c>
       <c r="R245" t="n">
-        <v>4553</v>
+        <v>4370</v>
       </c>
       <c r="S245" t="n">
-        <v>4475</v>
+        <v>4292</v>
       </c>
       <c r="T245" t="n">
-        <v>4322</v>
+        <v>4106</v>
       </c>
       <c r="U245" t="n">
-        <v>4322</v>
+        <v>4105</v>
       </c>
       <c r="V245" t="n">
-        <v>4467</v>
+        <v>4280</v>
       </c>
       <c r="W245" t="n">
-        <v>4742</v>
+        <v>4652</v>
       </c>
       <c r="X245" t="n">
-        <v>4679</v>
+        <v>4600</v>
       </c>
       <c r="Y245" t="n">
-        <v>4425</v>
+        <v>4340</v>
       </c>
       <c r="Z245" t="n">
-        <v>4081</v>
+        <v>4035</v>
       </c>
       <c r="AA245" t="n">
-        <v>3783</v>
+        <v>3726</v>
       </c>
     </row>
     <row r="246">
@@ -20826,76 +20826,159 @@
         <v>7</v>
       </c>
       <c r="D246" t="n">
-        <v>3311</v>
+        <v>3408</v>
       </c>
       <c r="E246" t="n">
-        <v>3165</v>
+        <v>3214</v>
       </c>
       <c r="F246" t="n">
-        <v>3097</v>
+        <v>3121</v>
       </c>
       <c r="G246" t="n">
-        <v>3078</v>
+        <v>3088</v>
       </c>
       <c r="H246" t="n">
-        <v>3096</v>
+        <v>3104</v>
       </c>
       <c r="I246" t="n">
-        <v>3201</v>
+        <v>3221</v>
       </c>
       <c r="J246" t="n">
-        <v>3648</v>
+        <v>3643</v>
       </c>
       <c r="K246" t="n">
-        <v>4031</v>
+        <v>3965</v>
       </c>
       <c r="L246" t="n">
-        <v>4385</v>
+        <v>4268</v>
       </c>
       <c r="M246" t="n">
-        <v>4507</v>
+        <v>4393</v>
       </c>
       <c r="N246" t="n">
-        <v>4460</v>
+        <v>4339</v>
       </c>
       <c r="O246" t="n">
-        <v>4452</v>
+        <v>4347</v>
       </c>
       <c r="P246" t="n">
-        <v>4466</v>
+        <v>4366</v>
       </c>
       <c r="Q246" t="n">
-        <v>4541</v>
+        <v>4431</v>
       </c>
       <c r="R246" t="n">
-        <v>4475</v>
+        <v>4319</v>
       </c>
       <c r="S246" t="n">
-        <v>4394</v>
+        <v>4239</v>
       </c>
       <c r="T246" t="n">
-        <v>4235</v>
+        <v>4046</v>
       </c>
       <c r="U246" t="n">
-        <v>4236</v>
+        <v>4044</v>
       </c>
       <c r="V246" t="n">
-        <v>4385</v>
+        <v>4225</v>
       </c>
       <c r="W246" t="n">
-        <v>4670</v>
+        <v>4608</v>
       </c>
       <c r="X246" t="n">
-        <v>4608</v>
+        <v>4556</v>
       </c>
       <c r="Y246" t="n">
-        <v>4360</v>
+        <v>4300</v>
       </c>
       <c r="Z246" t="n">
-        <v>4025</v>
+        <v>4000</v>
       </c>
       <c r="AA246" t="n">
-        <v>3734</v>
+        <v>3696</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B247" t="n">
+        <v>10</v>
+      </c>
+      <c r="C247" t="n">
+        <v>8</v>
+      </c>
+      <c r="D247" t="n">
+        <v>3398</v>
+      </c>
+      <c r="E247" t="n">
+        <v>3203</v>
+      </c>
+      <c r="F247" t="n">
+        <v>3109</v>
+      </c>
+      <c r="G247" t="n">
+        <v>3075</v>
+      </c>
+      <c r="H247" t="n">
+        <v>3092</v>
+      </c>
+      <c r="I247" t="n">
+        <v>3208</v>
+      </c>
+      <c r="J247" t="n">
+        <v>3629</v>
+      </c>
+      <c r="K247" t="n">
+        <v>3949</v>
+      </c>
+      <c r="L247" t="n">
+        <v>4250</v>
+      </c>
+      <c r="M247" t="n">
+        <v>4375</v>
+      </c>
+      <c r="N247" t="n">
+        <v>4321</v>
+      </c>
+      <c r="O247" t="n">
+        <v>4329</v>
+      </c>
+      <c r="P247" t="n">
+        <v>4348</v>
+      </c>
+      <c r="Q247" t="n">
+        <v>4413</v>
+      </c>
+      <c r="R247" t="n">
+        <v>4299</v>
+      </c>
+      <c r="S247" t="n">
+        <v>4217</v>
+      </c>
+      <c r="T247" t="n">
+        <v>4021</v>
+      </c>
+      <c r="U247" t="n">
+        <v>4019</v>
+      </c>
+      <c r="V247" t="n">
+        <v>4202</v>
+      </c>
+      <c r="W247" t="n">
+        <v>4590</v>
+      </c>
+      <c r="X247" t="n">
+        <v>4539</v>
+      </c>
+      <c r="Y247" t="n">
+        <v>4284</v>
+      </c>
+      <c r="Z247" t="n">
+        <v>3986</v>
+      </c>
+      <c r="AA247" t="n">
+        <v>3683</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA247"/>
+  <dimension ref="A1:AA248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20577,76 +20577,76 @@
         <v>4</v>
       </c>
       <c r="D243" t="n">
-        <v>3357</v>
+        <v>3378</v>
       </c>
       <c r="E243" t="n">
-        <v>3176</v>
+        <v>3182</v>
       </c>
       <c r="F243" t="n">
-        <v>3067</v>
+        <v>3065</v>
       </c>
       <c r="G243" t="n">
-        <v>3015</v>
+        <v>3008</v>
       </c>
       <c r="H243" t="n">
-        <v>2993</v>
+        <v>2985</v>
       </c>
       <c r="I243" t="n">
-        <v>3012</v>
+        <v>3001</v>
       </c>
       <c r="J243" t="n">
-        <v>3157</v>
+        <v>3121</v>
       </c>
       <c r="K243" t="n">
-        <v>3312</v>
+        <v>3249</v>
       </c>
       <c r="L243" t="n">
-        <v>3568</v>
+        <v>3460</v>
       </c>
       <c r="M243" t="n">
-        <v>3766</v>
+        <v>3624</v>
       </c>
       <c r="N243" t="n">
-        <v>3878</v>
+        <v>3717</v>
       </c>
       <c r="O243" t="n">
-        <v>3889</v>
+        <v>3726</v>
       </c>
       <c r="P243" t="n">
-        <v>4039</v>
+        <v>3850</v>
       </c>
       <c r="Q243" t="n">
-        <v>4016</v>
+        <v>3838</v>
       </c>
       <c r="R243" t="n">
-        <v>3936</v>
+        <v>3796</v>
       </c>
       <c r="S243" t="n">
-        <v>3888</v>
+        <v>3770</v>
       </c>
       <c r="T243" t="n">
-        <v>3821</v>
+        <v>3734</v>
       </c>
       <c r="U243" t="n">
-        <v>3902</v>
+        <v>3829</v>
       </c>
       <c r="V243" t="n">
-        <v>4026</v>
+        <v>3974</v>
       </c>
       <c r="W243" t="n">
-        <v>4468</v>
+        <v>4490</v>
       </c>
       <c r="X243" t="n">
-        <v>4478</v>
+        <v>4502</v>
       </c>
       <c r="Y243" t="n">
-        <v>4185</v>
+        <v>4216</v>
       </c>
       <c r="Z243" t="n">
-        <v>3877</v>
+        <v>3918</v>
       </c>
       <c r="AA243" t="n">
-        <v>3592</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="244">
@@ -20660,76 +20660,76 @@
         <v>5</v>
       </c>
       <c r="D244" t="n">
-        <v>3388</v>
+        <v>3407</v>
       </c>
       <c r="E244" t="n">
-        <v>3186</v>
+        <v>3189</v>
       </c>
       <c r="F244" t="n">
-        <v>3088</v>
+        <v>3081</v>
       </c>
       <c r="G244" t="n">
-        <v>3053</v>
+        <v>3044</v>
       </c>
       <c r="H244" t="n">
-        <v>3078</v>
+        <v>3066</v>
       </c>
       <c r="I244" t="n">
-        <v>3253</v>
+        <v>3218</v>
       </c>
       <c r="J244" t="n">
-        <v>3816</v>
+        <v>3711</v>
       </c>
       <c r="K244" t="n">
-        <v>4209</v>
+        <v>4054</v>
       </c>
       <c r="L244" t="n">
-        <v>4447</v>
+        <v>4262</v>
       </c>
       <c r="M244" t="n">
-        <v>4498</v>
+        <v>4307</v>
       </c>
       <c r="N244" t="n">
-        <v>4354</v>
+        <v>4203</v>
       </c>
       <c r="O244" t="n">
-        <v>4340</v>
+        <v>4193</v>
       </c>
       <c r="P244" t="n">
-        <v>4427</v>
+        <v>4255</v>
       </c>
       <c r="Q244" t="n">
-        <v>4422</v>
+        <v>4252</v>
       </c>
       <c r="R244" t="n">
-        <v>4341</v>
+        <v>4194</v>
       </c>
       <c r="S244" t="n">
-        <v>4230</v>
+        <v>4114</v>
       </c>
       <c r="T244" t="n">
-        <v>4133</v>
+        <v>4044</v>
       </c>
       <c r="U244" t="n">
-        <v>4147</v>
+        <v>4061</v>
       </c>
       <c r="V244" t="n">
-        <v>4355</v>
+        <v>4312</v>
       </c>
       <c r="W244" t="n">
-        <v>4673</v>
+        <v>4694</v>
       </c>
       <c r="X244" t="n">
-        <v>4625</v>
+        <v>4648</v>
       </c>
       <c r="Y244" t="n">
-        <v>4304</v>
+        <v>4335</v>
       </c>
       <c r="Z244" t="n">
-        <v>4036</v>
+        <v>4075</v>
       </c>
       <c r="AA244" t="n">
-        <v>3739</v>
+        <v>3786</v>
       </c>
     </row>
     <row r="245">
@@ -20743,76 +20743,76 @@
         <v>6</v>
       </c>
       <c r="D245" t="n">
-        <v>3432</v>
+        <v>3441</v>
       </c>
       <c r="E245" t="n">
-        <v>3242</v>
+        <v>3230</v>
       </c>
       <c r="F245" t="n">
-        <v>3151</v>
+        <v>3136</v>
       </c>
       <c r="G245" t="n">
-        <v>3118</v>
+        <v>3096</v>
       </c>
       <c r="H245" t="n">
-        <v>3134</v>
+        <v>3113</v>
       </c>
       <c r="I245" t="n">
-        <v>3252</v>
+        <v>3235</v>
       </c>
       <c r="J245" t="n">
-        <v>3680</v>
+        <v>3641</v>
       </c>
       <c r="K245" t="n">
-        <v>4006</v>
+        <v>3953</v>
       </c>
       <c r="L245" t="n">
-        <v>4312</v>
+        <v>4198</v>
       </c>
       <c r="M245" t="n">
-        <v>4439</v>
+        <v>4262</v>
       </c>
       <c r="N245" t="n">
-        <v>4384</v>
+        <v>4178</v>
       </c>
       <c r="O245" t="n">
-        <v>4392</v>
+        <v>4154</v>
       </c>
       <c r="P245" t="n">
-        <v>4412</v>
+        <v>4155</v>
       </c>
       <c r="Q245" t="n">
-        <v>4477</v>
+        <v>4233</v>
       </c>
       <c r="R245" t="n">
-        <v>4370</v>
+        <v>4166</v>
       </c>
       <c r="S245" t="n">
-        <v>4292</v>
+        <v>4108</v>
       </c>
       <c r="T245" t="n">
-        <v>4106</v>
+        <v>3997</v>
       </c>
       <c r="U245" t="n">
-        <v>4105</v>
+        <v>4010</v>
       </c>
       <c r="V245" t="n">
-        <v>4280</v>
+        <v>4223</v>
       </c>
       <c r="W245" t="n">
-        <v>4652</v>
+        <v>4655</v>
       </c>
       <c r="X245" t="n">
-        <v>4600</v>
+        <v>4613</v>
       </c>
       <c r="Y245" t="n">
-        <v>4340</v>
+        <v>4364</v>
       </c>
       <c r="Z245" t="n">
-        <v>4035</v>
+        <v>4056</v>
       </c>
       <c r="AA245" t="n">
-        <v>3726</v>
+        <v>3760</v>
       </c>
     </row>
     <row r="246">
@@ -20826,76 +20826,76 @@
         <v>7</v>
       </c>
       <c r="D246" t="n">
-        <v>3408</v>
+        <v>3434</v>
       </c>
       <c r="E246" t="n">
-        <v>3214</v>
+        <v>3221</v>
       </c>
       <c r="F246" t="n">
-        <v>3121</v>
+        <v>3127</v>
       </c>
       <c r="G246" t="n">
-        <v>3088</v>
+        <v>3087</v>
       </c>
       <c r="H246" t="n">
         <v>3104</v>
       </c>
       <c r="I246" t="n">
-        <v>3221</v>
+        <v>3225</v>
       </c>
       <c r="J246" t="n">
-        <v>3643</v>
+        <v>3629</v>
       </c>
       <c r="K246" t="n">
-        <v>3965</v>
+        <v>3939</v>
       </c>
       <c r="L246" t="n">
-        <v>4268</v>
+        <v>4183</v>
       </c>
       <c r="M246" t="n">
-        <v>4393</v>
+        <v>4247</v>
       </c>
       <c r="N246" t="n">
-        <v>4339</v>
+        <v>4162</v>
       </c>
       <c r="O246" t="n">
-        <v>4347</v>
+        <v>4139</v>
       </c>
       <c r="P246" t="n">
-        <v>4366</v>
+        <v>4140</v>
       </c>
       <c r="Q246" t="n">
-        <v>4431</v>
+        <v>4218</v>
       </c>
       <c r="R246" t="n">
-        <v>4319</v>
+        <v>4151</v>
       </c>
       <c r="S246" t="n">
-        <v>4239</v>
+        <v>4092</v>
       </c>
       <c r="T246" t="n">
+        <v>3981</v>
+      </c>
+      <c r="U246" t="n">
+        <v>3994</v>
+      </c>
+      <c r="V246" t="n">
+        <v>4208</v>
+      </c>
+      <c r="W246" t="n">
+        <v>4642</v>
+      </c>
+      <c r="X246" t="n">
+        <v>4600</v>
+      </c>
+      <c r="Y246" t="n">
+        <v>4352</v>
+      </c>
+      <c r="Z246" t="n">
         <v>4046</v>
       </c>
-      <c r="U246" t="n">
-        <v>4044</v>
-      </c>
-      <c r="V246" t="n">
-        <v>4225</v>
-      </c>
-      <c r="W246" t="n">
-        <v>4608</v>
-      </c>
-      <c r="X246" t="n">
-        <v>4556</v>
-      </c>
-      <c r="Y246" t="n">
-        <v>4300</v>
-      </c>
-      <c r="Z246" t="n">
-        <v>4000</v>
-      </c>
       <c r="AA246" t="n">
-        <v>3696</v>
+        <v>3751</v>
       </c>
     </row>
     <row r="247">
@@ -20909,76 +20909,159 @@
         <v>8</v>
       </c>
       <c r="D247" t="n">
-        <v>3398</v>
+        <v>3422</v>
       </c>
       <c r="E247" t="n">
-        <v>3203</v>
+        <v>3207</v>
       </c>
       <c r="F247" t="n">
-        <v>3109</v>
+        <v>3112</v>
       </c>
       <c r="G247" t="n">
-        <v>3075</v>
+        <v>3072</v>
       </c>
       <c r="H247" t="n">
-        <v>3092</v>
+        <v>3089</v>
       </c>
       <c r="I247" t="n">
-        <v>3208</v>
+        <v>3209</v>
       </c>
       <c r="J247" t="n">
-        <v>3629</v>
+        <v>3610</v>
       </c>
       <c r="K247" t="n">
-        <v>3949</v>
+        <v>3917</v>
       </c>
       <c r="L247" t="n">
-        <v>4250</v>
+        <v>4158</v>
       </c>
       <c r="M247" t="n">
-        <v>4375</v>
+        <v>4222</v>
       </c>
       <c r="N247" t="n">
-        <v>4321</v>
+        <v>4137</v>
       </c>
       <c r="O247" t="n">
-        <v>4329</v>
+        <v>4114</v>
       </c>
       <c r="P247" t="n">
-        <v>4348</v>
+        <v>4114</v>
       </c>
       <c r="Q247" t="n">
-        <v>4413</v>
+        <v>4193</v>
       </c>
       <c r="R247" t="n">
-        <v>4299</v>
+        <v>4125</v>
       </c>
       <c r="S247" t="n">
+        <v>4066</v>
+      </c>
+      <c r="T247" t="n">
+        <v>3956</v>
+      </c>
+      <c r="U247" t="n">
+        <v>3969</v>
+      </c>
+      <c r="V247" t="n">
+        <v>4184</v>
+      </c>
+      <c r="W247" t="n">
+        <v>4620</v>
+      </c>
+      <c r="X247" t="n">
+        <v>4579</v>
+      </c>
+      <c r="Y247" t="n">
+        <v>4333</v>
+      </c>
+      <c r="Z247" t="n">
+        <v>4029</v>
+      </c>
+      <c r="AA247" t="n">
+        <v>3736</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B248" t="n">
+        <v>10</v>
+      </c>
+      <c r="C248" t="n">
+        <v>9</v>
+      </c>
+      <c r="D248" t="n">
+        <v>3394</v>
+      </c>
+      <c r="E248" t="n">
+        <v>3175</v>
+      </c>
+      <c r="F248" t="n">
+        <v>3078</v>
+      </c>
+      <c r="G248" t="n">
+        <v>3037</v>
+      </c>
+      <c r="H248" t="n">
+        <v>3054</v>
+      </c>
+      <c r="I248" t="n">
+        <v>3171</v>
+      </c>
+      <c r="J248" t="n">
+        <v>3563</v>
+      </c>
+      <c r="K248" t="n">
+        <v>3865</v>
+      </c>
+      <c r="L248" t="n">
+        <v>4101</v>
+      </c>
+      <c r="M248" t="n">
+        <v>4163</v>
+      </c>
+      <c r="N248" t="n">
+        <v>4078</v>
+      </c>
+      <c r="O248" t="n">
+        <v>4054</v>
+      </c>
+      <c r="P248" t="n">
+        <v>4055</v>
+      </c>
+      <c r="Q248" t="n">
+        <v>4134</v>
+      </c>
+      <c r="R248" t="n">
+        <v>4066</v>
+      </c>
+      <c r="S248" t="n">
+        <v>4006</v>
+      </c>
+      <c r="T248" t="n">
+        <v>3894</v>
+      </c>
+      <c r="U248" t="n">
+        <v>3906</v>
+      </c>
+      <c r="V248" t="n">
+        <v>4099</v>
+      </c>
+      <c r="W248" t="n">
+        <v>4489</v>
+      </c>
+      <c r="X248" t="n">
+        <v>4450</v>
+      </c>
+      <c r="Y248" t="n">
         <v>4217</v>
       </c>
-      <c r="T247" t="n">
-        <v>4021</v>
-      </c>
-      <c r="U247" t="n">
-        <v>4019</v>
-      </c>
-      <c r="V247" t="n">
-        <v>4202</v>
-      </c>
-      <c r="W247" t="n">
-        <v>4590</v>
-      </c>
-      <c r="X247" t="n">
-        <v>4539</v>
-      </c>
-      <c r="Y247" t="n">
-        <v>4284</v>
-      </c>
-      <c r="Z247" t="n">
-        <v>3986</v>
-      </c>
-      <c r="AA247" t="n">
-        <v>3683</v>
+      <c r="Z248" t="n">
+        <v>3930</v>
+      </c>
+      <c r="AA248" t="n">
+        <v>3653</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA248"/>
+  <dimension ref="A1:AA249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20660,76 +20660,76 @@
         <v>5</v>
       </c>
       <c r="D244" t="n">
-        <v>3407</v>
+        <v>3325</v>
       </c>
       <c r="E244" t="n">
-        <v>3189</v>
+        <v>3116</v>
       </c>
       <c r="F244" t="n">
-        <v>3081</v>
+        <v>3013</v>
       </c>
       <c r="G244" t="n">
-        <v>3044</v>
+        <v>2978</v>
       </c>
       <c r="H244" t="n">
-        <v>3066</v>
+        <v>3002</v>
       </c>
       <c r="I244" t="n">
-        <v>3218</v>
+        <v>3170</v>
       </c>
       <c r="J244" t="n">
-        <v>3711</v>
+        <v>3716</v>
       </c>
       <c r="K244" t="n">
-        <v>4054</v>
+        <v>4096</v>
       </c>
       <c r="L244" t="n">
-        <v>4262</v>
+        <v>4326</v>
       </c>
       <c r="M244" t="n">
-        <v>4307</v>
+        <v>4375</v>
       </c>
       <c r="N244" t="n">
-        <v>4203</v>
+        <v>4186</v>
       </c>
       <c r="O244" t="n">
-        <v>4193</v>
+        <v>4168</v>
       </c>
       <c r="P244" t="n">
-        <v>4255</v>
+        <v>4281</v>
       </c>
       <c r="Q244" t="n">
-        <v>4252</v>
+        <v>4275</v>
       </c>
       <c r="R244" t="n">
-        <v>4194</v>
+        <v>4169</v>
       </c>
       <c r="S244" t="n">
-        <v>4114</v>
+        <v>4023</v>
       </c>
       <c r="T244" t="n">
-        <v>4044</v>
+        <v>3896</v>
       </c>
       <c r="U244" t="n">
-        <v>4061</v>
+        <v>3909</v>
       </c>
       <c r="V244" t="n">
-        <v>4312</v>
+        <v>4100</v>
       </c>
       <c r="W244" t="n">
-        <v>4694</v>
+        <v>4392</v>
       </c>
       <c r="X244" t="n">
-        <v>4648</v>
+        <v>4356</v>
       </c>
       <c r="Y244" t="n">
-        <v>4335</v>
+        <v>4113</v>
       </c>
       <c r="Z244" t="n">
-        <v>4075</v>
+        <v>3911</v>
       </c>
       <c r="AA244" t="n">
-        <v>3786</v>
+        <v>3686</v>
       </c>
     </row>
     <row r="245">
@@ -20743,76 +20743,76 @@
         <v>6</v>
       </c>
       <c r="D245" t="n">
-        <v>3441</v>
+        <v>3360</v>
       </c>
       <c r="E245" t="n">
-        <v>3230</v>
+        <v>3156</v>
       </c>
       <c r="F245" t="n">
-        <v>3136</v>
+        <v>3067</v>
       </c>
       <c r="G245" t="n">
-        <v>3096</v>
+        <v>3030</v>
       </c>
       <c r="H245" t="n">
-        <v>3113</v>
+        <v>3053</v>
       </c>
       <c r="I245" t="n">
-        <v>3235</v>
+        <v>3192</v>
       </c>
       <c r="J245" t="n">
         <v>3641</v>
       </c>
       <c r="K245" t="n">
-        <v>3953</v>
+        <v>3986</v>
       </c>
       <c r="L245" t="n">
-        <v>4198</v>
+        <v>4256</v>
       </c>
       <c r="M245" t="n">
+        <v>4332</v>
+      </c>
+      <c r="N245" t="n">
+        <v>4179</v>
+      </c>
+      <c r="O245" t="n">
+        <v>4156</v>
+      </c>
+      <c r="P245" t="n">
+        <v>4146</v>
+      </c>
+      <c r="Q245" t="n">
         <v>4262</v>
       </c>
-      <c r="N245" t="n">
-        <v>4178</v>
-      </c>
-      <c r="O245" t="n">
-        <v>4154</v>
-      </c>
-      <c r="P245" t="n">
-        <v>4155</v>
-      </c>
-      <c r="Q245" t="n">
-        <v>4233</v>
-      </c>
       <c r="R245" t="n">
-        <v>4166</v>
+        <v>4141</v>
       </c>
       <c r="S245" t="n">
-        <v>4108</v>
+        <v>4050</v>
       </c>
       <c r="T245" t="n">
-        <v>3997</v>
+        <v>3851</v>
       </c>
       <c r="U245" t="n">
-        <v>4010</v>
+        <v>3860</v>
       </c>
       <c r="V245" t="n">
-        <v>4223</v>
+        <v>4022</v>
       </c>
       <c r="W245" t="n">
-        <v>4655</v>
+        <v>4354</v>
       </c>
       <c r="X245" t="n">
-        <v>4613</v>
+        <v>4317</v>
       </c>
       <c r="Y245" t="n">
-        <v>4364</v>
+        <v>4123</v>
       </c>
       <c r="Z245" t="n">
-        <v>4056</v>
+        <v>3888</v>
       </c>
       <c r="AA245" t="n">
-        <v>3760</v>
+        <v>3661</v>
       </c>
     </row>
     <row r="246">
@@ -20826,76 +20826,76 @@
         <v>7</v>
       </c>
       <c r="D246" t="n">
-        <v>3434</v>
+        <v>3355</v>
       </c>
       <c r="E246" t="n">
-        <v>3221</v>
+        <v>3151</v>
       </c>
       <c r="F246" t="n">
-        <v>3127</v>
+        <v>3061</v>
       </c>
       <c r="G246" t="n">
-        <v>3087</v>
+        <v>3025</v>
       </c>
       <c r="H246" t="n">
-        <v>3104</v>
+        <v>3048</v>
       </c>
       <c r="I246" t="n">
-        <v>3225</v>
+        <v>3186</v>
       </c>
       <c r="J246" t="n">
-        <v>3629</v>
+        <v>3633</v>
       </c>
       <c r="K246" t="n">
-        <v>3939</v>
+        <v>3977</v>
       </c>
       <c r="L246" t="n">
-        <v>4183</v>
+        <v>4247</v>
       </c>
       <c r="M246" t="n">
-        <v>4247</v>
+        <v>4323</v>
       </c>
       <c r="N246" t="n">
-        <v>4162</v>
+        <v>4169</v>
       </c>
       <c r="O246" t="n">
-        <v>4139</v>
+        <v>4146</v>
       </c>
       <c r="P246" t="n">
-        <v>4140</v>
+        <v>4137</v>
       </c>
       <c r="Q246" t="n">
-        <v>4218</v>
+        <v>4253</v>
       </c>
       <c r="R246" t="n">
-        <v>4151</v>
+        <v>4132</v>
       </c>
       <c r="S246" t="n">
-        <v>4092</v>
+        <v>4041</v>
       </c>
       <c r="T246" t="n">
-        <v>3981</v>
+        <v>3841</v>
       </c>
       <c r="U246" t="n">
-        <v>3994</v>
+        <v>3850</v>
       </c>
       <c r="V246" t="n">
-        <v>4208</v>
+        <v>4013</v>
       </c>
       <c r="W246" t="n">
-        <v>4642</v>
+        <v>4346</v>
       </c>
       <c r="X246" t="n">
-        <v>4600</v>
+        <v>4309</v>
       </c>
       <c r="Y246" t="n">
-        <v>4352</v>
+        <v>4116</v>
       </c>
       <c r="Z246" t="n">
-        <v>4046</v>
+        <v>3881</v>
       </c>
       <c r="AA246" t="n">
-        <v>3751</v>
+        <v>3655</v>
       </c>
     </row>
     <row r="247">
@@ -20909,76 +20909,76 @@
         <v>8</v>
       </c>
       <c r="D247" t="n">
-        <v>3422</v>
+        <v>3326</v>
       </c>
       <c r="E247" t="n">
-        <v>3207</v>
+        <v>3118</v>
       </c>
       <c r="F247" t="n">
-        <v>3112</v>
+        <v>3027</v>
       </c>
       <c r="G247" t="n">
-        <v>3072</v>
+        <v>2989</v>
       </c>
       <c r="H247" t="n">
-        <v>3089</v>
+        <v>3012</v>
       </c>
       <c r="I247" t="n">
-        <v>3209</v>
+        <v>3148</v>
       </c>
       <c r="J247" t="n">
-        <v>3610</v>
+        <v>3587</v>
       </c>
       <c r="K247" t="n">
-        <v>3917</v>
+        <v>3924</v>
       </c>
       <c r="L247" t="n">
-        <v>4158</v>
+        <v>4189</v>
       </c>
       <c r="M247" t="n">
-        <v>4222</v>
+        <v>4263</v>
       </c>
       <c r="N247" t="n">
-        <v>4137</v>
+        <v>4109</v>
       </c>
       <c r="O247" t="n">
-        <v>4114</v>
+        <v>4086</v>
       </c>
       <c r="P247" t="n">
-        <v>4114</v>
+        <v>4076</v>
       </c>
       <c r="Q247" t="n">
-        <v>4193</v>
+        <v>4192</v>
       </c>
       <c r="R247" t="n">
-        <v>4125</v>
+        <v>4071</v>
       </c>
       <c r="S247" t="n">
-        <v>4066</v>
+        <v>3979</v>
       </c>
       <c r="T247" t="n">
-        <v>3956</v>
+        <v>3779</v>
       </c>
       <c r="U247" t="n">
-        <v>3969</v>
+        <v>3788</v>
       </c>
       <c r="V247" t="n">
-        <v>4184</v>
+        <v>3955</v>
       </c>
       <c r="W247" t="n">
-        <v>4620</v>
+        <v>4294</v>
       </c>
       <c r="X247" t="n">
-        <v>4579</v>
+        <v>4258</v>
       </c>
       <c r="Y247" t="n">
-        <v>4333</v>
+        <v>4070</v>
       </c>
       <c r="Z247" t="n">
-        <v>4029</v>
+        <v>3841</v>
       </c>
       <c r="AA247" t="n">
-        <v>3736</v>
+        <v>3620</v>
       </c>
     </row>
     <row r="248">
@@ -20992,76 +20992,159 @@
         <v>9</v>
       </c>
       <c r="D248" t="n">
-        <v>3394</v>
+        <v>3279</v>
       </c>
       <c r="E248" t="n">
-        <v>3175</v>
+        <v>3064</v>
       </c>
       <c r="F248" t="n">
-        <v>3078</v>
+        <v>2970</v>
       </c>
       <c r="G248" t="n">
-        <v>3037</v>
+        <v>2931</v>
       </c>
       <c r="H248" t="n">
-        <v>3054</v>
+        <v>2953</v>
       </c>
       <c r="I248" t="n">
-        <v>3171</v>
+        <v>3085</v>
       </c>
       <c r="J248" t="n">
-        <v>3563</v>
+        <v>3509</v>
       </c>
       <c r="K248" t="n">
-        <v>3865</v>
+        <v>3836</v>
       </c>
       <c r="L248" t="n">
-        <v>4101</v>
+        <v>4092</v>
       </c>
       <c r="M248" t="n">
-        <v>4163</v>
+        <v>4164</v>
       </c>
       <c r="N248" t="n">
-        <v>4078</v>
+        <v>4009</v>
       </c>
       <c r="O248" t="n">
-        <v>4054</v>
+        <v>3986</v>
       </c>
       <c r="P248" t="n">
-        <v>4055</v>
+        <v>3976</v>
       </c>
       <c r="Q248" t="n">
-        <v>4134</v>
+        <v>4093</v>
       </c>
       <c r="R248" t="n">
-        <v>4066</v>
+        <v>3971</v>
       </c>
       <c r="S248" t="n">
-        <v>4006</v>
+        <v>3879</v>
       </c>
       <c r="T248" t="n">
-        <v>3894</v>
+        <v>3677</v>
       </c>
       <c r="U248" t="n">
-        <v>3906</v>
+        <v>3685</v>
       </c>
       <c r="V248" t="n">
-        <v>4099</v>
+        <v>3831</v>
       </c>
       <c r="W248" t="n">
-        <v>4489</v>
+        <v>4128</v>
       </c>
       <c r="X248" t="n">
-        <v>4450</v>
+        <v>4096</v>
       </c>
       <c r="Y248" t="n">
-        <v>4217</v>
+        <v>3924</v>
       </c>
       <c r="Z248" t="n">
-        <v>3930</v>
+        <v>3715</v>
       </c>
       <c r="AA248" t="n">
-        <v>3653</v>
+        <v>3514</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B249" t="n">
+        <v>10</v>
+      </c>
+      <c r="C249" t="n">
+        <v>10</v>
+      </c>
+      <c r="D249" t="n">
+        <v>3256</v>
+      </c>
+      <c r="E249" t="n">
+        <v>3044</v>
+      </c>
+      <c r="F249" t="n">
+        <v>2923</v>
+      </c>
+      <c r="G249" t="n">
+        <v>2870</v>
+      </c>
+      <c r="H249" t="n">
+        <v>2853</v>
+      </c>
+      <c r="I249" t="n">
+        <v>2896</v>
+      </c>
+      <c r="J249" t="n">
+        <v>3070</v>
+      </c>
+      <c r="K249" t="n">
+        <v>3273</v>
+      </c>
+      <c r="L249" t="n">
+        <v>3552</v>
+      </c>
+      <c r="M249" t="n">
+        <v>3737</v>
+      </c>
+      <c r="N249" t="n">
+        <v>3761</v>
+      </c>
+      <c r="O249" t="n">
+        <v>3755</v>
+      </c>
+      <c r="P249" t="n">
+        <v>3822</v>
+      </c>
+      <c r="Q249" t="n">
+        <v>3700</v>
+      </c>
+      <c r="R249" t="n">
+        <v>3519</v>
+      </c>
+      <c r="S249" t="n">
+        <v>3481</v>
+      </c>
+      <c r="T249" t="n">
+        <v>3421</v>
+      </c>
+      <c r="U249" t="n">
+        <v>3508</v>
+      </c>
+      <c r="V249" t="n">
+        <v>3608</v>
+      </c>
+      <c r="W249" t="n">
+        <v>3910</v>
+      </c>
+      <c r="X249" t="n">
+        <v>3822</v>
+      </c>
+      <c r="Y249" t="n">
+        <v>3708</v>
+      </c>
+      <c r="Z249" t="n">
+        <v>3541</v>
+      </c>
+      <c r="AA249" t="n">
+        <v>3400</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA249"/>
+  <dimension ref="A1:AA250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20743,76 +20743,76 @@
         <v>6</v>
       </c>
       <c r="D245" t="n">
-        <v>3360</v>
+        <v>3313</v>
       </c>
       <c r="E245" t="n">
-        <v>3156</v>
+        <v>3139</v>
       </c>
       <c r="F245" t="n">
-        <v>3067</v>
+        <v>3062</v>
       </c>
       <c r="G245" t="n">
-        <v>3030</v>
+        <v>3025</v>
       </c>
       <c r="H245" t="n">
-        <v>3053</v>
+        <v>3044</v>
       </c>
       <c r="I245" t="n">
-        <v>3192</v>
+        <v>3189</v>
       </c>
       <c r="J245" t="n">
-        <v>3641</v>
+        <v>3604</v>
       </c>
       <c r="K245" t="n">
-        <v>3986</v>
+        <v>3923</v>
       </c>
       <c r="L245" t="n">
-        <v>4256</v>
+        <v>4175</v>
       </c>
       <c r="M245" t="n">
-        <v>4332</v>
+        <v>4245</v>
       </c>
       <c r="N245" t="n">
-        <v>4179</v>
+        <v>4116</v>
       </c>
       <c r="O245" t="n">
-        <v>4156</v>
+        <v>4107</v>
       </c>
       <c r="P245" t="n">
-        <v>4146</v>
+        <v>4088</v>
       </c>
       <c r="Q245" t="n">
-        <v>4262</v>
+        <v>4192</v>
       </c>
       <c r="R245" t="n">
-        <v>4141</v>
+        <v>4078</v>
       </c>
       <c r="S245" t="n">
-        <v>4050</v>
+        <v>3995</v>
       </c>
       <c r="T245" t="n">
-        <v>3851</v>
+        <v>3847</v>
       </c>
       <c r="U245" t="n">
-        <v>3860</v>
+        <v>3871</v>
       </c>
       <c r="V245" t="n">
-        <v>4022</v>
+        <v>4087</v>
       </c>
       <c r="W245" t="n">
-        <v>4354</v>
+        <v>4486</v>
       </c>
       <c r="X245" t="n">
-        <v>4317</v>
+        <v>4442</v>
       </c>
       <c r="Y245" t="n">
-        <v>4123</v>
+        <v>4181</v>
       </c>
       <c r="Z245" t="n">
-        <v>3888</v>
+        <v>3923</v>
       </c>
       <c r="AA245" t="n">
-        <v>3661</v>
+        <v>3673</v>
       </c>
     </row>
     <row r="246">
@@ -20826,76 +20826,76 @@
         <v>7</v>
       </c>
       <c r="D246" t="n">
-        <v>3355</v>
+        <v>3288</v>
       </c>
       <c r="E246" t="n">
-        <v>3151</v>
+        <v>3111</v>
       </c>
       <c r="F246" t="n">
-        <v>3061</v>
+        <v>3033</v>
       </c>
       <c r="G246" t="n">
-        <v>3025</v>
+        <v>2995</v>
       </c>
       <c r="H246" t="n">
-        <v>3048</v>
+        <v>3013</v>
       </c>
       <c r="I246" t="n">
-        <v>3186</v>
+        <v>3156</v>
       </c>
       <c r="J246" t="n">
-        <v>3633</v>
+        <v>3564</v>
       </c>
       <c r="K246" t="n">
-        <v>3977</v>
+        <v>3878</v>
       </c>
       <c r="L246" t="n">
-        <v>4247</v>
+        <v>4126</v>
       </c>
       <c r="M246" t="n">
-        <v>4323</v>
+        <v>4194</v>
       </c>
       <c r="N246" t="n">
-        <v>4169</v>
+        <v>4065</v>
       </c>
       <c r="O246" t="n">
-        <v>4146</v>
+        <v>4056</v>
       </c>
       <c r="P246" t="n">
-        <v>4137</v>
+        <v>4037</v>
       </c>
       <c r="Q246" t="n">
-        <v>4253</v>
+        <v>4141</v>
       </c>
       <c r="R246" t="n">
-        <v>4132</v>
+        <v>4026</v>
       </c>
       <c r="S246" t="n">
-        <v>4041</v>
+        <v>3943</v>
       </c>
       <c r="T246" t="n">
-        <v>3841</v>
+        <v>3795</v>
       </c>
       <c r="U246" t="n">
-        <v>3850</v>
+        <v>3819</v>
       </c>
       <c r="V246" t="n">
-        <v>4013</v>
+        <v>4038</v>
       </c>
       <c r="W246" t="n">
-        <v>4346</v>
+        <v>4442</v>
       </c>
       <c r="X246" t="n">
-        <v>4309</v>
+        <v>4399</v>
       </c>
       <c r="Y246" t="n">
-        <v>4116</v>
+        <v>4142</v>
       </c>
       <c r="Z246" t="n">
-        <v>3881</v>
+        <v>3888</v>
       </c>
       <c r="AA246" t="n">
-        <v>3655</v>
+        <v>3643</v>
       </c>
     </row>
     <row r="247">
@@ -20909,76 +20909,76 @@
         <v>8</v>
       </c>
       <c r="D247" t="n">
-        <v>3326</v>
+        <v>3265</v>
       </c>
       <c r="E247" t="n">
-        <v>3118</v>
+        <v>3085</v>
       </c>
       <c r="F247" t="n">
-        <v>3027</v>
+        <v>3005</v>
       </c>
       <c r="G247" t="n">
-        <v>2989</v>
+        <v>2966</v>
       </c>
       <c r="H247" t="n">
-        <v>3012</v>
+        <v>2984</v>
       </c>
       <c r="I247" t="n">
-        <v>3148</v>
+        <v>3125</v>
       </c>
       <c r="J247" t="n">
-        <v>3587</v>
+        <v>3526</v>
       </c>
       <c r="K247" t="n">
-        <v>3924</v>
+        <v>3835</v>
       </c>
       <c r="L247" t="n">
-        <v>4189</v>
+        <v>4078</v>
       </c>
       <c r="M247" t="n">
-        <v>4263</v>
+        <v>4145</v>
       </c>
       <c r="N247" t="n">
-        <v>4109</v>
+        <v>4016</v>
       </c>
       <c r="O247" t="n">
-        <v>4086</v>
+        <v>4006</v>
       </c>
       <c r="P247" t="n">
-        <v>4076</v>
+        <v>3988</v>
       </c>
       <c r="Q247" t="n">
-        <v>4192</v>
+        <v>4092</v>
       </c>
       <c r="R247" t="n">
-        <v>4071</v>
+        <v>3977</v>
       </c>
       <c r="S247" t="n">
-        <v>3979</v>
+        <v>3894</v>
       </c>
       <c r="T247" t="n">
-        <v>3779</v>
+        <v>3744</v>
       </c>
       <c r="U247" t="n">
-        <v>3788</v>
+        <v>3769</v>
       </c>
       <c r="V247" t="n">
-        <v>3955</v>
+        <v>3991</v>
       </c>
       <c r="W247" t="n">
-        <v>4294</v>
+        <v>4400</v>
       </c>
       <c r="X247" t="n">
-        <v>4258</v>
+        <v>4358</v>
       </c>
       <c r="Y247" t="n">
-        <v>4070</v>
+        <v>4105</v>
       </c>
       <c r="Z247" t="n">
-        <v>3841</v>
+        <v>3856</v>
       </c>
       <c r="AA247" t="n">
-        <v>3620</v>
+        <v>3615</v>
       </c>
     </row>
     <row r="248">
@@ -20992,76 +20992,76 @@
         <v>9</v>
       </c>
       <c r="D248" t="n">
-        <v>3279</v>
+        <v>3223</v>
       </c>
       <c r="E248" t="n">
-        <v>3064</v>
+        <v>3038</v>
       </c>
       <c r="F248" t="n">
-        <v>2970</v>
+        <v>2955</v>
       </c>
       <c r="G248" t="n">
-        <v>2931</v>
+        <v>2915</v>
       </c>
       <c r="H248" t="n">
-        <v>2953</v>
+        <v>2933</v>
       </c>
       <c r="I248" t="n">
-        <v>3085</v>
+        <v>3069</v>
       </c>
       <c r="J248" t="n">
-        <v>3509</v>
+        <v>3459</v>
       </c>
       <c r="K248" t="n">
-        <v>3836</v>
+        <v>3758</v>
       </c>
       <c r="L248" t="n">
-        <v>4092</v>
+        <v>3994</v>
       </c>
       <c r="M248" t="n">
-        <v>4164</v>
+        <v>4059</v>
       </c>
       <c r="N248" t="n">
-        <v>4009</v>
+        <v>3929</v>
       </c>
       <c r="O248" t="n">
-        <v>3986</v>
+        <v>3919</v>
       </c>
       <c r="P248" t="n">
-        <v>3976</v>
+        <v>3900</v>
       </c>
       <c r="Q248" t="n">
-        <v>4093</v>
+        <v>4006</v>
       </c>
       <c r="R248" t="n">
-        <v>3971</v>
+        <v>3890</v>
       </c>
       <c r="S248" t="n">
-        <v>3879</v>
+        <v>3806</v>
       </c>
       <c r="T248" t="n">
+        <v>3655</v>
+      </c>
+      <c r="U248" t="n">
         <v>3677</v>
       </c>
-      <c r="U248" t="n">
-        <v>3685</v>
-      </c>
       <c r="V248" t="n">
-        <v>3831</v>
+        <v>3877</v>
       </c>
       <c r="W248" t="n">
-        <v>4128</v>
+        <v>4245</v>
       </c>
       <c r="X248" t="n">
-        <v>4096</v>
+        <v>4206</v>
       </c>
       <c r="Y248" t="n">
-        <v>3924</v>
+        <v>3972</v>
       </c>
       <c r="Z248" t="n">
-        <v>3715</v>
+        <v>3740</v>
       </c>
       <c r="AA248" t="n">
-        <v>3514</v>
+        <v>3516</v>
       </c>
     </row>
     <row r="249">
@@ -21075,76 +21075,159 @@
         <v>10</v>
       </c>
       <c r="D249" t="n">
-        <v>3256</v>
+        <v>3214</v>
       </c>
       <c r="E249" t="n">
-        <v>3044</v>
+        <v>3017</v>
       </c>
       <c r="F249" t="n">
-        <v>2923</v>
+        <v>2909</v>
       </c>
       <c r="G249" t="n">
-        <v>2870</v>
+        <v>2866</v>
       </c>
       <c r="H249" t="n">
-        <v>2853</v>
+        <v>2854</v>
       </c>
       <c r="I249" t="n">
-        <v>2896</v>
+        <v>2897</v>
       </c>
       <c r="J249" t="n">
-        <v>3070</v>
+        <v>3050</v>
       </c>
       <c r="K249" t="n">
-        <v>3273</v>
+        <v>3231</v>
       </c>
       <c r="L249" t="n">
-        <v>3552</v>
+        <v>3478</v>
       </c>
       <c r="M249" t="n">
-        <v>3737</v>
+        <v>3626</v>
       </c>
       <c r="N249" t="n">
-        <v>3761</v>
+        <v>3667</v>
       </c>
       <c r="O249" t="n">
-        <v>3755</v>
+        <v>3683</v>
       </c>
       <c r="P249" t="n">
-        <v>3822</v>
+        <v>3741</v>
       </c>
       <c r="Q249" t="n">
-        <v>3700</v>
+        <v>3670</v>
       </c>
       <c r="R249" t="n">
-        <v>3519</v>
+        <v>3541</v>
       </c>
       <c r="S249" t="n">
-        <v>3481</v>
+        <v>3502</v>
       </c>
       <c r="T249" t="n">
-        <v>3421</v>
+        <v>3427</v>
       </c>
       <c r="U249" t="n">
-        <v>3508</v>
+        <v>3495</v>
       </c>
       <c r="V249" t="n">
-        <v>3608</v>
+        <v>3653</v>
       </c>
       <c r="W249" t="n">
-        <v>3910</v>
+        <v>4050</v>
       </c>
       <c r="X249" t="n">
-        <v>3822</v>
+        <v>3974</v>
       </c>
       <c r="Y249" t="n">
-        <v>3708</v>
+        <v>3760</v>
       </c>
       <c r="Z249" t="n">
-        <v>3541</v>
+        <v>3580</v>
       </c>
       <c r="AA249" t="n">
-        <v>3400</v>
+        <v>3418</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B250" t="n">
+        <v>10</v>
+      </c>
+      <c r="C250" t="n">
+        <v>11</v>
+      </c>
+      <c r="D250" t="n">
+        <v>3188</v>
+      </c>
+      <c r="E250" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F250" t="n">
+        <v>2918</v>
+      </c>
+      <c r="G250" t="n">
+        <v>2859</v>
+      </c>
+      <c r="H250" t="n">
+        <v>2844</v>
+      </c>
+      <c r="I250" t="n">
+        <v>2877</v>
+      </c>
+      <c r="J250" t="n">
+        <v>3033</v>
+      </c>
+      <c r="K250" t="n">
+        <v>3201</v>
+      </c>
+      <c r="L250" t="n">
+        <v>3473</v>
+      </c>
+      <c r="M250" t="n">
+        <v>3684</v>
+      </c>
+      <c r="N250" t="n">
+        <v>3739</v>
+      </c>
+      <c r="O250" t="n">
+        <v>3733</v>
+      </c>
+      <c r="P250" t="n">
+        <v>3789</v>
+      </c>
+      <c r="Q250" t="n">
+        <v>3747</v>
+      </c>
+      <c r="R250" t="n">
+        <v>3670</v>
+      </c>
+      <c r="S250" t="n">
+        <v>3596</v>
+      </c>
+      <c r="T250" t="n">
+        <v>3553</v>
+      </c>
+      <c r="U250" t="n">
+        <v>3696</v>
+      </c>
+      <c r="V250" t="n">
+        <v>3852</v>
+      </c>
+      <c r="W250" t="n">
+        <v>4324</v>
+      </c>
+      <c r="X250" t="n">
+        <v>4298</v>
+      </c>
+      <c r="Y250" t="n">
+        <v>4129</v>
+      </c>
+      <c r="Z250" t="n">
+        <v>3807</v>
+      </c>
+      <c r="AA250" t="n">
+        <v>3549</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA250"/>
+  <dimension ref="A1:AA251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20826,76 +20826,76 @@
         <v>7</v>
       </c>
       <c r="D246" t="n">
-        <v>3288</v>
+        <v>3329</v>
       </c>
       <c r="E246" t="n">
-        <v>3111</v>
+        <v>3129</v>
       </c>
       <c r="F246" t="n">
-        <v>3033</v>
+        <v>3040</v>
       </c>
       <c r="G246" t="n">
-        <v>2995</v>
+        <v>2997</v>
       </c>
       <c r="H246" t="n">
-        <v>3013</v>
+        <v>3015</v>
       </c>
       <c r="I246" t="n">
-        <v>3156</v>
+        <v>3160</v>
       </c>
       <c r="J246" t="n">
-        <v>3564</v>
+        <v>3573</v>
       </c>
       <c r="K246" t="n">
-        <v>3878</v>
+        <v>3890</v>
       </c>
       <c r="L246" t="n">
-        <v>4126</v>
+        <v>4141</v>
       </c>
       <c r="M246" t="n">
-        <v>4194</v>
+        <v>4210</v>
       </c>
       <c r="N246" t="n">
-        <v>4065</v>
+        <v>4083</v>
       </c>
       <c r="O246" t="n">
-        <v>4056</v>
+        <v>4074</v>
       </c>
       <c r="P246" t="n">
-        <v>4037</v>
+        <v>4055</v>
       </c>
       <c r="Q246" t="n">
-        <v>4141</v>
+        <v>4158</v>
       </c>
       <c r="R246" t="n">
-        <v>4026</v>
+        <v>4045</v>
       </c>
       <c r="S246" t="n">
-        <v>3943</v>
+        <v>3963</v>
       </c>
       <c r="T246" t="n">
-        <v>3795</v>
+        <v>3816</v>
       </c>
       <c r="U246" t="n">
-        <v>3819</v>
+        <v>3841</v>
       </c>
       <c r="V246" t="n">
-        <v>4038</v>
+        <v>4066</v>
       </c>
       <c r="W246" t="n">
-        <v>4442</v>
+        <v>4480</v>
       </c>
       <c r="X246" t="n">
-        <v>4399</v>
+        <v>4437</v>
       </c>
       <c r="Y246" t="n">
-        <v>4142</v>
+        <v>4178</v>
       </c>
       <c r="Z246" t="n">
-        <v>3888</v>
+        <v>3923</v>
       </c>
       <c r="AA246" t="n">
-        <v>3643</v>
+        <v>3677</v>
       </c>
     </row>
     <row r="247">
@@ -20909,76 +20909,76 @@
         <v>8</v>
       </c>
       <c r="D247" t="n">
-        <v>3265</v>
+        <v>3306</v>
       </c>
       <c r="E247" t="n">
-        <v>3085</v>
+        <v>3102</v>
       </c>
       <c r="F247" t="n">
-        <v>3005</v>
+        <v>3012</v>
       </c>
       <c r="G247" t="n">
-        <v>2966</v>
+        <v>2968</v>
       </c>
       <c r="H247" t="n">
-        <v>2984</v>
+        <v>2987</v>
       </c>
       <c r="I247" t="n">
-        <v>3125</v>
+        <v>3129</v>
       </c>
       <c r="J247" t="n">
-        <v>3526</v>
+        <v>3535</v>
       </c>
       <c r="K247" t="n">
-        <v>3835</v>
+        <v>3847</v>
       </c>
       <c r="L247" t="n">
-        <v>4078</v>
+        <v>4093</v>
       </c>
       <c r="M247" t="n">
-        <v>4145</v>
+        <v>4161</v>
       </c>
       <c r="N247" t="n">
-        <v>4016</v>
+        <v>4034</v>
       </c>
       <c r="O247" t="n">
+        <v>4024</v>
+      </c>
+      <c r="P247" t="n">
         <v>4006</v>
       </c>
-      <c r="P247" t="n">
-        <v>3988</v>
-      </c>
       <c r="Q247" t="n">
-        <v>4092</v>
+        <v>4109</v>
       </c>
       <c r="R247" t="n">
-        <v>3977</v>
+        <v>3995</v>
       </c>
       <c r="S247" t="n">
-        <v>3894</v>
+        <v>3913</v>
       </c>
       <c r="T247" t="n">
-        <v>3744</v>
+        <v>3766</v>
       </c>
       <c r="U247" t="n">
-        <v>3769</v>
+        <v>3791</v>
       </c>
       <c r="V247" t="n">
-        <v>3991</v>
+        <v>4019</v>
       </c>
       <c r="W247" t="n">
-        <v>4400</v>
+        <v>4438</v>
       </c>
       <c r="X247" t="n">
-        <v>4358</v>
+        <v>4395</v>
       </c>
       <c r="Y247" t="n">
-        <v>4105</v>
+        <v>4141</v>
       </c>
       <c r="Z247" t="n">
-        <v>3856</v>
+        <v>3890</v>
       </c>
       <c r="AA247" t="n">
-        <v>3615</v>
+        <v>3648</v>
       </c>
     </row>
     <row r="248">
@@ -20992,76 +20992,76 @@
         <v>9</v>
       </c>
       <c r="D248" t="n">
-        <v>3223</v>
+        <v>3264</v>
       </c>
       <c r="E248" t="n">
-        <v>3038</v>
+        <v>3055</v>
       </c>
       <c r="F248" t="n">
-        <v>2955</v>
+        <v>2962</v>
       </c>
       <c r="G248" t="n">
-        <v>2915</v>
+        <v>2917</v>
       </c>
       <c r="H248" t="n">
-        <v>2933</v>
+        <v>2935</v>
       </c>
       <c r="I248" t="n">
-        <v>3069</v>
+        <v>3073</v>
       </c>
       <c r="J248" t="n">
-        <v>3459</v>
+        <v>3467</v>
       </c>
       <c r="K248" t="n">
-        <v>3758</v>
+        <v>3770</v>
       </c>
       <c r="L248" t="n">
-        <v>3994</v>
+        <v>4009</v>
       </c>
       <c r="M248" t="n">
-        <v>4059</v>
+        <v>4075</v>
       </c>
       <c r="N248" t="n">
-        <v>3929</v>
+        <v>3947</v>
       </c>
       <c r="O248" t="n">
+        <v>3937</v>
+      </c>
+      <c r="P248" t="n">
         <v>3919</v>
       </c>
-      <c r="P248" t="n">
-        <v>3900</v>
-      </c>
       <c r="Q248" t="n">
-        <v>4006</v>
+        <v>4023</v>
       </c>
       <c r="R248" t="n">
-        <v>3890</v>
+        <v>3908</v>
       </c>
       <c r="S248" t="n">
-        <v>3806</v>
+        <v>3825</v>
       </c>
       <c r="T248" t="n">
-        <v>3655</v>
+        <v>3677</v>
       </c>
       <c r="U248" t="n">
-        <v>3677</v>
+        <v>3699</v>
       </c>
       <c r="V248" t="n">
-        <v>3877</v>
+        <v>3905</v>
       </c>
       <c r="W248" t="n">
-        <v>4245</v>
+        <v>4283</v>
       </c>
       <c r="X248" t="n">
-        <v>4206</v>
+        <v>4244</v>
       </c>
       <c r="Y248" t="n">
-        <v>3972</v>
+        <v>4008</v>
       </c>
       <c r="Z248" t="n">
-        <v>3740</v>
+        <v>3774</v>
       </c>
       <c r="AA248" t="n">
-        <v>3516</v>
+        <v>3549</v>
       </c>
     </row>
     <row r="249">
@@ -21075,76 +21075,76 @@
         <v>10</v>
       </c>
       <c r="D249" t="n">
-        <v>3214</v>
+        <v>3255</v>
       </c>
       <c r="E249" t="n">
-        <v>3017</v>
+        <v>3037</v>
       </c>
       <c r="F249" t="n">
-        <v>2909</v>
+        <v>2917</v>
       </c>
       <c r="G249" t="n">
-        <v>2866</v>
+        <v>2870</v>
       </c>
       <c r="H249" t="n">
-        <v>2854</v>
+        <v>2856</v>
       </c>
       <c r="I249" t="n">
-        <v>2897</v>
+        <v>2900</v>
       </c>
       <c r="J249" t="n">
-        <v>3050</v>
+        <v>3055</v>
       </c>
       <c r="K249" t="n">
-        <v>3231</v>
+        <v>3239</v>
       </c>
       <c r="L249" t="n">
-        <v>3478</v>
+        <v>3490</v>
       </c>
       <c r="M249" t="n">
-        <v>3626</v>
+        <v>3640</v>
       </c>
       <c r="N249" t="n">
-        <v>3667</v>
+        <v>3681</v>
       </c>
       <c r="O249" t="n">
-        <v>3683</v>
+        <v>3698</v>
       </c>
       <c r="P249" t="n">
-        <v>3741</v>
+        <v>3757</v>
       </c>
       <c r="Q249" t="n">
-        <v>3670</v>
+        <v>3687</v>
       </c>
       <c r="R249" t="n">
-        <v>3541</v>
+        <v>3561</v>
       </c>
       <c r="S249" t="n">
-        <v>3502</v>
+        <v>3522</v>
       </c>
       <c r="T249" t="n">
-        <v>3427</v>
+        <v>3449</v>
       </c>
       <c r="U249" t="n">
-        <v>3495</v>
+        <v>3518</v>
       </c>
       <c r="V249" t="n">
-        <v>3653</v>
+        <v>3680</v>
       </c>
       <c r="W249" t="n">
-        <v>4050</v>
+        <v>4088</v>
       </c>
       <c r="X249" t="n">
-        <v>3974</v>
+        <v>4011</v>
       </c>
       <c r="Y249" t="n">
-        <v>3760</v>
+        <v>3795</v>
       </c>
       <c r="Z249" t="n">
-        <v>3580</v>
+        <v>3615</v>
       </c>
       <c r="AA249" t="n">
-        <v>3418</v>
+        <v>3452</v>
       </c>
     </row>
     <row r="250">
@@ -21158,76 +21158,159 @@
         <v>11</v>
       </c>
       <c r="D250" t="n">
-        <v>3188</v>
+        <v>3229</v>
       </c>
       <c r="E250" t="n">
-        <v>3000</v>
+        <v>3024</v>
       </c>
       <c r="F250" t="n">
-        <v>2918</v>
+        <v>2920</v>
       </c>
       <c r="G250" t="n">
-        <v>2859</v>
+        <v>2860</v>
       </c>
       <c r="H250" t="n">
-        <v>2844</v>
+        <v>2846</v>
       </c>
       <c r="I250" t="n">
-        <v>2877</v>
+        <v>2880</v>
       </c>
       <c r="J250" t="n">
-        <v>3033</v>
+        <v>3039</v>
       </c>
       <c r="K250" t="n">
-        <v>3201</v>
+        <v>3207</v>
       </c>
       <c r="L250" t="n">
-        <v>3473</v>
+        <v>3495</v>
       </c>
       <c r="M250" t="n">
-        <v>3684</v>
+        <v>3687</v>
       </c>
       <c r="N250" t="n">
-        <v>3739</v>
+        <v>3759</v>
       </c>
       <c r="O250" t="n">
-        <v>3733</v>
+        <v>3752</v>
       </c>
       <c r="P250" t="n">
-        <v>3789</v>
+        <v>3805</v>
       </c>
       <c r="Q250" t="n">
-        <v>3747</v>
+        <v>3754</v>
       </c>
       <c r="R250" t="n">
-        <v>3670</v>
+        <v>3668</v>
       </c>
       <c r="S250" t="n">
-        <v>3596</v>
+        <v>3604</v>
       </c>
       <c r="T250" t="n">
-        <v>3553</v>
+        <v>3575</v>
       </c>
       <c r="U250" t="n">
-        <v>3696</v>
+        <v>3697</v>
       </c>
       <c r="V250" t="n">
-        <v>3852</v>
+        <v>3882</v>
       </c>
       <c r="W250" t="n">
-        <v>4324</v>
+        <v>4344</v>
       </c>
       <c r="X250" t="n">
-        <v>4298</v>
+        <v>4361</v>
       </c>
       <c r="Y250" t="n">
-        <v>4129</v>
+        <v>4107</v>
       </c>
       <c r="Z250" t="n">
-        <v>3807</v>
+        <v>3824</v>
       </c>
       <c r="AA250" t="n">
-        <v>3549</v>
+        <v>3582</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B251" t="n">
+        <v>10</v>
+      </c>
+      <c r="C251" t="n">
+        <v>12</v>
+      </c>
+      <c r="D251" t="n">
+        <v>3280</v>
+      </c>
+      <c r="E251" t="n">
+        <v>3071</v>
+      </c>
+      <c r="F251" t="n">
+        <v>2969</v>
+      </c>
+      <c r="G251" t="n">
+        <v>2933</v>
+      </c>
+      <c r="H251" t="n">
+        <v>2957</v>
+      </c>
+      <c r="I251" t="n">
+        <v>3123</v>
+      </c>
+      <c r="J251" t="n">
+        <v>3660</v>
+      </c>
+      <c r="K251" t="n">
+        <v>4034</v>
+      </c>
+      <c r="L251" t="n">
+        <v>4261</v>
+      </c>
+      <c r="M251" t="n">
+        <v>4310</v>
+      </c>
+      <c r="N251" t="n">
+        <v>4161</v>
+      </c>
+      <c r="O251" t="n">
+        <v>4147</v>
+      </c>
+      <c r="P251" t="n">
+        <v>4236</v>
+      </c>
+      <c r="Q251" t="n">
+        <v>4231</v>
+      </c>
+      <c r="R251" t="n">
+        <v>4148</v>
+      </c>
+      <c r="S251" t="n">
+        <v>4033</v>
+      </c>
+      <c r="T251" t="n">
+        <v>3933</v>
+      </c>
+      <c r="U251" t="n">
+        <v>3951</v>
+      </c>
+      <c r="V251" t="n">
+        <v>4206</v>
+      </c>
+      <c r="W251" t="n">
+        <v>4594</v>
+      </c>
+      <c r="X251" t="n">
+        <v>4551</v>
+      </c>
+      <c r="Y251" t="n">
+        <v>4263</v>
+      </c>
+      <c r="Z251" t="n">
+        <v>4023</v>
+      </c>
+      <c r="AA251" t="n">
+        <v>3756</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA251"/>
+  <dimension ref="A1:AA252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20909,76 +20909,76 @@
         <v>8</v>
       </c>
       <c r="D247" t="n">
-        <v>3306</v>
+        <v>3404</v>
       </c>
       <c r="E247" t="n">
-        <v>3102</v>
+        <v>3222</v>
       </c>
       <c r="F247" t="n">
-        <v>3012</v>
+        <v>3139</v>
       </c>
       <c r="G247" t="n">
-        <v>2968</v>
+        <v>3094</v>
       </c>
       <c r="H247" t="n">
-        <v>2987</v>
+        <v>3121</v>
       </c>
       <c r="I247" t="n">
-        <v>3129</v>
+        <v>3268</v>
       </c>
       <c r="J247" t="n">
-        <v>3535</v>
+        <v>3678</v>
       </c>
       <c r="K247" t="n">
-        <v>3847</v>
+        <v>3997</v>
       </c>
       <c r="L247" t="n">
-        <v>4093</v>
+        <v>4234</v>
       </c>
       <c r="M247" t="n">
-        <v>4161</v>
+        <v>4287</v>
       </c>
       <c r="N247" t="n">
-        <v>4034</v>
+        <v>4096</v>
       </c>
       <c r="O247" t="n">
-        <v>4024</v>
+        <v>4006</v>
       </c>
       <c r="P247" t="n">
-        <v>4006</v>
+        <v>3865</v>
       </c>
       <c r="Q247" t="n">
-        <v>4109</v>
+        <v>3996</v>
       </c>
       <c r="R247" t="n">
-        <v>3995</v>
+        <v>3856</v>
       </c>
       <c r="S247" t="n">
-        <v>3913</v>
+        <v>3805</v>
       </c>
       <c r="T247" t="n">
-        <v>3766</v>
+        <v>3689</v>
       </c>
       <c r="U247" t="n">
-        <v>3791</v>
+        <v>3724</v>
       </c>
       <c r="V247" t="n">
-        <v>4019</v>
+        <v>4013</v>
       </c>
       <c r="W247" t="n">
-        <v>4438</v>
+        <v>4571</v>
       </c>
       <c r="X247" t="n">
-        <v>4395</v>
+        <v>4502</v>
       </c>
       <c r="Y247" t="n">
-        <v>4141</v>
+        <v>4264</v>
       </c>
       <c r="Z247" t="n">
-        <v>3890</v>
+        <v>3996</v>
       </c>
       <c r="AA247" t="n">
-        <v>3648</v>
+        <v>3729</v>
       </c>
     </row>
     <row r="248">
@@ -20992,76 +20992,76 @@
         <v>9</v>
       </c>
       <c r="D248" t="n">
-        <v>3264</v>
+        <v>3342</v>
       </c>
       <c r="E248" t="n">
-        <v>3055</v>
+        <v>3152</v>
       </c>
       <c r="F248" t="n">
-        <v>2962</v>
+        <v>3065</v>
       </c>
       <c r="G248" t="n">
-        <v>2917</v>
+        <v>3018</v>
       </c>
       <c r="H248" t="n">
-        <v>2935</v>
+        <v>3043</v>
       </c>
       <c r="I248" t="n">
-        <v>3073</v>
+        <v>3184</v>
       </c>
       <c r="J248" t="n">
-        <v>3467</v>
+        <v>3575</v>
       </c>
       <c r="K248" t="n">
-        <v>3770</v>
+        <v>3880</v>
       </c>
       <c r="L248" t="n">
-        <v>4009</v>
+        <v>4107</v>
       </c>
       <c r="M248" t="n">
-        <v>4075</v>
+        <v>4157</v>
       </c>
       <c r="N248" t="n">
-        <v>3947</v>
+        <v>3965</v>
       </c>
       <c r="O248" t="n">
-        <v>3937</v>
+        <v>3874</v>
       </c>
       <c r="P248" t="n">
-        <v>3919</v>
+        <v>3732</v>
       </c>
       <c r="Q248" t="n">
-        <v>4023</v>
+        <v>3864</v>
       </c>
       <c r="R248" t="n">
-        <v>3908</v>
+        <v>3723</v>
       </c>
       <c r="S248" t="n">
-        <v>3825</v>
+        <v>3672</v>
       </c>
       <c r="T248" t="n">
-        <v>3677</v>
+        <v>3555</v>
       </c>
       <c r="U248" t="n">
-        <v>3699</v>
+        <v>3587</v>
       </c>
       <c r="V248" t="n">
-        <v>3905</v>
+        <v>3857</v>
       </c>
       <c r="W248" t="n">
-        <v>4283</v>
+        <v>4379</v>
       </c>
       <c r="X248" t="n">
-        <v>4244</v>
+        <v>4316</v>
       </c>
       <c r="Y248" t="n">
-        <v>4008</v>
+        <v>4097</v>
       </c>
       <c r="Z248" t="n">
-        <v>3774</v>
+        <v>3850</v>
       </c>
       <c r="AA248" t="n">
-        <v>3549</v>
+        <v>3604</v>
       </c>
     </row>
     <row r="249">
@@ -21075,76 +21075,76 @@
         <v>10</v>
       </c>
       <c r="D249" t="n">
-        <v>3255</v>
+        <v>3296</v>
       </c>
       <c r="E249" t="n">
-        <v>3037</v>
+        <v>3080</v>
       </c>
       <c r="F249" t="n">
-        <v>2917</v>
+        <v>2962</v>
       </c>
       <c r="G249" t="n">
-        <v>2870</v>
+        <v>2915</v>
       </c>
       <c r="H249" t="n">
-        <v>2856</v>
+        <v>2911</v>
       </c>
       <c r="I249" t="n">
-        <v>2900</v>
+        <v>2963</v>
       </c>
       <c r="J249" t="n">
-        <v>3055</v>
+        <v>3152</v>
       </c>
       <c r="K249" t="n">
-        <v>3239</v>
+        <v>3366</v>
       </c>
       <c r="L249" t="n">
-        <v>3490</v>
+        <v>3643</v>
       </c>
       <c r="M249" t="n">
-        <v>3640</v>
+        <v>3768</v>
       </c>
       <c r="N249" t="n">
-        <v>3681</v>
+        <v>3763</v>
       </c>
       <c r="O249" t="n">
-        <v>3698</v>
+        <v>3726</v>
       </c>
       <c r="P249" t="n">
-        <v>3757</v>
+        <v>3694</v>
       </c>
       <c r="Q249" t="n">
-        <v>3687</v>
+        <v>3546</v>
       </c>
       <c r="R249" t="n">
-        <v>3561</v>
+        <v>3432</v>
       </c>
       <c r="S249" t="n">
-        <v>3522</v>
+        <v>3298</v>
       </c>
       <c r="T249" t="n">
-        <v>3449</v>
+        <v>3250</v>
       </c>
       <c r="U249" t="n">
-        <v>3518</v>
+        <v>3417</v>
       </c>
       <c r="V249" t="n">
-        <v>3680</v>
+        <v>3651</v>
       </c>
       <c r="W249" t="n">
-        <v>4088</v>
+        <v>4119</v>
       </c>
       <c r="X249" t="n">
-        <v>4011</v>
+        <v>4073</v>
       </c>
       <c r="Y249" t="n">
-        <v>3795</v>
+        <v>3842</v>
       </c>
       <c r="Z249" t="n">
-        <v>3615</v>
+        <v>3638</v>
       </c>
       <c r="AA249" t="n">
-        <v>3452</v>
+        <v>3463</v>
       </c>
     </row>
     <row r="250">
@@ -21158,76 +21158,76 @@
         <v>11</v>
       </c>
       <c r="D250" t="n">
-        <v>3229</v>
+        <v>3259</v>
       </c>
       <c r="E250" t="n">
-        <v>3024</v>
+        <v>3060</v>
       </c>
       <c r="F250" t="n">
-        <v>2920</v>
+        <v>2959</v>
       </c>
       <c r="G250" t="n">
-        <v>2860</v>
+        <v>2901</v>
       </c>
       <c r="H250" t="n">
-        <v>2846</v>
+        <v>2888</v>
       </c>
       <c r="I250" t="n">
-        <v>2880</v>
+        <v>2919</v>
       </c>
       <c r="J250" t="n">
-        <v>3039</v>
+        <v>3070</v>
       </c>
       <c r="K250" t="n">
-        <v>3207</v>
+        <v>3230</v>
       </c>
       <c r="L250" t="n">
-        <v>3495</v>
+        <v>3502</v>
       </c>
       <c r="M250" t="n">
-        <v>3687</v>
+        <v>3684</v>
       </c>
       <c r="N250" t="n">
-        <v>3759</v>
+        <v>3752</v>
       </c>
       <c r="O250" t="n">
-        <v>3752</v>
+        <v>3745</v>
       </c>
       <c r="P250" t="n">
-        <v>3805</v>
+        <v>3795</v>
       </c>
       <c r="Q250" t="n">
-        <v>3754</v>
+        <v>3697</v>
       </c>
       <c r="R250" t="n">
-        <v>3668</v>
+        <v>3531</v>
       </c>
       <c r="S250" t="n">
-        <v>3604</v>
+        <v>3409</v>
       </c>
       <c r="T250" t="n">
-        <v>3575</v>
+        <v>3353</v>
       </c>
       <c r="U250" t="n">
-        <v>3697</v>
+        <v>3511</v>
       </c>
       <c r="V250" t="n">
-        <v>3882</v>
+        <v>3751</v>
       </c>
       <c r="W250" t="n">
-        <v>4344</v>
+        <v>4351</v>
       </c>
       <c r="X250" t="n">
-        <v>4361</v>
+        <v>4373</v>
       </c>
       <c r="Y250" t="n">
-        <v>4107</v>
+        <v>4115</v>
       </c>
       <c r="Z250" t="n">
-        <v>3824</v>
+        <v>3827</v>
       </c>
       <c r="AA250" t="n">
-        <v>3582</v>
+        <v>3580</v>
       </c>
     </row>
     <row r="251">
@@ -21241,76 +21241,159 @@
         <v>12</v>
       </c>
       <c r="D251" t="n">
-        <v>3280</v>
+        <v>3360</v>
       </c>
       <c r="E251" t="n">
-        <v>3071</v>
+        <v>3160</v>
       </c>
       <c r="F251" t="n">
-        <v>2969</v>
+        <v>3070</v>
       </c>
       <c r="G251" t="n">
-        <v>2933</v>
+        <v>3034</v>
       </c>
       <c r="H251" t="n">
-        <v>2957</v>
+        <v>3070</v>
       </c>
       <c r="I251" t="n">
-        <v>3123</v>
+        <v>3245</v>
       </c>
       <c r="J251" t="n">
-        <v>3660</v>
+        <v>3789</v>
       </c>
       <c r="K251" t="n">
-        <v>4034</v>
+        <v>4180</v>
       </c>
       <c r="L251" t="n">
-        <v>4261</v>
+        <v>4404</v>
       </c>
       <c r="M251" t="n">
-        <v>4310</v>
+        <v>4402</v>
       </c>
       <c r="N251" t="n">
-        <v>4161</v>
+        <v>4164</v>
       </c>
       <c r="O251" t="n">
-        <v>4147</v>
+        <v>4059</v>
       </c>
       <c r="P251" t="n">
-        <v>4236</v>
+        <v>4054</v>
       </c>
       <c r="Q251" t="n">
-        <v>4231</v>
+        <v>4063</v>
       </c>
       <c r="R251" t="n">
-        <v>4148</v>
+        <v>3974</v>
       </c>
       <c r="S251" t="n">
-        <v>4033</v>
+        <v>3889</v>
       </c>
       <c r="T251" t="n">
-        <v>3933</v>
+        <v>3814</v>
       </c>
       <c r="U251" t="n">
-        <v>3951</v>
+        <v>3854</v>
       </c>
       <c r="V251" t="n">
-        <v>4206</v>
+        <v>4141</v>
       </c>
       <c r="W251" t="n">
-        <v>4594</v>
+        <v>4693</v>
       </c>
       <c r="X251" t="n">
-        <v>4551</v>
+        <v>4660</v>
       </c>
       <c r="Y251" t="n">
-        <v>4263</v>
+        <v>4378</v>
       </c>
       <c r="Z251" t="n">
-        <v>4023</v>
+        <v>4090</v>
       </c>
       <c r="AA251" t="n">
-        <v>3756</v>
+        <v>3813</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B252" t="n">
+        <v>10</v>
+      </c>
+      <c r="C252" t="n">
+        <v>13</v>
+      </c>
+      <c r="D252" t="n">
+        <v>3459</v>
+      </c>
+      <c r="E252" t="n">
+        <v>3286</v>
+      </c>
+      <c r="F252" t="n">
+        <v>3207</v>
+      </c>
+      <c r="G252" t="n">
+        <v>3164</v>
+      </c>
+      <c r="H252" t="n">
+        <v>3194</v>
+      </c>
+      <c r="I252" t="n">
+        <v>3358</v>
+      </c>
+      <c r="J252" t="n">
+        <v>3815</v>
+      </c>
+      <c r="K252" t="n">
+        <v>4170</v>
+      </c>
+      <c r="L252" t="n">
+        <v>4435</v>
+      </c>
+      <c r="M252" t="n">
+        <v>4494</v>
+      </c>
+      <c r="N252" t="n">
+        <v>4306</v>
+      </c>
+      <c r="O252" t="n">
+        <v>4218</v>
+      </c>
+      <c r="P252" t="n">
+        <v>4079</v>
+      </c>
+      <c r="Q252" t="n">
+        <v>4208</v>
+      </c>
+      <c r="R252" t="n">
+        <v>4071</v>
+      </c>
+      <c r="S252" t="n">
+        <v>4021</v>
+      </c>
+      <c r="T252" t="n">
+        <v>3907</v>
+      </c>
+      <c r="U252" t="n">
+        <v>3941</v>
+      </c>
+      <c r="V252" t="n">
+        <v>4224</v>
+      </c>
+      <c r="W252" t="n">
+        <v>4770</v>
+      </c>
+      <c r="X252" t="n">
+        <v>4697</v>
+      </c>
+      <c r="Y252" t="n">
+        <v>4441</v>
+      </c>
+      <c r="Z252" t="n">
+        <v>4153</v>
+      </c>
+      <c r="AA252" t="n">
+        <v>3866</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA252"/>
+  <dimension ref="A1:AA253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20992,76 +20992,76 @@
         <v>9</v>
       </c>
       <c r="D248" t="n">
-        <v>3342</v>
+        <v>3302</v>
       </c>
       <c r="E248" t="n">
-        <v>3152</v>
+        <v>3119</v>
       </c>
       <c r="F248" t="n">
-        <v>3065</v>
+        <v>3027</v>
       </c>
       <c r="G248" t="n">
-        <v>3018</v>
+        <v>2967</v>
       </c>
       <c r="H248" t="n">
-        <v>3043</v>
+        <v>2994</v>
       </c>
       <c r="I248" t="n">
-        <v>3184</v>
+        <v>3127</v>
       </c>
       <c r="J248" t="n">
-        <v>3575</v>
+        <v>3512</v>
       </c>
       <c r="K248" t="n">
+        <v>3817</v>
+      </c>
+      <c r="L248" t="n">
+        <v>4036</v>
+      </c>
+      <c r="M248" t="n">
+        <v>4088</v>
+      </c>
+      <c r="N248" t="n">
+        <v>3932</v>
+      </c>
+      <c r="O248" t="n">
         <v>3880</v>
       </c>
-      <c r="L248" t="n">
-        <v>4107</v>
-      </c>
-      <c r="M248" t="n">
-        <v>4157</v>
-      </c>
-      <c r="N248" t="n">
-        <v>3965</v>
-      </c>
-      <c r="O248" t="n">
-        <v>3874</v>
-      </c>
       <c r="P248" t="n">
-        <v>3732</v>
+        <v>3823</v>
       </c>
       <c r="Q248" t="n">
-        <v>3864</v>
+        <v>3905</v>
       </c>
       <c r="R248" t="n">
-        <v>3723</v>
+        <v>3819</v>
       </c>
       <c r="S248" t="n">
-        <v>3672</v>
+        <v>3743</v>
       </c>
       <c r="T248" t="n">
-        <v>3555</v>
+        <v>3627</v>
       </c>
       <c r="U248" t="n">
-        <v>3587</v>
+        <v>3659</v>
       </c>
       <c r="V248" t="n">
-        <v>3857</v>
+        <v>3905</v>
       </c>
       <c r="W248" t="n">
-        <v>4379</v>
+        <v>4364</v>
       </c>
       <c r="X248" t="n">
-        <v>4316</v>
+        <v>4335</v>
       </c>
       <c r="Y248" t="n">
-        <v>4097</v>
+        <v>4074</v>
       </c>
       <c r="Z248" t="n">
-        <v>3850</v>
+        <v>3806</v>
       </c>
       <c r="AA248" t="n">
-        <v>3604</v>
+        <v>3547</v>
       </c>
     </row>
     <row r="249">
@@ -21075,76 +21075,76 @@
         <v>10</v>
       </c>
       <c r="D249" t="n">
-        <v>3296</v>
+        <v>3257</v>
       </c>
       <c r="E249" t="n">
-        <v>3080</v>
+        <v>3034</v>
       </c>
       <c r="F249" t="n">
-        <v>2962</v>
+        <v>2912</v>
       </c>
       <c r="G249" t="n">
-        <v>2915</v>
+        <v>2864</v>
       </c>
       <c r="H249" t="n">
+        <v>2859</v>
+      </c>
+      <c r="I249" t="n">
         <v>2911</v>
       </c>
-      <c r="I249" t="n">
-        <v>2963</v>
-      </c>
       <c r="J249" t="n">
-        <v>3152</v>
+        <v>3096</v>
       </c>
       <c r="K249" t="n">
-        <v>3366</v>
+        <v>3306</v>
       </c>
       <c r="L249" t="n">
-        <v>3643</v>
+        <v>3577</v>
       </c>
       <c r="M249" t="n">
-        <v>3768</v>
+        <v>3699</v>
       </c>
       <c r="N249" t="n">
-        <v>3763</v>
+        <v>3695</v>
       </c>
       <c r="O249" t="n">
-        <v>3726</v>
+        <v>3669</v>
       </c>
       <c r="P249" t="n">
-        <v>3694</v>
+        <v>3645</v>
       </c>
       <c r="Q249" t="n">
-        <v>3546</v>
+        <v>3538</v>
       </c>
       <c r="R249" t="n">
-        <v>3432</v>
+        <v>3455</v>
       </c>
       <c r="S249" t="n">
-        <v>3298</v>
+        <v>3358</v>
       </c>
       <c r="T249" t="n">
-        <v>3250</v>
+        <v>3323</v>
       </c>
       <c r="U249" t="n">
-        <v>3417</v>
+        <v>3472</v>
       </c>
       <c r="V249" t="n">
-        <v>3651</v>
+        <v>3683</v>
       </c>
       <c r="W249" t="n">
-        <v>4119</v>
+        <v>4105</v>
       </c>
       <c r="X249" t="n">
-        <v>4073</v>
+        <v>4056</v>
       </c>
       <c r="Y249" t="n">
-        <v>3842</v>
+        <v>3810</v>
       </c>
       <c r="Z249" t="n">
-        <v>3638</v>
+        <v>3592</v>
       </c>
       <c r="AA249" t="n">
-        <v>3463</v>
+        <v>3406</v>
       </c>
     </row>
     <row r="250">
@@ -21158,76 +21158,76 @@
         <v>11</v>
       </c>
       <c r="D250" t="n">
-        <v>3259</v>
+        <v>3220</v>
       </c>
       <c r="E250" t="n">
-        <v>3060</v>
+        <v>3015</v>
       </c>
       <c r="F250" t="n">
-        <v>2959</v>
+        <v>2910</v>
       </c>
       <c r="G250" t="n">
-        <v>2901</v>
+        <v>2850</v>
       </c>
       <c r="H250" t="n">
-        <v>2888</v>
+        <v>2836</v>
       </c>
       <c r="I250" t="n">
-        <v>2919</v>
+        <v>2867</v>
       </c>
       <c r="J250" t="n">
-        <v>3070</v>
+        <v>3016</v>
       </c>
       <c r="K250" t="n">
-        <v>3230</v>
+        <v>3172</v>
       </c>
       <c r="L250" t="n">
-        <v>3502</v>
+        <v>3439</v>
       </c>
       <c r="M250" t="n">
+        <v>3617</v>
+      </c>
+      <c r="N250" t="n">
         <v>3684</v>
       </c>
-      <c r="N250" t="n">
-        <v>3752</v>
-      </c>
       <c r="O250" t="n">
-        <v>3745</v>
+        <v>3677</v>
       </c>
       <c r="P250" t="n">
-        <v>3795</v>
+        <v>3726</v>
       </c>
       <c r="Q250" t="n">
-        <v>3697</v>
+        <v>3659</v>
       </c>
       <c r="R250" t="n">
-        <v>3531</v>
+        <v>3547</v>
       </c>
       <c r="S250" t="n">
-        <v>3409</v>
+        <v>3463</v>
       </c>
       <c r="T250" t="n">
-        <v>3353</v>
+        <v>3425</v>
       </c>
       <c r="U250" t="n">
-        <v>3511</v>
+        <v>3570</v>
       </c>
       <c r="V250" t="n">
-        <v>3751</v>
+        <v>3789</v>
       </c>
       <c r="W250" t="n">
-        <v>4351</v>
+        <v>4339</v>
       </c>
       <c r="X250" t="n">
-        <v>4373</v>
+        <v>4359</v>
       </c>
       <c r="Y250" t="n">
-        <v>4115</v>
+        <v>4087</v>
       </c>
       <c r="Z250" t="n">
-        <v>3827</v>
+        <v>3783</v>
       </c>
       <c r="AA250" t="n">
-        <v>3580</v>
+        <v>3523</v>
       </c>
     </row>
     <row r="251">
@@ -21241,76 +21241,76 @@
         <v>12</v>
       </c>
       <c r="D251" t="n">
-        <v>3360</v>
+        <v>3320</v>
       </c>
       <c r="E251" t="n">
-        <v>3160</v>
+        <v>3114</v>
       </c>
       <c r="F251" t="n">
-        <v>3070</v>
+        <v>3020</v>
       </c>
       <c r="G251" t="n">
-        <v>3034</v>
+        <v>2982</v>
       </c>
       <c r="H251" t="n">
-        <v>3070</v>
+        <v>3018</v>
       </c>
       <c r="I251" t="n">
-        <v>3245</v>
+        <v>3191</v>
       </c>
       <c r="J251" t="n">
-        <v>3789</v>
+        <v>3728</v>
       </c>
       <c r="K251" t="n">
-        <v>4180</v>
+        <v>4114</v>
       </c>
       <c r="L251" t="n">
-        <v>4404</v>
+        <v>4335</v>
       </c>
       <c r="M251" t="n">
-        <v>4402</v>
+        <v>4334</v>
       </c>
       <c r="N251" t="n">
-        <v>4164</v>
+        <v>4152</v>
       </c>
       <c r="O251" t="n">
-        <v>4059</v>
+        <v>4073</v>
       </c>
       <c r="P251" t="n">
-        <v>4054</v>
+        <v>4069</v>
       </c>
       <c r="Q251" t="n">
-        <v>4063</v>
+        <v>4076</v>
       </c>
       <c r="R251" t="n">
-        <v>3974</v>
+        <v>4008</v>
       </c>
       <c r="S251" t="n">
-        <v>3889</v>
+        <v>3944</v>
       </c>
       <c r="T251" t="n">
-        <v>3814</v>
+        <v>3887</v>
       </c>
       <c r="U251" t="n">
-        <v>3854</v>
+        <v>3922</v>
       </c>
       <c r="V251" t="n">
-        <v>4141</v>
+        <v>4181</v>
       </c>
       <c r="W251" t="n">
-        <v>4693</v>
+        <v>4679</v>
       </c>
       <c r="X251" t="n">
-        <v>4660</v>
+        <v>4644</v>
       </c>
       <c r="Y251" t="n">
-        <v>4378</v>
+        <v>4349</v>
       </c>
       <c r="Z251" t="n">
-        <v>4090</v>
+        <v>4046</v>
       </c>
       <c r="AA251" t="n">
-        <v>3813</v>
+        <v>3756</v>
       </c>
     </row>
     <row r="252">
@@ -21324,75 +21324,158 @@
         <v>13</v>
       </c>
       <c r="D252" t="n">
-        <v>3459</v>
+        <v>3419</v>
       </c>
       <c r="E252" t="n">
-        <v>3286</v>
+        <v>3252</v>
       </c>
       <c r="F252" t="n">
-        <v>3207</v>
+        <v>3168</v>
       </c>
       <c r="G252" t="n">
-        <v>3164</v>
+        <v>3113</v>
       </c>
       <c r="H252" t="n">
-        <v>3194</v>
+        <v>3145</v>
       </c>
       <c r="I252" t="n">
-        <v>3358</v>
+        <v>3300</v>
       </c>
       <c r="J252" t="n">
-        <v>3815</v>
+        <v>3751</v>
       </c>
       <c r="K252" t="n">
-        <v>4170</v>
+        <v>4107</v>
       </c>
       <c r="L252" t="n">
-        <v>4435</v>
+        <v>4364</v>
       </c>
       <c r="M252" t="n">
+        <v>4425</v>
+      </c>
+      <c r="N252" t="n">
+        <v>4274</v>
+      </c>
+      <c r="O252" t="n">
+        <v>4224</v>
+      </c>
+      <c r="P252" t="n">
+        <v>4169</v>
+      </c>
+      <c r="Q252" t="n">
+        <v>4248</v>
+      </c>
+      <c r="R252" t="n">
+        <v>4164</v>
+      </c>
+      <c r="S252" t="n">
+        <v>4091</v>
+      </c>
+      <c r="T252" t="n">
+        <v>3979</v>
+      </c>
+      <c r="U252" t="n">
+        <v>4013</v>
+      </c>
+      <c r="V252" t="n">
+        <v>4272</v>
+      </c>
+      <c r="W252" t="n">
+        <v>4756</v>
+      </c>
+      <c r="X252" t="n">
+        <v>4722</v>
+      </c>
+      <c r="Y252" t="n">
+        <v>4420</v>
+      </c>
+      <c r="Z252" t="n">
+        <v>4109</v>
+      </c>
+      <c r="AA252" t="n">
+        <v>3809</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B253" t="n">
+        <v>10</v>
+      </c>
+      <c r="C253" t="n">
+        <v>14</v>
+      </c>
+      <c r="D253" t="n">
+        <v>3465</v>
+      </c>
+      <c r="E253" t="n">
+        <v>3304</v>
+      </c>
+      <c r="F253" t="n">
+        <v>3223</v>
+      </c>
+      <c r="G253" t="n">
+        <v>3170</v>
+      </c>
+      <c r="H253" t="n">
+        <v>3202</v>
+      </c>
+      <c r="I253" t="n">
+        <v>3362</v>
+      </c>
+      <c r="J253" t="n">
+        <v>3827</v>
+      </c>
+      <c r="K253" t="n">
+        <v>4193</v>
+      </c>
+      <c r="L253" t="n">
+        <v>4458</v>
+      </c>
+      <c r="M253" t="n">
+        <v>4521</v>
+      </c>
+      <c r="N253" t="n">
+        <v>4371</v>
+      </c>
+      <c r="O253" t="n">
+        <v>4322</v>
+      </c>
+      <c r="P253" t="n">
+        <v>4267</v>
+      </c>
+      <c r="Q253" t="n">
+        <v>4345</v>
+      </c>
+      <c r="R253" t="n">
+        <v>4263</v>
+      </c>
+      <c r="S253" t="n">
+        <v>4190</v>
+      </c>
+      <c r="T253" t="n">
+        <v>4079</v>
+      </c>
+      <c r="U253" t="n">
+        <v>4112</v>
+      </c>
+      <c r="V253" t="n">
+        <v>4366</v>
+      </c>
+      <c r="W253" t="n">
+        <v>4839</v>
+      </c>
+      <c r="X253" t="n">
+        <v>4804</v>
+      </c>
+      <c r="Y253" t="n">
         <v>4494</v>
       </c>
-      <c r="N252" t="n">
-        <v>4306</v>
-      </c>
-      <c r="O252" t="n">
-        <v>4218</v>
-      </c>
-      <c r="P252" t="n">
-        <v>4079</v>
-      </c>
-      <c r="Q252" t="n">
-        <v>4208</v>
-      </c>
-      <c r="R252" t="n">
-        <v>4071</v>
-      </c>
-      <c r="S252" t="n">
-        <v>4021</v>
-      </c>
-      <c r="T252" t="n">
-        <v>3907</v>
-      </c>
-      <c r="U252" t="n">
-        <v>3941</v>
-      </c>
-      <c r="V252" t="n">
-        <v>4224</v>
-      </c>
-      <c r="W252" t="n">
-        <v>4770</v>
-      </c>
-      <c r="X252" t="n">
-        <v>4697</v>
-      </c>
-      <c r="Y252" t="n">
-        <v>4441</v>
-      </c>
-      <c r="Z252" t="n">
-        <v>4153</v>
-      </c>
-      <c r="AA252" t="n">
+      <c r="Z253" t="n">
+        <v>4174</v>
+      </c>
+      <c r="AA253" t="n">
         <v>3866</v>
       </c>
     </row>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA253"/>
+  <dimension ref="A1:AA254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21075,76 +21075,76 @@
         <v>10</v>
       </c>
       <c r="D249" t="n">
-        <v>3257</v>
+        <v>3350</v>
       </c>
       <c r="E249" t="n">
-        <v>3034</v>
+        <v>3113</v>
       </c>
       <c r="F249" t="n">
-        <v>2912</v>
+        <v>2983</v>
       </c>
       <c r="G249" t="n">
-        <v>2864</v>
+        <v>2932</v>
       </c>
       <c r="H249" t="n">
-        <v>2859</v>
+        <v>2926</v>
       </c>
       <c r="I249" t="n">
-        <v>2911</v>
+        <v>2984</v>
       </c>
       <c r="J249" t="n">
-        <v>3096</v>
+        <v>3192</v>
       </c>
       <c r="K249" t="n">
-        <v>3306</v>
+        <v>3427</v>
       </c>
       <c r="L249" t="n">
-        <v>3577</v>
+        <v>3731</v>
       </c>
       <c r="M249" t="n">
-        <v>3699</v>
+        <v>3868</v>
       </c>
       <c r="N249" t="n">
-        <v>3695</v>
+        <v>3866</v>
       </c>
       <c r="O249" t="n">
-        <v>3669</v>
+        <v>3847</v>
       </c>
       <c r="P249" t="n">
-        <v>3645</v>
+        <v>3830</v>
       </c>
       <c r="Q249" t="n">
-        <v>3538</v>
+        <v>3753</v>
       </c>
       <c r="R249" t="n">
-        <v>3455</v>
+        <v>3694</v>
       </c>
       <c r="S249" t="n">
-        <v>3358</v>
+        <v>3624</v>
       </c>
       <c r="T249" t="n">
-        <v>3323</v>
+        <v>3599</v>
       </c>
       <c r="U249" t="n">
-        <v>3472</v>
+        <v>3709</v>
       </c>
       <c r="V249" t="n">
-        <v>3683</v>
+        <v>3863</v>
       </c>
       <c r="W249" t="n">
-        <v>4105</v>
+        <v>4173</v>
       </c>
       <c r="X249" t="n">
-        <v>4056</v>
+        <v>4131</v>
       </c>
       <c r="Y249" t="n">
-        <v>3810</v>
+        <v>3915</v>
       </c>
       <c r="Z249" t="n">
-        <v>3592</v>
+        <v>3724</v>
       </c>
       <c r="AA249" t="n">
-        <v>3406</v>
+        <v>3561</v>
       </c>
     </row>
     <row r="250">
@@ -21158,76 +21158,76 @@
         <v>11</v>
       </c>
       <c r="D250" t="n">
-        <v>3220</v>
+        <v>3328</v>
       </c>
       <c r="E250" t="n">
-        <v>3015</v>
+        <v>3095</v>
       </c>
       <c r="F250" t="n">
-        <v>2910</v>
+        <v>2995</v>
       </c>
       <c r="G250" t="n">
-        <v>2850</v>
+        <v>2927</v>
       </c>
       <c r="H250" t="n">
-        <v>2836</v>
+        <v>2923</v>
       </c>
       <c r="I250" t="n">
-        <v>2867</v>
+        <v>2976</v>
       </c>
       <c r="J250" t="n">
-        <v>3016</v>
+        <v>3163</v>
       </c>
       <c r="K250" t="n">
-        <v>3172</v>
+        <v>3357</v>
       </c>
       <c r="L250" t="n">
-        <v>3439</v>
+        <v>3701</v>
       </c>
       <c r="M250" t="n">
-        <v>3617</v>
+        <v>3897</v>
       </c>
       <c r="N250" t="n">
-        <v>3684</v>
+        <v>3922</v>
       </c>
       <c r="O250" t="n">
-        <v>3677</v>
+        <v>3900</v>
       </c>
       <c r="P250" t="n">
-        <v>3726</v>
+        <v>3849</v>
       </c>
       <c r="Q250" t="n">
-        <v>3659</v>
+        <v>3805</v>
       </c>
       <c r="R250" t="n">
-        <v>3547</v>
+        <v>3768</v>
       </c>
       <c r="S250" t="n">
-        <v>3463</v>
+        <v>3731</v>
       </c>
       <c r="T250" t="n">
-        <v>3425</v>
+        <v>3758</v>
       </c>
       <c r="U250" t="n">
-        <v>3570</v>
+        <v>3879</v>
       </c>
       <c r="V250" t="n">
-        <v>3789</v>
+        <v>4061</v>
       </c>
       <c r="W250" t="n">
-        <v>4339</v>
+        <v>4437</v>
       </c>
       <c r="X250" t="n">
-        <v>4359</v>
+        <v>4454</v>
       </c>
       <c r="Y250" t="n">
-        <v>4087</v>
+        <v>4211</v>
       </c>
       <c r="Z250" t="n">
-        <v>3783</v>
+        <v>3924</v>
       </c>
       <c r="AA250" t="n">
-        <v>3523</v>
+        <v>3696</v>
       </c>
     </row>
     <row r="251">
@@ -21241,76 +21241,76 @@
         <v>12</v>
       </c>
       <c r="D251" t="n">
-        <v>3320</v>
+        <v>3415</v>
       </c>
       <c r="E251" t="n">
-        <v>3114</v>
+        <v>3193</v>
       </c>
       <c r="F251" t="n">
-        <v>3020</v>
+        <v>3093</v>
       </c>
       <c r="G251" t="n">
-        <v>2982</v>
+        <v>3052</v>
       </c>
       <c r="H251" t="n">
-        <v>3018</v>
+        <v>3091</v>
       </c>
       <c r="I251" t="n">
-        <v>3191</v>
+        <v>3276</v>
       </c>
       <c r="J251" t="n">
-        <v>3728</v>
+        <v>3852</v>
       </c>
       <c r="K251" t="n">
-        <v>4114</v>
+        <v>4266</v>
       </c>
       <c r="L251" t="n">
-        <v>4335</v>
+        <v>4502</v>
       </c>
       <c r="M251" t="n">
-        <v>4334</v>
+        <v>4501</v>
       </c>
       <c r="N251" t="n">
-        <v>4152</v>
+        <v>4365</v>
       </c>
       <c r="O251" t="n">
-        <v>4073</v>
+        <v>4305</v>
       </c>
       <c r="P251" t="n">
-        <v>4069</v>
+        <v>4302</v>
       </c>
       <c r="Q251" t="n">
-        <v>4076</v>
+        <v>4307</v>
       </c>
       <c r="R251" t="n">
-        <v>4008</v>
+        <v>4256</v>
       </c>
       <c r="S251" t="n">
-        <v>3944</v>
+        <v>4207</v>
       </c>
       <c r="T251" t="n">
-        <v>3887</v>
+        <v>4165</v>
       </c>
       <c r="U251" t="n">
-        <v>3922</v>
+        <v>4191</v>
       </c>
       <c r="V251" t="n">
-        <v>4181</v>
+        <v>4382</v>
       </c>
       <c r="W251" t="n">
-        <v>4679</v>
+        <v>4750</v>
       </c>
       <c r="X251" t="n">
-        <v>4644</v>
+        <v>4719</v>
       </c>
       <c r="Y251" t="n">
-        <v>4349</v>
+        <v>4451</v>
       </c>
       <c r="Z251" t="n">
-        <v>4046</v>
+        <v>4176</v>
       </c>
       <c r="AA251" t="n">
-        <v>3756</v>
+        <v>3913</v>
       </c>
     </row>
     <row r="252">
@@ -21324,76 +21324,76 @@
         <v>13</v>
       </c>
       <c r="D252" t="n">
-        <v>3419</v>
+        <v>3534</v>
       </c>
       <c r="E252" t="n">
-        <v>3252</v>
+        <v>3353</v>
       </c>
       <c r="F252" t="n">
-        <v>3168</v>
+        <v>3260</v>
       </c>
       <c r="G252" t="n">
-        <v>3113</v>
+        <v>3208</v>
       </c>
       <c r="H252" t="n">
-        <v>3145</v>
+        <v>3243</v>
       </c>
       <c r="I252" t="n">
-        <v>3300</v>
+        <v>3417</v>
       </c>
       <c r="J252" t="n">
-        <v>3751</v>
+        <v>3923</v>
       </c>
       <c r="K252" t="n">
-        <v>4107</v>
+        <v>4314</v>
       </c>
       <c r="L252" t="n">
-        <v>4364</v>
+        <v>4582</v>
       </c>
       <c r="M252" t="n">
-        <v>4425</v>
+        <v>4634</v>
       </c>
       <c r="N252" t="n">
+        <v>4518</v>
+      </c>
+      <c r="O252" t="n">
+        <v>4477</v>
+      </c>
+      <c r="P252" t="n">
+        <v>4415</v>
+      </c>
+      <c r="Q252" t="n">
+        <v>4474</v>
+      </c>
+      <c r="R252" t="n">
+        <v>4406</v>
+      </c>
+      <c r="S252" t="n">
+        <v>4373</v>
+      </c>
+      <c r="T252" t="n">
+        <v>4301</v>
+      </c>
+      <c r="U252" t="n">
+        <v>4331</v>
+      </c>
+      <c r="V252" t="n">
+        <v>4511</v>
+      </c>
+      <c r="W252" t="n">
+        <v>4864</v>
+      </c>
+      <c r="X252" t="n">
+        <v>4797</v>
+      </c>
+      <c r="Y252" t="n">
+        <v>4542</v>
+      </c>
+      <c r="Z252" t="n">
         <v>4274</v>
       </c>
-      <c r="O252" t="n">
-        <v>4224</v>
-      </c>
-      <c r="P252" t="n">
-        <v>4169</v>
-      </c>
-      <c r="Q252" t="n">
-        <v>4248</v>
-      </c>
-      <c r="R252" t="n">
-        <v>4164</v>
-      </c>
-      <c r="S252" t="n">
-        <v>4091</v>
-      </c>
-      <c r="T252" t="n">
-        <v>3979</v>
-      </c>
-      <c r="U252" t="n">
-        <v>4013</v>
-      </c>
-      <c r="V252" t="n">
-        <v>4272</v>
-      </c>
-      <c r="W252" t="n">
-        <v>4756</v>
-      </c>
-      <c r="X252" t="n">
-        <v>4722</v>
-      </c>
-      <c r="Y252" t="n">
-        <v>4420</v>
-      </c>
-      <c r="Z252" t="n">
-        <v>4109</v>
-      </c>
       <c r="AA252" t="n">
-        <v>3809</v>
+        <v>3991</v>
       </c>
     </row>
     <row r="253">
@@ -21407,76 +21407,159 @@
         <v>14</v>
       </c>
       <c r="D253" t="n">
-        <v>3465</v>
+        <v>3619</v>
       </c>
       <c r="E253" t="n">
-        <v>3304</v>
+        <v>3449</v>
       </c>
       <c r="F253" t="n">
-        <v>3223</v>
+        <v>3361</v>
       </c>
       <c r="G253" t="n">
-        <v>3170</v>
+        <v>3313</v>
       </c>
       <c r="H253" t="n">
-        <v>3202</v>
+        <v>3349</v>
       </c>
       <c r="I253" t="n">
-        <v>3362</v>
+        <v>3532</v>
       </c>
       <c r="J253" t="n">
-        <v>3827</v>
+        <v>4064</v>
       </c>
       <c r="K253" t="n">
-        <v>4193</v>
+        <v>4475</v>
       </c>
       <c r="L253" t="n">
-        <v>4458</v>
+        <v>4757</v>
       </c>
       <c r="M253" t="n">
-        <v>4521</v>
+        <v>4811</v>
       </c>
       <c r="N253" t="n">
-        <v>4371</v>
+        <v>4698</v>
       </c>
       <c r="O253" t="n">
-        <v>4322</v>
+        <v>4657</v>
       </c>
       <c r="P253" t="n">
-        <v>4267</v>
+        <v>4597</v>
       </c>
       <c r="Q253" t="n">
-        <v>4345</v>
+        <v>4655</v>
       </c>
       <c r="R253" t="n">
-        <v>4263</v>
+        <v>4588</v>
       </c>
       <c r="S253" t="n">
-        <v>4190</v>
+        <v>4555</v>
       </c>
       <c r="T253" t="n">
-        <v>4079</v>
+        <v>4484</v>
       </c>
       <c r="U253" t="n">
-        <v>4112</v>
+        <v>4513</v>
       </c>
       <c r="V253" t="n">
-        <v>4366</v>
+        <v>4683</v>
       </c>
       <c r="W253" t="n">
-        <v>4839</v>
+        <v>5017</v>
       </c>
       <c r="X253" t="n">
-        <v>4804</v>
+        <v>4947</v>
       </c>
       <c r="Y253" t="n">
-        <v>4494</v>
+        <v>4678</v>
       </c>
       <c r="Z253" t="n">
-        <v>4174</v>
+        <v>4395</v>
       </c>
       <c r="AA253" t="n">
-        <v>3866</v>
+        <v>4095</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B254" t="n">
+        <v>10</v>
+      </c>
+      <c r="C254" t="n">
+        <v>15</v>
+      </c>
+      <c r="D254" t="n">
+        <v>3649</v>
+      </c>
+      <c r="E254" t="n">
+        <v>3483</v>
+      </c>
+      <c r="F254" t="n">
+        <v>3397</v>
+      </c>
+      <c r="G254" t="n">
+        <v>3349</v>
+      </c>
+      <c r="H254" t="n">
+        <v>3387</v>
+      </c>
+      <c r="I254" t="n">
+        <v>3573</v>
+      </c>
+      <c r="J254" t="n">
+        <v>4113</v>
+      </c>
+      <c r="K254" t="n">
+        <v>4531</v>
+      </c>
+      <c r="L254" t="n">
+        <v>4818</v>
+      </c>
+      <c r="M254" t="n">
+        <v>4873</v>
+      </c>
+      <c r="N254" t="n">
+        <v>4760</v>
+      </c>
+      <c r="O254" t="n">
+        <v>4720</v>
+      </c>
+      <c r="P254" t="n">
+        <v>4660</v>
+      </c>
+      <c r="Q254" t="n">
+        <v>4718</v>
+      </c>
+      <c r="R254" t="n">
+        <v>4652</v>
+      </c>
+      <c r="S254" t="n">
+        <v>4619</v>
+      </c>
+      <c r="T254" t="n">
+        <v>4549</v>
+      </c>
+      <c r="U254" t="n">
+        <v>4577</v>
+      </c>
+      <c r="V254" t="n">
+        <v>4744</v>
+      </c>
+      <c r="W254" t="n">
+        <v>5071</v>
+      </c>
+      <c r="X254" t="n">
+        <v>4999</v>
+      </c>
+      <c r="Y254" t="n">
+        <v>4725</v>
+      </c>
+      <c r="Z254" t="n">
+        <v>4437</v>
+      </c>
+      <c r="AA254" t="n">
+        <v>4132</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA254"/>
+  <dimension ref="A1:AA255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21158,76 +21158,76 @@
         <v>11</v>
       </c>
       <c r="D250" t="n">
-        <v>3328</v>
+        <v>3364</v>
       </c>
       <c r="E250" t="n">
-        <v>3095</v>
+        <v>3134</v>
       </c>
       <c r="F250" t="n">
-        <v>2995</v>
+        <v>3037</v>
       </c>
       <c r="G250" t="n">
-        <v>2927</v>
+        <v>2969</v>
       </c>
       <c r="H250" t="n">
-        <v>2923</v>
+        <v>2965</v>
       </c>
       <c r="I250" t="n">
-        <v>2976</v>
+        <v>3009</v>
       </c>
       <c r="J250" t="n">
-        <v>3163</v>
+        <v>3160</v>
       </c>
       <c r="K250" t="n">
-        <v>3357</v>
+        <v>3318</v>
       </c>
       <c r="L250" t="n">
-        <v>3701</v>
+        <v>3597</v>
       </c>
       <c r="M250" t="n">
-        <v>3897</v>
+        <v>3756</v>
       </c>
       <c r="N250" t="n">
-        <v>3922</v>
+        <v>3777</v>
       </c>
       <c r="O250" t="n">
-        <v>3900</v>
+        <v>3777</v>
       </c>
       <c r="P250" t="n">
-        <v>3849</v>
+        <v>3778</v>
       </c>
       <c r="Q250" t="n">
-        <v>3805</v>
+        <v>3779</v>
       </c>
       <c r="R250" t="n">
-        <v>3768</v>
+        <v>3780</v>
       </c>
       <c r="S250" t="n">
-        <v>3731</v>
+        <v>3781</v>
       </c>
       <c r="T250" t="n">
-        <v>3758</v>
+        <v>3804</v>
       </c>
       <c r="U250" t="n">
-        <v>3879</v>
+        <v>3911</v>
       </c>
       <c r="V250" t="n">
-        <v>4061</v>
+        <v>4071</v>
       </c>
       <c r="W250" t="n">
-        <v>4437</v>
+        <v>4403</v>
       </c>
       <c r="X250" t="n">
-        <v>4454</v>
+        <v>4418</v>
       </c>
       <c r="Y250" t="n">
-        <v>4211</v>
+        <v>4161</v>
       </c>
       <c r="Z250" t="n">
-        <v>3924</v>
+        <v>3858</v>
       </c>
       <c r="AA250" t="n">
-        <v>3696</v>
+        <v>3616</v>
       </c>
     </row>
     <row r="251">
@@ -21241,76 +21241,76 @@
         <v>12</v>
       </c>
       <c r="D251" t="n">
-        <v>3415</v>
+        <v>3548</v>
       </c>
       <c r="E251" t="n">
-        <v>3193</v>
+        <v>3303</v>
       </c>
       <c r="F251" t="n">
-        <v>3093</v>
+        <v>3201</v>
       </c>
       <c r="G251" t="n">
-        <v>3052</v>
+        <v>3153</v>
       </c>
       <c r="H251" t="n">
-        <v>3091</v>
+        <v>3195</v>
       </c>
       <c r="I251" t="n">
-        <v>3276</v>
+        <v>3355</v>
       </c>
       <c r="J251" t="n">
-        <v>3852</v>
+        <v>3833</v>
       </c>
       <c r="K251" t="n">
-        <v>4266</v>
+        <v>4187</v>
       </c>
       <c r="L251" t="n">
-        <v>4502</v>
+        <v>4379</v>
       </c>
       <c r="M251" t="n">
-        <v>4501</v>
+        <v>4354</v>
       </c>
       <c r="N251" t="n">
-        <v>4365</v>
+        <v>4276</v>
       </c>
       <c r="O251" t="n">
-        <v>4305</v>
+        <v>4224</v>
       </c>
       <c r="P251" t="n">
-        <v>4302</v>
+        <v>4190</v>
       </c>
       <c r="Q251" t="n">
-        <v>4307</v>
+        <v>4197</v>
       </c>
       <c r="R251" t="n">
-        <v>4256</v>
+        <v>4178</v>
       </c>
       <c r="S251" t="n">
-        <v>4207</v>
+        <v>4172</v>
       </c>
       <c r="T251" t="n">
-        <v>4165</v>
+        <v>4166</v>
       </c>
       <c r="U251" t="n">
-        <v>4191</v>
+        <v>4196</v>
       </c>
       <c r="V251" t="n">
-        <v>4382</v>
+        <v>4341</v>
       </c>
       <c r="W251" t="n">
-        <v>4750</v>
+        <v>4679</v>
       </c>
       <c r="X251" t="n">
-        <v>4719</v>
+        <v>4661</v>
       </c>
       <c r="Y251" t="n">
-        <v>4451</v>
+        <v>4442</v>
       </c>
       <c r="Z251" t="n">
-        <v>4176</v>
+        <v>4170</v>
       </c>
       <c r="AA251" t="n">
-        <v>3913</v>
+        <v>3941</v>
       </c>
     </row>
     <row r="252">
@@ -21324,76 +21324,76 @@
         <v>13</v>
       </c>
       <c r="D252" t="n">
-        <v>3534</v>
+        <v>3735</v>
       </c>
       <c r="E252" t="n">
-        <v>3353</v>
+        <v>3548</v>
       </c>
       <c r="F252" t="n">
-        <v>3260</v>
+        <v>3450</v>
       </c>
       <c r="G252" t="n">
-        <v>3208</v>
+        <v>3390</v>
       </c>
       <c r="H252" t="n">
-        <v>3243</v>
+        <v>3424</v>
       </c>
       <c r="I252" t="n">
-        <v>3417</v>
+        <v>3588</v>
       </c>
       <c r="J252" t="n">
-        <v>3923</v>
+        <v>4039</v>
       </c>
       <c r="K252" t="n">
-        <v>4314</v>
+        <v>4387</v>
       </c>
       <c r="L252" t="n">
-        <v>4582</v>
+        <v>4603</v>
       </c>
       <c r="M252" t="n">
-        <v>4634</v>
+        <v>4629</v>
       </c>
       <c r="N252" t="n">
-        <v>4518</v>
+        <v>4550</v>
       </c>
       <c r="O252" t="n">
-        <v>4477</v>
+        <v>4505</v>
       </c>
       <c r="P252" t="n">
-        <v>4415</v>
+        <v>4458</v>
       </c>
       <c r="Q252" t="n">
-        <v>4474</v>
+        <v>4483</v>
       </c>
       <c r="R252" t="n">
+        <v>4445</v>
+      </c>
+      <c r="S252" t="n">
+        <v>4429</v>
+      </c>
+      <c r="T252" t="n">
         <v>4406</v>
       </c>
-      <c r="S252" t="n">
-        <v>4373</v>
-      </c>
-      <c r="T252" t="n">
-        <v>4301</v>
-      </c>
       <c r="U252" t="n">
-        <v>4331</v>
+        <v>4423</v>
       </c>
       <c r="V252" t="n">
-        <v>4511</v>
+        <v>4560</v>
       </c>
       <c r="W252" t="n">
-        <v>4864</v>
+        <v>4834</v>
       </c>
       <c r="X252" t="n">
-        <v>4797</v>
+        <v>4781</v>
       </c>
       <c r="Y252" t="n">
-        <v>4542</v>
+        <v>4541</v>
       </c>
       <c r="Z252" t="n">
-        <v>4274</v>
+        <v>4300</v>
       </c>
       <c r="AA252" t="n">
-        <v>3991</v>
+        <v>4051</v>
       </c>
     </row>
     <row r="253">
@@ -21407,76 +21407,76 @@
         <v>14</v>
       </c>
       <c r="D253" t="n">
-        <v>3619</v>
+        <v>3797</v>
       </c>
       <c r="E253" t="n">
-        <v>3449</v>
+        <v>3618</v>
       </c>
       <c r="F253" t="n">
-        <v>3361</v>
+        <v>3524</v>
       </c>
       <c r="G253" t="n">
-        <v>3313</v>
+        <v>3467</v>
       </c>
       <c r="H253" t="n">
-        <v>3349</v>
+        <v>3501</v>
       </c>
       <c r="I253" t="n">
-        <v>3532</v>
+        <v>3670</v>
       </c>
       <c r="J253" t="n">
-        <v>4064</v>
+        <v>4133</v>
       </c>
       <c r="K253" t="n">
-        <v>4475</v>
+        <v>4490</v>
       </c>
       <c r="L253" t="n">
-        <v>4757</v>
+        <v>4712</v>
       </c>
       <c r="M253" t="n">
-        <v>4811</v>
+        <v>4739</v>
       </c>
       <c r="N253" t="n">
-        <v>4698</v>
+        <v>4668</v>
       </c>
       <c r="O253" t="n">
-        <v>4657</v>
+        <v>4628</v>
       </c>
       <c r="P253" t="n">
-        <v>4597</v>
+        <v>4587</v>
       </c>
       <c r="Q253" t="n">
-        <v>4655</v>
+        <v>4609</v>
       </c>
       <c r="R253" t="n">
-        <v>4588</v>
+        <v>4575</v>
       </c>
       <c r="S253" t="n">
+        <v>4561</v>
+      </c>
+      <c r="T253" t="n">
+        <v>4540</v>
+      </c>
+      <c r="U253" t="n">
         <v>4555</v>
       </c>
-      <c r="T253" t="n">
-        <v>4484</v>
-      </c>
-      <c r="U253" t="n">
-        <v>4513</v>
-      </c>
       <c r="V253" t="n">
-        <v>4683</v>
+        <v>4675</v>
       </c>
       <c r="W253" t="n">
-        <v>5017</v>
+        <v>4916</v>
       </c>
       <c r="X253" t="n">
-        <v>4947</v>
+        <v>4859</v>
       </c>
       <c r="Y253" t="n">
-        <v>4678</v>
+        <v>4602</v>
       </c>
       <c r="Z253" t="n">
-        <v>4395</v>
+        <v>4344</v>
       </c>
       <c r="AA253" t="n">
-        <v>4095</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="254">
@@ -21490,76 +21490,159 @@
         <v>15</v>
       </c>
       <c r="D254" t="n">
-        <v>3649</v>
+        <v>3802</v>
       </c>
       <c r="E254" t="n">
+        <v>3623</v>
+      </c>
+      <c r="F254" t="n">
+        <v>3530</v>
+      </c>
+      <c r="G254" t="n">
+        <v>3473</v>
+      </c>
+      <c r="H254" t="n">
+        <v>3507</v>
+      </c>
+      <c r="I254" t="n">
+        <v>3677</v>
+      </c>
+      <c r="J254" t="n">
+        <v>4141</v>
+      </c>
+      <c r="K254" t="n">
+        <v>4499</v>
+      </c>
+      <c r="L254" t="n">
+        <v>4722</v>
+      </c>
+      <c r="M254" t="n">
+        <v>4749</v>
+      </c>
+      <c r="N254" t="n">
+        <v>4679</v>
+      </c>
+      <c r="O254" t="n">
+        <v>4639</v>
+      </c>
+      <c r="P254" t="n">
+        <v>4597</v>
+      </c>
+      <c r="Q254" t="n">
+        <v>4619</v>
+      </c>
+      <c r="R254" t="n">
+        <v>4586</v>
+      </c>
+      <c r="S254" t="n">
+        <v>4571</v>
+      </c>
+      <c r="T254" t="n">
+        <v>4551</v>
+      </c>
+      <c r="U254" t="n">
+        <v>4566</v>
+      </c>
+      <c r="V254" t="n">
+        <v>4685</v>
+      </c>
+      <c r="W254" t="n">
+        <v>4925</v>
+      </c>
+      <c r="X254" t="n">
+        <v>4865</v>
+      </c>
+      <c r="Y254" t="n">
+        <v>4591</v>
+      </c>
+      <c r="Z254" t="n">
+        <v>4317</v>
+      </c>
+      <c r="AA254" t="n">
+        <v>4033</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B255" t="n">
+        <v>10</v>
+      </c>
+      <c r="C255" t="n">
+        <v>16</v>
+      </c>
+      <c r="D255" t="n">
+        <v>3762</v>
+      </c>
+      <c r="E255" t="n">
+        <v>3579</v>
+      </c>
+      <c r="F255" t="n">
         <v>3483</v>
       </c>
-      <c r="F254" t="n">
-        <v>3397</v>
-      </c>
-      <c r="G254" t="n">
-        <v>3349</v>
-      </c>
-      <c r="H254" t="n">
-        <v>3387</v>
-      </c>
-      <c r="I254" t="n">
-        <v>3573</v>
-      </c>
-      <c r="J254" t="n">
-        <v>4113</v>
-      </c>
-      <c r="K254" t="n">
-        <v>4531</v>
-      </c>
-      <c r="L254" t="n">
-        <v>4818</v>
-      </c>
-      <c r="M254" t="n">
-        <v>4873</v>
-      </c>
-      <c r="N254" t="n">
-        <v>4760</v>
-      </c>
-      <c r="O254" t="n">
-        <v>4720</v>
-      </c>
-      <c r="P254" t="n">
-        <v>4660</v>
-      </c>
-      <c r="Q254" t="n">
-        <v>4718</v>
-      </c>
-      <c r="R254" t="n">
-        <v>4652</v>
-      </c>
-      <c r="S254" t="n">
-        <v>4619</v>
-      </c>
-      <c r="T254" t="n">
-        <v>4549</v>
-      </c>
-      <c r="U254" t="n">
-        <v>4577</v>
-      </c>
-      <c r="V254" t="n">
-        <v>4744</v>
-      </c>
-      <c r="W254" t="n">
-        <v>5071</v>
-      </c>
-      <c r="X254" t="n">
-        <v>4999</v>
-      </c>
-      <c r="Y254" t="n">
-        <v>4725</v>
-      </c>
-      <c r="Z254" t="n">
-        <v>4437</v>
-      </c>
-      <c r="AA254" t="n">
-        <v>4132</v>
+      <c r="G255" t="n">
+        <v>3424</v>
+      </c>
+      <c r="H255" t="n">
+        <v>3458</v>
+      </c>
+      <c r="I255" t="n">
+        <v>3623</v>
+      </c>
+      <c r="J255" t="n">
+        <v>4075</v>
+      </c>
+      <c r="K255" t="n">
+        <v>4423</v>
+      </c>
+      <c r="L255" t="n">
+        <v>4641</v>
+      </c>
+      <c r="M255" t="n">
+        <v>4667</v>
+      </c>
+      <c r="N255" t="n">
+        <v>4595</v>
+      </c>
+      <c r="O255" t="n">
+        <v>4554</v>
+      </c>
+      <c r="P255" t="n">
+        <v>4512</v>
+      </c>
+      <c r="Q255" t="n">
+        <v>4535</v>
+      </c>
+      <c r="R255" t="n">
+        <v>4501</v>
+      </c>
+      <c r="S255" t="n">
+        <v>4486</v>
+      </c>
+      <c r="T255" t="n">
+        <v>4466</v>
+      </c>
+      <c r="U255" t="n">
+        <v>4478</v>
+      </c>
+      <c r="V255" t="n">
+        <v>4576</v>
+      </c>
+      <c r="W255" t="n">
+        <v>4773</v>
+      </c>
+      <c r="X255" t="n">
+        <v>4717</v>
+      </c>
+      <c r="Y255" t="n">
+        <v>4460</v>
+      </c>
+      <c r="Z255" t="n">
+        <v>4203</v>
+      </c>
+      <c r="AA255" t="n">
+        <v>3937</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA255"/>
+  <dimension ref="A1:AA256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21241,76 +21241,76 @@
         <v>12</v>
       </c>
       <c r="D251" t="n">
-        <v>3548</v>
+        <v>3410</v>
       </c>
       <c r="E251" t="n">
-        <v>3303</v>
+        <v>3245</v>
       </c>
       <c r="F251" t="n">
-        <v>3201</v>
+        <v>3176</v>
       </c>
       <c r="G251" t="n">
-        <v>3153</v>
+        <v>3143</v>
       </c>
       <c r="H251" t="n">
-        <v>3195</v>
+        <v>3192</v>
       </c>
       <c r="I251" t="n">
-        <v>3355</v>
+        <v>3376</v>
       </c>
       <c r="J251" t="n">
-        <v>3833</v>
+        <v>3927</v>
       </c>
       <c r="K251" t="n">
-        <v>4187</v>
+        <v>4334</v>
       </c>
       <c r="L251" t="n">
-        <v>4379</v>
+        <v>4555</v>
       </c>
       <c r="M251" t="n">
-        <v>4354</v>
+        <v>4545</v>
       </c>
       <c r="N251" t="n">
-        <v>4276</v>
+        <v>4515</v>
       </c>
       <c r="O251" t="n">
-        <v>4224</v>
+        <v>4494</v>
       </c>
       <c r="P251" t="n">
-        <v>4190</v>
+        <v>4481</v>
       </c>
       <c r="Q251" t="n">
-        <v>4197</v>
+        <v>4483</v>
       </c>
       <c r="R251" t="n">
-        <v>4178</v>
+        <v>4476</v>
       </c>
       <c r="S251" t="n">
-        <v>4172</v>
+        <v>4474</v>
       </c>
       <c r="T251" t="n">
-        <v>4166</v>
+        <v>4471</v>
       </c>
       <c r="U251" t="n">
-        <v>4196</v>
+        <v>4485</v>
       </c>
       <c r="V251" t="n">
-        <v>4341</v>
+        <v>4548</v>
       </c>
       <c r="W251" t="n">
-        <v>4679</v>
+        <v>4698</v>
       </c>
       <c r="X251" t="n">
-        <v>4661</v>
+        <v>4678</v>
       </c>
       <c r="Y251" t="n">
-        <v>4442</v>
+        <v>4436</v>
       </c>
       <c r="Z251" t="n">
-        <v>4170</v>
+        <v>4137</v>
       </c>
       <c r="AA251" t="n">
-        <v>3941</v>
+        <v>3884</v>
       </c>
     </row>
     <row r="252">
@@ -21324,76 +21324,76 @@
         <v>13</v>
       </c>
       <c r="D252" t="n">
-        <v>3735</v>
+        <v>3662</v>
       </c>
       <c r="E252" t="n">
-        <v>3548</v>
+        <v>3519</v>
       </c>
       <c r="F252" t="n">
-        <v>3450</v>
+        <v>3443</v>
       </c>
       <c r="G252" t="n">
-        <v>3390</v>
+        <v>3400</v>
       </c>
       <c r="H252" t="n">
-        <v>3424</v>
+        <v>3441</v>
       </c>
       <c r="I252" t="n">
-        <v>3588</v>
+        <v>3622</v>
       </c>
       <c r="J252" t="n">
-        <v>4039</v>
+        <v>4109</v>
       </c>
       <c r="K252" t="n">
-        <v>4387</v>
+        <v>4496</v>
       </c>
       <c r="L252" t="n">
-        <v>4603</v>
+        <v>4718</v>
       </c>
       <c r="M252" t="n">
-        <v>4629</v>
+        <v>4737</v>
       </c>
       <c r="N252" t="n">
-        <v>4550</v>
+        <v>4700</v>
       </c>
       <c r="O252" t="n">
-        <v>4505</v>
+        <v>4677</v>
       </c>
       <c r="P252" t="n">
-        <v>4458</v>
+        <v>4654</v>
       </c>
       <c r="Q252" t="n">
-        <v>4483</v>
+        <v>4660</v>
       </c>
       <c r="R252" t="n">
-        <v>4445</v>
+        <v>4646</v>
       </c>
       <c r="S252" t="n">
-        <v>4429</v>
+        <v>4643</v>
       </c>
       <c r="T252" t="n">
-        <v>4406</v>
+        <v>4635</v>
       </c>
       <c r="U252" t="n">
-        <v>4423</v>
+        <v>4643</v>
       </c>
       <c r="V252" t="n">
-        <v>4560</v>
+        <v>4708</v>
       </c>
       <c r="W252" t="n">
-        <v>4834</v>
+        <v>4840</v>
       </c>
       <c r="X252" t="n">
-        <v>4781</v>
+        <v>4782</v>
       </c>
       <c r="Y252" t="n">
-        <v>4541</v>
+        <v>4562</v>
       </c>
       <c r="Z252" t="n">
-        <v>4300</v>
+        <v>4338</v>
       </c>
       <c r="AA252" t="n">
-        <v>4051</v>
+        <v>4113</v>
       </c>
     </row>
     <row r="253">
@@ -21407,76 +21407,76 @@
         <v>14</v>
       </c>
       <c r="D253" t="n">
-        <v>3797</v>
+        <v>3749</v>
       </c>
       <c r="E253" t="n">
-        <v>3618</v>
+        <v>3617</v>
       </c>
       <c r="F253" t="n">
-        <v>3524</v>
+        <v>3546</v>
       </c>
       <c r="G253" t="n">
-        <v>3467</v>
+        <v>3506</v>
       </c>
       <c r="H253" t="n">
-        <v>3501</v>
+        <v>3547</v>
       </c>
       <c r="I253" t="n">
-        <v>3670</v>
+        <v>3727</v>
       </c>
       <c r="J253" t="n">
-        <v>4133</v>
+        <v>4212</v>
       </c>
       <c r="K253" t="n">
-        <v>4490</v>
+        <v>4597</v>
       </c>
       <c r="L253" t="n">
-        <v>4712</v>
+        <v>4818</v>
       </c>
       <c r="M253" t="n">
-        <v>4739</v>
+        <v>4837</v>
       </c>
       <c r="N253" t="n">
-        <v>4668</v>
+        <v>4832</v>
       </c>
       <c r="O253" t="n">
-        <v>4628</v>
+        <v>4828</v>
       </c>
       <c r="P253" t="n">
-        <v>4587</v>
+        <v>4824</v>
       </c>
       <c r="Q253" t="n">
-        <v>4609</v>
+        <v>4825</v>
       </c>
       <c r="R253" t="n">
-        <v>4575</v>
+        <v>4823</v>
       </c>
       <c r="S253" t="n">
-        <v>4561</v>
+        <v>4823</v>
       </c>
       <c r="T253" t="n">
-        <v>4540</v>
+        <v>4821</v>
       </c>
       <c r="U253" t="n">
-        <v>4555</v>
+        <v>4828</v>
       </c>
       <c r="V253" t="n">
-        <v>4675</v>
+        <v>4884</v>
       </c>
       <c r="W253" t="n">
-        <v>4916</v>
+        <v>4996</v>
       </c>
       <c r="X253" t="n">
-        <v>4859</v>
+        <v>4934</v>
       </c>
       <c r="Y253" t="n">
-        <v>4602</v>
+        <v>4699</v>
       </c>
       <c r="Z253" t="n">
-        <v>4344</v>
+        <v>4460</v>
       </c>
       <c r="AA253" t="n">
-        <v>4077</v>
+        <v>4219</v>
       </c>
     </row>
     <row r="254">
@@ -21490,76 +21490,76 @@
         <v>15</v>
       </c>
       <c r="D254" t="n">
-        <v>3802</v>
+        <v>3745</v>
       </c>
       <c r="E254" t="n">
-        <v>3623</v>
+        <v>3612</v>
       </c>
       <c r="F254" t="n">
-        <v>3530</v>
+        <v>3541</v>
       </c>
       <c r="G254" t="n">
-        <v>3473</v>
+        <v>3502</v>
       </c>
       <c r="H254" t="n">
-        <v>3507</v>
+        <v>3542</v>
       </c>
       <c r="I254" t="n">
-        <v>3677</v>
+        <v>3722</v>
       </c>
       <c r="J254" t="n">
-        <v>4141</v>
+        <v>4206</v>
       </c>
       <c r="K254" t="n">
-        <v>4499</v>
+        <v>4590</v>
       </c>
       <c r="L254" t="n">
-        <v>4722</v>
+        <v>4810</v>
       </c>
       <c r="M254" t="n">
-        <v>4749</v>
+        <v>4829</v>
       </c>
       <c r="N254" t="n">
-        <v>4679</v>
+        <v>4823</v>
       </c>
       <c r="O254" t="n">
-        <v>4639</v>
+        <v>4820</v>
       </c>
       <c r="P254" t="n">
-        <v>4597</v>
+        <v>4816</v>
       </c>
       <c r="Q254" t="n">
-        <v>4619</v>
+        <v>4817</v>
       </c>
       <c r="R254" t="n">
-        <v>4586</v>
+        <v>4815</v>
       </c>
       <c r="S254" t="n">
-        <v>4571</v>
+        <v>4814</v>
       </c>
       <c r="T254" t="n">
-        <v>4551</v>
+        <v>4813</v>
       </c>
       <c r="U254" t="n">
-        <v>4566</v>
+        <v>4820</v>
       </c>
       <c r="V254" t="n">
-        <v>4685</v>
+        <v>4876</v>
       </c>
       <c r="W254" t="n">
-        <v>4925</v>
+        <v>4989</v>
       </c>
       <c r="X254" t="n">
-        <v>4865</v>
+        <v>4927</v>
       </c>
       <c r="Y254" t="n">
-        <v>4591</v>
+        <v>4693</v>
       </c>
       <c r="Z254" t="n">
-        <v>4317</v>
+        <v>4454</v>
       </c>
       <c r="AA254" t="n">
-        <v>4033</v>
+        <v>4214</v>
       </c>
     </row>
     <row r="255">
@@ -21576,73 +21576,156 @@
         <v>3762</v>
       </c>
       <c r="E255" t="n">
-        <v>3579</v>
+        <v>3631</v>
       </c>
       <c r="F255" t="n">
-        <v>3483</v>
+        <v>3561</v>
       </c>
       <c r="G255" t="n">
-        <v>3424</v>
+        <v>3522</v>
       </c>
       <c r="H255" t="n">
-        <v>3458</v>
+        <v>3563</v>
       </c>
       <c r="I255" t="n">
-        <v>3623</v>
+        <v>3744</v>
       </c>
       <c r="J255" t="n">
-        <v>4075</v>
+        <v>4234</v>
       </c>
       <c r="K255" t="n">
-        <v>4423</v>
+        <v>4622</v>
       </c>
       <c r="L255" t="n">
-        <v>4641</v>
+        <v>4845</v>
       </c>
       <c r="M255" t="n">
-        <v>4667</v>
+        <v>4864</v>
       </c>
       <c r="N255" t="n">
-        <v>4595</v>
+        <v>4859</v>
       </c>
       <c r="O255" t="n">
-        <v>4554</v>
+        <v>4855</v>
       </c>
       <c r="P255" t="n">
-        <v>4512</v>
+        <v>4852</v>
       </c>
       <c r="Q255" t="n">
-        <v>4535</v>
+        <v>4853</v>
       </c>
       <c r="R255" t="n">
-        <v>4501</v>
+        <v>4851</v>
       </c>
       <c r="S255" t="n">
-        <v>4486</v>
+        <v>4850</v>
       </c>
       <c r="T255" t="n">
-        <v>4466</v>
+        <v>4849</v>
       </c>
       <c r="U255" t="n">
-        <v>4478</v>
+        <v>4853</v>
       </c>
       <c r="V255" t="n">
-        <v>4576</v>
+        <v>4881</v>
       </c>
       <c r="W255" t="n">
-        <v>4773</v>
+        <v>4940</v>
       </c>
       <c r="X255" t="n">
-        <v>4717</v>
+        <v>4879</v>
       </c>
       <c r="Y255" t="n">
-        <v>4460</v>
+        <v>4651</v>
       </c>
       <c r="Z255" t="n">
-        <v>4203</v>
+        <v>4420</v>
       </c>
       <c r="AA255" t="n">
-        <v>3937</v>
+        <v>4187</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B256" t="n">
+        <v>10</v>
+      </c>
+      <c r="C256" t="n">
+        <v>17</v>
+      </c>
+      <c r="D256" t="n">
+        <v>3738</v>
+      </c>
+      <c r="E256" t="n">
+        <v>3572</v>
+      </c>
+      <c r="F256" t="n">
+        <v>3489</v>
+      </c>
+      <c r="G256" t="n">
+        <v>3459</v>
+      </c>
+      <c r="H256" t="n">
+        <v>3442</v>
+      </c>
+      <c r="I256" t="n">
+        <v>3505</v>
+      </c>
+      <c r="J256" t="n">
+        <v>3720</v>
+      </c>
+      <c r="K256" t="n">
+        <v>3982</v>
+      </c>
+      <c r="L256" t="n">
+        <v>4307</v>
+      </c>
+      <c r="M256" t="n">
+        <v>4479</v>
+      </c>
+      <c r="N256" t="n">
+        <v>4520</v>
+      </c>
+      <c r="O256" t="n">
+        <v>4529</v>
+      </c>
+      <c r="P256" t="n">
+        <v>4562</v>
+      </c>
+      <c r="Q256" t="n">
+        <v>4569</v>
+      </c>
+      <c r="R256" t="n">
+        <v>4584</v>
+      </c>
+      <c r="S256" t="n">
+        <v>4591</v>
+      </c>
+      <c r="T256" t="n">
+        <v>4596</v>
+      </c>
+      <c r="U256" t="n">
+        <v>4619</v>
+      </c>
+      <c r="V256" t="n">
+        <v>4647</v>
+      </c>
+      <c r="W256" t="n">
+        <v>4719</v>
+      </c>
+      <c r="X256" t="n">
+        <v>4626</v>
+      </c>
+      <c r="Y256" t="n">
+        <v>4456</v>
+      </c>
+      <c r="Z256" t="n">
+        <v>4222</v>
+      </c>
+      <c r="AA256" t="n">
+        <v>4072</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA256"/>
+  <dimension ref="A1:AA257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21324,76 +21324,76 @@
         <v>13</v>
       </c>
       <c r="D252" t="n">
-        <v>3662</v>
+        <v>3398</v>
       </c>
       <c r="E252" t="n">
-        <v>3519</v>
+        <v>3240</v>
       </c>
       <c r="F252" t="n">
-        <v>3443</v>
+        <v>3156</v>
       </c>
       <c r="G252" t="n">
-        <v>3400</v>
+        <v>3105</v>
       </c>
       <c r="H252" t="n">
-        <v>3441</v>
+        <v>3146</v>
       </c>
       <c r="I252" t="n">
-        <v>3622</v>
+        <v>3317</v>
       </c>
       <c r="J252" t="n">
-        <v>4109</v>
+        <v>3778</v>
       </c>
       <c r="K252" t="n">
-        <v>4496</v>
+        <v>4147</v>
       </c>
       <c r="L252" t="n">
-        <v>4718</v>
+        <v>4356</v>
       </c>
       <c r="M252" t="n">
-        <v>4737</v>
+        <v>4365</v>
       </c>
       <c r="N252" t="n">
-        <v>4700</v>
+        <v>4333</v>
       </c>
       <c r="O252" t="n">
-        <v>4677</v>
+        <v>4311</v>
       </c>
       <c r="P252" t="n">
-        <v>4654</v>
+        <v>4290</v>
       </c>
       <c r="Q252" t="n">
-        <v>4660</v>
+        <v>4292</v>
       </c>
       <c r="R252" t="n">
-        <v>4646</v>
+        <v>4281</v>
       </c>
       <c r="S252" t="n">
-        <v>4643</v>
+        <v>4281</v>
       </c>
       <c r="T252" t="n">
-        <v>4635</v>
+        <v>4275</v>
       </c>
       <c r="U252" t="n">
-        <v>4643</v>
+        <v>4292</v>
       </c>
       <c r="V252" t="n">
-        <v>4708</v>
+        <v>4416</v>
       </c>
       <c r="W252" t="n">
-        <v>4840</v>
+        <v>4671</v>
       </c>
       <c r="X252" t="n">
-        <v>4782</v>
+        <v>4597</v>
       </c>
       <c r="Y252" t="n">
-        <v>4562</v>
+        <v>4355</v>
       </c>
       <c r="Z252" t="n">
-        <v>4338</v>
+        <v>4121</v>
       </c>
       <c r="AA252" t="n">
-        <v>4113</v>
+        <v>3870</v>
       </c>
     </row>
     <row r="253">
@@ -21407,76 +21407,76 @@
         <v>14</v>
       </c>
       <c r="D253" t="n">
-        <v>3749</v>
+        <v>3472</v>
       </c>
       <c r="E253" t="n">
-        <v>3617</v>
+        <v>3323</v>
       </c>
       <c r="F253" t="n">
-        <v>3546</v>
+        <v>3244</v>
       </c>
       <c r="G253" t="n">
-        <v>3506</v>
+        <v>3196</v>
       </c>
       <c r="H253" t="n">
-        <v>3547</v>
+        <v>3239</v>
       </c>
       <c r="I253" t="n">
-        <v>3727</v>
+        <v>3418</v>
       </c>
       <c r="J253" t="n">
-        <v>4212</v>
+        <v>3902</v>
       </c>
       <c r="K253" t="n">
-        <v>4597</v>
+        <v>4290</v>
       </c>
       <c r="L253" t="n">
-        <v>4818</v>
+        <v>4510</v>
       </c>
       <c r="M253" t="n">
-        <v>4837</v>
+        <v>4519</v>
       </c>
       <c r="N253" t="n">
-        <v>4832</v>
+        <v>4489</v>
       </c>
       <c r="O253" t="n">
-        <v>4828</v>
+        <v>4468</v>
       </c>
       <c r="P253" t="n">
-        <v>4824</v>
+        <v>4448</v>
       </c>
       <c r="Q253" t="n">
-        <v>4825</v>
+        <v>4450</v>
       </c>
       <c r="R253" t="n">
-        <v>4823</v>
+        <v>4440</v>
       </c>
       <c r="S253" t="n">
-        <v>4823</v>
+        <v>4440</v>
       </c>
       <c r="T253" t="n">
-        <v>4821</v>
+        <v>4435</v>
       </c>
       <c r="U253" t="n">
-        <v>4828</v>
+        <v>4450</v>
       </c>
       <c r="V253" t="n">
-        <v>4884</v>
+        <v>4566</v>
       </c>
       <c r="W253" t="n">
-        <v>4996</v>
+        <v>4804</v>
       </c>
       <c r="X253" t="n">
-        <v>4934</v>
+        <v>4722</v>
       </c>
       <c r="Y253" t="n">
-        <v>4699</v>
+        <v>4452</v>
       </c>
       <c r="Z253" t="n">
-        <v>4460</v>
+        <v>4191</v>
       </c>
       <c r="AA253" t="n">
-        <v>4219</v>
+        <v>3911</v>
       </c>
     </row>
     <row r="254">
@@ -21490,76 +21490,76 @@
         <v>15</v>
       </c>
       <c r="D254" t="n">
-        <v>3745</v>
+        <v>3492</v>
       </c>
       <c r="E254" t="n">
-        <v>3612</v>
+        <v>3345</v>
       </c>
       <c r="F254" t="n">
-        <v>3541</v>
+        <v>3267</v>
       </c>
       <c r="G254" t="n">
-        <v>3502</v>
+        <v>3220</v>
       </c>
       <c r="H254" t="n">
-        <v>3542</v>
+        <v>3263</v>
       </c>
       <c r="I254" t="n">
-        <v>3722</v>
+        <v>3444</v>
       </c>
       <c r="J254" t="n">
-        <v>4206</v>
+        <v>3934</v>
       </c>
       <c r="K254" t="n">
-        <v>4590</v>
+        <v>4327</v>
       </c>
       <c r="L254" t="n">
-        <v>4810</v>
+        <v>4549</v>
       </c>
       <c r="M254" t="n">
-        <v>4829</v>
+        <v>4559</v>
       </c>
       <c r="N254" t="n">
-        <v>4823</v>
+        <v>4529</v>
       </c>
       <c r="O254" t="n">
-        <v>4820</v>
+        <v>4508</v>
       </c>
       <c r="P254" t="n">
-        <v>4816</v>
+        <v>4489</v>
       </c>
       <c r="Q254" t="n">
-        <v>4817</v>
+        <v>4491</v>
       </c>
       <c r="R254" t="n">
-        <v>4815</v>
+        <v>4481</v>
       </c>
       <c r="S254" t="n">
-        <v>4814</v>
+        <v>4481</v>
       </c>
       <c r="T254" t="n">
-        <v>4813</v>
+        <v>4476</v>
       </c>
       <c r="U254" t="n">
-        <v>4820</v>
+        <v>4491</v>
       </c>
       <c r="V254" t="n">
-        <v>4876</v>
+        <v>4604</v>
       </c>
       <c r="W254" t="n">
-        <v>4989</v>
+        <v>4839</v>
       </c>
       <c r="X254" t="n">
-        <v>4927</v>
+        <v>4755</v>
       </c>
       <c r="Y254" t="n">
-        <v>4693</v>
+        <v>4482</v>
       </c>
       <c r="Z254" t="n">
-        <v>4454</v>
+        <v>4218</v>
       </c>
       <c r="AA254" t="n">
-        <v>4214</v>
+        <v>3934</v>
       </c>
     </row>
     <row r="255">
@@ -21573,76 +21573,76 @@
         <v>16</v>
       </c>
       <c r="D255" t="n">
-        <v>3762</v>
+        <v>3523</v>
       </c>
       <c r="E255" t="n">
-        <v>3631</v>
+        <v>3380</v>
       </c>
       <c r="F255" t="n">
-        <v>3561</v>
+        <v>3304</v>
       </c>
       <c r="G255" t="n">
-        <v>3522</v>
+        <v>3258</v>
       </c>
       <c r="H255" t="n">
-        <v>3563</v>
+        <v>3302</v>
       </c>
       <c r="I255" t="n">
-        <v>3744</v>
+        <v>3488</v>
       </c>
       <c r="J255" t="n">
-        <v>4234</v>
+        <v>3987</v>
       </c>
       <c r="K255" t="n">
-        <v>4622</v>
+        <v>4388</v>
       </c>
       <c r="L255" t="n">
-        <v>4845</v>
+        <v>4614</v>
       </c>
       <c r="M255" t="n">
-        <v>4864</v>
+        <v>4624</v>
       </c>
       <c r="N255" t="n">
-        <v>4859</v>
+        <v>4596</v>
       </c>
       <c r="O255" t="n">
-        <v>4855</v>
+        <v>4575</v>
       </c>
       <c r="P255" t="n">
-        <v>4852</v>
+        <v>4557</v>
       </c>
       <c r="Q255" t="n">
-        <v>4853</v>
+        <v>4558</v>
       </c>
       <c r="R255" t="n">
-        <v>4851</v>
+        <v>4549</v>
       </c>
       <c r="S255" t="n">
-        <v>4850</v>
+        <v>4549</v>
       </c>
       <c r="T255" t="n">
-        <v>4849</v>
+        <v>4544</v>
       </c>
       <c r="U255" t="n">
-        <v>4853</v>
+        <v>4555</v>
       </c>
       <c r="V255" t="n">
-        <v>4881</v>
+        <v>4640</v>
       </c>
       <c r="W255" t="n">
-        <v>4940</v>
+        <v>4815</v>
       </c>
       <c r="X255" t="n">
-        <v>4879</v>
+        <v>4733</v>
       </c>
       <c r="Y255" t="n">
-        <v>4651</v>
+        <v>4464</v>
       </c>
       <c r="Z255" t="n">
-        <v>4420</v>
+        <v>4204</v>
       </c>
       <c r="AA255" t="n">
-        <v>4187</v>
+        <v>3925</v>
       </c>
     </row>
     <row r="256">
@@ -21656,76 +21656,159 @@
         <v>17</v>
       </c>
       <c r="D256" t="n">
-        <v>3738</v>
+        <v>3499</v>
       </c>
       <c r="E256" t="n">
-        <v>3572</v>
+        <v>3319</v>
       </c>
       <c r="F256" t="n">
-        <v>3489</v>
+        <v>3229</v>
       </c>
       <c r="G256" t="n">
-        <v>3459</v>
+        <v>3196</v>
       </c>
       <c r="H256" t="n">
-        <v>3442</v>
+        <v>3178</v>
       </c>
       <c r="I256" t="n">
-        <v>3505</v>
+        <v>3242</v>
       </c>
       <c r="J256" t="n">
-        <v>3720</v>
+        <v>3461</v>
       </c>
       <c r="K256" t="n">
-        <v>3982</v>
+        <v>3729</v>
       </c>
       <c r="L256" t="n">
-        <v>4307</v>
+        <v>4061</v>
       </c>
       <c r="M256" t="n">
-        <v>4479</v>
+        <v>4237</v>
       </c>
       <c r="N256" t="n">
-        <v>4520</v>
+        <v>4279</v>
       </c>
       <c r="O256" t="n">
-        <v>4529</v>
+        <v>4280</v>
       </c>
       <c r="P256" t="n">
-        <v>4562</v>
+        <v>4282</v>
       </c>
       <c r="Q256" t="n">
-        <v>4569</v>
+        <v>4283</v>
       </c>
       <c r="R256" t="n">
-        <v>4584</v>
+        <v>4284</v>
       </c>
       <c r="S256" t="n">
-        <v>4591</v>
+        <v>4284</v>
       </c>
       <c r="T256" t="n">
-        <v>4596</v>
+        <v>4295</v>
       </c>
       <c r="U256" t="n">
-        <v>4619</v>
+        <v>4351</v>
       </c>
       <c r="V256" t="n">
-        <v>4647</v>
+        <v>4419</v>
       </c>
       <c r="W256" t="n">
-        <v>4719</v>
+        <v>4593</v>
       </c>
       <c r="X256" t="n">
-        <v>4626</v>
+        <v>4481</v>
       </c>
       <c r="Y256" t="n">
-        <v>4456</v>
+        <v>4275</v>
       </c>
       <c r="Z256" t="n">
-        <v>4222</v>
+        <v>3991</v>
       </c>
       <c r="AA256" t="n">
-        <v>4072</v>
+        <v>3809</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B257" t="n">
+        <v>10</v>
+      </c>
+      <c r="C257" t="n">
+        <v>18</v>
+      </c>
+      <c r="D257" t="n">
+        <v>3406</v>
+      </c>
+      <c r="E257" t="n">
+        <v>3233</v>
+      </c>
+      <c r="F257" t="n">
+        <v>3145</v>
+      </c>
+      <c r="G257" t="n">
+        <v>3093</v>
+      </c>
+      <c r="H257" t="n">
+        <v>3084</v>
+      </c>
+      <c r="I257" t="n">
+        <v>3128</v>
+      </c>
+      <c r="J257" t="n">
+        <v>3309</v>
+      </c>
+      <c r="K257" t="n">
+        <v>3523</v>
+      </c>
+      <c r="L257" t="n">
+        <v>3849</v>
+      </c>
+      <c r="M257" t="n">
+        <v>4070</v>
+      </c>
+      <c r="N257" t="n">
+        <v>4169</v>
+      </c>
+      <c r="O257" t="n">
+        <v>4203</v>
+      </c>
+      <c r="P257" t="n">
+        <v>4240</v>
+      </c>
+      <c r="Q257" t="n">
+        <v>4221</v>
+      </c>
+      <c r="R257" t="n">
+        <v>4215</v>
+      </c>
+      <c r="S257" t="n">
+        <v>4269</v>
+      </c>
+      <c r="T257" t="n">
+        <v>4276</v>
+      </c>
+      <c r="U257" t="n">
+        <v>4323</v>
+      </c>
+      <c r="V257" t="n">
+        <v>4461</v>
+      </c>
+      <c r="W257" t="n">
+        <v>4748</v>
+      </c>
+      <c r="X257" t="n">
+        <v>4714</v>
+      </c>
+      <c r="Y257" t="n">
+        <v>4452</v>
+      </c>
+      <c r="Z257" t="n">
+        <v>4112</v>
+      </c>
+      <c r="AA257" t="n">
+        <v>3858</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA257"/>
+  <dimension ref="A1:AA258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21407,76 +21407,76 @@
         <v>14</v>
       </c>
       <c r="D253" t="n">
-        <v>3472</v>
+        <v>3433</v>
       </c>
       <c r="E253" t="n">
-        <v>3323</v>
+        <v>3341</v>
       </c>
       <c r="F253" t="n">
-        <v>3244</v>
+        <v>3292</v>
       </c>
       <c r="G253" t="n">
-        <v>3196</v>
+        <v>3261</v>
       </c>
       <c r="H253" t="n">
-        <v>3239</v>
+        <v>3308</v>
       </c>
       <c r="I253" t="n">
-        <v>3418</v>
+        <v>3494</v>
       </c>
       <c r="J253" t="n">
-        <v>3902</v>
+        <v>4008</v>
       </c>
       <c r="K253" t="n">
-        <v>4290</v>
+        <v>4425</v>
       </c>
       <c r="L253" t="n">
-        <v>4510</v>
+        <v>4666</v>
       </c>
       <c r="M253" t="n">
-        <v>4519</v>
+        <v>4668</v>
       </c>
       <c r="N253" t="n">
-        <v>4489</v>
+        <v>4642</v>
       </c>
       <c r="O253" t="n">
-        <v>4468</v>
+        <v>4624</v>
       </c>
       <c r="P253" t="n">
-        <v>4448</v>
+        <v>4611</v>
       </c>
       <c r="Q253" t="n">
-        <v>4450</v>
+        <v>4611</v>
       </c>
       <c r="R253" t="n">
-        <v>4440</v>
+        <v>4605</v>
       </c>
       <c r="S253" t="n">
-        <v>4440</v>
+        <v>4602</v>
       </c>
       <c r="T253" t="n">
-        <v>4435</v>
+        <v>4598</v>
       </c>
       <c r="U253" t="n">
-        <v>4450</v>
+        <v>4626</v>
       </c>
       <c r="V253" t="n">
-        <v>4566</v>
+        <v>4754</v>
       </c>
       <c r="W253" t="n">
-        <v>4804</v>
+        <v>5005</v>
       </c>
       <c r="X253" t="n">
-        <v>4722</v>
+        <v>4925</v>
       </c>
       <c r="Y253" t="n">
-        <v>4452</v>
+        <v>4592</v>
       </c>
       <c r="Z253" t="n">
-        <v>4191</v>
+        <v>4259</v>
       </c>
       <c r="AA253" t="n">
-        <v>3911</v>
+        <v>3927</v>
       </c>
     </row>
     <row r="254">
@@ -21490,76 +21490,76 @@
         <v>15</v>
       </c>
       <c r="D254" t="n">
-        <v>3492</v>
+        <v>3452</v>
       </c>
       <c r="E254" t="n">
-        <v>3345</v>
+        <v>3363</v>
       </c>
       <c r="F254" t="n">
-        <v>3267</v>
+        <v>3315</v>
       </c>
       <c r="G254" t="n">
-        <v>3220</v>
+        <v>3285</v>
       </c>
       <c r="H254" t="n">
-        <v>3263</v>
+        <v>3331</v>
       </c>
       <c r="I254" t="n">
-        <v>3444</v>
+        <v>3520</v>
       </c>
       <c r="J254" t="n">
-        <v>3934</v>
+        <v>4040</v>
       </c>
       <c r="K254" t="n">
-        <v>4327</v>
+        <v>4462</v>
       </c>
       <c r="L254" t="n">
-        <v>4549</v>
+        <v>4706</v>
       </c>
       <c r="M254" t="n">
-        <v>4559</v>
+        <v>4707</v>
       </c>
       <c r="N254" t="n">
-        <v>4529</v>
+        <v>4682</v>
       </c>
       <c r="O254" t="n">
-        <v>4508</v>
+        <v>4664</v>
       </c>
       <c r="P254" t="n">
-        <v>4489</v>
+        <v>4651</v>
       </c>
       <c r="Q254" t="n">
-        <v>4491</v>
+        <v>4652</v>
       </c>
       <c r="R254" t="n">
-        <v>4481</v>
+        <v>4646</v>
       </c>
       <c r="S254" t="n">
-        <v>4481</v>
+        <v>4642</v>
       </c>
       <c r="T254" t="n">
-        <v>4476</v>
+        <v>4639</v>
       </c>
       <c r="U254" t="n">
-        <v>4491</v>
+        <v>4667</v>
       </c>
       <c r="V254" t="n">
-        <v>4604</v>
+        <v>4792</v>
       </c>
       <c r="W254" t="n">
-        <v>4839</v>
+        <v>5039</v>
       </c>
       <c r="X254" t="n">
-        <v>4755</v>
+        <v>4959</v>
       </c>
       <c r="Y254" t="n">
-        <v>4482</v>
+        <v>4622</v>
       </c>
       <c r="Z254" t="n">
-        <v>4218</v>
+        <v>4285</v>
       </c>
       <c r="AA254" t="n">
-        <v>3934</v>
+        <v>3951</v>
       </c>
     </row>
     <row r="255">
@@ -21573,76 +21573,76 @@
         <v>16</v>
       </c>
       <c r="D255" t="n">
-        <v>3523</v>
+        <v>3483</v>
       </c>
       <c r="E255" t="n">
-        <v>3380</v>
+        <v>3398</v>
       </c>
       <c r="F255" t="n">
-        <v>3304</v>
+        <v>3352</v>
       </c>
       <c r="G255" t="n">
-        <v>3258</v>
+        <v>3323</v>
       </c>
       <c r="H255" t="n">
-        <v>3302</v>
+        <v>3371</v>
       </c>
       <c r="I255" t="n">
-        <v>3488</v>
+        <v>3563</v>
       </c>
       <c r="J255" t="n">
-        <v>3987</v>
+        <v>4093</v>
       </c>
       <c r="K255" t="n">
-        <v>4388</v>
+        <v>4523</v>
       </c>
       <c r="L255" t="n">
-        <v>4614</v>
+        <v>4771</v>
       </c>
       <c r="M255" t="n">
-        <v>4624</v>
+        <v>4773</v>
       </c>
       <c r="N255" t="n">
-        <v>4596</v>
+        <v>4748</v>
       </c>
       <c r="O255" t="n">
-        <v>4575</v>
+        <v>4731</v>
       </c>
       <c r="P255" t="n">
-        <v>4557</v>
+        <v>4719</v>
       </c>
       <c r="Q255" t="n">
-        <v>4558</v>
+        <v>4719</v>
       </c>
       <c r="R255" t="n">
-        <v>4549</v>
+        <v>4714</v>
       </c>
       <c r="S255" t="n">
-        <v>4549</v>
+        <v>4710</v>
       </c>
       <c r="T255" t="n">
-        <v>4544</v>
+        <v>4707</v>
       </c>
       <c r="U255" t="n">
-        <v>4555</v>
+        <v>4729</v>
       </c>
       <c r="V255" t="n">
-        <v>4640</v>
+        <v>4825</v>
       </c>
       <c r="W255" t="n">
-        <v>4815</v>
+        <v>5016</v>
       </c>
       <c r="X255" t="n">
-        <v>4733</v>
+        <v>4937</v>
       </c>
       <c r="Y255" t="n">
-        <v>4464</v>
+        <v>4604</v>
       </c>
       <c r="Z255" t="n">
-        <v>4204</v>
+        <v>4272</v>
       </c>
       <c r="AA255" t="n">
-        <v>3925</v>
+        <v>3941</v>
       </c>
     </row>
     <row r="256">
@@ -21656,76 +21656,76 @@
         <v>17</v>
       </c>
       <c r="D256" t="n">
-        <v>3499</v>
+        <v>3459</v>
       </c>
       <c r="E256" t="n">
-        <v>3319</v>
+        <v>3336</v>
       </c>
       <c r="F256" t="n">
-        <v>3229</v>
+        <v>3274</v>
       </c>
       <c r="G256" t="n">
-        <v>3196</v>
+        <v>3252</v>
       </c>
       <c r="H256" t="n">
-        <v>3178</v>
+        <v>3243</v>
       </c>
       <c r="I256" t="n">
-        <v>3242</v>
+        <v>3305</v>
       </c>
       <c r="J256" t="n">
-        <v>3461</v>
+        <v>3551</v>
       </c>
       <c r="K256" t="n">
-        <v>3729</v>
+        <v>3825</v>
       </c>
       <c r="L256" t="n">
-        <v>4061</v>
+        <v>4215</v>
       </c>
       <c r="M256" t="n">
-        <v>4237</v>
+        <v>4391</v>
       </c>
       <c r="N256" t="n">
-        <v>4279</v>
+        <v>4426</v>
       </c>
       <c r="O256" t="n">
-        <v>4280</v>
+        <v>4428</v>
       </c>
       <c r="P256" t="n">
-        <v>4282</v>
+        <v>4434</v>
       </c>
       <c r="Q256" t="n">
-        <v>4283</v>
+        <v>4436</v>
       </c>
       <c r="R256" t="n">
-        <v>4284</v>
+        <v>4445</v>
       </c>
       <c r="S256" t="n">
-        <v>4284</v>
+        <v>4448</v>
       </c>
       <c r="T256" t="n">
-        <v>4295</v>
+        <v>4450</v>
       </c>
       <c r="U256" t="n">
-        <v>4351</v>
+        <v>4527</v>
       </c>
       <c r="V256" t="n">
-        <v>4419</v>
+        <v>4612</v>
       </c>
       <c r="W256" t="n">
-        <v>4593</v>
+        <v>4794</v>
       </c>
       <c r="X256" t="n">
-        <v>4481</v>
+        <v>4662</v>
       </c>
       <c r="Y256" t="n">
-        <v>4275</v>
+        <v>4349</v>
       </c>
       <c r="Z256" t="n">
-        <v>3991</v>
+        <v>4055</v>
       </c>
       <c r="AA256" t="n">
-        <v>3809</v>
+        <v>3826</v>
       </c>
     </row>
     <row r="257">
@@ -21739,76 +21739,159 @@
         <v>18</v>
       </c>
       <c r="D257" t="n">
-        <v>3406</v>
+        <v>3367</v>
       </c>
       <c r="E257" t="n">
-        <v>3233</v>
+        <v>3247</v>
       </c>
       <c r="F257" t="n">
-        <v>3145</v>
+        <v>3186</v>
       </c>
       <c r="G257" t="n">
-        <v>3093</v>
+        <v>3155</v>
       </c>
       <c r="H257" t="n">
-        <v>3084</v>
+        <v>3149</v>
       </c>
       <c r="I257" t="n">
-        <v>3128</v>
+        <v>3193</v>
       </c>
       <c r="J257" t="n">
-        <v>3309</v>
+        <v>3392</v>
       </c>
       <c r="K257" t="n">
-        <v>3523</v>
+        <v>3610</v>
       </c>
       <c r="L257" t="n">
-        <v>3849</v>
+        <v>3991</v>
       </c>
       <c r="M257" t="n">
-        <v>4070</v>
+        <v>4243</v>
       </c>
       <c r="N257" t="n">
-        <v>4169</v>
+        <v>4337</v>
       </c>
       <c r="O257" t="n">
-        <v>4203</v>
+        <v>4352</v>
       </c>
       <c r="P257" t="n">
-        <v>4240</v>
+        <v>4401</v>
       </c>
       <c r="Q257" t="n">
-        <v>4221</v>
+        <v>4414</v>
       </c>
       <c r="R257" t="n">
-        <v>4215</v>
+        <v>4404</v>
       </c>
       <c r="S257" t="n">
-        <v>4269</v>
+        <v>4417</v>
       </c>
       <c r="T257" t="n">
-        <v>4276</v>
+        <v>4431</v>
       </c>
       <c r="U257" t="n">
-        <v>4323</v>
+        <v>4533</v>
       </c>
       <c r="V257" t="n">
-        <v>4461</v>
+        <v>4682</v>
       </c>
       <c r="W257" t="n">
-        <v>4748</v>
+        <v>4949</v>
       </c>
       <c r="X257" t="n">
+        <v>4862</v>
+      </c>
+      <c r="Y257" t="n">
+        <v>4540</v>
+      </c>
+      <c r="Z257" t="n">
+        <v>4163</v>
+      </c>
+      <c r="AA257" t="n">
+        <v>3875</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B258" t="n">
+        <v>10</v>
+      </c>
+      <c r="C258" t="n">
+        <v>19</v>
+      </c>
+      <c r="D258" t="n">
+        <v>3375</v>
+      </c>
+      <c r="E258" t="n">
+        <v>3256</v>
+      </c>
+      <c r="F258" t="n">
+        <v>3206</v>
+      </c>
+      <c r="G258" t="n">
+        <v>3183</v>
+      </c>
+      <c r="H258" t="n">
+        <v>3237</v>
+      </c>
+      <c r="I258" t="n">
+        <v>3444</v>
+      </c>
+      <c r="J258" t="n">
+        <v>4060</v>
+      </c>
+      <c r="K258" t="n">
+        <v>4516</v>
+      </c>
+      <c r="L258" t="n">
+        <v>4764</v>
+      </c>
+      <c r="M258" t="n">
+        <v>4756</v>
+      </c>
+      <c r="N258" t="n">
+        <v>4731</v>
+      </c>
+      <c r="O258" t="n">
         <v>4714</v>
       </c>
-      <c r="Y257" t="n">
-        <v>4452</v>
-      </c>
-      <c r="Z257" t="n">
-        <v>4112</v>
-      </c>
-      <c r="AA257" t="n">
-        <v>3858</v>
+      <c r="P258" t="n">
+        <v>4703</v>
+      </c>
+      <c r="Q258" t="n">
+        <v>4705</v>
+      </c>
+      <c r="R258" t="n">
+        <v>4699</v>
+      </c>
+      <c r="S258" t="n">
+        <v>4697</v>
+      </c>
+      <c r="T258" t="n">
+        <v>4695</v>
+      </c>
+      <c r="U258" t="n">
+        <v>4719</v>
+      </c>
+      <c r="V258" t="n">
+        <v>4834</v>
+      </c>
+      <c r="W258" t="n">
+        <v>5103</v>
+      </c>
+      <c r="X258" t="n">
+        <v>5077</v>
+      </c>
+      <c r="Y258" t="n">
+        <v>4747</v>
+      </c>
+      <c r="Z258" t="n">
+        <v>4340</v>
+      </c>
+      <c r="AA258" t="n">
+        <v>3996</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA258"/>
+  <dimension ref="A1:AA259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21490,76 +21490,76 @@
         <v>15</v>
       </c>
       <c r="D254" t="n">
-        <v>3452</v>
+        <v>3407</v>
       </c>
       <c r="E254" t="n">
-        <v>3363</v>
+        <v>3329</v>
       </c>
       <c r="F254" t="n">
-        <v>3315</v>
+        <v>3283</v>
       </c>
       <c r="G254" t="n">
-        <v>3285</v>
+        <v>3254</v>
       </c>
       <c r="H254" t="n">
-        <v>3331</v>
+        <v>3305</v>
       </c>
       <c r="I254" t="n">
-        <v>3520</v>
+        <v>3479</v>
       </c>
       <c r="J254" t="n">
-        <v>4040</v>
+        <v>3971</v>
       </c>
       <c r="K254" t="n">
-        <v>4462</v>
+        <v>4377</v>
       </c>
       <c r="L254" t="n">
-        <v>4706</v>
+        <v>4609</v>
       </c>
       <c r="M254" t="n">
-        <v>4707</v>
+        <v>4614</v>
       </c>
       <c r="N254" t="n">
-        <v>4682</v>
+        <v>4565</v>
       </c>
       <c r="O254" t="n">
-        <v>4664</v>
+        <v>4532</v>
       </c>
       <c r="P254" t="n">
-        <v>4651</v>
+        <v>4507</v>
       </c>
       <c r="Q254" t="n">
-        <v>4652</v>
+        <v>4510</v>
       </c>
       <c r="R254" t="n">
-        <v>4646</v>
+        <v>4501</v>
       </c>
       <c r="S254" t="n">
-        <v>4642</v>
+        <v>4495</v>
       </c>
       <c r="T254" t="n">
-        <v>4639</v>
+        <v>4489</v>
       </c>
       <c r="U254" t="n">
-        <v>4667</v>
+        <v>4516</v>
       </c>
       <c r="V254" t="n">
-        <v>4792</v>
+        <v>4625</v>
       </c>
       <c r="W254" t="n">
-        <v>5039</v>
+        <v>4845</v>
       </c>
       <c r="X254" t="n">
-        <v>4959</v>
+        <v>4770</v>
       </c>
       <c r="Y254" t="n">
-        <v>4622</v>
+        <v>4461</v>
       </c>
       <c r="Z254" t="n">
-        <v>4285</v>
+        <v>4148</v>
       </c>
       <c r="AA254" t="n">
-        <v>3951</v>
+        <v>3834</v>
       </c>
     </row>
     <row r="255">
@@ -21573,76 +21573,76 @@
         <v>16</v>
       </c>
       <c r="D255" t="n">
-        <v>3483</v>
+        <v>3448</v>
       </c>
       <c r="E255" t="n">
-        <v>3398</v>
+        <v>3374</v>
       </c>
       <c r="F255" t="n">
-        <v>3352</v>
+        <v>3331</v>
       </c>
       <c r="G255" t="n">
-        <v>3323</v>
+        <v>3304</v>
       </c>
       <c r="H255" t="n">
-        <v>3371</v>
+        <v>3356</v>
       </c>
       <c r="I255" t="n">
-        <v>3563</v>
+        <v>3535</v>
       </c>
       <c r="J255" t="n">
-        <v>4093</v>
+        <v>4040</v>
       </c>
       <c r="K255" t="n">
-        <v>4523</v>
+        <v>4455</v>
       </c>
       <c r="L255" t="n">
-        <v>4771</v>
+        <v>4694</v>
       </c>
       <c r="M255" t="n">
-        <v>4773</v>
+        <v>4699</v>
       </c>
       <c r="N255" t="n">
-        <v>4748</v>
+        <v>4651</v>
       </c>
       <c r="O255" t="n">
-        <v>4731</v>
+        <v>4619</v>
       </c>
       <c r="P255" t="n">
-        <v>4719</v>
+        <v>4594</v>
       </c>
       <c r="Q255" t="n">
-        <v>4719</v>
+        <v>4597</v>
       </c>
       <c r="R255" t="n">
-        <v>4714</v>
+        <v>4589</v>
       </c>
       <c r="S255" t="n">
-        <v>4710</v>
+        <v>4583</v>
       </c>
       <c r="T255" t="n">
-        <v>4707</v>
+        <v>4577</v>
       </c>
       <c r="U255" t="n">
-        <v>4729</v>
+        <v>4597</v>
       </c>
       <c r="V255" t="n">
-        <v>4825</v>
+        <v>4677</v>
       </c>
       <c r="W255" t="n">
-        <v>5016</v>
+        <v>4839</v>
       </c>
       <c r="X255" t="n">
-        <v>4937</v>
+        <v>4765</v>
       </c>
       <c r="Y255" t="n">
-        <v>4604</v>
+        <v>4458</v>
       </c>
       <c r="Z255" t="n">
-        <v>4272</v>
+        <v>4147</v>
       </c>
       <c r="AA255" t="n">
-        <v>3941</v>
+        <v>3836</v>
       </c>
     </row>
     <row r="256">
@@ -21656,76 +21656,76 @@
         <v>17</v>
       </c>
       <c r="D256" t="n">
-        <v>3459</v>
+        <v>3438</v>
       </c>
       <c r="E256" t="n">
-        <v>3336</v>
+        <v>3326</v>
       </c>
       <c r="F256" t="n">
-        <v>3274</v>
+        <v>3270</v>
       </c>
       <c r="G256" t="n">
-        <v>3252</v>
+        <v>3250</v>
       </c>
       <c r="H256" t="n">
-        <v>3243</v>
+        <v>3241</v>
       </c>
       <c r="I256" t="n">
-        <v>3305</v>
+        <v>3301</v>
       </c>
       <c r="J256" t="n">
-        <v>3551</v>
+        <v>3537</v>
       </c>
       <c r="K256" t="n">
-        <v>3825</v>
+        <v>3801</v>
       </c>
       <c r="L256" t="n">
-        <v>4215</v>
+        <v>4175</v>
       </c>
       <c r="M256" t="n">
-        <v>4391</v>
+        <v>4345</v>
       </c>
       <c r="N256" t="n">
-        <v>4426</v>
+        <v>4378</v>
       </c>
       <c r="O256" t="n">
-        <v>4428</v>
+        <v>4379</v>
       </c>
       <c r="P256" t="n">
-        <v>4434</v>
+        <v>4369</v>
       </c>
       <c r="Q256" t="n">
-        <v>4436</v>
+        <v>4365</v>
       </c>
       <c r="R256" t="n">
-        <v>4445</v>
+        <v>4352</v>
       </c>
       <c r="S256" t="n">
-        <v>4448</v>
+        <v>4347</v>
       </c>
       <c r="T256" t="n">
-        <v>4450</v>
+        <v>4349</v>
       </c>
       <c r="U256" t="n">
-        <v>4527</v>
+        <v>4414</v>
       </c>
       <c r="V256" t="n">
-        <v>4612</v>
+        <v>4487</v>
       </c>
       <c r="W256" t="n">
-        <v>4794</v>
+        <v>4642</v>
       </c>
       <c r="X256" t="n">
-        <v>4662</v>
+        <v>4518</v>
       </c>
       <c r="Y256" t="n">
-        <v>4349</v>
+        <v>4226</v>
       </c>
       <c r="Z256" t="n">
-        <v>4055</v>
+        <v>3952</v>
       </c>
       <c r="AA256" t="n">
-        <v>3826</v>
+        <v>3738</v>
       </c>
     </row>
     <row r="257">
@@ -21739,76 +21739,76 @@
         <v>18</v>
       </c>
       <c r="D257" t="n">
-        <v>3367</v>
+        <v>3343</v>
       </c>
       <c r="E257" t="n">
-        <v>3247</v>
+        <v>3234</v>
       </c>
       <c r="F257" t="n">
-        <v>3186</v>
+        <v>3179</v>
       </c>
       <c r="G257" t="n">
-        <v>3155</v>
+        <v>3150</v>
       </c>
       <c r="H257" t="n">
-        <v>3149</v>
+        <v>3145</v>
       </c>
       <c r="I257" t="n">
-        <v>3193</v>
+        <v>3187</v>
       </c>
       <c r="J257" t="n">
-        <v>3392</v>
+        <v>3378</v>
       </c>
       <c r="K257" t="n">
-        <v>3610</v>
+        <v>3587</v>
       </c>
       <c r="L257" t="n">
-        <v>3991</v>
+        <v>3952</v>
       </c>
       <c r="M257" t="n">
-        <v>4243</v>
+        <v>4195</v>
       </c>
       <c r="N257" t="n">
-        <v>4337</v>
+        <v>4285</v>
       </c>
       <c r="O257" t="n">
-        <v>4352</v>
+        <v>4299</v>
       </c>
       <c r="P257" t="n">
-        <v>4401</v>
+        <v>4315</v>
       </c>
       <c r="Q257" t="n">
-        <v>4414</v>
+        <v>4319</v>
       </c>
       <c r="R257" t="n">
-        <v>4404</v>
+        <v>4316</v>
       </c>
       <c r="S257" t="n">
+        <v>4320</v>
+      </c>
+      <c r="T257" t="n">
+        <v>4325</v>
+      </c>
+      <c r="U257" t="n">
         <v>4417</v>
       </c>
-      <c r="T257" t="n">
-        <v>4431</v>
-      </c>
-      <c r="U257" t="n">
-        <v>4533</v>
-      </c>
       <c r="V257" t="n">
-        <v>4682</v>
+        <v>4552</v>
       </c>
       <c r="W257" t="n">
-        <v>4949</v>
+        <v>4792</v>
       </c>
       <c r="X257" t="n">
-        <v>4862</v>
+        <v>4710</v>
       </c>
       <c r="Y257" t="n">
-        <v>4540</v>
+        <v>4408</v>
       </c>
       <c r="Z257" t="n">
-        <v>4163</v>
+        <v>4054</v>
       </c>
       <c r="AA257" t="n">
-        <v>3875</v>
+        <v>3784</v>
       </c>
     </row>
     <row r="258">
@@ -21822,76 +21822,159 @@
         <v>19</v>
       </c>
       <c r="D258" t="n">
-        <v>3375</v>
+        <v>3343</v>
       </c>
       <c r="E258" t="n">
-        <v>3256</v>
+        <v>3235</v>
       </c>
       <c r="F258" t="n">
-        <v>3206</v>
+        <v>3188</v>
       </c>
       <c r="G258" t="n">
-        <v>3183</v>
+        <v>3168</v>
       </c>
       <c r="H258" t="n">
-        <v>3237</v>
+        <v>3191</v>
       </c>
       <c r="I258" t="n">
-        <v>3444</v>
+        <v>3371</v>
       </c>
       <c r="J258" t="n">
-        <v>4060</v>
+        <v>3926</v>
       </c>
       <c r="K258" t="n">
-        <v>4516</v>
+        <v>4357</v>
       </c>
       <c r="L258" t="n">
-        <v>4764</v>
+        <v>4651</v>
       </c>
       <c r="M258" t="n">
-        <v>4756</v>
+        <v>4696</v>
       </c>
       <c r="N258" t="n">
-        <v>4731</v>
+        <v>4648</v>
       </c>
       <c r="O258" t="n">
-        <v>4714</v>
+        <v>4630</v>
       </c>
       <c r="P258" t="n">
-        <v>4703</v>
+        <v>4610</v>
       </c>
       <c r="Q258" t="n">
-        <v>4705</v>
+        <v>4610</v>
       </c>
       <c r="R258" t="n">
-        <v>4699</v>
+        <v>4591</v>
       </c>
       <c r="S258" t="n">
-        <v>4697</v>
+        <v>4577</v>
       </c>
       <c r="T258" t="n">
-        <v>4695</v>
+        <v>4571</v>
       </c>
       <c r="U258" t="n">
-        <v>4719</v>
+        <v>4596</v>
       </c>
       <c r="V258" t="n">
-        <v>4834</v>
+        <v>4715</v>
       </c>
       <c r="W258" t="n">
-        <v>5103</v>
+        <v>4932</v>
       </c>
       <c r="X258" t="n">
-        <v>5077</v>
+        <v>4830</v>
       </c>
       <c r="Y258" t="n">
-        <v>4747</v>
+        <v>4528</v>
       </c>
       <c r="Z258" t="n">
-        <v>4340</v>
+        <v>4185</v>
       </c>
       <c r="AA258" t="n">
-        <v>3996</v>
+        <v>3894</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B259" t="n">
+        <v>10</v>
+      </c>
+      <c r="C259" t="n">
+        <v>20</v>
+      </c>
+      <c r="D259" t="n">
+        <v>3384</v>
+      </c>
+      <c r="E259" t="n">
+        <v>3304</v>
+      </c>
+      <c r="F259" t="n">
+        <v>3257</v>
+      </c>
+      <c r="G259" t="n">
+        <v>3228</v>
+      </c>
+      <c r="H259" t="n">
+        <v>3282</v>
+      </c>
+      <c r="I259" t="n">
+        <v>3466</v>
+      </c>
+      <c r="J259" t="n">
+        <v>3987</v>
+      </c>
+      <c r="K259" t="n">
+        <v>4415</v>
+      </c>
+      <c r="L259" t="n">
+        <v>4661</v>
+      </c>
+      <c r="M259" t="n">
+        <v>4666</v>
+      </c>
+      <c r="N259" t="n">
+        <v>4616</v>
+      </c>
+      <c r="O259" t="n">
+        <v>4584</v>
+      </c>
+      <c r="P259" t="n">
+        <v>4558</v>
+      </c>
+      <c r="Q259" t="n">
+        <v>4561</v>
+      </c>
+      <c r="R259" t="n">
+        <v>4552</v>
+      </c>
+      <c r="S259" t="n">
+        <v>4546</v>
+      </c>
+      <c r="T259" t="n">
+        <v>4540</v>
+      </c>
+      <c r="U259" t="n">
+        <v>4568</v>
+      </c>
+      <c r="V259" t="n">
+        <v>4679</v>
+      </c>
+      <c r="W259" t="n">
+        <v>4906</v>
+      </c>
+      <c r="X259" t="n">
+        <v>4830</v>
+      </c>
+      <c r="Y259" t="n">
+        <v>4515</v>
+      </c>
+      <c r="Z259" t="n">
+        <v>4196</v>
+      </c>
+      <c r="AA259" t="n">
+        <v>3877</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA259"/>
+  <dimension ref="A1:AA260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21573,76 +21573,76 @@
         <v>16</v>
       </c>
       <c r="D255" t="n">
-        <v>3448</v>
+        <v>3596</v>
       </c>
       <c r="E255" t="n">
-        <v>3374</v>
+        <v>3389</v>
       </c>
       <c r="F255" t="n">
-        <v>3331</v>
+        <v>3281</v>
       </c>
       <c r="G255" t="n">
-        <v>3304</v>
+        <v>3212</v>
       </c>
       <c r="H255" t="n">
-        <v>3356</v>
+        <v>3273</v>
       </c>
       <c r="I255" t="n">
-        <v>3535</v>
+        <v>3486</v>
       </c>
       <c r="J255" t="n">
-        <v>4040</v>
+        <v>4116</v>
       </c>
       <c r="K255" t="n">
-        <v>4455</v>
+        <v>4634</v>
       </c>
       <c r="L255" t="n">
-        <v>4694</v>
+        <v>4978</v>
       </c>
       <c r="M255" t="n">
-        <v>4699</v>
+        <v>5034</v>
       </c>
       <c r="N255" t="n">
-        <v>4651</v>
+        <v>4934</v>
       </c>
       <c r="O255" t="n">
-        <v>4619</v>
+        <v>4891</v>
       </c>
       <c r="P255" t="n">
-        <v>4594</v>
+        <v>4843</v>
       </c>
       <c r="Q255" t="n">
-        <v>4597</v>
+        <v>4864</v>
       </c>
       <c r="R255" t="n">
-        <v>4589</v>
+        <v>4839</v>
       </c>
       <c r="S255" t="n">
-        <v>4583</v>
+        <v>4817</v>
       </c>
       <c r="T255" t="n">
-        <v>4577</v>
+        <v>4794</v>
       </c>
       <c r="U255" t="n">
-        <v>4597</v>
+        <v>4804</v>
       </c>
       <c r="V255" t="n">
-        <v>4677</v>
+        <v>4865</v>
       </c>
       <c r="W255" t="n">
-        <v>4839</v>
+        <v>4979</v>
       </c>
       <c r="X255" t="n">
-        <v>4765</v>
+        <v>4875</v>
       </c>
       <c r="Y255" t="n">
-        <v>4458</v>
+        <v>4562</v>
       </c>
       <c r="Z255" t="n">
-        <v>4147</v>
+        <v>4239</v>
       </c>
       <c r="AA255" t="n">
-        <v>3836</v>
+        <v>3929</v>
       </c>
     </row>
     <row r="256">
@@ -21656,76 +21656,76 @@
         <v>17</v>
       </c>
       <c r="D256" t="n">
-        <v>3438</v>
+        <v>3597</v>
       </c>
       <c r="E256" t="n">
-        <v>3326</v>
+        <v>3347</v>
       </c>
       <c r="F256" t="n">
-        <v>3270</v>
+        <v>3230</v>
       </c>
       <c r="G256" t="n">
-        <v>3250</v>
+        <v>3194</v>
       </c>
       <c r="H256" t="n">
-        <v>3241</v>
+        <v>3163</v>
       </c>
       <c r="I256" t="n">
-        <v>3301</v>
+        <v>3232</v>
       </c>
       <c r="J256" t="n">
-        <v>3537</v>
+        <v>3533</v>
       </c>
       <c r="K256" t="n">
-        <v>3801</v>
+        <v>3862</v>
       </c>
       <c r="L256" t="n">
-        <v>4175</v>
+        <v>4377</v>
       </c>
       <c r="M256" t="n">
-        <v>4345</v>
+        <v>4612</v>
       </c>
       <c r="N256" t="n">
-        <v>4378</v>
+        <v>4702</v>
       </c>
       <c r="O256" t="n">
-        <v>4379</v>
+        <v>4736</v>
       </c>
       <c r="P256" t="n">
-        <v>4369</v>
+        <v>4654</v>
       </c>
       <c r="Q256" t="n">
-        <v>4365</v>
+        <v>4667</v>
       </c>
       <c r="R256" t="n">
-        <v>4352</v>
+        <v>4584</v>
       </c>
       <c r="S256" t="n">
-        <v>4347</v>
+        <v>4585</v>
       </c>
       <c r="T256" t="n">
-        <v>4349</v>
+        <v>4601</v>
       </c>
       <c r="U256" t="n">
-        <v>4414</v>
+        <v>4655</v>
       </c>
       <c r="V256" t="n">
-        <v>4487</v>
+        <v>4699</v>
       </c>
       <c r="W256" t="n">
-        <v>4642</v>
+        <v>4803</v>
       </c>
       <c r="X256" t="n">
-        <v>4518</v>
+        <v>4617</v>
       </c>
       <c r="Y256" t="n">
-        <v>4226</v>
+        <v>4331</v>
       </c>
       <c r="Z256" t="n">
-        <v>3952</v>
+        <v>4048</v>
       </c>
       <c r="AA256" t="n">
-        <v>3738</v>
+        <v>3845</v>
       </c>
     </row>
     <row r="257">
@@ -21739,76 +21739,76 @@
         <v>18</v>
       </c>
       <c r="D257" t="n">
-        <v>3343</v>
+        <v>3507</v>
       </c>
       <c r="E257" t="n">
-        <v>3234</v>
+        <v>3269</v>
       </c>
       <c r="F257" t="n">
-        <v>3179</v>
+        <v>3147</v>
       </c>
       <c r="G257" t="n">
-        <v>3150</v>
+        <v>3084</v>
       </c>
       <c r="H257" t="n">
-        <v>3145</v>
+        <v>3073</v>
       </c>
       <c r="I257" t="n">
-        <v>3187</v>
+        <v>3131</v>
       </c>
       <c r="J257" t="n">
-        <v>3378</v>
+        <v>3394</v>
       </c>
       <c r="K257" t="n">
-        <v>3587</v>
+        <v>3683</v>
       </c>
       <c r="L257" t="n">
-        <v>3952</v>
+        <v>4186</v>
       </c>
       <c r="M257" t="n">
-        <v>4195</v>
+        <v>4521</v>
       </c>
       <c r="N257" t="n">
-        <v>4285</v>
+        <v>4645</v>
       </c>
       <c r="O257" t="n">
-        <v>4299</v>
+        <v>4665</v>
       </c>
       <c r="P257" t="n">
-        <v>4315</v>
+        <v>4607</v>
       </c>
       <c r="Q257" t="n">
-        <v>4319</v>
+        <v>4592</v>
       </c>
       <c r="R257" t="n">
-        <v>4316</v>
+        <v>4603</v>
       </c>
       <c r="S257" t="n">
-        <v>4320</v>
+        <v>4588</v>
       </c>
       <c r="T257" t="n">
-        <v>4325</v>
+        <v>4572</v>
       </c>
       <c r="U257" t="n">
-        <v>4417</v>
+        <v>4649</v>
       </c>
       <c r="V257" t="n">
-        <v>4552</v>
+        <v>4761</v>
       </c>
       <c r="W257" t="n">
-        <v>4792</v>
+        <v>4962</v>
       </c>
       <c r="X257" t="n">
-        <v>4710</v>
+        <v>4876</v>
       </c>
       <c r="Y257" t="n">
-        <v>4408</v>
+        <v>4556</v>
       </c>
       <c r="Z257" t="n">
-        <v>4054</v>
+        <v>4182</v>
       </c>
       <c r="AA257" t="n">
-        <v>3784</v>
+        <v>3897</v>
       </c>
     </row>
     <row r="258">
@@ -21822,76 +21822,76 @@
         <v>19</v>
       </c>
       <c r="D258" t="n">
-        <v>3343</v>
+        <v>3502</v>
       </c>
       <c r="E258" t="n">
-        <v>3235</v>
+        <v>3248</v>
       </c>
       <c r="F258" t="n">
-        <v>3188</v>
+        <v>3137</v>
       </c>
       <c r="G258" t="n">
-        <v>3168</v>
+        <v>3089</v>
       </c>
       <c r="H258" t="n">
-        <v>3191</v>
+        <v>3120</v>
       </c>
       <c r="I258" t="n">
-        <v>3371</v>
+        <v>3351</v>
       </c>
       <c r="J258" t="n">
-        <v>3926</v>
+        <v>4063</v>
       </c>
       <c r="K258" t="n">
-        <v>4357</v>
+        <v>4615</v>
       </c>
       <c r="L258" t="n">
-        <v>4651</v>
+        <v>4993</v>
       </c>
       <c r="M258" t="n">
-        <v>4696</v>
+        <v>5051</v>
       </c>
       <c r="N258" t="n">
-        <v>4648</v>
+        <v>4957</v>
       </c>
       <c r="O258" t="n">
-        <v>4630</v>
+        <v>4921</v>
       </c>
       <c r="P258" t="n">
-        <v>4610</v>
+        <v>4882</v>
       </c>
       <c r="Q258" t="n">
-        <v>4610</v>
+        <v>4883</v>
       </c>
       <c r="R258" t="n">
-        <v>4591</v>
+        <v>4845</v>
       </c>
       <c r="S258" t="n">
-        <v>4577</v>
+        <v>4818</v>
       </c>
       <c r="T258" t="n">
-        <v>4571</v>
+        <v>4807</v>
       </c>
       <c r="U258" t="n">
-        <v>4596</v>
+        <v>4826</v>
       </c>
       <c r="V258" t="n">
-        <v>4715</v>
+        <v>4921</v>
       </c>
       <c r="W258" t="n">
-        <v>4932</v>
+        <v>5092</v>
       </c>
       <c r="X258" t="n">
-        <v>4830</v>
+        <v>4985</v>
       </c>
       <c r="Y258" t="n">
-        <v>4528</v>
+        <v>4667</v>
       </c>
       <c r="Z258" t="n">
-        <v>4185</v>
+        <v>4307</v>
       </c>
       <c r="AA258" t="n">
-        <v>3894</v>
+        <v>4001</v>
       </c>
     </row>
     <row r="259">
@@ -21905,76 +21905,159 @@
         <v>20</v>
       </c>
       <c r="D259" t="n">
-        <v>3384</v>
+        <v>3536</v>
       </c>
       <c r="E259" t="n">
-        <v>3304</v>
+        <v>3322</v>
       </c>
       <c r="F259" t="n">
-        <v>3257</v>
+        <v>3212</v>
       </c>
       <c r="G259" t="n">
-        <v>3228</v>
+        <v>3140</v>
       </c>
       <c r="H259" t="n">
-        <v>3282</v>
+        <v>3203</v>
       </c>
       <c r="I259" t="n">
-        <v>3466</v>
+        <v>3422</v>
       </c>
       <c r="J259" t="n">
-        <v>3987</v>
+        <v>4066</v>
       </c>
       <c r="K259" t="n">
-        <v>4415</v>
+        <v>4595</v>
       </c>
       <c r="L259" t="n">
-        <v>4661</v>
+        <v>4948</v>
       </c>
       <c r="M259" t="n">
-        <v>4666</v>
+        <v>5005</v>
       </c>
       <c r="N259" t="n">
-        <v>4616</v>
+        <v>4902</v>
       </c>
       <c r="O259" t="n">
-        <v>4584</v>
+        <v>4858</v>
       </c>
       <c r="P259" t="n">
-        <v>4558</v>
+        <v>4809</v>
       </c>
       <c r="Q259" t="n">
-        <v>4561</v>
+        <v>4830</v>
       </c>
       <c r="R259" t="n">
-        <v>4552</v>
+        <v>4805</v>
       </c>
       <c r="S259" t="n">
-        <v>4546</v>
+        <v>4783</v>
       </c>
       <c r="T259" t="n">
-        <v>4540</v>
+        <v>4759</v>
       </c>
       <c r="U259" t="n">
-        <v>4568</v>
+        <v>4775</v>
       </c>
       <c r="V259" t="n">
-        <v>4679</v>
+        <v>4870</v>
       </c>
       <c r="W259" t="n">
-        <v>4906</v>
+        <v>5052</v>
       </c>
       <c r="X259" t="n">
-        <v>4830</v>
+        <v>4945</v>
       </c>
       <c r="Y259" t="n">
-        <v>4515</v>
+        <v>4623</v>
       </c>
       <c r="Z259" t="n">
-        <v>4196</v>
+        <v>4291</v>
       </c>
       <c r="AA259" t="n">
-        <v>3877</v>
+        <v>3974</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B260" t="n">
+        <v>10</v>
+      </c>
+      <c r="C260" t="n">
+        <v>21</v>
+      </c>
+      <c r="D260" t="n">
+        <v>3532</v>
+      </c>
+      <c r="E260" t="n">
+        <v>3318</v>
+      </c>
+      <c r="F260" t="n">
+        <v>3207</v>
+      </c>
+      <c r="G260" t="n">
+        <v>3136</v>
+      </c>
+      <c r="H260" t="n">
+        <v>3198</v>
+      </c>
+      <c r="I260" t="n">
+        <v>3416</v>
+      </c>
+      <c r="J260" t="n">
+        <v>4059</v>
+      </c>
+      <c r="K260" t="n">
+        <v>4588</v>
+      </c>
+      <c r="L260" t="n">
+        <v>4940</v>
+      </c>
+      <c r="M260" t="n">
+        <v>4997</v>
+      </c>
+      <c r="N260" t="n">
+        <v>4894</v>
+      </c>
+      <c r="O260" t="n">
+        <v>4850</v>
+      </c>
+      <c r="P260" t="n">
+        <v>4800</v>
+      </c>
+      <c r="Q260" t="n">
+        <v>4822</v>
+      </c>
+      <c r="R260" t="n">
+        <v>4797</v>
+      </c>
+      <c r="S260" t="n">
+        <v>4775</v>
+      </c>
+      <c r="T260" t="n">
+        <v>4751</v>
+      </c>
+      <c r="U260" t="n">
+        <v>4767</v>
+      </c>
+      <c r="V260" t="n">
+        <v>4863</v>
+      </c>
+      <c r="W260" t="n">
+        <v>5045</v>
+      </c>
+      <c r="X260" t="n">
+        <v>4938</v>
+      </c>
+      <c r="Y260" t="n">
+        <v>4617</v>
+      </c>
+      <c r="Z260" t="n">
+        <v>4286</v>
+      </c>
+      <c r="AA260" t="n">
+        <v>3969</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA260"/>
+  <dimension ref="A1:AA261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21656,76 +21656,76 @@
         <v>17</v>
       </c>
       <c r="D256" t="n">
-        <v>3597</v>
+        <v>3728</v>
       </c>
       <c r="E256" t="n">
-        <v>3347</v>
+        <v>3501</v>
       </c>
       <c r="F256" t="n">
-        <v>3230</v>
+        <v>3395</v>
       </c>
       <c r="G256" t="n">
-        <v>3194</v>
+        <v>3362</v>
       </c>
       <c r="H256" t="n">
-        <v>3163</v>
+        <v>3334</v>
       </c>
       <c r="I256" t="n">
-        <v>3232</v>
+        <v>3387</v>
       </c>
       <c r="J256" t="n">
-        <v>3533</v>
+        <v>3620</v>
       </c>
       <c r="K256" t="n">
-        <v>3862</v>
+        <v>3875</v>
       </c>
       <c r="L256" t="n">
+        <v>4274</v>
+      </c>
+      <c r="M256" t="n">
+        <v>4456</v>
+      </c>
+      <c r="N256" t="n">
+        <v>4526</v>
+      </c>
+      <c r="O256" t="n">
+        <v>4552</v>
+      </c>
+      <c r="P256" t="n">
+        <v>4436</v>
+      </c>
+      <c r="Q256" t="n">
+        <v>4454</v>
+      </c>
+      <c r="R256" t="n">
+        <v>4337</v>
+      </c>
+      <c r="S256" t="n">
+        <v>4339</v>
+      </c>
+      <c r="T256" t="n">
         <v>4377</v>
       </c>
-      <c r="M256" t="n">
-        <v>4612</v>
-      </c>
-      <c r="N256" t="n">
-        <v>4702</v>
-      </c>
-      <c r="O256" t="n">
-        <v>4736</v>
-      </c>
-      <c r="P256" t="n">
-        <v>4654</v>
-      </c>
-      <c r="Q256" t="n">
-        <v>4667</v>
-      </c>
-      <c r="R256" t="n">
-        <v>4584</v>
-      </c>
-      <c r="S256" t="n">
-        <v>4585</v>
-      </c>
-      <c r="T256" t="n">
-        <v>4601</v>
-      </c>
       <c r="U256" t="n">
-        <v>4655</v>
+        <v>4502</v>
       </c>
       <c r="V256" t="n">
-        <v>4699</v>
+        <v>4605</v>
       </c>
       <c r="W256" t="n">
-        <v>4803</v>
+        <v>4847</v>
       </c>
       <c r="X256" t="n">
-        <v>4617</v>
+        <v>4682</v>
       </c>
       <c r="Y256" t="n">
-        <v>4331</v>
+        <v>4427</v>
       </c>
       <c r="Z256" t="n">
-        <v>4048</v>
+        <v>4175</v>
       </c>
       <c r="AA256" t="n">
-        <v>3845</v>
+        <v>3995</v>
       </c>
     </row>
     <row r="257">
@@ -21739,76 +21739,76 @@
         <v>18</v>
       </c>
       <c r="D257" t="n">
-        <v>3507</v>
+        <v>3644</v>
       </c>
       <c r="E257" t="n">
+        <v>3440</v>
+      </c>
+      <c r="F257" t="n">
+        <v>3315</v>
+      </c>
+      <c r="G257" t="n">
         <v>3269</v>
       </c>
-      <c r="F257" t="n">
-        <v>3147</v>
-      </c>
-      <c r="G257" t="n">
-        <v>3084</v>
-      </c>
       <c r="H257" t="n">
-        <v>3073</v>
+        <v>3251</v>
       </c>
       <c r="I257" t="n">
-        <v>3131</v>
+        <v>3275</v>
       </c>
       <c r="J257" t="n">
-        <v>3394</v>
+        <v>3447</v>
       </c>
       <c r="K257" t="n">
-        <v>3683</v>
+        <v>3646</v>
       </c>
       <c r="L257" t="n">
-        <v>4186</v>
+        <v>3987</v>
       </c>
       <c r="M257" t="n">
-        <v>4521</v>
+        <v>4248</v>
       </c>
       <c r="N257" t="n">
-        <v>4645</v>
+        <v>4395</v>
       </c>
       <c r="O257" t="n">
-        <v>4665</v>
+        <v>4454</v>
       </c>
       <c r="P257" t="n">
-        <v>4607</v>
+        <v>4451</v>
       </c>
       <c r="Q257" t="n">
-        <v>4592</v>
+        <v>4492</v>
       </c>
       <c r="R257" t="n">
-        <v>4603</v>
+        <v>4338</v>
       </c>
       <c r="S257" t="n">
-        <v>4588</v>
+        <v>4338</v>
       </c>
       <c r="T257" t="n">
-        <v>4572</v>
+        <v>4338</v>
       </c>
       <c r="U257" t="n">
-        <v>4649</v>
+        <v>4493</v>
       </c>
       <c r="V257" t="n">
-        <v>4761</v>
+        <v>4710</v>
       </c>
       <c r="W257" t="n">
-        <v>4962</v>
+        <v>5016</v>
       </c>
       <c r="X257" t="n">
-        <v>4876</v>
+        <v>4852</v>
       </c>
       <c r="Y257" t="n">
-        <v>4556</v>
+        <v>4586</v>
       </c>
       <c r="Z257" t="n">
-        <v>4182</v>
+        <v>4279</v>
       </c>
       <c r="AA257" t="n">
-        <v>3897</v>
+        <v>4055</v>
       </c>
     </row>
     <row r="258">
@@ -21822,76 +21822,76 @@
         <v>19</v>
       </c>
       <c r="D258" t="n">
-        <v>3502</v>
+        <v>3630</v>
       </c>
       <c r="E258" t="n">
-        <v>3248</v>
+        <v>3401</v>
       </c>
       <c r="F258" t="n">
-        <v>3137</v>
+        <v>3300</v>
       </c>
       <c r="G258" t="n">
-        <v>3089</v>
+        <v>3257</v>
       </c>
       <c r="H258" t="n">
-        <v>3120</v>
+        <v>3282</v>
       </c>
       <c r="I258" t="n">
-        <v>3351</v>
+        <v>3471</v>
       </c>
       <c r="J258" t="n">
-        <v>4063</v>
+        <v>4053</v>
       </c>
       <c r="K258" t="n">
-        <v>4615</v>
+        <v>4505</v>
       </c>
       <c r="L258" t="n">
-        <v>4993</v>
+        <v>4813</v>
       </c>
       <c r="M258" t="n">
-        <v>5051</v>
+        <v>4860</v>
       </c>
       <c r="N258" t="n">
-        <v>4957</v>
+        <v>4744</v>
       </c>
       <c r="O258" t="n">
-        <v>4921</v>
+        <v>4698</v>
       </c>
       <c r="P258" t="n">
-        <v>4882</v>
+        <v>4649</v>
       </c>
       <c r="Q258" t="n">
-        <v>4883</v>
+        <v>4651</v>
       </c>
       <c r="R258" t="n">
-        <v>4845</v>
+        <v>4603</v>
       </c>
       <c r="S258" t="n">
-        <v>4818</v>
+        <v>4569</v>
       </c>
       <c r="T258" t="n">
-        <v>4807</v>
+        <v>4555</v>
       </c>
       <c r="U258" t="n">
-        <v>4826</v>
+        <v>4595</v>
       </c>
       <c r="V258" t="n">
-        <v>4921</v>
+        <v>4785</v>
       </c>
       <c r="W258" t="n">
-        <v>5092</v>
+        <v>5131</v>
       </c>
       <c r="X258" t="n">
-        <v>4985</v>
+        <v>5035</v>
       </c>
       <c r="Y258" t="n">
-        <v>4667</v>
+        <v>4748</v>
       </c>
       <c r="Z258" t="n">
-        <v>4307</v>
+        <v>4424</v>
       </c>
       <c r="AA258" t="n">
-        <v>4001</v>
+        <v>4148</v>
       </c>
     </row>
     <row r="259">
@@ -21905,76 +21905,76 @@
         <v>20</v>
       </c>
       <c r="D259" t="n">
-        <v>3536</v>
+        <v>3657</v>
       </c>
       <c r="E259" t="n">
-        <v>3322</v>
+        <v>3465</v>
       </c>
       <c r="F259" t="n">
-        <v>3212</v>
+        <v>3363</v>
       </c>
       <c r="G259" t="n">
-        <v>3140</v>
+        <v>3300</v>
       </c>
       <c r="H259" t="n">
-        <v>3203</v>
+        <v>3345</v>
       </c>
       <c r="I259" t="n">
-        <v>3422</v>
+        <v>3512</v>
       </c>
       <c r="J259" t="n">
-        <v>4066</v>
+        <v>4018</v>
       </c>
       <c r="K259" t="n">
+        <v>4426</v>
+      </c>
+      <c r="L259" t="n">
+        <v>4723</v>
+      </c>
+      <c r="M259" t="n">
+        <v>4800</v>
+      </c>
+      <c r="N259" t="n">
+        <v>4691</v>
+      </c>
+      <c r="O259" t="n">
+        <v>4646</v>
+      </c>
+      <c r="P259" t="n">
         <v>4595</v>
       </c>
-      <c r="L259" t="n">
-        <v>4948</v>
-      </c>
-      <c r="M259" t="n">
-        <v>5005</v>
-      </c>
-      <c r="N259" t="n">
-        <v>4902</v>
-      </c>
-      <c r="O259" t="n">
-        <v>4858</v>
-      </c>
-      <c r="P259" t="n">
-        <v>4809</v>
-      </c>
       <c r="Q259" t="n">
-        <v>4830</v>
+        <v>4614</v>
       </c>
       <c r="R259" t="n">
-        <v>4805</v>
+        <v>4575</v>
       </c>
       <c r="S259" t="n">
-        <v>4783</v>
+        <v>4546</v>
       </c>
       <c r="T259" t="n">
-        <v>4759</v>
+        <v>4493</v>
       </c>
       <c r="U259" t="n">
-        <v>4775</v>
+        <v>4520</v>
       </c>
       <c r="V259" t="n">
-        <v>4870</v>
+        <v>4722</v>
       </c>
       <c r="W259" t="n">
-        <v>5052</v>
+        <v>5079</v>
       </c>
       <c r="X259" t="n">
-        <v>4945</v>
+        <v>4976</v>
       </c>
       <c r="Y259" t="n">
-        <v>4623</v>
+        <v>4693</v>
       </c>
       <c r="Z259" t="n">
-        <v>4291</v>
+        <v>4397</v>
       </c>
       <c r="AA259" t="n">
-        <v>3974</v>
+        <v>4113</v>
       </c>
     </row>
     <row r="260">
@@ -21988,76 +21988,159 @@
         <v>21</v>
       </c>
       <c r="D260" t="n">
-        <v>3532</v>
+        <v>3654</v>
       </c>
       <c r="E260" t="n">
-        <v>3318</v>
+        <v>3462</v>
       </c>
       <c r="F260" t="n">
-        <v>3207</v>
+        <v>3359</v>
       </c>
       <c r="G260" t="n">
-        <v>3136</v>
+        <v>3296</v>
       </c>
       <c r="H260" t="n">
-        <v>3198</v>
+        <v>3341</v>
       </c>
       <c r="I260" t="n">
-        <v>3416</v>
+        <v>3508</v>
       </c>
       <c r="J260" t="n">
-        <v>4059</v>
+        <v>4013</v>
       </c>
       <c r="K260" t="n">
+        <v>4420</v>
+      </c>
+      <c r="L260" t="n">
+        <v>4716</v>
+      </c>
+      <c r="M260" t="n">
+        <v>4794</v>
+      </c>
+      <c r="N260" t="n">
+        <v>4684</v>
+      </c>
+      <c r="O260" t="n">
+        <v>4640</v>
+      </c>
+      <c r="P260" t="n">
         <v>4588</v>
       </c>
-      <c r="L260" t="n">
-        <v>4940</v>
-      </c>
-      <c r="M260" t="n">
-        <v>4997</v>
-      </c>
-      <c r="N260" t="n">
-        <v>4894</v>
-      </c>
-      <c r="O260" t="n">
-        <v>4850</v>
-      </c>
-      <c r="P260" t="n">
-        <v>4800</v>
-      </c>
       <c r="Q260" t="n">
-        <v>4822</v>
+        <v>4607</v>
       </c>
       <c r="R260" t="n">
-        <v>4797</v>
+        <v>4568</v>
       </c>
       <c r="S260" t="n">
-        <v>4775</v>
+        <v>4540</v>
       </c>
       <c r="T260" t="n">
-        <v>4751</v>
+        <v>4486</v>
       </c>
       <c r="U260" t="n">
-        <v>4767</v>
+        <v>4513</v>
       </c>
       <c r="V260" t="n">
-        <v>4863</v>
+        <v>4716</v>
       </c>
       <c r="W260" t="n">
-        <v>5045</v>
+        <v>5073</v>
       </c>
       <c r="X260" t="n">
-        <v>4938</v>
+        <v>4971</v>
       </c>
       <c r="Y260" t="n">
-        <v>4617</v>
+        <v>4688</v>
       </c>
       <c r="Z260" t="n">
-        <v>4286</v>
+        <v>4392</v>
       </c>
       <c r="AA260" t="n">
-        <v>3969</v>
+        <v>4109</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B261" t="n">
+        <v>10</v>
+      </c>
+      <c r="C261" t="n">
+        <v>22</v>
+      </c>
+      <c r="D261" t="n">
+        <v>3653</v>
+      </c>
+      <c r="E261" t="n">
+        <v>3461</v>
+      </c>
+      <c r="F261" t="n">
+        <v>3358</v>
+      </c>
+      <c r="G261" t="n">
+        <v>3295</v>
+      </c>
+      <c r="H261" t="n">
+        <v>3340</v>
+      </c>
+      <c r="I261" t="n">
+        <v>3507</v>
+      </c>
+      <c r="J261" t="n">
+        <v>4012</v>
+      </c>
+      <c r="K261" t="n">
+        <v>4419</v>
+      </c>
+      <c r="L261" t="n">
+        <v>4715</v>
+      </c>
+      <c r="M261" t="n">
+        <v>4793</v>
+      </c>
+      <c r="N261" t="n">
+        <v>4683</v>
+      </c>
+      <c r="O261" t="n">
+        <v>4638</v>
+      </c>
+      <c r="P261" t="n">
+        <v>4587</v>
+      </c>
+      <c r="Q261" t="n">
+        <v>4606</v>
+      </c>
+      <c r="R261" t="n">
+        <v>4567</v>
+      </c>
+      <c r="S261" t="n">
+        <v>4538</v>
+      </c>
+      <c r="T261" t="n">
+        <v>4485</v>
+      </c>
+      <c r="U261" t="n">
+        <v>4512</v>
+      </c>
+      <c r="V261" t="n">
+        <v>4714</v>
+      </c>
+      <c r="W261" t="n">
+        <v>5072</v>
+      </c>
+      <c r="X261" t="n">
+        <v>4970</v>
+      </c>
+      <c r="Y261" t="n">
+        <v>4687</v>
+      </c>
+      <c r="Z261" t="n">
+        <v>4392</v>
+      </c>
+      <c r="AA261" t="n">
+        <v>4108</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA261"/>
+  <dimension ref="A1:AA262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21739,76 +21739,76 @@
         <v>18</v>
       </c>
       <c r="D257" t="n">
-        <v>3644</v>
+        <v>3628</v>
       </c>
       <c r="E257" t="n">
-        <v>3440</v>
+        <v>3421</v>
       </c>
       <c r="F257" t="n">
-        <v>3315</v>
+        <v>3294</v>
       </c>
       <c r="G257" t="n">
-        <v>3269</v>
+        <v>3248</v>
       </c>
       <c r="H257" t="n">
-        <v>3251</v>
+        <v>3230</v>
       </c>
       <c r="I257" t="n">
-        <v>3275</v>
+        <v>3255</v>
       </c>
       <c r="J257" t="n">
-        <v>3447</v>
+        <v>3432</v>
       </c>
       <c r="K257" t="n">
-        <v>3646</v>
+        <v>3639</v>
       </c>
       <c r="L257" t="n">
-        <v>3987</v>
+        <v>3992</v>
       </c>
       <c r="M257" t="n">
-        <v>4248</v>
+        <v>4263</v>
       </c>
       <c r="N257" t="n">
-        <v>4395</v>
+        <v>4415</v>
       </c>
       <c r="O257" t="n">
-        <v>4454</v>
+        <v>4476</v>
       </c>
       <c r="P257" t="n">
-        <v>4451</v>
+        <v>4473</v>
       </c>
       <c r="Q257" t="n">
-        <v>4492</v>
+        <v>4515</v>
       </c>
       <c r="R257" t="n">
-        <v>4338</v>
+        <v>4312</v>
       </c>
       <c r="S257" t="n">
-        <v>4338</v>
+        <v>4312</v>
       </c>
       <c r="T257" t="n">
-        <v>4338</v>
+        <v>4312</v>
       </c>
       <c r="U257" t="n">
-        <v>4493</v>
+        <v>4489</v>
       </c>
       <c r="V257" t="n">
-        <v>4710</v>
+        <v>4738</v>
       </c>
       <c r="W257" t="n">
-        <v>5016</v>
+        <v>5088</v>
       </c>
       <c r="X257" t="n">
-        <v>4852</v>
+        <v>4902</v>
       </c>
       <c r="Y257" t="n">
-        <v>4586</v>
+        <v>4601</v>
       </c>
       <c r="Z257" t="n">
-        <v>4279</v>
+        <v>4254</v>
       </c>
       <c r="AA257" t="n">
-        <v>4055</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="258">
@@ -21822,76 +21822,76 @@
         <v>19</v>
       </c>
       <c r="D258" t="n">
-        <v>3630</v>
+        <v>3613</v>
       </c>
       <c r="E258" t="n">
-        <v>3401</v>
+        <v>3386</v>
       </c>
       <c r="F258" t="n">
-        <v>3300</v>
+        <v>3279</v>
       </c>
       <c r="G258" t="n">
-        <v>3257</v>
+        <v>3239</v>
       </c>
       <c r="H258" t="n">
-        <v>3282</v>
+        <v>3232</v>
       </c>
       <c r="I258" t="n">
-        <v>3471</v>
+        <v>3400</v>
       </c>
       <c r="J258" t="n">
-        <v>4053</v>
+        <v>3934</v>
       </c>
       <c r="K258" t="n">
-        <v>4505</v>
+        <v>4372</v>
       </c>
       <c r="L258" t="n">
-        <v>4813</v>
+        <v>4733</v>
       </c>
       <c r="M258" t="n">
+        <v>4882</v>
+      </c>
+      <c r="N258" t="n">
+        <v>4773</v>
+      </c>
+      <c r="O258" t="n">
+        <v>4832</v>
+      </c>
+      <c r="P258" t="n">
+        <v>4793</v>
+      </c>
+      <c r="Q258" t="n">
+        <v>4769</v>
+      </c>
+      <c r="R258" t="n">
+        <v>4667</v>
+      </c>
+      <c r="S258" t="n">
+        <v>4558</v>
+      </c>
+      <c r="T258" t="n">
+        <v>4527</v>
+      </c>
+      <c r="U258" t="n">
+        <v>4585</v>
+      </c>
+      <c r="V258" t="n">
         <v>4860</v>
       </c>
-      <c r="N258" t="n">
-        <v>4744</v>
-      </c>
-      <c r="O258" t="n">
-        <v>4698</v>
-      </c>
-      <c r="P258" t="n">
-        <v>4649</v>
-      </c>
-      <c r="Q258" t="n">
-        <v>4651</v>
-      </c>
-      <c r="R258" t="n">
-        <v>4603</v>
-      </c>
-      <c r="S258" t="n">
-        <v>4569</v>
-      </c>
-      <c r="T258" t="n">
-        <v>4555</v>
-      </c>
-      <c r="U258" t="n">
-        <v>4595</v>
-      </c>
-      <c r="V258" t="n">
-        <v>4785</v>
-      </c>
       <c r="W258" t="n">
-        <v>5131</v>
+        <v>5201</v>
       </c>
       <c r="X258" t="n">
-        <v>5035</v>
+        <v>5023</v>
       </c>
       <c r="Y258" t="n">
-        <v>4748</v>
+        <v>4706</v>
       </c>
       <c r="Z258" t="n">
-        <v>4424</v>
+        <v>4376</v>
       </c>
       <c r="AA258" t="n">
-        <v>4148</v>
+        <v>4093</v>
       </c>
     </row>
     <row r="259">
@@ -21905,76 +21905,76 @@
         <v>20</v>
       </c>
       <c r="D259" t="n">
-        <v>3657</v>
+        <v>3632</v>
       </c>
       <c r="E259" t="n">
-        <v>3465</v>
+        <v>3429</v>
       </c>
       <c r="F259" t="n">
-        <v>3363</v>
+        <v>3327</v>
       </c>
       <c r="G259" t="n">
-        <v>3300</v>
+        <v>3264</v>
       </c>
       <c r="H259" t="n">
-        <v>3345</v>
+        <v>3310</v>
       </c>
       <c r="I259" t="n">
-        <v>3512</v>
+        <v>3480</v>
       </c>
       <c r="J259" t="n">
-        <v>4018</v>
+        <v>4009</v>
       </c>
       <c r="K259" t="n">
-        <v>4426</v>
+        <v>4437</v>
       </c>
       <c r="L259" t="n">
-        <v>4723</v>
+        <v>4740</v>
       </c>
       <c r="M259" t="n">
-        <v>4800</v>
+        <v>4804</v>
       </c>
       <c r="N259" t="n">
-        <v>4691</v>
+        <v>4658</v>
       </c>
       <c r="O259" t="n">
-        <v>4646</v>
+        <v>4593</v>
       </c>
       <c r="P259" t="n">
-        <v>4595</v>
+        <v>4530</v>
       </c>
       <c r="Q259" t="n">
-        <v>4614</v>
+        <v>4560</v>
       </c>
       <c r="R259" t="n">
-        <v>4575</v>
+        <v>4526</v>
       </c>
       <c r="S259" t="n">
-        <v>4546</v>
+        <v>4498</v>
       </c>
       <c r="T259" t="n">
-        <v>4493</v>
+        <v>4446</v>
       </c>
       <c r="U259" t="n">
-        <v>4520</v>
+        <v>4476</v>
       </c>
       <c r="V259" t="n">
-        <v>4722</v>
+        <v>4726</v>
       </c>
       <c r="W259" t="n">
-        <v>5079</v>
+        <v>5133</v>
       </c>
       <c r="X259" t="n">
-        <v>4976</v>
+        <v>5014</v>
       </c>
       <c r="Y259" t="n">
-        <v>4693</v>
+        <v>4701</v>
       </c>
       <c r="Z259" t="n">
-        <v>4397</v>
+        <v>4371</v>
       </c>
       <c r="AA259" t="n">
-        <v>4113</v>
+        <v>4047</v>
       </c>
     </row>
     <row r="260">
@@ -21988,76 +21988,76 @@
         <v>21</v>
       </c>
       <c r="D260" t="n">
-        <v>3654</v>
+        <v>3624</v>
       </c>
       <c r="E260" t="n">
-        <v>3462</v>
+        <v>3421</v>
       </c>
       <c r="F260" t="n">
-        <v>3359</v>
+        <v>3319</v>
       </c>
       <c r="G260" t="n">
-        <v>3296</v>
+        <v>3255</v>
       </c>
       <c r="H260" t="n">
-        <v>3341</v>
+        <v>3301</v>
       </c>
       <c r="I260" t="n">
-        <v>3508</v>
+        <v>3470</v>
       </c>
       <c r="J260" t="n">
-        <v>4013</v>
+        <v>3997</v>
       </c>
       <c r="K260" t="n">
-        <v>4420</v>
+        <v>4423</v>
       </c>
       <c r="L260" t="n">
-        <v>4716</v>
+        <v>4725</v>
       </c>
       <c r="M260" t="n">
-        <v>4794</v>
+        <v>4788</v>
       </c>
       <c r="N260" t="n">
-        <v>4684</v>
+        <v>4643</v>
       </c>
       <c r="O260" t="n">
-        <v>4640</v>
+        <v>4577</v>
       </c>
       <c r="P260" t="n">
-        <v>4588</v>
+        <v>4514</v>
       </c>
       <c r="Q260" t="n">
-        <v>4607</v>
+        <v>4544</v>
       </c>
       <c r="R260" t="n">
-        <v>4568</v>
+        <v>4510</v>
       </c>
       <c r="S260" t="n">
-        <v>4540</v>
+        <v>4482</v>
       </c>
       <c r="T260" t="n">
-        <v>4486</v>
+        <v>4429</v>
       </c>
       <c r="U260" t="n">
-        <v>4513</v>
+        <v>4460</v>
       </c>
       <c r="V260" t="n">
-        <v>4716</v>
+        <v>4711</v>
       </c>
       <c r="W260" t="n">
-        <v>5073</v>
+        <v>5120</v>
       </c>
       <c r="X260" t="n">
-        <v>4971</v>
+        <v>5001</v>
       </c>
       <c r="Y260" t="n">
-        <v>4688</v>
+        <v>4690</v>
       </c>
       <c r="Z260" t="n">
-        <v>4392</v>
+        <v>4360</v>
       </c>
       <c r="AA260" t="n">
-        <v>4109</v>
+        <v>4037</v>
       </c>
     </row>
     <row r="261">
@@ -22071,76 +22071,159 @@
         <v>22</v>
       </c>
       <c r="D261" t="n">
-        <v>3653</v>
+        <v>3619</v>
       </c>
       <c r="E261" t="n">
-        <v>3461</v>
+        <v>3415</v>
       </c>
       <c r="F261" t="n">
-        <v>3358</v>
+        <v>3313</v>
       </c>
       <c r="G261" t="n">
-        <v>3295</v>
+        <v>3249</v>
       </c>
       <c r="H261" t="n">
-        <v>3340</v>
+        <v>3294</v>
       </c>
       <c r="I261" t="n">
-        <v>3507</v>
+        <v>3463</v>
       </c>
       <c r="J261" t="n">
-        <v>4012</v>
+        <v>3989</v>
       </c>
       <c r="K261" t="n">
+        <v>4414</v>
+      </c>
+      <c r="L261" t="n">
+        <v>4714</v>
+      </c>
+      <c r="M261" t="n">
+        <v>4778</v>
+      </c>
+      <c r="N261" t="n">
+        <v>4632</v>
+      </c>
+      <c r="O261" t="n">
+        <v>4566</v>
+      </c>
+      <c r="P261" t="n">
+        <v>4503</v>
+      </c>
+      <c r="Q261" t="n">
+        <v>4533</v>
+      </c>
+      <c r="R261" t="n">
+        <v>4500</v>
+      </c>
+      <c r="S261" t="n">
+        <v>4472</v>
+      </c>
+      <c r="T261" t="n">
         <v>4419</v>
       </c>
-      <c r="L261" t="n">
-        <v>4715</v>
-      </c>
-      <c r="M261" t="n">
-        <v>4793</v>
-      </c>
-      <c r="N261" t="n">
-        <v>4683</v>
-      </c>
-      <c r="O261" t="n">
-        <v>4638</v>
-      </c>
-      <c r="P261" t="n">
-        <v>4587</v>
-      </c>
-      <c r="Q261" t="n">
-        <v>4606</v>
-      </c>
-      <c r="R261" t="n">
-        <v>4567</v>
-      </c>
-      <c r="S261" t="n">
-        <v>4538</v>
-      </c>
-      <c r="T261" t="n">
-        <v>4485</v>
-      </c>
       <c r="U261" t="n">
-        <v>4512</v>
+        <v>4449</v>
       </c>
       <c r="V261" t="n">
-        <v>4714</v>
+        <v>4701</v>
       </c>
       <c r="W261" t="n">
-        <v>5072</v>
+        <v>5111</v>
       </c>
       <c r="X261" t="n">
-        <v>4970</v>
+        <v>4992</v>
       </c>
       <c r="Y261" t="n">
-        <v>4687</v>
+        <v>4682</v>
       </c>
       <c r="Z261" t="n">
-        <v>4392</v>
+        <v>4353</v>
       </c>
       <c r="AA261" t="n">
-        <v>4108</v>
+        <v>4031</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B262" t="n">
+        <v>10</v>
+      </c>
+      <c r="C262" t="n">
+        <v>23</v>
+      </c>
+      <c r="D262" t="n">
+        <v>3616</v>
+      </c>
+      <c r="E262" t="n">
+        <v>3412</v>
+      </c>
+      <c r="F262" t="n">
+        <v>3309</v>
+      </c>
+      <c r="G262" t="n">
+        <v>3245</v>
+      </c>
+      <c r="H262" t="n">
+        <v>3291</v>
+      </c>
+      <c r="I262" t="n">
+        <v>3459</v>
+      </c>
+      <c r="J262" t="n">
+        <v>3984</v>
+      </c>
+      <c r="K262" t="n">
+        <v>4408</v>
+      </c>
+      <c r="L262" t="n">
+        <v>4709</v>
+      </c>
+      <c r="M262" t="n">
+        <v>4772</v>
+      </c>
+      <c r="N262" t="n">
+        <v>4626</v>
+      </c>
+      <c r="O262" t="n">
+        <v>4560</v>
+      </c>
+      <c r="P262" t="n">
+        <v>4497</v>
+      </c>
+      <c r="Q262" t="n">
+        <v>4527</v>
+      </c>
+      <c r="R262" t="n">
+        <v>4494</v>
+      </c>
+      <c r="S262" t="n">
+        <v>4466</v>
+      </c>
+      <c r="T262" t="n">
+        <v>4413</v>
+      </c>
+      <c r="U262" t="n">
+        <v>4440</v>
+      </c>
+      <c r="V262" t="n">
+        <v>4662</v>
+      </c>
+      <c r="W262" t="n">
+        <v>5026</v>
+      </c>
+      <c r="X262" t="n">
+        <v>4911</v>
+      </c>
+      <c r="Y262" t="n">
+        <v>4610</v>
+      </c>
+      <c r="Z262" t="n">
+        <v>4292</v>
+      </c>
+      <c r="AA262" t="n">
+        <v>3980</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA262"/>
+  <dimension ref="A1:AA263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21822,76 +21822,76 @@
         <v>19</v>
       </c>
       <c r="D258" t="n">
-        <v>3613</v>
+        <v>3649</v>
       </c>
       <c r="E258" t="n">
-        <v>3386</v>
+        <v>3422</v>
       </c>
       <c r="F258" t="n">
-        <v>3279</v>
+        <v>3315</v>
       </c>
       <c r="G258" t="n">
-        <v>3239</v>
+        <v>3275</v>
       </c>
       <c r="H258" t="n">
-        <v>3232</v>
+        <v>3268</v>
       </c>
       <c r="I258" t="n">
-        <v>3400</v>
+        <v>3439</v>
       </c>
       <c r="J258" t="n">
-        <v>3934</v>
+        <v>3982</v>
       </c>
       <c r="K258" t="n">
-        <v>4372</v>
+        <v>4426</v>
       </c>
       <c r="L258" t="n">
-        <v>4733</v>
+        <v>4794</v>
       </c>
       <c r="M258" t="n">
-        <v>4882</v>
+        <v>4945</v>
       </c>
       <c r="N258" t="n">
-        <v>4773</v>
+        <v>4854</v>
       </c>
       <c r="O258" t="n">
-        <v>4832</v>
+        <v>4903</v>
       </c>
       <c r="P258" t="n">
-        <v>4793</v>
+        <v>4870</v>
       </c>
       <c r="Q258" t="n">
-        <v>4769</v>
+        <v>4850</v>
       </c>
       <c r="R258" t="n">
-        <v>4667</v>
+        <v>4764</v>
       </c>
       <c r="S258" t="n">
-        <v>4558</v>
+        <v>4672</v>
       </c>
       <c r="T258" t="n">
-        <v>4527</v>
+        <v>4646</v>
       </c>
       <c r="U258" t="n">
-        <v>4585</v>
+        <v>4706</v>
       </c>
       <c r="V258" t="n">
-        <v>4860</v>
+        <v>4990</v>
       </c>
       <c r="W258" t="n">
-        <v>5201</v>
+        <v>5342</v>
       </c>
       <c r="X258" t="n">
-        <v>5023</v>
+        <v>5165</v>
       </c>
       <c r="Y258" t="n">
-        <v>4706</v>
+        <v>4850</v>
       </c>
       <c r="Z258" t="n">
-        <v>4376</v>
+        <v>4523</v>
       </c>
       <c r="AA258" t="n">
-        <v>4093</v>
+        <v>4242</v>
       </c>
     </row>
     <row r="259">
@@ -21905,76 +21905,76 @@
         <v>20</v>
       </c>
       <c r="D259" t="n">
-        <v>3632</v>
+        <v>3672</v>
       </c>
       <c r="E259" t="n">
-        <v>3429</v>
+        <v>3462</v>
       </c>
       <c r="F259" t="n">
-        <v>3327</v>
+        <v>3365</v>
       </c>
       <c r="G259" t="n">
-        <v>3264</v>
+        <v>3305</v>
       </c>
       <c r="H259" t="n">
-        <v>3310</v>
+        <v>3341</v>
       </c>
       <c r="I259" t="n">
-        <v>3480</v>
+        <v>3506</v>
       </c>
       <c r="J259" t="n">
-        <v>4009</v>
+        <v>4037</v>
       </c>
       <c r="K259" t="n">
-        <v>4437</v>
+        <v>4460</v>
       </c>
       <c r="L259" t="n">
-        <v>4740</v>
+        <v>4784</v>
       </c>
       <c r="M259" t="n">
-        <v>4804</v>
+        <v>4874</v>
       </c>
       <c r="N259" t="n">
-        <v>4658</v>
+        <v>4747</v>
       </c>
       <c r="O259" t="n">
-        <v>4593</v>
+        <v>4692</v>
       </c>
       <c r="P259" t="n">
-        <v>4530</v>
+        <v>4623</v>
       </c>
       <c r="Q259" t="n">
-        <v>4560</v>
+        <v>4676</v>
       </c>
       <c r="R259" t="n">
-        <v>4526</v>
+        <v>4694</v>
       </c>
       <c r="S259" t="n">
-        <v>4498</v>
+        <v>4640</v>
       </c>
       <c r="T259" t="n">
-        <v>4446</v>
+        <v>4574</v>
       </c>
       <c r="U259" t="n">
-        <v>4476</v>
+        <v>4601</v>
       </c>
       <c r="V259" t="n">
-        <v>4726</v>
+        <v>4889</v>
       </c>
       <c r="W259" t="n">
+        <v>5281</v>
+      </c>
+      <c r="X259" t="n">
         <v>5133</v>
       </c>
-      <c r="X259" t="n">
-        <v>5014</v>
-      </c>
       <c r="Y259" t="n">
-        <v>4701</v>
+        <v>4822</v>
       </c>
       <c r="Z259" t="n">
-        <v>4371</v>
+        <v>4515</v>
       </c>
       <c r="AA259" t="n">
-        <v>4047</v>
+        <v>4201</v>
       </c>
     </row>
     <row r="260">
@@ -21988,76 +21988,76 @@
         <v>21</v>
       </c>
       <c r="D260" t="n">
-        <v>3624</v>
+        <v>3651</v>
       </c>
       <c r="E260" t="n">
-        <v>3421</v>
+        <v>3438</v>
       </c>
       <c r="F260" t="n">
-        <v>3319</v>
+        <v>3341</v>
       </c>
       <c r="G260" t="n">
-        <v>3255</v>
+        <v>3280</v>
       </c>
       <c r="H260" t="n">
-        <v>3301</v>
+        <v>3316</v>
       </c>
       <c r="I260" t="n">
-        <v>3470</v>
+        <v>3479</v>
       </c>
       <c r="J260" t="n">
-        <v>3997</v>
+        <v>4004</v>
       </c>
       <c r="K260" t="n">
         <v>4423</v>
       </c>
       <c r="L260" t="n">
-        <v>4725</v>
+        <v>4742</v>
       </c>
       <c r="M260" t="n">
-        <v>4788</v>
+        <v>4832</v>
       </c>
       <c r="N260" t="n">
-        <v>4643</v>
+        <v>4704</v>
       </c>
       <c r="O260" t="n">
-        <v>4577</v>
+        <v>4648</v>
       </c>
       <c r="P260" t="n">
-        <v>4514</v>
+        <v>4579</v>
       </c>
       <c r="Q260" t="n">
-        <v>4544</v>
+        <v>4632</v>
       </c>
       <c r="R260" t="n">
-        <v>4510</v>
+        <v>4650</v>
       </c>
       <c r="S260" t="n">
-        <v>4482</v>
+        <v>4596</v>
       </c>
       <c r="T260" t="n">
-        <v>4429</v>
+        <v>4529</v>
       </c>
       <c r="U260" t="n">
-        <v>4460</v>
+        <v>4557</v>
       </c>
       <c r="V260" t="n">
-        <v>4711</v>
+        <v>4848</v>
       </c>
       <c r="W260" t="n">
-        <v>5120</v>
+        <v>5244</v>
       </c>
       <c r="X260" t="n">
-        <v>5001</v>
+        <v>5097</v>
       </c>
       <c r="Y260" t="n">
-        <v>4690</v>
+        <v>4790</v>
       </c>
       <c r="Z260" t="n">
-        <v>4360</v>
+        <v>4487</v>
       </c>
       <c r="AA260" t="n">
-        <v>4037</v>
+        <v>4176</v>
       </c>
     </row>
     <row r="261">
@@ -22071,76 +22071,76 @@
         <v>22</v>
       </c>
       <c r="D261" t="n">
-        <v>3619</v>
+        <v>3624</v>
       </c>
       <c r="E261" t="n">
-        <v>3415</v>
+        <v>3408</v>
       </c>
       <c r="F261" t="n">
-        <v>3313</v>
+        <v>3309</v>
       </c>
       <c r="G261" t="n">
-        <v>3249</v>
+        <v>3247</v>
       </c>
       <c r="H261" t="n">
-        <v>3294</v>
+        <v>3283</v>
       </c>
       <c r="I261" t="n">
-        <v>3463</v>
+        <v>3443</v>
       </c>
       <c r="J261" t="n">
-        <v>3989</v>
+        <v>3961</v>
       </c>
       <c r="K261" t="n">
-        <v>4414</v>
+        <v>4373</v>
       </c>
       <c r="L261" t="n">
-        <v>4714</v>
+        <v>4689</v>
       </c>
       <c r="M261" t="n">
-        <v>4778</v>
+        <v>4777</v>
       </c>
       <c r="N261" t="n">
-        <v>4632</v>
+        <v>4648</v>
       </c>
       <c r="O261" t="n">
-        <v>4566</v>
+        <v>4592</v>
       </c>
       <c r="P261" t="n">
-        <v>4503</v>
+        <v>4523</v>
       </c>
       <c r="Q261" t="n">
-        <v>4533</v>
+        <v>4576</v>
       </c>
       <c r="R261" t="n">
+        <v>4594</v>
+      </c>
+      <c r="S261" t="n">
+        <v>4539</v>
+      </c>
+      <c r="T261" t="n">
+        <v>4472</v>
+      </c>
+      <c r="U261" t="n">
         <v>4500</v>
       </c>
-      <c r="S261" t="n">
-        <v>4472</v>
-      </c>
-      <c r="T261" t="n">
-        <v>4419</v>
-      </c>
-      <c r="U261" t="n">
-        <v>4449</v>
-      </c>
       <c r="V261" t="n">
-        <v>4701</v>
+        <v>4795</v>
       </c>
       <c r="W261" t="n">
-        <v>5111</v>
+        <v>5196</v>
       </c>
       <c r="X261" t="n">
-        <v>4992</v>
+        <v>5051</v>
       </c>
       <c r="Y261" t="n">
-        <v>4682</v>
+        <v>4748</v>
       </c>
       <c r="Z261" t="n">
-        <v>4353</v>
+        <v>4450</v>
       </c>
       <c r="AA261" t="n">
-        <v>4031</v>
+        <v>4143</v>
       </c>
     </row>
     <row r="262">
@@ -22154,76 +22154,159 @@
         <v>23</v>
       </c>
       <c r="D262" t="n">
-        <v>3616</v>
+        <v>3613</v>
       </c>
       <c r="E262" t="n">
-        <v>3412</v>
+        <v>3396</v>
       </c>
       <c r="F262" t="n">
-        <v>3309</v>
+        <v>3296</v>
       </c>
       <c r="G262" t="n">
-        <v>3245</v>
+        <v>3234</v>
       </c>
       <c r="H262" t="n">
-        <v>3291</v>
+        <v>3269</v>
       </c>
       <c r="I262" t="n">
-        <v>3459</v>
+        <v>3428</v>
       </c>
       <c r="J262" t="n">
-        <v>3984</v>
+        <v>3943</v>
       </c>
       <c r="K262" t="n">
-        <v>4408</v>
+        <v>4353</v>
       </c>
       <c r="L262" t="n">
-        <v>4709</v>
+        <v>4666</v>
       </c>
       <c r="M262" t="n">
-        <v>4772</v>
+        <v>4754</v>
       </c>
       <c r="N262" t="n">
-        <v>4626</v>
+        <v>4625</v>
       </c>
       <c r="O262" t="n">
-        <v>4560</v>
+        <v>4568</v>
       </c>
       <c r="P262" t="n">
-        <v>4497</v>
+        <v>4499</v>
       </c>
       <c r="Q262" t="n">
-        <v>4527</v>
+        <v>4552</v>
       </c>
       <c r="R262" t="n">
-        <v>4494</v>
+        <v>4570</v>
       </c>
       <c r="S262" t="n">
-        <v>4466</v>
+        <v>4515</v>
       </c>
       <c r="T262" t="n">
-        <v>4413</v>
+        <v>4448</v>
       </c>
       <c r="U262" t="n">
-        <v>4440</v>
+        <v>4474</v>
       </c>
       <c r="V262" t="n">
-        <v>4662</v>
+        <v>4737</v>
       </c>
       <c r="W262" t="n">
-        <v>5026</v>
+        <v>5096</v>
       </c>
       <c r="X262" t="n">
-        <v>4911</v>
+        <v>4957</v>
       </c>
       <c r="Y262" t="n">
-        <v>4610</v>
+        <v>4665</v>
       </c>
       <c r="Z262" t="n">
-        <v>4292</v>
+        <v>4377</v>
       </c>
       <c r="AA262" t="n">
-        <v>3980</v>
+        <v>4082</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B263" t="n">
+        <v>10</v>
+      </c>
+      <c r="C263" t="n">
+        <v>24</v>
+      </c>
+      <c r="D263" t="n">
+        <v>3596</v>
+      </c>
+      <c r="E263" t="n">
+        <v>3346</v>
+      </c>
+      <c r="F263" t="n">
+        <v>3230</v>
+      </c>
+      <c r="G263" t="n">
+        <v>3194</v>
+      </c>
+      <c r="H263" t="n">
+        <v>3163</v>
+      </c>
+      <c r="I263" t="n">
+        <v>3217</v>
+      </c>
+      <c r="J263" t="n">
+        <v>3458</v>
+      </c>
+      <c r="K263" t="n">
+        <v>3722</v>
+      </c>
+      <c r="L263" t="n">
+        <v>4134</v>
+      </c>
+      <c r="M263" t="n">
+        <v>4322</v>
+      </c>
+      <c r="N263" t="n">
+        <v>4395</v>
+      </c>
+      <c r="O263" t="n">
+        <v>4422</v>
+      </c>
+      <c r="P263" t="n">
+        <v>4305</v>
+      </c>
+      <c r="Q263" t="n">
+        <v>4323</v>
+      </c>
+      <c r="R263" t="n">
+        <v>4204</v>
+      </c>
+      <c r="S263" t="n">
+        <v>4207</v>
+      </c>
+      <c r="T263" t="n">
+        <v>4257</v>
+      </c>
+      <c r="U263" t="n">
+        <v>4425</v>
+      </c>
+      <c r="V263" t="n">
+        <v>4564</v>
+      </c>
+      <c r="W263" t="n">
+        <v>4887</v>
+      </c>
+      <c r="X263" t="n">
+        <v>4711</v>
+      </c>
+      <c r="Y263" t="n">
+        <v>4438</v>
+      </c>
+      <c r="Z263" t="n">
+        <v>4168</v>
+      </c>
+      <c r="AA263" t="n">
+        <v>3975</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA263"/>
+  <dimension ref="A1:AA264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21905,76 +21905,76 @@
         <v>20</v>
       </c>
       <c r="D259" t="n">
-        <v>3672</v>
+        <v>3762</v>
       </c>
       <c r="E259" t="n">
-        <v>3462</v>
+        <v>3539</v>
       </c>
       <c r="F259" t="n">
-        <v>3365</v>
+        <v>3440</v>
       </c>
       <c r="G259" t="n">
-        <v>3305</v>
+        <v>3371</v>
       </c>
       <c r="H259" t="n">
-        <v>3341</v>
+        <v>3404</v>
       </c>
       <c r="I259" t="n">
-        <v>3506</v>
+        <v>3558</v>
       </c>
       <c r="J259" t="n">
-        <v>4037</v>
+        <v>4060</v>
       </c>
       <c r="K259" t="n">
-        <v>4460</v>
+        <v>4462</v>
       </c>
       <c r="L259" t="n">
         <v>4784</v>
       </c>
       <c r="M259" t="n">
-        <v>4874</v>
+        <v>4893</v>
       </c>
       <c r="N259" t="n">
-        <v>4747</v>
+        <v>4623</v>
       </c>
       <c r="O259" t="n">
-        <v>4692</v>
+        <v>4523</v>
       </c>
       <c r="P259" t="n">
-        <v>4623</v>
+        <v>4390</v>
       </c>
       <c r="Q259" t="n">
-        <v>4676</v>
+        <v>4508</v>
       </c>
       <c r="R259" t="n">
-        <v>4694</v>
+        <v>4569</v>
       </c>
       <c r="S259" t="n">
-        <v>4640</v>
+        <v>4439</v>
       </c>
       <c r="T259" t="n">
-        <v>4574</v>
+        <v>4285</v>
       </c>
       <c r="U259" t="n">
-        <v>4601</v>
+        <v>4309</v>
       </c>
       <c r="V259" t="n">
-        <v>4889</v>
+        <v>4703</v>
       </c>
       <c r="W259" t="n">
-        <v>5281</v>
+        <v>5208</v>
       </c>
       <c r="X259" t="n">
-        <v>5133</v>
+        <v>5040</v>
       </c>
       <c r="Y259" t="n">
-        <v>4822</v>
+        <v>4721</v>
       </c>
       <c r="Z259" t="n">
-        <v>4515</v>
+        <v>4409</v>
       </c>
       <c r="AA259" t="n">
-        <v>4201</v>
+        <v>4095</v>
       </c>
     </row>
     <row r="260">
@@ -21988,76 +21988,76 @@
         <v>21</v>
       </c>
       <c r="D260" t="n">
-        <v>3651</v>
+        <v>3747</v>
       </c>
       <c r="E260" t="n">
-        <v>3438</v>
+        <v>3521</v>
       </c>
       <c r="F260" t="n">
-        <v>3341</v>
+        <v>3421</v>
       </c>
       <c r="G260" t="n">
-        <v>3280</v>
+        <v>3352</v>
       </c>
       <c r="H260" t="n">
-        <v>3316</v>
+        <v>3384</v>
       </c>
       <c r="I260" t="n">
-        <v>3479</v>
+        <v>3537</v>
       </c>
       <c r="J260" t="n">
-        <v>4004</v>
+        <v>4035</v>
       </c>
       <c r="K260" t="n">
-        <v>4423</v>
+        <v>4433</v>
       </c>
       <c r="L260" t="n">
-        <v>4742</v>
+        <v>4752</v>
       </c>
       <c r="M260" t="n">
-        <v>4832</v>
+        <v>4860</v>
       </c>
       <c r="N260" t="n">
-        <v>4704</v>
+        <v>4589</v>
       </c>
       <c r="O260" t="n">
-        <v>4648</v>
+        <v>4489</v>
       </c>
       <c r="P260" t="n">
-        <v>4579</v>
+        <v>4356</v>
       </c>
       <c r="Q260" t="n">
-        <v>4632</v>
+        <v>4474</v>
       </c>
       <c r="R260" t="n">
-        <v>4650</v>
+        <v>4535</v>
       </c>
       <c r="S260" t="n">
-        <v>4596</v>
+        <v>4405</v>
       </c>
       <c r="T260" t="n">
-        <v>4529</v>
+        <v>4251</v>
       </c>
       <c r="U260" t="n">
-        <v>4557</v>
+        <v>4275</v>
       </c>
       <c r="V260" t="n">
-        <v>4848</v>
+        <v>4671</v>
       </c>
       <c r="W260" t="n">
-        <v>5244</v>
+        <v>5179</v>
       </c>
       <c r="X260" t="n">
-        <v>5097</v>
+        <v>5012</v>
       </c>
       <c r="Y260" t="n">
-        <v>4790</v>
+        <v>4696</v>
       </c>
       <c r="Z260" t="n">
-        <v>4487</v>
+        <v>4387</v>
       </c>
       <c r="AA260" t="n">
-        <v>4176</v>
+        <v>4075</v>
       </c>
     </row>
     <row r="261">
@@ -22071,76 +22071,76 @@
         <v>22</v>
       </c>
       <c r="D261" t="n">
-        <v>3624</v>
+        <v>3714</v>
       </c>
       <c r="E261" t="n">
-        <v>3408</v>
+        <v>3484</v>
       </c>
       <c r="F261" t="n">
-        <v>3309</v>
+        <v>3383</v>
       </c>
       <c r="G261" t="n">
-        <v>3247</v>
+        <v>3312</v>
       </c>
       <c r="H261" t="n">
-        <v>3283</v>
+        <v>3344</v>
       </c>
       <c r="I261" t="n">
-        <v>3443</v>
+        <v>3494</v>
       </c>
       <c r="J261" t="n">
-        <v>3961</v>
+        <v>3983</v>
       </c>
       <c r="K261" t="n">
-        <v>4373</v>
+        <v>4374</v>
       </c>
       <c r="L261" t="n">
-        <v>4689</v>
+        <v>4687</v>
       </c>
       <c r="M261" t="n">
-        <v>4777</v>
+        <v>4794</v>
       </c>
       <c r="N261" t="n">
-        <v>4648</v>
+        <v>4522</v>
       </c>
       <c r="O261" t="n">
-        <v>4592</v>
+        <v>4421</v>
       </c>
       <c r="P261" t="n">
-        <v>4523</v>
+        <v>4288</v>
       </c>
       <c r="Q261" t="n">
-        <v>4576</v>
+        <v>4406</v>
       </c>
       <c r="R261" t="n">
-        <v>4594</v>
+        <v>4467</v>
       </c>
       <c r="S261" t="n">
-        <v>4539</v>
+        <v>4336</v>
       </c>
       <c r="T261" t="n">
-        <v>4472</v>
+        <v>4182</v>
       </c>
       <c r="U261" t="n">
-        <v>4500</v>
+        <v>4206</v>
       </c>
       <c r="V261" t="n">
-        <v>4795</v>
+        <v>4607</v>
       </c>
       <c r="W261" t="n">
-        <v>5196</v>
+        <v>5121</v>
       </c>
       <c r="X261" t="n">
-        <v>5051</v>
+        <v>4958</v>
       </c>
       <c r="Y261" t="n">
-        <v>4748</v>
+        <v>4646</v>
       </c>
       <c r="Z261" t="n">
-        <v>4450</v>
+        <v>4342</v>
       </c>
       <c r="AA261" t="n">
-        <v>4143</v>
+        <v>4036</v>
       </c>
     </row>
     <row r="262">
@@ -22154,76 +22154,76 @@
         <v>23</v>
       </c>
       <c r="D262" t="n">
-        <v>3613</v>
+        <v>3705</v>
       </c>
       <c r="E262" t="n">
-        <v>3396</v>
+        <v>3474</v>
       </c>
       <c r="F262" t="n">
-        <v>3296</v>
+        <v>3372</v>
       </c>
       <c r="G262" t="n">
-        <v>3234</v>
+        <v>3301</v>
       </c>
       <c r="H262" t="n">
-        <v>3269</v>
+        <v>3332</v>
       </c>
       <c r="I262" t="n">
-        <v>3428</v>
+        <v>3482</v>
       </c>
       <c r="J262" t="n">
-        <v>3943</v>
+        <v>3968</v>
       </c>
       <c r="K262" t="n">
-        <v>4353</v>
+        <v>4357</v>
       </c>
       <c r="L262" t="n">
-        <v>4666</v>
+        <v>4669</v>
       </c>
       <c r="M262" t="n">
-        <v>4754</v>
+        <v>4774</v>
       </c>
       <c r="N262" t="n">
-        <v>4625</v>
+        <v>4502</v>
       </c>
       <c r="O262" t="n">
-        <v>4568</v>
+        <v>4401</v>
       </c>
       <c r="P262" t="n">
-        <v>4499</v>
+        <v>4268</v>
       </c>
       <c r="Q262" t="n">
-        <v>4552</v>
+        <v>4386</v>
       </c>
       <c r="R262" t="n">
-        <v>4570</v>
+        <v>4448</v>
       </c>
       <c r="S262" t="n">
-        <v>4515</v>
+        <v>4317</v>
       </c>
       <c r="T262" t="n">
-        <v>4448</v>
+        <v>4162</v>
       </c>
       <c r="U262" t="n">
-        <v>4474</v>
+        <v>4184</v>
       </c>
       <c r="V262" t="n">
-        <v>4737</v>
+        <v>4553</v>
       </c>
       <c r="W262" t="n">
-        <v>5096</v>
+        <v>5025</v>
       </c>
       <c r="X262" t="n">
-        <v>4957</v>
+        <v>4867</v>
       </c>
       <c r="Y262" t="n">
-        <v>4665</v>
+        <v>4566</v>
       </c>
       <c r="Z262" t="n">
-        <v>4377</v>
+        <v>4273</v>
       </c>
       <c r="AA262" t="n">
-        <v>4082</v>
+        <v>3977</v>
       </c>
     </row>
     <row r="263">
@@ -22237,76 +22237,159 @@
         <v>24</v>
       </c>
       <c r="D263" t="n">
-        <v>3596</v>
+        <v>3702</v>
       </c>
       <c r="E263" t="n">
-        <v>3346</v>
+        <v>3450</v>
       </c>
       <c r="F263" t="n">
-        <v>3230</v>
+        <v>3327</v>
       </c>
       <c r="G263" t="n">
-        <v>3194</v>
+        <v>3262</v>
       </c>
       <c r="H263" t="n">
-        <v>3163</v>
+        <v>3248</v>
       </c>
       <c r="I263" t="n">
-        <v>3217</v>
+        <v>3314</v>
       </c>
       <c r="J263" t="n">
-        <v>3458</v>
+        <v>3541</v>
       </c>
       <c r="K263" t="n">
-        <v>3722</v>
+        <v>3883</v>
       </c>
       <c r="L263" t="n">
-        <v>4134</v>
+        <v>4312</v>
       </c>
       <c r="M263" t="n">
-        <v>4322</v>
+        <v>4472</v>
       </c>
       <c r="N263" t="n">
-        <v>4395</v>
+        <v>4451</v>
       </c>
       <c r="O263" t="n">
+        <v>4350</v>
+      </c>
+      <c r="P263" t="n">
+        <v>4205</v>
+      </c>
+      <c r="Q263" t="n">
+        <v>4261</v>
+      </c>
+      <c r="R263" t="n">
+        <v>4017</v>
+      </c>
+      <c r="S263" t="n">
+        <v>3947</v>
+      </c>
+      <c r="T263" t="n">
+        <v>4030</v>
+      </c>
+      <c r="U263" t="n">
+        <v>4271</v>
+      </c>
+      <c r="V263" t="n">
+        <v>4546</v>
+      </c>
+      <c r="W263" t="n">
+        <v>4841</v>
+      </c>
+      <c r="X263" t="n">
+        <v>4687</v>
+      </c>
+      <c r="Y263" t="n">
+        <v>4359</v>
+      </c>
+      <c r="Z263" t="n">
+        <v>4087</v>
+      </c>
+      <c r="AA263" t="n">
+        <v>3887</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B264" t="n">
+        <v>10</v>
+      </c>
+      <c r="C264" t="n">
+        <v>25</v>
+      </c>
+      <c r="D264" t="n">
+        <v>3644</v>
+      </c>
+      <c r="E264" t="n">
+        <v>3412</v>
+      </c>
+      <c r="F264" t="n">
+        <v>3241</v>
+      </c>
+      <c r="G264" t="n">
+        <v>3218</v>
+      </c>
+      <c r="H264" t="n">
+        <v>3198</v>
+      </c>
+      <c r="I264" t="n">
+        <v>3223</v>
+      </c>
+      <c r="J264" t="n">
+        <v>3397</v>
+      </c>
+      <c r="K264" t="n">
+        <v>3601</v>
+      </c>
+      <c r="L264" t="n">
+        <v>3947</v>
+      </c>
+      <c r="M264" t="n">
+        <v>4213</v>
+      </c>
+      <c r="N264" t="n">
+        <v>4362</v>
+      </c>
+      <c r="O264" t="n">
         <v>4422</v>
       </c>
-      <c r="P263" t="n">
-        <v>4305</v>
-      </c>
-      <c r="Q263" t="n">
-        <v>4323</v>
-      </c>
-      <c r="R263" t="n">
-        <v>4204</v>
-      </c>
-      <c r="S263" t="n">
-        <v>4207</v>
-      </c>
-      <c r="T263" t="n">
-        <v>4257</v>
-      </c>
-      <c r="U263" t="n">
-        <v>4425</v>
-      </c>
-      <c r="V263" t="n">
-        <v>4564</v>
-      </c>
-      <c r="W263" t="n">
-        <v>4887</v>
-      </c>
-      <c r="X263" t="n">
-        <v>4711</v>
-      </c>
-      <c r="Y263" t="n">
-        <v>4438</v>
-      </c>
-      <c r="Z263" t="n">
-        <v>4168</v>
-      </c>
-      <c r="AA263" t="n">
-        <v>3975</v>
+      <c r="P264" t="n">
+        <v>4419</v>
+      </c>
+      <c r="Q264" t="n">
+        <v>4461</v>
+      </c>
+      <c r="R264" t="n">
+        <v>4004</v>
+      </c>
+      <c r="S264" t="n">
+        <v>4004</v>
+      </c>
+      <c r="T264" t="n">
+        <v>4004</v>
+      </c>
+      <c r="U264" t="n">
+        <v>4245</v>
+      </c>
+      <c r="V264" t="n">
+        <v>4583</v>
+      </c>
+      <c r="W264" t="n">
+        <v>5058</v>
+      </c>
+      <c r="X264" t="n">
+        <v>4873</v>
+      </c>
+      <c r="Y264" t="n">
+        <v>4575</v>
+      </c>
+      <c r="Z264" t="n">
+        <v>4231</v>
+      </c>
+      <c r="AA264" t="n">
+        <v>3979</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA264"/>
+  <dimension ref="A1:AA265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21988,76 +21988,76 @@
         <v>21</v>
       </c>
       <c r="D260" t="n">
-        <v>3747</v>
+        <v>3737</v>
       </c>
       <c r="E260" t="n">
-        <v>3521</v>
+        <v>3514</v>
       </c>
       <c r="F260" t="n">
-        <v>3421</v>
+        <v>3425</v>
       </c>
       <c r="G260" t="n">
-        <v>3352</v>
+        <v>3366</v>
       </c>
       <c r="H260" t="n">
-        <v>3384</v>
+        <v>3396</v>
       </c>
       <c r="I260" t="n">
-        <v>3537</v>
+        <v>3533</v>
       </c>
       <c r="J260" t="n">
-        <v>4035</v>
+        <v>4001</v>
       </c>
       <c r="K260" t="n">
-        <v>4433</v>
+        <v>4375</v>
       </c>
       <c r="L260" t="n">
-        <v>4752</v>
+        <v>4669</v>
       </c>
       <c r="M260" t="n">
-        <v>4860</v>
+        <v>4769</v>
       </c>
       <c r="N260" t="n">
-        <v>4589</v>
+        <v>4668</v>
       </c>
       <c r="O260" t="n">
-        <v>4489</v>
+        <v>4644</v>
       </c>
       <c r="P260" t="n">
-        <v>4356</v>
+        <v>4605</v>
       </c>
       <c r="Q260" t="n">
-        <v>4474</v>
+        <v>4674</v>
       </c>
       <c r="R260" t="n">
-        <v>4535</v>
+        <v>4664</v>
       </c>
       <c r="S260" t="n">
-        <v>4405</v>
+        <v>4622</v>
       </c>
       <c r="T260" t="n">
-        <v>4251</v>
+        <v>4538</v>
       </c>
       <c r="U260" t="n">
-        <v>4275</v>
+        <v>4559</v>
       </c>
       <c r="V260" t="n">
-        <v>4671</v>
+        <v>4822</v>
       </c>
       <c r="W260" t="n">
-        <v>5179</v>
+        <v>5148</v>
       </c>
       <c r="X260" t="n">
-        <v>5012</v>
+        <v>4977</v>
       </c>
       <c r="Y260" t="n">
-        <v>4696</v>
+        <v>4682</v>
       </c>
       <c r="Z260" t="n">
-        <v>4387</v>
+        <v>4375</v>
       </c>
       <c r="AA260" t="n">
-        <v>4075</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="261">
@@ -22071,76 +22071,76 @@
         <v>22</v>
       </c>
       <c r="D261" t="n">
-        <v>3714</v>
+        <v>3726</v>
       </c>
       <c r="E261" t="n">
-        <v>3484</v>
+        <v>3502</v>
       </c>
       <c r="F261" t="n">
+        <v>3412</v>
+      </c>
+      <c r="G261" t="n">
+        <v>3353</v>
+      </c>
+      <c r="H261" t="n">
         <v>3383</v>
       </c>
-      <c r="G261" t="n">
-        <v>3312</v>
-      </c>
-      <c r="H261" t="n">
-        <v>3344</v>
-      </c>
       <c r="I261" t="n">
-        <v>3494</v>
+        <v>3519</v>
       </c>
       <c r="J261" t="n">
         <v>3983</v>
       </c>
       <c r="K261" t="n">
-        <v>4374</v>
+        <v>4355</v>
       </c>
       <c r="L261" t="n">
-        <v>4687</v>
+        <v>4647</v>
       </c>
       <c r="M261" t="n">
-        <v>4794</v>
+        <v>4747</v>
       </c>
       <c r="N261" t="n">
-        <v>4522</v>
+        <v>4645</v>
       </c>
       <c r="O261" t="n">
-        <v>4421</v>
+        <v>4620</v>
       </c>
       <c r="P261" t="n">
-        <v>4288</v>
+        <v>4582</v>
       </c>
       <c r="Q261" t="n">
-        <v>4406</v>
+        <v>4651</v>
       </c>
       <c r="R261" t="n">
-        <v>4467</v>
+        <v>4641</v>
       </c>
       <c r="S261" t="n">
-        <v>4336</v>
+        <v>4599</v>
       </c>
       <c r="T261" t="n">
-        <v>4182</v>
+        <v>4515</v>
       </c>
       <c r="U261" t="n">
-        <v>4206</v>
+        <v>4536</v>
       </c>
       <c r="V261" t="n">
-        <v>4607</v>
+        <v>4801</v>
       </c>
       <c r="W261" t="n">
-        <v>5121</v>
+        <v>5128</v>
       </c>
       <c r="X261" t="n">
         <v>4958</v>
       </c>
       <c r="Y261" t="n">
-        <v>4646</v>
+        <v>4665</v>
       </c>
       <c r="Z261" t="n">
-        <v>4342</v>
+        <v>4360</v>
       </c>
       <c r="AA261" t="n">
-        <v>4036</v>
+        <v>4064</v>
       </c>
     </row>
     <row r="262">
@@ -22154,76 +22154,76 @@
         <v>23</v>
       </c>
       <c r="D262" t="n">
-        <v>3705</v>
+        <v>3720</v>
       </c>
       <c r="E262" t="n">
-        <v>3474</v>
+        <v>3496</v>
       </c>
       <c r="F262" t="n">
-        <v>3372</v>
+        <v>3405</v>
       </c>
       <c r="G262" t="n">
-        <v>3301</v>
+        <v>3346</v>
       </c>
       <c r="H262" t="n">
-        <v>3332</v>
+        <v>3376</v>
       </c>
       <c r="I262" t="n">
-        <v>3482</v>
+        <v>3511</v>
       </c>
       <c r="J262" t="n">
-        <v>3968</v>
+        <v>3974</v>
       </c>
       <c r="K262" t="n">
-        <v>4357</v>
+        <v>4345</v>
       </c>
       <c r="L262" t="n">
-        <v>4669</v>
+        <v>4636</v>
       </c>
       <c r="M262" t="n">
-        <v>4774</v>
+        <v>4735</v>
       </c>
       <c r="N262" t="n">
-        <v>4502</v>
+        <v>4634</v>
       </c>
       <c r="O262" t="n">
-        <v>4401</v>
+        <v>4609</v>
       </c>
       <c r="P262" t="n">
-        <v>4268</v>
+        <v>4570</v>
       </c>
       <c r="Q262" t="n">
-        <v>4386</v>
+        <v>4639</v>
       </c>
       <c r="R262" t="n">
-        <v>4448</v>
+        <v>4629</v>
       </c>
       <c r="S262" t="n">
-        <v>4317</v>
+        <v>4587</v>
       </c>
       <c r="T262" t="n">
-        <v>4162</v>
+        <v>4503</v>
       </c>
       <c r="U262" t="n">
-        <v>4184</v>
+        <v>4521</v>
       </c>
       <c r="V262" t="n">
-        <v>4553</v>
+        <v>4752</v>
       </c>
       <c r="W262" t="n">
-        <v>5025</v>
+        <v>5038</v>
       </c>
       <c r="X262" t="n">
-        <v>4867</v>
+        <v>4874</v>
       </c>
       <c r="Y262" t="n">
-        <v>4566</v>
+        <v>4591</v>
       </c>
       <c r="Z262" t="n">
-        <v>4273</v>
+        <v>4295</v>
       </c>
       <c r="AA262" t="n">
-        <v>3977</v>
+        <v>4009</v>
       </c>
     </row>
     <row r="263">
@@ -22237,76 +22237,76 @@
         <v>24</v>
       </c>
       <c r="D263" t="n">
-        <v>3702</v>
+        <v>3732</v>
       </c>
       <c r="E263" t="n">
-        <v>3450</v>
+        <v>3499</v>
       </c>
       <c r="F263" t="n">
-        <v>3327</v>
+        <v>3385</v>
       </c>
       <c r="G263" t="n">
-        <v>3262</v>
+        <v>3331</v>
       </c>
       <c r="H263" t="n">
-        <v>3248</v>
+        <v>3312</v>
       </c>
       <c r="I263" t="n">
-        <v>3314</v>
+        <v>3367</v>
       </c>
       <c r="J263" t="n">
-        <v>3541</v>
+        <v>3564</v>
       </c>
       <c r="K263" t="n">
-        <v>3883</v>
+        <v>3842</v>
       </c>
       <c r="L263" t="n">
-        <v>4312</v>
+        <v>4226</v>
       </c>
       <c r="M263" t="n">
-        <v>4472</v>
+        <v>4426</v>
       </c>
       <c r="N263" t="n">
-        <v>4451</v>
+        <v>4455</v>
       </c>
       <c r="O263" t="n">
-        <v>4350</v>
+        <v>4432</v>
       </c>
       <c r="P263" t="n">
-        <v>4205</v>
+        <v>4378</v>
       </c>
       <c r="Q263" t="n">
-        <v>4261</v>
+        <v>4376</v>
       </c>
       <c r="R263" t="n">
-        <v>4017</v>
+        <v>4337</v>
       </c>
       <c r="S263" t="n">
-        <v>3947</v>
+        <v>4319</v>
       </c>
       <c r="T263" t="n">
-        <v>4030</v>
+        <v>4353</v>
       </c>
       <c r="U263" t="n">
-        <v>4271</v>
+        <v>4501</v>
       </c>
       <c r="V263" t="n">
-        <v>4546</v>
+        <v>4680</v>
       </c>
       <c r="W263" t="n">
-        <v>4841</v>
+        <v>4881</v>
       </c>
       <c r="X263" t="n">
-        <v>4687</v>
+        <v>4692</v>
       </c>
       <c r="Y263" t="n">
-        <v>4359</v>
+        <v>4411</v>
       </c>
       <c r="Z263" t="n">
-        <v>4087</v>
+        <v>4137</v>
       </c>
       <c r="AA263" t="n">
-        <v>3887</v>
+        <v>3937</v>
       </c>
     </row>
     <row r="264">
@@ -22320,76 +22320,159 @@
         <v>25</v>
       </c>
       <c r="D264" t="n">
-        <v>3644</v>
+        <v>3673</v>
       </c>
       <c r="E264" t="n">
-        <v>3412</v>
+        <v>3467</v>
       </c>
       <c r="F264" t="n">
-        <v>3241</v>
+        <v>3308</v>
       </c>
       <c r="G264" t="n">
-        <v>3218</v>
+        <v>3279</v>
       </c>
       <c r="H264" t="n">
-        <v>3198</v>
+        <v>3261</v>
       </c>
       <c r="I264" t="n">
-        <v>3223</v>
+        <v>3297</v>
       </c>
       <c r="J264" t="n">
-        <v>3397</v>
+        <v>3467</v>
       </c>
       <c r="K264" t="n">
-        <v>3601</v>
+        <v>3665</v>
       </c>
       <c r="L264" t="n">
-        <v>3947</v>
+        <v>4015</v>
       </c>
       <c r="M264" t="n">
-        <v>4213</v>
+        <v>4271</v>
       </c>
       <c r="N264" t="n">
-        <v>4362</v>
+        <v>4400</v>
       </c>
       <c r="O264" t="n">
-        <v>4422</v>
+        <v>4443</v>
       </c>
       <c r="P264" t="n">
-        <v>4419</v>
+        <v>4399</v>
       </c>
       <c r="Q264" t="n">
-        <v>4461</v>
+        <v>4376</v>
       </c>
       <c r="R264" t="n">
-        <v>4004</v>
+        <v>4394</v>
       </c>
       <c r="S264" t="n">
-        <v>4004</v>
+        <v>4435</v>
       </c>
       <c r="T264" t="n">
-        <v>4004</v>
+        <v>4376</v>
       </c>
       <c r="U264" t="n">
-        <v>4245</v>
+        <v>4537</v>
       </c>
       <c r="V264" t="n">
-        <v>4583</v>
+        <v>4786</v>
       </c>
       <c r="W264" t="n">
-        <v>5058</v>
+        <v>5097</v>
       </c>
       <c r="X264" t="n">
-        <v>4873</v>
+        <v>4943</v>
       </c>
       <c r="Y264" t="n">
-        <v>4575</v>
+        <v>4649</v>
       </c>
       <c r="Z264" t="n">
-        <v>4231</v>
+        <v>4304</v>
       </c>
       <c r="AA264" t="n">
-        <v>3979</v>
+        <v>4028</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B265" t="n">
+        <v>10</v>
+      </c>
+      <c r="C265" t="n">
+        <v>26</v>
+      </c>
+      <c r="D265" t="n">
+        <v>3714</v>
+      </c>
+      <c r="E265" t="n">
+        <v>3488</v>
+      </c>
+      <c r="F265" t="n">
+        <v>3381</v>
+      </c>
+      <c r="G265" t="n">
+        <v>3341</v>
+      </c>
+      <c r="H265" t="n">
+        <v>3335</v>
+      </c>
+      <c r="I265" t="n">
+        <v>3496</v>
+      </c>
+      <c r="J265" t="n">
+        <v>4011</v>
+      </c>
+      <c r="K265" t="n">
+        <v>4433</v>
+      </c>
+      <c r="L265" t="n">
+        <v>4782</v>
+      </c>
+      <c r="M265" t="n">
+        <v>4925</v>
+      </c>
+      <c r="N265" t="n">
+        <v>4859</v>
+      </c>
+      <c r="O265" t="n">
+        <v>4895</v>
+      </c>
+      <c r="P265" t="n">
+        <v>4871</v>
+      </c>
+      <c r="Q265" t="n">
+        <v>4856</v>
+      </c>
+      <c r="R265" t="n">
+        <v>4795</v>
+      </c>
+      <c r="S265" t="n">
+        <v>4729</v>
+      </c>
+      <c r="T265" t="n">
+        <v>4710</v>
+      </c>
+      <c r="U265" t="n">
+        <v>4762</v>
+      </c>
+      <c r="V265" t="n">
+        <v>5007</v>
+      </c>
+      <c r="W265" t="n">
+        <v>5310</v>
+      </c>
+      <c r="X265" t="n">
+        <v>5130</v>
+      </c>
+      <c r="Y265" t="n">
+        <v>4809</v>
+      </c>
+      <c r="Z265" t="n">
+        <v>4475</v>
+      </c>
+      <c r="AA265" t="n">
+        <v>4189</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA265"/>
+  <dimension ref="A1:AA266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22071,76 +22071,76 @@
         <v>22</v>
       </c>
       <c r="D261" t="n">
-        <v>3726</v>
+        <v>3657</v>
       </c>
       <c r="E261" t="n">
-        <v>3502</v>
+        <v>3441</v>
       </c>
       <c r="F261" t="n">
-        <v>3412</v>
+        <v>3361</v>
       </c>
       <c r="G261" t="n">
-        <v>3353</v>
+        <v>3309</v>
       </c>
       <c r="H261" t="n">
-        <v>3383</v>
+        <v>3333</v>
       </c>
       <c r="I261" t="n">
-        <v>3519</v>
+        <v>3457</v>
       </c>
       <c r="J261" t="n">
-        <v>3983</v>
+        <v>3905</v>
       </c>
       <c r="K261" t="n">
-        <v>4355</v>
+        <v>4268</v>
       </c>
       <c r="L261" t="n">
-        <v>4647</v>
+        <v>4569</v>
       </c>
       <c r="M261" t="n">
-        <v>4747</v>
+        <v>4679</v>
       </c>
       <c r="N261" t="n">
-        <v>4645</v>
+        <v>4436</v>
       </c>
       <c r="O261" t="n">
-        <v>4620</v>
+        <v>4417</v>
       </c>
       <c r="P261" t="n">
-        <v>4582</v>
+        <v>4334</v>
       </c>
       <c r="Q261" t="n">
-        <v>4651</v>
+        <v>4320</v>
       </c>
       <c r="R261" t="n">
-        <v>4641</v>
+        <v>4387</v>
       </c>
       <c r="S261" t="n">
-        <v>4599</v>
+        <v>4250</v>
       </c>
       <c r="T261" t="n">
-        <v>4515</v>
+        <v>4108</v>
       </c>
       <c r="U261" t="n">
-        <v>4536</v>
+        <v>4130</v>
       </c>
       <c r="V261" t="n">
-        <v>4801</v>
+        <v>4453</v>
       </c>
       <c r="W261" t="n">
-        <v>5128</v>
+        <v>4812</v>
       </c>
       <c r="X261" t="n">
-        <v>4958</v>
+        <v>4667</v>
       </c>
       <c r="Y261" t="n">
-        <v>4665</v>
+        <v>4420</v>
       </c>
       <c r="Z261" t="n">
-        <v>4360</v>
+        <v>4155</v>
       </c>
       <c r="AA261" t="n">
-        <v>4064</v>
+        <v>3894</v>
       </c>
     </row>
     <row r="262">
@@ -22154,76 +22154,76 @@
         <v>23</v>
       </c>
       <c r="D262" t="n">
-        <v>3720</v>
+        <v>3692</v>
       </c>
       <c r="E262" t="n">
-        <v>3496</v>
+        <v>3481</v>
       </c>
       <c r="F262" t="n">
-        <v>3405</v>
+        <v>3403</v>
       </c>
       <c r="G262" t="n">
-        <v>3346</v>
+        <v>3352</v>
       </c>
       <c r="H262" t="n">
-        <v>3376</v>
+        <v>3377</v>
       </c>
       <c r="I262" t="n">
-        <v>3511</v>
+        <v>3504</v>
       </c>
       <c r="J262" t="n">
-        <v>3974</v>
+        <v>3962</v>
       </c>
       <c r="K262" t="n">
-        <v>4345</v>
+        <v>4333</v>
       </c>
       <c r="L262" t="n">
-        <v>4636</v>
+        <v>4641</v>
       </c>
       <c r="M262" t="n">
-        <v>4735</v>
+        <v>4753</v>
       </c>
       <c r="N262" t="n">
-        <v>4634</v>
+        <v>4511</v>
       </c>
       <c r="O262" t="n">
-        <v>4609</v>
+        <v>4492</v>
       </c>
       <c r="P262" t="n">
-        <v>4570</v>
+        <v>4410</v>
       </c>
       <c r="Q262" t="n">
-        <v>4639</v>
+        <v>4394</v>
       </c>
       <c r="R262" t="n">
-        <v>4629</v>
+        <v>4361</v>
       </c>
       <c r="S262" t="n">
-        <v>4587</v>
+        <v>4226</v>
       </c>
       <c r="T262" t="n">
-        <v>4503</v>
+        <v>4184</v>
       </c>
       <c r="U262" t="n">
-        <v>4521</v>
+        <v>4203</v>
       </c>
       <c r="V262" t="n">
-        <v>4752</v>
+        <v>4484</v>
       </c>
       <c r="W262" t="n">
-        <v>5038</v>
+        <v>4796</v>
       </c>
       <c r="X262" t="n">
-        <v>4874</v>
+        <v>4653</v>
       </c>
       <c r="Y262" t="n">
-        <v>4591</v>
+        <v>4409</v>
       </c>
       <c r="Z262" t="n">
-        <v>4295</v>
+        <v>4147</v>
       </c>
       <c r="AA262" t="n">
-        <v>4009</v>
+        <v>3890</v>
       </c>
     </row>
     <row r="263">
@@ -22237,76 +22237,76 @@
         <v>24</v>
       </c>
       <c r="D263" t="n">
-        <v>3732</v>
+        <v>3687</v>
       </c>
       <c r="E263" t="n">
-        <v>3499</v>
+        <v>3470</v>
       </c>
       <c r="F263" t="n">
-        <v>3385</v>
+        <v>3364</v>
       </c>
       <c r="G263" t="n">
-        <v>3331</v>
+        <v>3314</v>
       </c>
       <c r="H263" t="n">
-        <v>3312</v>
+        <v>3295</v>
       </c>
       <c r="I263" t="n">
-        <v>3367</v>
+        <v>3351</v>
       </c>
       <c r="J263" t="n">
-        <v>3564</v>
+        <v>3548</v>
       </c>
       <c r="K263" t="n">
-        <v>3842</v>
+        <v>3827</v>
       </c>
       <c r="L263" t="n">
-        <v>4226</v>
+        <v>4212</v>
       </c>
       <c r="M263" t="n">
-        <v>4426</v>
+        <v>4412</v>
       </c>
       <c r="N263" t="n">
-        <v>4455</v>
+        <v>4441</v>
       </c>
       <c r="O263" t="n">
-        <v>4432</v>
+        <v>4361</v>
       </c>
       <c r="P263" t="n">
-        <v>4378</v>
+        <v>4169</v>
       </c>
       <c r="Q263" t="n">
-        <v>4376</v>
+        <v>4164</v>
       </c>
       <c r="R263" t="n">
-        <v>4337</v>
+        <v>4027</v>
       </c>
       <c r="S263" t="n">
-        <v>4319</v>
+        <v>3964</v>
       </c>
       <c r="T263" t="n">
-        <v>4353</v>
+        <v>4003</v>
       </c>
       <c r="U263" t="n">
-        <v>4501</v>
+        <v>4172</v>
       </c>
       <c r="V263" t="n">
-        <v>4680</v>
+        <v>4377</v>
       </c>
       <c r="W263" t="n">
-        <v>4881</v>
+        <v>4607</v>
       </c>
       <c r="X263" t="n">
-        <v>4692</v>
+        <v>4445</v>
       </c>
       <c r="Y263" t="n">
-        <v>4411</v>
+        <v>4204</v>
       </c>
       <c r="Z263" t="n">
-        <v>4137</v>
+        <v>3969</v>
       </c>
       <c r="AA263" t="n">
-        <v>3937</v>
+        <v>3797</v>
       </c>
     </row>
     <row r="264">
@@ -22320,76 +22320,76 @@
         <v>25</v>
       </c>
       <c r="D264" t="n">
-        <v>3673</v>
+        <v>3638</v>
       </c>
       <c r="E264" t="n">
-        <v>3467</v>
+        <v>3447</v>
       </c>
       <c r="F264" t="n">
-        <v>3308</v>
+        <v>3301</v>
       </c>
       <c r="G264" t="n">
-        <v>3279</v>
+        <v>3274</v>
       </c>
       <c r="H264" t="n">
-        <v>3261</v>
+        <v>3258</v>
       </c>
       <c r="I264" t="n">
-        <v>3297</v>
+        <v>3294</v>
       </c>
       <c r="J264" t="n">
-        <v>3467</v>
+        <v>3465</v>
       </c>
       <c r="K264" t="n">
-        <v>3665</v>
+        <v>3664</v>
       </c>
       <c r="L264" t="n">
-        <v>4015</v>
+        <v>4017</v>
       </c>
       <c r="M264" t="n">
-        <v>4271</v>
+        <v>4274</v>
       </c>
       <c r="N264" t="n">
-        <v>4400</v>
+        <v>4405</v>
       </c>
       <c r="O264" t="n">
-        <v>4443</v>
+        <v>4448</v>
       </c>
       <c r="P264" t="n">
-        <v>4399</v>
+        <v>4281</v>
       </c>
       <c r="Q264" t="n">
-        <v>4376</v>
+        <v>4141</v>
       </c>
       <c r="R264" t="n">
-        <v>4394</v>
+        <v>4104</v>
       </c>
       <c r="S264" t="n">
-        <v>4435</v>
+        <v>4100</v>
       </c>
       <c r="T264" t="n">
-        <v>4376</v>
+        <v>4041</v>
       </c>
       <c r="U264" t="n">
-        <v>4537</v>
+        <v>4220</v>
       </c>
       <c r="V264" t="n">
-        <v>4786</v>
+        <v>4496</v>
       </c>
       <c r="W264" t="n">
-        <v>5097</v>
+        <v>4841</v>
       </c>
       <c r="X264" t="n">
-        <v>4943</v>
+        <v>4705</v>
       </c>
       <c r="Y264" t="n">
-        <v>4649</v>
+        <v>4446</v>
       </c>
       <c r="Z264" t="n">
-        <v>4304</v>
+        <v>4142</v>
       </c>
       <c r="AA264" t="n">
-        <v>4028</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="265">
@@ -22403,76 +22403,159 @@
         <v>26</v>
       </c>
       <c r="D265" t="n">
-        <v>3714</v>
+        <v>3673</v>
       </c>
       <c r="E265" t="n">
-        <v>3488</v>
+        <v>3469</v>
       </c>
       <c r="F265" t="n">
-        <v>3381</v>
+        <v>3369</v>
       </c>
       <c r="G265" t="n">
-        <v>3341</v>
+        <v>3324</v>
       </c>
       <c r="H265" t="n">
-        <v>3335</v>
+        <v>3332</v>
       </c>
       <c r="I265" t="n">
-        <v>3496</v>
+        <v>3494</v>
       </c>
       <c r="J265" t="n">
-        <v>4011</v>
+        <v>4047</v>
       </c>
       <c r="K265" t="n">
-        <v>4433</v>
+        <v>4492</v>
       </c>
       <c r="L265" t="n">
-        <v>4782</v>
+        <v>4834</v>
       </c>
       <c r="M265" t="n">
-        <v>4925</v>
+        <v>4917</v>
       </c>
       <c r="N265" t="n">
-        <v>4859</v>
+        <v>4719</v>
       </c>
       <c r="O265" t="n">
-        <v>4895</v>
+        <v>4660</v>
       </c>
       <c r="P265" t="n">
-        <v>4871</v>
+        <v>4555</v>
       </c>
       <c r="Q265" t="n">
-        <v>4856</v>
+        <v>4563</v>
       </c>
       <c r="R265" t="n">
-        <v>4795</v>
+        <v>4502</v>
       </c>
       <c r="S265" t="n">
-        <v>4729</v>
+        <v>4399</v>
       </c>
       <c r="T265" t="n">
-        <v>4710</v>
+        <v>4363</v>
       </c>
       <c r="U265" t="n">
-        <v>4762</v>
+        <v>4411</v>
       </c>
       <c r="V265" t="n">
-        <v>5007</v>
+        <v>4686</v>
       </c>
       <c r="W265" t="n">
-        <v>5310</v>
+        <v>5044</v>
       </c>
       <c r="X265" t="n">
-        <v>5130</v>
+        <v>4905</v>
       </c>
       <c r="Y265" t="n">
-        <v>4809</v>
+        <v>4617</v>
       </c>
       <c r="Z265" t="n">
-        <v>4475</v>
+        <v>4309</v>
       </c>
       <c r="AA265" t="n">
-        <v>4189</v>
+        <v>4053</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B266" t="n">
+        <v>10</v>
+      </c>
+      <c r="C266" t="n">
+        <v>27</v>
+      </c>
+      <c r="D266" t="n">
+        <v>3752</v>
+      </c>
+      <c r="E266" t="n">
+        <v>3553</v>
+      </c>
+      <c r="F266" t="n">
+        <v>3479</v>
+      </c>
+      <c r="G266" t="n">
+        <v>3431</v>
+      </c>
+      <c r="H266" t="n">
+        <v>3458</v>
+      </c>
+      <c r="I266" t="n">
+        <v>3597</v>
+      </c>
+      <c r="J266" t="n">
+        <v>4099</v>
+      </c>
+      <c r="K266" t="n">
+        <v>4505</v>
+      </c>
+      <c r="L266" t="n">
+        <v>4843</v>
+      </c>
+      <c r="M266" t="n">
+        <v>4966</v>
+      </c>
+      <c r="N266" t="n">
+        <v>4731</v>
+      </c>
+      <c r="O266" t="n">
+        <v>4712</v>
+      </c>
+      <c r="P266" t="n">
+        <v>4633</v>
+      </c>
+      <c r="Q266" t="n">
+        <v>4512</v>
+      </c>
+      <c r="R266" t="n">
+        <v>4580</v>
+      </c>
+      <c r="S266" t="n">
+        <v>4548</v>
+      </c>
+      <c r="T266" t="n">
+        <v>4413</v>
+      </c>
+      <c r="U266" t="n">
+        <v>4435</v>
+      </c>
+      <c r="V266" t="n">
+        <v>4744</v>
+      </c>
+      <c r="W266" t="n">
+        <v>5086</v>
+      </c>
+      <c r="X266" t="n">
+        <v>4927</v>
+      </c>
+      <c r="Y266" t="n">
+        <v>4657</v>
+      </c>
+      <c r="Z266" t="n">
+        <v>4367</v>
+      </c>
+      <c r="AA266" t="n">
+        <v>4082</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA266"/>
+  <dimension ref="A1:AA267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22154,76 +22154,76 @@
         <v>23</v>
       </c>
       <c r="D262" t="n">
-        <v>3692</v>
+        <v>3745</v>
       </c>
       <c r="E262" t="n">
-        <v>3481</v>
+        <v>3482</v>
       </c>
       <c r="F262" t="n">
-        <v>3403</v>
+        <v>3371</v>
       </c>
       <c r="G262" t="n">
-        <v>3352</v>
+        <v>3303</v>
       </c>
       <c r="H262" t="n">
-        <v>3377</v>
+        <v>3330</v>
       </c>
       <c r="I262" t="n">
-        <v>3504</v>
+        <v>3471</v>
       </c>
       <c r="J262" t="n">
-        <v>3962</v>
+        <v>3974</v>
       </c>
       <c r="K262" t="n">
-        <v>4333</v>
+        <v>4386</v>
       </c>
       <c r="L262" t="n">
-        <v>4641</v>
+        <v>4708</v>
       </c>
       <c r="M262" t="n">
-        <v>4753</v>
+        <v>4804</v>
       </c>
       <c r="N262" t="n">
-        <v>4511</v>
+        <v>4681</v>
       </c>
       <c r="O262" t="n">
-        <v>4492</v>
+        <v>4637</v>
       </c>
       <c r="P262" t="n">
-        <v>4410</v>
+        <v>4578</v>
       </c>
       <c r="Q262" t="n">
-        <v>4394</v>
+        <v>4631</v>
       </c>
       <c r="R262" t="n">
-        <v>4361</v>
+        <v>4597</v>
       </c>
       <c r="S262" t="n">
-        <v>4226</v>
+        <v>4558</v>
       </c>
       <c r="T262" t="n">
-        <v>4184</v>
+        <v>4489</v>
       </c>
       <c r="U262" t="n">
-        <v>4203</v>
+        <v>4509</v>
       </c>
       <c r="V262" t="n">
-        <v>4484</v>
+        <v>4759</v>
       </c>
       <c r="W262" t="n">
-        <v>4796</v>
+        <v>5039</v>
       </c>
       <c r="X262" t="n">
-        <v>4653</v>
+        <v>4879</v>
       </c>
       <c r="Y262" t="n">
-        <v>4409</v>
+        <v>4589</v>
       </c>
       <c r="Z262" t="n">
-        <v>4147</v>
+        <v>4272</v>
       </c>
       <c r="AA262" t="n">
-        <v>3890</v>
+        <v>3960</v>
       </c>
     </row>
     <row r="263">
@@ -22237,76 +22237,76 @@
         <v>24</v>
       </c>
       <c r="D263" t="n">
-        <v>3687</v>
+        <v>3759</v>
       </c>
       <c r="E263" t="n">
-        <v>3470</v>
+        <v>3526</v>
       </c>
       <c r="F263" t="n">
-        <v>3364</v>
+        <v>3406</v>
       </c>
       <c r="G263" t="n">
-        <v>3314</v>
+        <v>3330</v>
       </c>
       <c r="H263" t="n">
-        <v>3295</v>
+        <v>3321</v>
       </c>
       <c r="I263" t="n">
-        <v>3351</v>
+        <v>3387</v>
       </c>
       <c r="J263" t="n">
-        <v>3548</v>
+        <v>3581</v>
       </c>
       <c r="K263" t="n">
-        <v>3827</v>
+        <v>3918</v>
       </c>
       <c r="L263" t="n">
-        <v>4212</v>
+        <v>4345</v>
       </c>
       <c r="M263" t="n">
-        <v>4412</v>
+        <v>4588</v>
       </c>
       <c r="N263" t="n">
-        <v>4441</v>
+        <v>4588</v>
       </c>
       <c r="O263" t="n">
-        <v>4361</v>
+        <v>4550</v>
       </c>
       <c r="P263" t="n">
-        <v>4169</v>
+        <v>4511</v>
       </c>
       <c r="Q263" t="n">
-        <v>4164</v>
+        <v>4503</v>
       </c>
       <c r="R263" t="n">
-        <v>4027</v>
+        <v>4486</v>
       </c>
       <c r="S263" t="n">
-        <v>3964</v>
+        <v>4461</v>
       </c>
       <c r="T263" t="n">
-        <v>4003</v>
+        <v>4485</v>
       </c>
       <c r="U263" t="n">
-        <v>4172</v>
+        <v>4615</v>
       </c>
       <c r="V263" t="n">
-        <v>4377</v>
+        <v>4799</v>
       </c>
       <c r="W263" t="n">
-        <v>4607</v>
+        <v>4936</v>
       </c>
       <c r="X263" t="n">
-        <v>4445</v>
+        <v>4733</v>
       </c>
       <c r="Y263" t="n">
-        <v>4204</v>
+        <v>4437</v>
       </c>
       <c r="Z263" t="n">
-        <v>3969</v>
+        <v>4152</v>
       </c>
       <c r="AA263" t="n">
-        <v>3797</v>
+        <v>3941</v>
       </c>
     </row>
     <row r="264">
@@ -22320,76 +22320,76 @@
         <v>25</v>
       </c>
       <c r="D264" t="n">
-        <v>3638</v>
+        <v>3702</v>
       </c>
       <c r="E264" t="n">
-        <v>3447</v>
+        <v>3487</v>
       </c>
       <c r="F264" t="n">
-        <v>3301</v>
+        <v>3321</v>
       </c>
       <c r="G264" t="n">
-        <v>3274</v>
+        <v>3292</v>
       </c>
       <c r="H264" t="n">
-        <v>3258</v>
+        <v>3273</v>
       </c>
       <c r="I264" t="n">
-        <v>3294</v>
+        <v>3314</v>
       </c>
       <c r="J264" t="n">
-        <v>3465</v>
+        <v>3509</v>
       </c>
       <c r="K264" t="n">
-        <v>3664</v>
+        <v>3736</v>
       </c>
       <c r="L264" t="n">
-        <v>4017</v>
+        <v>4138</v>
       </c>
       <c r="M264" t="n">
-        <v>4274</v>
+        <v>4431</v>
       </c>
       <c r="N264" t="n">
-        <v>4405</v>
+        <v>4580</v>
       </c>
       <c r="O264" t="n">
-        <v>4448</v>
+        <v>4629</v>
       </c>
       <c r="P264" t="n">
-        <v>4281</v>
+        <v>4492</v>
       </c>
       <c r="Q264" t="n">
-        <v>4141</v>
+        <v>4420</v>
       </c>
       <c r="R264" t="n">
-        <v>4104</v>
+        <v>4478</v>
       </c>
       <c r="S264" t="n">
-        <v>4100</v>
+        <v>4444</v>
       </c>
       <c r="T264" t="n">
-        <v>4041</v>
+        <v>4420</v>
       </c>
       <c r="U264" t="n">
-        <v>4220</v>
+        <v>4562</v>
       </c>
       <c r="V264" t="n">
-        <v>4496</v>
+        <v>4781</v>
       </c>
       <c r="W264" t="n">
-        <v>4841</v>
+        <v>5055</v>
       </c>
       <c r="X264" t="n">
-        <v>4705</v>
+        <v>4908</v>
       </c>
       <c r="Y264" t="n">
-        <v>4446</v>
+        <v>4627</v>
       </c>
       <c r="Z264" t="n">
-        <v>4142</v>
+        <v>4297</v>
       </c>
       <c r="AA264" t="n">
-        <v>3900</v>
+        <v>4034</v>
       </c>
     </row>
     <row r="265">
@@ -22403,76 +22403,76 @@
         <v>26</v>
       </c>
       <c r="D265" t="n">
-        <v>3673</v>
+        <v>3744</v>
       </c>
       <c r="E265" t="n">
-        <v>3469</v>
+        <v>3512</v>
       </c>
       <c r="F265" t="n">
-        <v>3369</v>
+        <v>3399</v>
       </c>
       <c r="G265" t="n">
-        <v>3324</v>
+        <v>3348</v>
       </c>
       <c r="H265" t="n">
-        <v>3332</v>
+        <v>3356</v>
       </c>
       <c r="I265" t="n">
-        <v>3494</v>
+        <v>3521</v>
       </c>
       <c r="J265" t="n">
-        <v>4047</v>
+        <v>4081</v>
       </c>
       <c r="K265" t="n">
-        <v>4492</v>
+        <v>4533</v>
       </c>
       <c r="L265" t="n">
-        <v>4834</v>
+        <v>4879</v>
       </c>
       <c r="M265" t="n">
-        <v>4917</v>
+        <v>4964</v>
       </c>
       <c r="N265" t="n">
-        <v>4719</v>
+        <v>4890</v>
       </c>
       <c r="O265" t="n">
-        <v>4660</v>
+        <v>4868</v>
       </c>
       <c r="P265" t="n">
-        <v>4555</v>
+        <v>4829</v>
       </c>
       <c r="Q265" t="n">
-        <v>4563</v>
+        <v>4832</v>
       </c>
       <c r="R265" t="n">
-        <v>4502</v>
+        <v>4809</v>
       </c>
       <c r="S265" t="n">
-        <v>4399</v>
+        <v>4771</v>
       </c>
       <c r="T265" t="n">
-        <v>4363</v>
+        <v>4757</v>
       </c>
       <c r="U265" t="n">
-        <v>4411</v>
+        <v>4786</v>
       </c>
       <c r="V265" t="n">
-        <v>4686</v>
+        <v>4954</v>
       </c>
       <c r="W265" t="n">
-        <v>5044</v>
+        <v>5171</v>
       </c>
       <c r="X265" t="n">
-        <v>4905</v>
+        <v>5034</v>
       </c>
       <c r="Y265" t="n">
-        <v>4617</v>
+        <v>4751</v>
       </c>
       <c r="Z265" t="n">
-        <v>4309</v>
+        <v>4447</v>
       </c>
       <c r="AA265" t="n">
-        <v>4053</v>
+        <v>4196</v>
       </c>
     </row>
     <row r="266">
@@ -22486,76 +22486,159 @@
         <v>27</v>
       </c>
       <c r="D266" t="n">
-        <v>3752</v>
+        <v>3808</v>
       </c>
       <c r="E266" t="n">
-        <v>3553</v>
+        <v>3586</v>
       </c>
       <c r="F266" t="n">
-        <v>3479</v>
+        <v>3492</v>
       </c>
       <c r="G266" t="n">
-        <v>3431</v>
+        <v>3435</v>
       </c>
       <c r="H266" t="n">
-        <v>3458</v>
+        <v>3460</v>
       </c>
       <c r="I266" t="n">
-        <v>3597</v>
+        <v>3592</v>
       </c>
       <c r="J266" t="n">
-        <v>4099</v>
+        <v>4058</v>
       </c>
       <c r="K266" t="n">
-        <v>4505</v>
+        <v>4440</v>
       </c>
       <c r="L266" t="n">
-        <v>4843</v>
+        <v>4739</v>
       </c>
       <c r="M266" t="n">
-        <v>4966</v>
+        <v>4829</v>
       </c>
       <c r="N266" t="n">
-        <v>4731</v>
+        <v>4807</v>
       </c>
       <c r="O266" t="n">
-        <v>4712</v>
+        <v>4799</v>
       </c>
       <c r="P266" t="n">
-        <v>4633</v>
+        <v>4789</v>
       </c>
       <c r="Q266" t="n">
-        <v>4512</v>
+        <v>4798</v>
       </c>
       <c r="R266" t="n">
-        <v>4580</v>
+        <v>4792</v>
       </c>
       <c r="S266" t="n">
-        <v>4548</v>
+        <v>4785</v>
       </c>
       <c r="T266" t="n">
-        <v>4413</v>
+        <v>4773</v>
       </c>
       <c r="U266" t="n">
-        <v>4435</v>
+        <v>4788</v>
       </c>
       <c r="V266" t="n">
-        <v>4744</v>
+        <v>4975</v>
       </c>
       <c r="W266" t="n">
-        <v>5086</v>
+        <v>5184</v>
       </c>
       <c r="X266" t="n">
-        <v>4927</v>
+        <v>5039</v>
       </c>
       <c r="Y266" t="n">
-        <v>4657</v>
+        <v>4776</v>
       </c>
       <c r="Z266" t="n">
-        <v>4367</v>
+        <v>4489</v>
       </c>
       <c r="AA266" t="n">
-        <v>4082</v>
+        <v>4205</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B267" t="n">
+        <v>10</v>
+      </c>
+      <c r="C267" t="n">
+        <v>28</v>
+      </c>
+      <c r="D267" t="n">
+        <v>3799</v>
+      </c>
+      <c r="E267" t="n">
+        <v>3577</v>
+      </c>
+      <c r="F267" t="n">
+        <v>3482</v>
+      </c>
+      <c r="G267" t="n">
+        <v>3425</v>
+      </c>
+      <c r="H267" t="n">
+        <v>3450</v>
+      </c>
+      <c r="I267" t="n">
+        <v>3581</v>
+      </c>
+      <c r="J267" t="n">
+        <v>4045</v>
+      </c>
+      <c r="K267" t="n">
+        <v>4425</v>
+      </c>
+      <c r="L267" t="n">
+        <v>4723</v>
+      </c>
+      <c r="M267" t="n">
+        <v>4812</v>
+      </c>
+      <c r="N267" t="n">
+        <v>4790</v>
+      </c>
+      <c r="O267" t="n">
+        <v>4782</v>
+      </c>
+      <c r="P267" t="n">
+        <v>4771</v>
+      </c>
+      <c r="Q267" t="n">
+        <v>4781</v>
+      </c>
+      <c r="R267" t="n">
+        <v>4775</v>
+      </c>
+      <c r="S267" t="n">
+        <v>4768</v>
+      </c>
+      <c r="T267" t="n">
+        <v>4755</v>
+      </c>
+      <c r="U267" t="n">
+        <v>4770</v>
+      </c>
+      <c r="V267" t="n">
+        <v>4958</v>
+      </c>
+      <c r="W267" t="n">
+        <v>5169</v>
+      </c>
+      <c r="X267" t="n">
+        <v>5025</v>
+      </c>
+      <c r="Y267" t="n">
+        <v>4763</v>
+      </c>
+      <c r="Z267" t="n">
+        <v>4477</v>
+      </c>
+      <c r="AA267" t="n">
+        <v>4195</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA267"/>
+  <dimension ref="A1:AA268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22237,76 +22237,76 @@
         <v>24</v>
       </c>
       <c r="D263" t="n">
-        <v>3759</v>
+        <v>3658</v>
       </c>
       <c r="E263" t="n">
-        <v>3526</v>
+        <v>3505</v>
       </c>
       <c r="F263" t="n">
-        <v>3406</v>
+        <v>3426</v>
       </c>
       <c r="G263" t="n">
-        <v>3330</v>
+        <v>3376</v>
       </c>
       <c r="H263" t="n">
-        <v>3321</v>
+        <v>3370</v>
       </c>
       <c r="I263" t="n">
-        <v>3387</v>
+        <v>3434</v>
       </c>
       <c r="J263" t="n">
-        <v>3581</v>
+        <v>3620</v>
       </c>
       <c r="K263" t="n">
-        <v>3918</v>
+        <v>3945</v>
       </c>
       <c r="L263" t="n">
-        <v>4345</v>
+        <v>4355</v>
       </c>
       <c r="M263" t="n">
-        <v>4588</v>
+        <v>4589</v>
       </c>
       <c r="N263" t="n">
-        <v>4588</v>
+        <v>4589</v>
       </c>
       <c r="O263" t="n">
-        <v>4550</v>
+        <v>4401</v>
       </c>
       <c r="P263" t="n">
-        <v>4511</v>
+        <v>4213</v>
       </c>
       <c r="Q263" t="n">
-        <v>4503</v>
+        <v>4174</v>
       </c>
       <c r="R263" t="n">
-        <v>4486</v>
+        <v>4094</v>
       </c>
       <c r="S263" t="n">
-        <v>4461</v>
+        <v>3969</v>
       </c>
       <c r="T263" t="n">
-        <v>4485</v>
+        <v>4011</v>
       </c>
       <c r="U263" t="n">
-        <v>4615</v>
+        <v>4226</v>
       </c>
       <c r="V263" t="n">
-        <v>4799</v>
+        <v>4532</v>
       </c>
       <c r="W263" t="n">
-        <v>4936</v>
+        <v>4761</v>
       </c>
       <c r="X263" t="n">
-        <v>4733</v>
+        <v>4579</v>
       </c>
       <c r="Y263" t="n">
-        <v>4437</v>
+        <v>4316</v>
       </c>
       <c r="Z263" t="n">
-        <v>4152</v>
+        <v>4063</v>
       </c>
       <c r="AA263" t="n">
-        <v>3941</v>
+        <v>3876</v>
       </c>
     </row>
     <row r="264">
@@ -22320,76 +22320,76 @@
         <v>25</v>
       </c>
       <c r="D264" t="n">
-        <v>3702</v>
+        <v>3612</v>
       </c>
       <c r="E264" t="n">
-        <v>3487</v>
+        <v>3477</v>
       </c>
       <c r="F264" t="n">
-        <v>3321</v>
+        <v>3369</v>
       </c>
       <c r="G264" t="n">
-        <v>3292</v>
+        <v>3347</v>
       </c>
       <c r="H264" t="n">
-        <v>3273</v>
+        <v>3336</v>
       </c>
       <c r="I264" t="n">
-        <v>3314</v>
+        <v>3386</v>
       </c>
       <c r="J264" t="n">
-        <v>3509</v>
+        <v>3569</v>
       </c>
       <c r="K264" t="n">
-        <v>3736</v>
+        <v>3783</v>
       </c>
       <c r="L264" t="n">
-        <v>4138</v>
+        <v>4172</v>
       </c>
       <c r="M264" t="n">
-        <v>4431</v>
+        <v>4444</v>
       </c>
       <c r="N264" t="n">
-        <v>4580</v>
+        <v>4569</v>
       </c>
       <c r="O264" t="n">
-        <v>4629</v>
+        <v>4600</v>
       </c>
       <c r="P264" t="n">
-        <v>4492</v>
+        <v>4520</v>
       </c>
       <c r="Q264" t="n">
-        <v>4420</v>
+        <v>4189</v>
       </c>
       <c r="R264" t="n">
-        <v>4478</v>
+        <v>4093</v>
       </c>
       <c r="S264" t="n">
-        <v>4444</v>
+        <v>4051</v>
       </c>
       <c r="T264" t="n">
-        <v>4420</v>
+        <v>4077</v>
       </c>
       <c r="U264" t="n">
-        <v>4562</v>
+        <v>4280</v>
       </c>
       <c r="V264" t="n">
-        <v>4781</v>
+        <v>4614</v>
       </c>
       <c r="W264" t="n">
-        <v>5055</v>
+        <v>4999</v>
       </c>
       <c r="X264" t="n">
-        <v>4908</v>
+        <v>4875</v>
       </c>
       <c r="Y264" t="n">
-        <v>4627</v>
+        <v>4597</v>
       </c>
       <c r="Z264" t="n">
-        <v>4297</v>
+        <v>4265</v>
       </c>
       <c r="AA264" t="n">
-        <v>4034</v>
+        <v>3982</v>
       </c>
     </row>
     <row r="265">
@@ -22403,76 +22403,76 @@
         <v>26</v>
       </c>
       <c r="D265" t="n">
-        <v>3744</v>
+        <v>3645</v>
       </c>
       <c r="E265" t="n">
-        <v>3512</v>
+        <v>3501</v>
       </c>
       <c r="F265" t="n">
+        <v>3431</v>
+      </c>
+      <c r="G265" t="n">
         <v>3399</v>
       </c>
-      <c r="G265" t="n">
-        <v>3348</v>
-      </c>
       <c r="H265" t="n">
-        <v>3356</v>
+        <v>3408</v>
       </c>
       <c r="I265" t="n">
-        <v>3521</v>
+        <v>3578</v>
       </c>
       <c r="J265" t="n">
-        <v>4081</v>
+        <v>4155</v>
       </c>
       <c r="K265" t="n">
-        <v>4533</v>
+        <v>4621</v>
       </c>
       <c r="L265" t="n">
-        <v>4879</v>
+        <v>4978</v>
       </c>
       <c r="M265" t="n">
-        <v>4964</v>
+        <v>5065</v>
       </c>
       <c r="N265" t="n">
-        <v>4890</v>
+        <v>4816</v>
       </c>
       <c r="O265" t="n">
-        <v>4868</v>
+        <v>4742</v>
       </c>
       <c r="P265" t="n">
-        <v>4829</v>
+        <v>4610</v>
       </c>
       <c r="Q265" t="n">
-        <v>4832</v>
+        <v>4620</v>
       </c>
       <c r="R265" t="n">
-        <v>4809</v>
+        <v>4544</v>
       </c>
       <c r="S265" t="n">
-        <v>4771</v>
+        <v>4413</v>
       </c>
       <c r="T265" t="n">
-        <v>4757</v>
+        <v>4368</v>
       </c>
       <c r="U265" t="n">
-        <v>4786</v>
+        <v>4427</v>
       </c>
       <c r="V265" t="n">
-        <v>4954</v>
+        <v>4762</v>
       </c>
       <c r="W265" t="n">
-        <v>5171</v>
+        <v>5198</v>
       </c>
       <c r="X265" t="n">
-        <v>5034</v>
+        <v>5049</v>
       </c>
       <c r="Y265" t="n">
-        <v>4751</v>
+        <v>4739</v>
       </c>
       <c r="Z265" t="n">
-        <v>4447</v>
+        <v>4407</v>
       </c>
       <c r="AA265" t="n">
-        <v>4196</v>
+        <v>4133</v>
       </c>
     </row>
     <row r="266">
@@ -22486,76 +22486,76 @@
         <v>27</v>
       </c>
       <c r="D266" t="n">
-        <v>3808</v>
+        <v>3721</v>
       </c>
       <c r="E266" t="n">
-        <v>3586</v>
+        <v>3592</v>
       </c>
       <c r="F266" t="n">
-        <v>3492</v>
+        <v>3535</v>
       </c>
       <c r="G266" t="n">
-        <v>3435</v>
+        <v>3502</v>
       </c>
       <c r="H266" t="n">
-        <v>3460</v>
+        <v>3529</v>
       </c>
       <c r="I266" t="n">
-        <v>3592</v>
+        <v>3681</v>
       </c>
       <c r="J266" t="n">
-        <v>4058</v>
+        <v>4230</v>
       </c>
       <c r="K266" t="n">
-        <v>4440</v>
+        <v>4678</v>
       </c>
       <c r="L266" t="n">
-        <v>4739</v>
+        <v>5022</v>
       </c>
       <c r="M266" t="n">
-        <v>4829</v>
+        <v>5107</v>
       </c>
       <c r="N266" t="n">
-        <v>4807</v>
+        <v>4842</v>
       </c>
       <c r="O266" t="n">
-        <v>4799</v>
+        <v>4742</v>
       </c>
       <c r="P266" t="n">
-        <v>4789</v>
+        <v>4685</v>
       </c>
       <c r="Q266" t="n">
-        <v>4798</v>
+        <v>4676</v>
       </c>
       <c r="R266" t="n">
-        <v>4792</v>
+        <v>4584</v>
       </c>
       <c r="S266" t="n">
-        <v>4785</v>
+        <v>4468</v>
       </c>
       <c r="T266" t="n">
-        <v>4773</v>
+        <v>4412</v>
       </c>
       <c r="U266" t="n">
+        <v>4455</v>
+      </c>
+      <c r="V266" t="n">
+        <v>4827</v>
+      </c>
+      <c r="W266" t="n">
+        <v>5234</v>
+      </c>
+      <c r="X266" t="n">
+        <v>5080</v>
+      </c>
+      <c r="Y266" t="n">
         <v>4788</v>
       </c>
-      <c r="V266" t="n">
-        <v>4975</v>
-      </c>
-      <c r="W266" t="n">
-        <v>5184</v>
-      </c>
-      <c r="X266" t="n">
-        <v>5039</v>
-      </c>
-      <c r="Y266" t="n">
-        <v>4776</v>
-      </c>
       <c r="Z266" t="n">
-        <v>4489</v>
+        <v>4467</v>
       </c>
       <c r="AA266" t="n">
-        <v>4205</v>
+        <v>4157</v>
       </c>
     </row>
     <row r="267">
@@ -22569,76 +22569,159 @@
         <v>28</v>
       </c>
       <c r="D267" t="n">
-        <v>3799</v>
+        <v>3733</v>
       </c>
       <c r="E267" t="n">
-        <v>3577</v>
+        <v>3606</v>
       </c>
       <c r="F267" t="n">
-        <v>3482</v>
+        <v>3549</v>
       </c>
       <c r="G267" t="n">
-        <v>3425</v>
+        <v>3516</v>
       </c>
       <c r="H267" t="n">
-        <v>3450</v>
+        <v>3544</v>
       </c>
       <c r="I267" t="n">
-        <v>3581</v>
+        <v>3697</v>
       </c>
       <c r="J267" t="n">
-        <v>4045</v>
+        <v>4248</v>
       </c>
       <c r="K267" t="n">
-        <v>4425</v>
+        <v>4699</v>
       </c>
       <c r="L267" t="n">
-        <v>4723</v>
+        <v>5046</v>
       </c>
       <c r="M267" t="n">
-        <v>4812</v>
+        <v>5132</v>
       </c>
       <c r="N267" t="n">
-        <v>4790</v>
+        <v>4867</v>
       </c>
       <c r="O267" t="n">
-        <v>4782</v>
+        <v>4766</v>
       </c>
       <c r="P267" t="n">
-        <v>4771</v>
+        <v>4710</v>
       </c>
       <c r="Q267" t="n">
-        <v>4781</v>
+        <v>4700</v>
       </c>
       <c r="R267" t="n">
-        <v>4775</v>
+        <v>4609</v>
       </c>
       <c r="S267" t="n">
-        <v>4768</v>
+        <v>4493</v>
       </c>
       <c r="T267" t="n">
-        <v>4755</v>
+        <v>4437</v>
       </c>
       <c r="U267" t="n">
-        <v>4770</v>
+        <v>4480</v>
       </c>
       <c r="V267" t="n">
-        <v>4958</v>
+        <v>4850</v>
       </c>
       <c r="W267" t="n">
-        <v>5169</v>
+        <v>5255</v>
       </c>
       <c r="X267" t="n">
-        <v>5025</v>
+        <v>5100</v>
       </c>
       <c r="Y267" t="n">
+        <v>4806</v>
+      </c>
+      <c r="Z267" t="n">
+        <v>4483</v>
+      </c>
+      <c r="AA267" t="n">
+        <v>4172</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B268" t="n">
+        <v>10</v>
+      </c>
+      <c r="C268" t="n">
+        <v>29</v>
+      </c>
+      <c r="D268" t="n">
+        <v>3731</v>
+      </c>
+      <c r="E268" t="n">
+        <v>3604</v>
+      </c>
+      <c r="F268" t="n">
+        <v>3547</v>
+      </c>
+      <c r="G268" t="n">
+        <v>3514</v>
+      </c>
+      <c r="H268" t="n">
+        <v>3542</v>
+      </c>
+      <c r="I268" t="n">
+        <v>3695</v>
+      </c>
+      <c r="J268" t="n">
+        <v>4246</v>
+      </c>
+      <c r="K268" t="n">
+        <v>4696</v>
+      </c>
+      <c r="L268" t="n">
+        <v>5042</v>
+      </c>
+      <c r="M268" t="n">
+        <v>5128</v>
+      </c>
+      <c r="N268" t="n">
+        <v>4863</v>
+      </c>
+      <c r="O268" t="n">
         <v>4763</v>
       </c>
-      <c r="Z267" t="n">
-        <v>4477</v>
-      </c>
-      <c r="AA267" t="n">
-        <v>4195</v>
+      <c r="P268" t="n">
+        <v>4707</v>
+      </c>
+      <c r="Q268" t="n">
+        <v>4697</v>
+      </c>
+      <c r="R268" t="n">
+        <v>4605</v>
+      </c>
+      <c r="S268" t="n">
+        <v>4490</v>
+      </c>
+      <c r="T268" t="n">
+        <v>4433</v>
+      </c>
+      <c r="U268" t="n">
+        <v>4476</v>
+      </c>
+      <c r="V268" t="n">
+        <v>4847</v>
+      </c>
+      <c r="W268" t="n">
+        <v>5252</v>
+      </c>
+      <c r="X268" t="n">
+        <v>5097</v>
+      </c>
+      <c r="Y268" t="n">
+        <v>4804</v>
+      </c>
+      <c r="Z268" t="n">
+        <v>4481</v>
+      </c>
+      <c r="AA268" t="n">
+        <v>4170</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA268"/>
+  <dimension ref="A1:AA269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22320,76 +22320,76 @@
         <v>25</v>
       </c>
       <c r="D264" t="n">
-        <v>3612</v>
+        <v>3600</v>
       </c>
       <c r="E264" t="n">
-        <v>3477</v>
+        <v>3455</v>
       </c>
       <c r="F264" t="n">
-        <v>3369</v>
+        <v>3338</v>
       </c>
       <c r="G264" t="n">
-        <v>3347</v>
+        <v>3315</v>
       </c>
       <c r="H264" t="n">
-        <v>3336</v>
+        <v>3303</v>
       </c>
       <c r="I264" t="n">
-        <v>3386</v>
+        <v>3348</v>
       </c>
       <c r="J264" t="n">
-        <v>3569</v>
+        <v>3516</v>
       </c>
       <c r="K264" t="n">
-        <v>3783</v>
+        <v>3711</v>
       </c>
       <c r="L264" t="n">
-        <v>4172</v>
+        <v>4066</v>
       </c>
       <c r="M264" t="n">
-        <v>4444</v>
+        <v>4315</v>
       </c>
       <c r="N264" t="n">
-        <v>4569</v>
+        <v>4429</v>
       </c>
       <c r="O264" t="n">
-        <v>4600</v>
+        <v>4458</v>
       </c>
       <c r="P264" t="n">
-        <v>4520</v>
+        <v>4397</v>
       </c>
       <c r="Q264" t="n">
-        <v>4189</v>
+        <v>4144</v>
       </c>
       <c r="R264" t="n">
-        <v>4093</v>
+        <v>4071</v>
       </c>
       <c r="S264" t="n">
-        <v>4051</v>
+        <v>4039</v>
       </c>
       <c r="T264" t="n">
-        <v>4077</v>
+        <v>4061</v>
       </c>
       <c r="U264" t="n">
-        <v>4280</v>
+        <v>4237</v>
       </c>
       <c r="V264" t="n">
-        <v>4614</v>
+        <v>4526</v>
       </c>
       <c r="W264" t="n">
-        <v>4999</v>
+        <v>4859</v>
       </c>
       <c r="X264" t="n">
-        <v>4875</v>
+        <v>4756</v>
       </c>
       <c r="Y264" t="n">
-        <v>4597</v>
+        <v>4526</v>
       </c>
       <c r="Z264" t="n">
-        <v>4265</v>
+        <v>4250</v>
       </c>
       <c r="AA264" t="n">
-        <v>3982</v>
+        <v>4015</v>
       </c>
     </row>
     <row r="265">
@@ -22403,76 +22403,76 @@
         <v>26</v>
       </c>
       <c r="D265" t="n">
-        <v>3645</v>
+        <v>3656</v>
       </c>
       <c r="E265" t="n">
-        <v>3501</v>
+        <v>3507</v>
       </c>
       <c r="F265" t="n">
-        <v>3431</v>
+        <v>3433</v>
       </c>
       <c r="G265" t="n">
-        <v>3399</v>
+        <v>3395</v>
       </c>
       <c r="H265" t="n">
-        <v>3408</v>
+        <v>3416</v>
       </c>
       <c r="I265" t="n">
-        <v>3578</v>
+        <v>3577</v>
       </c>
       <c r="J265" t="n">
-        <v>4155</v>
+        <v>4157</v>
       </c>
       <c r="K265" t="n">
-        <v>4621</v>
+        <v>4618</v>
       </c>
       <c r="L265" t="n">
-        <v>4978</v>
+        <v>4947</v>
       </c>
       <c r="M265" t="n">
-        <v>5065</v>
+        <v>4972</v>
       </c>
       <c r="N265" t="n">
-        <v>4816</v>
+        <v>4761</v>
       </c>
       <c r="O265" t="n">
-        <v>4742</v>
+        <v>4662</v>
       </c>
       <c r="P265" t="n">
-        <v>4610</v>
+        <v>4542</v>
       </c>
       <c r="Q265" t="n">
-        <v>4620</v>
+        <v>4562</v>
       </c>
       <c r="R265" t="n">
-        <v>4544</v>
+        <v>4527</v>
       </c>
       <c r="S265" t="n">
-        <v>4413</v>
+        <v>4440</v>
       </c>
       <c r="T265" t="n">
-        <v>4368</v>
+        <v>4407</v>
       </c>
       <c r="U265" t="n">
-        <v>4427</v>
+        <v>4449</v>
       </c>
       <c r="V265" t="n">
-        <v>4762</v>
+        <v>4728</v>
       </c>
       <c r="W265" t="n">
-        <v>5198</v>
+        <v>5100</v>
       </c>
       <c r="X265" t="n">
-        <v>5049</v>
+        <v>4994</v>
       </c>
       <c r="Y265" t="n">
-        <v>4739</v>
+        <v>4726</v>
       </c>
       <c r="Z265" t="n">
-        <v>4407</v>
+        <v>4431</v>
       </c>
       <c r="AA265" t="n">
-        <v>4133</v>
+        <v>4195</v>
       </c>
     </row>
     <row r="266">
@@ -22486,76 +22486,76 @@
         <v>27</v>
       </c>
       <c r="D266" t="n">
-        <v>3721</v>
+        <v>3742</v>
       </c>
       <c r="E266" t="n">
-        <v>3592</v>
+        <v>3606</v>
       </c>
       <c r="F266" t="n">
-        <v>3535</v>
+        <v>3539</v>
       </c>
       <c r="G266" t="n">
-        <v>3502</v>
+        <v>3509</v>
       </c>
       <c r="H266" t="n">
-        <v>3529</v>
+        <v>3537</v>
       </c>
       <c r="I266" t="n">
-        <v>3681</v>
+        <v>3672</v>
       </c>
       <c r="J266" t="n">
-        <v>4230</v>
+        <v>4183</v>
       </c>
       <c r="K266" t="n">
-        <v>4678</v>
+        <v>4607</v>
       </c>
       <c r="L266" t="n">
-        <v>5022</v>
+        <v>4940</v>
       </c>
       <c r="M266" t="n">
-        <v>5107</v>
+        <v>5033</v>
       </c>
       <c r="N266" t="n">
-        <v>4842</v>
+        <v>4848</v>
       </c>
       <c r="O266" t="n">
-        <v>4742</v>
+        <v>4765</v>
       </c>
       <c r="P266" t="n">
-        <v>4685</v>
+        <v>4682</v>
       </c>
       <c r="Q266" t="n">
-        <v>4676</v>
+        <v>4626</v>
       </c>
       <c r="R266" t="n">
-        <v>4584</v>
+        <v>4561</v>
       </c>
       <c r="S266" t="n">
-        <v>4468</v>
+        <v>4508</v>
       </c>
       <c r="T266" t="n">
-        <v>4412</v>
+        <v>4470</v>
       </c>
       <c r="U266" t="n">
-        <v>4455</v>
+        <v>4530</v>
       </c>
       <c r="V266" t="n">
-        <v>4827</v>
+        <v>4844</v>
       </c>
       <c r="W266" t="n">
-        <v>5234</v>
+        <v>5154</v>
       </c>
       <c r="X266" t="n">
-        <v>5080</v>
+        <v>5020</v>
       </c>
       <c r="Y266" t="n">
-        <v>4788</v>
+        <v>4768</v>
       </c>
       <c r="Z266" t="n">
-        <v>4467</v>
+        <v>4499</v>
       </c>
       <c r="AA266" t="n">
-        <v>4157</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="267">
@@ -22569,76 +22569,76 @@
         <v>28</v>
       </c>
       <c r="D267" t="n">
-        <v>3733</v>
+        <v>3789</v>
       </c>
       <c r="E267" t="n">
-        <v>3606</v>
+        <v>3660</v>
       </c>
       <c r="F267" t="n">
-        <v>3549</v>
+        <v>3596</v>
       </c>
       <c r="G267" t="n">
-        <v>3516</v>
+        <v>3567</v>
       </c>
       <c r="H267" t="n">
-        <v>3544</v>
+        <v>3596</v>
       </c>
       <c r="I267" t="n">
-        <v>3697</v>
+        <v>3734</v>
       </c>
       <c r="J267" t="n">
-        <v>4248</v>
+        <v>4258</v>
       </c>
       <c r="K267" t="n">
-        <v>4699</v>
+        <v>4693</v>
       </c>
       <c r="L267" t="n">
-        <v>5046</v>
+        <v>5035</v>
       </c>
       <c r="M267" t="n">
-        <v>5132</v>
+        <v>5131</v>
       </c>
       <c r="N267" t="n">
-        <v>4867</v>
+        <v>4947</v>
       </c>
       <c r="O267" t="n">
-        <v>4766</v>
+        <v>4865</v>
       </c>
       <c r="P267" t="n">
-        <v>4710</v>
+        <v>4782</v>
       </c>
       <c r="Q267" t="n">
-        <v>4700</v>
+        <v>4726</v>
       </c>
       <c r="R267" t="n">
+        <v>4662</v>
+      </c>
+      <c r="S267" t="n">
         <v>4609</v>
       </c>
-      <c r="S267" t="n">
-        <v>4493</v>
-      </c>
       <c r="T267" t="n">
-        <v>4437</v>
+        <v>4572</v>
       </c>
       <c r="U267" t="n">
-        <v>4480</v>
+        <v>4630</v>
       </c>
       <c r="V267" t="n">
-        <v>4850</v>
+        <v>4936</v>
       </c>
       <c r="W267" t="n">
-        <v>5255</v>
+        <v>5238</v>
       </c>
       <c r="X267" t="n">
-        <v>5100</v>
+        <v>5101</v>
       </c>
       <c r="Y267" t="n">
-        <v>4806</v>
+        <v>4841</v>
       </c>
       <c r="Z267" t="n">
-        <v>4483</v>
+        <v>4565</v>
       </c>
       <c r="AA267" t="n">
-        <v>4172</v>
+        <v>4289</v>
       </c>
     </row>
     <row r="268">
@@ -22652,76 +22652,159 @@
         <v>29</v>
       </c>
       <c r="D268" t="n">
-        <v>3731</v>
+        <v>3797</v>
       </c>
       <c r="E268" t="n">
-        <v>3604</v>
+        <v>3668</v>
       </c>
       <c r="F268" t="n">
-        <v>3547</v>
+        <v>3605</v>
       </c>
       <c r="G268" t="n">
-        <v>3514</v>
+        <v>3576</v>
       </c>
       <c r="H268" t="n">
-        <v>3542</v>
+        <v>3605</v>
       </c>
       <c r="I268" t="n">
-        <v>3695</v>
+        <v>3744</v>
       </c>
       <c r="J268" t="n">
-        <v>4246</v>
+        <v>4270</v>
       </c>
       <c r="K268" t="n">
-        <v>4696</v>
+        <v>4707</v>
       </c>
       <c r="L268" t="n">
-        <v>5042</v>
+        <v>5050</v>
       </c>
       <c r="M268" t="n">
-        <v>5128</v>
+        <v>5146</v>
       </c>
       <c r="N268" t="n">
-        <v>4863</v>
+        <v>4963</v>
       </c>
       <c r="O268" t="n">
-        <v>4763</v>
+        <v>4880</v>
       </c>
       <c r="P268" t="n">
-        <v>4707</v>
+        <v>4798</v>
       </c>
       <c r="Q268" t="n">
-        <v>4697</v>
+        <v>4742</v>
       </c>
       <c r="R268" t="n">
-        <v>4605</v>
+        <v>4678</v>
       </c>
       <c r="S268" t="n">
-        <v>4490</v>
+        <v>4625</v>
       </c>
       <c r="T268" t="n">
-        <v>4433</v>
+        <v>4588</v>
       </c>
       <c r="U268" t="n">
-        <v>4476</v>
+        <v>4646</v>
       </c>
       <c r="V268" t="n">
-        <v>4847</v>
+        <v>4951</v>
       </c>
       <c r="W268" t="n">
         <v>5252</v>
       </c>
       <c r="X268" t="n">
-        <v>5097</v>
+        <v>5113</v>
       </c>
       <c r="Y268" t="n">
-        <v>4804</v>
+        <v>4853</v>
       </c>
       <c r="Z268" t="n">
-        <v>4481</v>
+        <v>4576</v>
       </c>
       <c r="AA268" t="n">
-        <v>4170</v>
+        <v>4298</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B269" t="n">
+        <v>10</v>
+      </c>
+      <c r="C269" t="n">
+        <v>30</v>
+      </c>
+      <c r="D269" t="n">
+        <v>3788</v>
+      </c>
+      <c r="E269" t="n">
+        <v>3658</v>
+      </c>
+      <c r="F269" t="n">
+        <v>3594</v>
+      </c>
+      <c r="G269" t="n">
+        <v>3565</v>
+      </c>
+      <c r="H269" t="n">
+        <v>3594</v>
+      </c>
+      <c r="I269" t="n">
+        <v>3732</v>
+      </c>
+      <c r="J269" t="n">
+        <v>4256</v>
+      </c>
+      <c r="K269" t="n">
+        <v>4691</v>
+      </c>
+      <c r="L269" t="n">
+        <v>5032</v>
+      </c>
+      <c r="M269" t="n">
+        <v>5128</v>
+      </c>
+      <c r="N269" t="n">
+        <v>4944</v>
+      </c>
+      <c r="O269" t="n">
+        <v>4862</v>
+      </c>
+      <c r="P269" t="n">
+        <v>4779</v>
+      </c>
+      <c r="Q269" t="n">
+        <v>4723</v>
+      </c>
+      <c r="R269" t="n">
+        <v>4659</v>
+      </c>
+      <c r="S269" t="n">
+        <v>4606</v>
+      </c>
+      <c r="T269" t="n">
+        <v>4569</v>
+      </c>
+      <c r="U269" t="n">
+        <v>4620</v>
+      </c>
+      <c r="V269" t="n">
+        <v>4890</v>
+      </c>
+      <c r="W269" t="n">
+        <v>5156</v>
+      </c>
+      <c r="X269" t="n">
+        <v>5023</v>
+      </c>
+      <c r="Y269" t="n">
+        <v>4773</v>
+      </c>
+      <c r="Z269" t="n">
+        <v>4506</v>
+      </c>
+      <c r="AA269" t="n">
+        <v>4239</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA269"/>
+  <dimension ref="A1:AA270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22403,76 +22403,76 @@
         <v>26</v>
       </c>
       <c r="D265" t="n">
-        <v>3656</v>
+        <v>3676</v>
       </c>
       <c r="E265" t="n">
-        <v>3507</v>
+        <v>3516</v>
       </c>
       <c r="F265" t="n">
-        <v>3433</v>
+        <v>3436</v>
       </c>
       <c r="G265" t="n">
         <v>3395</v>
       </c>
       <c r="H265" t="n">
-        <v>3416</v>
+        <v>3412</v>
       </c>
       <c r="I265" t="n">
-        <v>3577</v>
+        <v>3543</v>
       </c>
       <c r="J265" t="n">
-        <v>4157</v>
+        <v>4012</v>
       </c>
       <c r="K265" t="n">
-        <v>4618</v>
+        <v>4386</v>
       </c>
       <c r="L265" t="n">
-        <v>4947</v>
+        <v>4652</v>
       </c>
       <c r="M265" t="n">
-        <v>4972</v>
+        <v>4672</v>
       </c>
       <c r="N265" t="n">
-        <v>4761</v>
+        <v>4517</v>
       </c>
       <c r="O265" t="n">
-        <v>4662</v>
+        <v>4444</v>
       </c>
       <c r="P265" t="n">
-        <v>4542</v>
+        <v>4356</v>
       </c>
       <c r="Q265" t="n">
-        <v>4562</v>
+        <v>4371</v>
       </c>
       <c r="R265" t="n">
-        <v>4527</v>
+        <v>4345</v>
       </c>
       <c r="S265" t="n">
-        <v>4440</v>
+        <v>4281</v>
       </c>
       <c r="T265" t="n">
-        <v>4407</v>
+        <v>4257</v>
       </c>
       <c r="U265" t="n">
-        <v>4449</v>
+        <v>4299</v>
       </c>
       <c r="V265" t="n">
-        <v>4728</v>
+        <v>4578</v>
       </c>
       <c r="W265" t="n">
-        <v>5100</v>
+        <v>4950</v>
       </c>
       <c r="X265" t="n">
-        <v>4994</v>
+        <v>4850</v>
       </c>
       <c r="Y265" t="n">
-        <v>4726</v>
+        <v>4597</v>
       </c>
       <c r="Z265" t="n">
-        <v>4431</v>
+        <v>4318</v>
       </c>
       <c r="AA265" t="n">
-        <v>4195</v>
+        <v>4095</v>
       </c>
     </row>
     <row r="266">
@@ -22486,76 +22486,76 @@
         <v>27</v>
       </c>
       <c r="D266" t="n">
-        <v>3742</v>
+        <v>3762</v>
       </c>
       <c r="E266" t="n">
-        <v>3606</v>
+        <v>3615</v>
       </c>
       <c r="F266" t="n">
-        <v>3539</v>
+        <v>3542</v>
       </c>
       <c r="G266" t="n">
         <v>3509</v>
       </c>
       <c r="H266" t="n">
-        <v>3537</v>
+        <v>3532</v>
       </c>
       <c r="I266" t="n">
-        <v>3672</v>
+        <v>3640</v>
       </c>
       <c r="J266" t="n">
-        <v>4183</v>
+        <v>4050</v>
       </c>
       <c r="K266" t="n">
-        <v>4607</v>
+        <v>4391</v>
       </c>
       <c r="L266" t="n">
-        <v>4940</v>
+        <v>4658</v>
       </c>
       <c r="M266" t="n">
-        <v>5033</v>
+        <v>4733</v>
       </c>
       <c r="N266" t="n">
-        <v>4848</v>
+        <v>4597</v>
       </c>
       <c r="O266" t="n">
-        <v>4765</v>
+        <v>4537</v>
       </c>
       <c r="P266" t="n">
-        <v>4682</v>
+        <v>4476</v>
       </c>
       <c r="Q266" t="n">
-        <v>4626</v>
+        <v>4434</v>
       </c>
       <c r="R266" t="n">
-        <v>4561</v>
+        <v>4387</v>
       </c>
       <c r="S266" t="n">
-        <v>4508</v>
+        <v>4348</v>
       </c>
       <c r="T266" t="n">
-        <v>4470</v>
+        <v>4320</v>
       </c>
       <c r="U266" t="n">
-        <v>4530</v>
+        <v>4380</v>
       </c>
       <c r="V266" t="n">
-        <v>4844</v>
+        <v>4694</v>
       </c>
       <c r="W266" t="n">
-        <v>5154</v>
+        <v>5004</v>
       </c>
       <c r="X266" t="n">
-        <v>5020</v>
+        <v>4877</v>
       </c>
       <c r="Y266" t="n">
-        <v>4768</v>
+        <v>4639</v>
       </c>
       <c r="Z266" t="n">
-        <v>4499</v>
+        <v>4385</v>
       </c>
       <c r="AA266" t="n">
-        <v>4231</v>
+        <v>4131</v>
       </c>
     </row>
     <row r="267">
@@ -22569,76 +22569,76 @@
         <v>28</v>
       </c>
       <c r="D267" t="n">
-        <v>3789</v>
+        <v>3809</v>
       </c>
       <c r="E267" t="n">
-        <v>3660</v>
+        <v>3668</v>
       </c>
       <c r="F267" t="n">
-        <v>3596</v>
+        <v>3598</v>
       </c>
       <c r="G267" t="n">
         <v>3567</v>
       </c>
       <c r="H267" t="n">
-        <v>3596</v>
+        <v>3590</v>
       </c>
       <c r="I267" t="n">
-        <v>3734</v>
+        <v>3702</v>
       </c>
       <c r="J267" t="n">
-        <v>4258</v>
+        <v>4125</v>
       </c>
       <c r="K267" t="n">
-        <v>4693</v>
+        <v>4477</v>
       </c>
       <c r="L267" t="n">
-        <v>5035</v>
+        <v>4753</v>
       </c>
       <c r="M267" t="n">
-        <v>5131</v>
+        <v>4831</v>
       </c>
       <c r="N267" t="n">
-        <v>4947</v>
+        <v>4696</v>
       </c>
       <c r="O267" t="n">
-        <v>4865</v>
+        <v>4636</v>
       </c>
       <c r="P267" t="n">
-        <v>4782</v>
+        <v>4576</v>
       </c>
       <c r="Q267" t="n">
-        <v>4726</v>
+        <v>4535</v>
       </c>
       <c r="R267" t="n">
-        <v>4662</v>
+        <v>4488</v>
       </c>
       <c r="S267" t="n">
-        <v>4609</v>
+        <v>4449</v>
       </c>
       <c r="T267" t="n">
-        <v>4572</v>
+        <v>4422</v>
       </c>
       <c r="U267" t="n">
-        <v>4630</v>
+        <v>4480</v>
       </c>
       <c r="V267" t="n">
-        <v>4936</v>
+        <v>4786</v>
       </c>
       <c r="W267" t="n">
-        <v>5238</v>
+        <v>5088</v>
       </c>
       <c r="X267" t="n">
-        <v>5101</v>
+        <v>4958</v>
       </c>
       <c r="Y267" t="n">
-        <v>4841</v>
+        <v>4712</v>
       </c>
       <c r="Z267" t="n">
-        <v>4565</v>
+        <v>4451</v>
       </c>
       <c r="AA267" t="n">
-        <v>4289</v>
+        <v>4189</v>
       </c>
     </row>
     <row r="268">
@@ -22652,76 +22652,76 @@
         <v>29</v>
       </c>
       <c r="D268" t="n">
-        <v>3797</v>
+        <v>3817</v>
       </c>
       <c r="E268" t="n">
-        <v>3668</v>
+        <v>3677</v>
       </c>
       <c r="F268" t="n">
-        <v>3605</v>
+        <v>3607</v>
       </c>
       <c r="G268" t="n">
         <v>3576</v>
       </c>
       <c r="H268" t="n">
-        <v>3605</v>
+        <v>3600</v>
       </c>
       <c r="I268" t="n">
-        <v>3744</v>
+        <v>3712</v>
       </c>
       <c r="J268" t="n">
-        <v>4270</v>
+        <v>4137</v>
       </c>
       <c r="K268" t="n">
-        <v>4707</v>
+        <v>4491</v>
       </c>
       <c r="L268" t="n">
-        <v>5050</v>
+        <v>4769</v>
       </c>
       <c r="M268" t="n">
-        <v>5146</v>
+        <v>4846</v>
       </c>
       <c r="N268" t="n">
-        <v>4963</v>
+        <v>4712</v>
       </c>
       <c r="O268" t="n">
-        <v>4880</v>
+        <v>4652</v>
       </c>
       <c r="P268" t="n">
-        <v>4798</v>
+        <v>4591</v>
       </c>
       <c r="Q268" t="n">
-        <v>4742</v>
+        <v>4551</v>
       </c>
       <c r="R268" t="n">
-        <v>4678</v>
+        <v>4504</v>
       </c>
       <c r="S268" t="n">
-        <v>4625</v>
+        <v>4465</v>
       </c>
       <c r="T268" t="n">
-        <v>4588</v>
+        <v>4438</v>
       </c>
       <c r="U268" t="n">
-        <v>4646</v>
+        <v>4496</v>
       </c>
       <c r="V268" t="n">
-        <v>4951</v>
+        <v>4801</v>
       </c>
       <c r="W268" t="n">
-        <v>5252</v>
+        <v>5102</v>
       </c>
       <c r="X268" t="n">
-        <v>5113</v>
+        <v>4971</v>
       </c>
       <c r="Y268" t="n">
-        <v>4853</v>
+        <v>4724</v>
       </c>
       <c r="Z268" t="n">
-        <v>4576</v>
+        <v>4461</v>
       </c>
       <c r="AA268" t="n">
-        <v>4298</v>
+        <v>4198</v>
       </c>
     </row>
     <row r="269">
@@ -22735,76 +22735,159 @@
         <v>30</v>
       </c>
       <c r="D269" t="n">
-        <v>3788</v>
+        <v>3808</v>
       </c>
       <c r="E269" t="n">
-        <v>3658</v>
+        <v>3667</v>
       </c>
       <c r="F269" t="n">
-        <v>3594</v>
+        <v>3597</v>
       </c>
       <c r="G269" t="n">
         <v>3565</v>
       </c>
       <c r="H269" t="n">
-        <v>3594</v>
+        <v>3589</v>
       </c>
       <c r="I269" t="n">
-        <v>3732</v>
+        <v>3700</v>
       </c>
       <c r="J269" t="n">
-        <v>4256</v>
+        <v>4123</v>
       </c>
       <c r="K269" t="n">
-        <v>4691</v>
+        <v>4475</v>
       </c>
       <c r="L269" t="n">
-        <v>5032</v>
+        <v>4751</v>
       </c>
       <c r="M269" t="n">
-        <v>5128</v>
+        <v>4828</v>
       </c>
       <c r="N269" t="n">
-        <v>4944</v>
+        <v>4693</v>
       </c>
       <c r="O269" t="n">
-        <v>4862</v>
+        <v>4633</v>
       </c>
       <c r="P269" t="n">
-        <v>4779</v>
+        <v>4573</v>
       </c>
       <c r="Q269" t="n">
-        <v>4723</v>
+        <v>4532</v>
       </c>
       <c r="R269" t="n">
-        <v>4659</v>
+        <v>4485</v>
       </c>
       <c r="S269" t="n">
-        <v>4606</v>
+        <v>4446</v>
       </c>
       <c r="T269" t="n">
-        <v>4569</v>
+        <v>4419</v>
       </c>
       <c r="U269" t="n">
-        <v>4620</v>
+        <v>4470</v>
       </c>
       <c r="V269" t="n">
-        <v>4890</v>
+        <v>4740</v>
       </c>
       <c r="W269" t="n">
-        <v>5156</v>
+        <v>5006</v>
       </c>
       <c r="X269" t="n">
-        <v>5023</v>
+        <v>4880</v>
       </c>
       <c r="Y269" t="n">
-        <v>4773</v>
+        <v>4644</v>
       </c>
       <c r="Z269" t="n">
-        <v>4506</v>
+        <v>4391</v>
       </c>
       <c r="AA269" t="n">
-        <v>4239</v>
+        <v>4139</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B270" t="n">
+        <v>10</v>
+      </c>
+      <c r="C270" t="n">
+        <v>31</v>
+      </c>
+      <c r="D270" t="n">
+        <v>3791</v>
+      </c>
+      <c r="E270" t="n">
+        <v>3634</v>
+      </c>
+      <c r="F270" t="n">
+        <v>3552</v>
+      </c>
+      <c r="G270" t="n">
+        <v>3501</v>
+      </c>
+      <c r="H270" t="n">
+        <v>3495</v>
+      </c>
+      <c r="I270" t="n">
+        <v>3547</v>
+      </c>
+      <c r="J270" t="n">
+        <v>3701</v>
+      </c>
+      <c r="K270" t="n">
+        <v>3967</v>
+      </c>
+      <c r="L270" t="n">
+        <v>4305</v>
+      </c>
+      <c r="M270" t="n">
+        <v>4498</v>
+      </c>
+      <c r="N270" t="n">
+        <v>4498</v>
+      </c>
+      <c r="O270" t="n">
+        <v>4400</v>
+      </c>
+      <c r="P270" t="n">
+        <v>4303</v>
+      </c>
+      <c r="Q270" t="n">
+        <v>4282</v>
+      </c>
+      <c r="R270" t="n">
+        <v>4241</v>
+      </c>
+      <c r="S270" t="n">
+        <v>4176</v>
+      </c>
+      <c r="T270" t="n">
+        <v>4208</v>
+      </c>
+      <c r="U270" t="n">
+        <v>4378</v>
+      </c>
+      <c r="V270" t="n">
+        <v>4618</v>
+      </c>
+      <c r="W270" t="n">
+        <v>4798</v>
+      </c>
+      <c r="X270" t="n">
+        <v>4641</v>
+      </c>
+      <c r="Y270" t="n">
+        <v>4414</v>
+      </c>
+      <c r="Z270" t="n">
+        <v>4195</v>
+      </c>
+      <c r="AA270" t="n">
+        <v>4033</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA270"/>
+  <dimension ref="A1:AA271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22486,76 +22486,76 @@
         <v>27</v>
       </c>
       <c r="D266" t="n">
-        <v>3762</v>
+        <v>3827</v>
       </c>
       <c r="E266" t="n">
-        <v>3615</v>
+        <v>3586</v>
       </c>
       <c r="F266" t="n">
-        <v>3542</v>
+        <v>3471</v>
       </c>
       <c r="G266" t="n">
-        <v>3509</v>
+        <v>3421</v>
       </c>
       <c r="H266" t="n">
-        <v>3532</v>
+        <v>3445</v>
       </c>
       <c r="I266" t="n">
-        <v>3640</v>
+        <v>3562</v>
       </c>
       <c r="J266" t="n">
-        <v>4050</v>
+        <v>4013</v>
       </c>
       <c r="K266" t="n">
-        <v>4391</v>
+        <v>4395</v>
       </c>
       <c r="L266" t="n">
-        <v>4658</v>
+        <v>4681</v>
       </c>
       <c r="M266" t="n">
-        <v>4733</v>
+        <v>4742</v>
       </c>
       <c r="N266" t="n">
-        <v>4597</v>
+        <v>4649</v>
       </c>
       <c r="O266" t="n">
-        <v>4537</v>
+        <v>4606</v>
       </c>
       <c r="P266" t="n">
-        <v>4476</v>
+        <v>4563</v>
       </c>
       <c r="Q266" t="n">
-        <v>4434</v>
+        <v>4535</v>
       </c>
       <c r="R266" t="n">
-        <v>4387</v>
+        <v>4509</v>
       </c>
       <c r="S266" t="n">
-        <v>4348</v>
+        <v>4484</v>
       </c>
       <c r="T266" t="n">
-        <v>4320</v>
+        <v>4481</v>
       </c>
       <c r="U266" t="n">
-        <v>4380</v>
+        <v>4542</v>
       </c>
       <c r="V266" t="n">
-        <v>4694</v>
+        <v>4833</v>
       </c>
       <c r="W266" t="n">
-        <v>5004</v>
+        <v>5107</v>
       </c>
       <c r="X266" t="n">
-        <v>4877</v>
+        <v>4966</v>
       </c>
       <c r="Y266" t="n">
-        <v>4639</v>
+        <v>4703</v>
       </c>
       <c r="Z266" t="n">
-        <v>4385</v>
+        <v>4425</v>
       </c>
       <c r="AA266" t="n">
-        <v>4131</v>
+        <v>4145</v>
       </c>
     </row>
     <row r="267">
@@ -22569,76 +22569,76 @@
         <v>28</v>
       </c>
       <c r="D267" t="n">
-        <v>3809</v>
+        <v>3859</v>
       </c>
       <c r="E267" t="n">
-        <v>3668</v>
+        <v>3622</v>
       </c>
       <c r="F267" t="n">
-        <v>3598</v>
+        <v>3509</v>
       </c>
       <c r="G267" t="n">
-        <v>3567</v>
+        <v>3460</v>
       </c>
       <c r="H267" t="n">
-        <v>3590</v>
+        <v>3485</v>
       </c>
       <c r="I267" t="n">
-        <v>3702</v>
+        <v>3605</v>
       </c>
       <c r="J267" t="n">
-        <v>4125</v>
+        <v>4064</v>
       </c>
       <c r="K267" t="n">
-        <v>4477</v>
+        <v>4454</v>
       </c>
       <c r="L267" t="n">
+        <v>4746</v>
+      </c>
+      <c r="M267" t="n">
+        <v>4809</v>
+      </c>
+      <c r="N267" t="n">
+        <v>4716</v>
+      </c>
+      <c r="O267" t="n">
+        <v>4673</v>
+      </c>
+      <c r="P267" t="n">
+        <v>4631</v>
+      </c>
+      <c r="Q267" t="n">
+        <v>4604</v>
+      </c>
+      <c r="R267" t="n">
+        <v>4578</v>
+      </c>
+      <c r="S267" t="n">
+        <v>4553</v>
+      </c>
+      <c r="T267" t="n">
+        <v>4550</v>
+      </c>
+      <c r="U267" t="n">
+        <v>4610</v>
+      </c>
+      <c r="V267" t="n">
+        <v>4895</v>
+      </c>
+      <c r="W267" t="n">
+        <v>5165</v>
+      </c>
+      <c r="X267" t="n">
+        <v>5021</v>
+      </c>
+      <c r="Y267" t="n">
         <v>4753</v>
       </c>
-      <c r="M267" t="n">
-        <v>4831</v>
-      </c>
-      <c r="N267" t="n">
-        <v>4696</v>
-      </c>
-      <c r="O267" t="n">
-        <v>4636</v>
-      </c>
-      <c r="P267" t="n">
-        <v>4576</v>
-      </c>
-      <c r="Q267" t="n">
-        <v>4535</v>
-      </c>
-      <c r="R267" t="n">
-        <v>4488</v>
-      </c>
-      <c r="S267" t="n">
-        <v>4449</v>
-      </c>
-      <c r="T267" t="n">
-        <v>4422</v>
-      </c>
-      <c r="U267" t="n">
-        <v>4480</v>
-      </c>
-      <c r="V267" t="n">
-        <v>4786</v>
-      </c>
-      <c r="W267" t="n">
-        <v>5088</v>
-      </c>
-      <c r="X267" t="n">
-        <v>4958</v>
-      </c>
-      <c r="Y267" t="n">
-        <v>4712</v>
-      </c>
       <c r="Z267" t="n">
-        <v>4451</v>
+        <v>4470</v>
       </c>
       <c r="AA267" t="n">
-        <v>4189</v>
+        <v>4185</v>
       </c>
     </row>
     <row r="268">
@@ -22652,76 +22652,76 @@
         <v>29</v>
       </c>
       <c r="D268" t="n">
-        <v>3817</v>
+        <v>3837</v>
       </c>
       <c r="E268" t="n">
-        <v>3677</v>
+        <v>3597</v>
       </c>
       <c r="F268" t="n">
-        <v>3607</v>
+        <v>3483</v>
       </c>
       <c r="G268" t="n">
-        <v>3576</v>
+        <v>3433</v>
       </c>
       <c r="H268" t="n">
-        <v>3600</v>
+        <v>3458</v>
       </c>
       <c r="I268" t="n">
-        <v>3712</v>
+        <v>3575</v>
       </c>
       <c r="J268" t="n">
-        <v>4137</v>
+        <v>4029</v>
       </c>
       <c r="K268" t="n">
-        <v>4491</v>
+        <v>4413</v>
       </c>
       <c r="L268" t="n">
-        <v>4769</v>
+        <v>4701</v>
       </c>
       <c r="M268" t="n">
-        <v>4846</v>
+        <v>4763</v>
       </c>
       <c r="N268" t="n">
-        <v>4712</v>
+        <v>4669</v>
       </c>
       <c r="O268" t="n">
-        <v>4652</v>
+        <v>4626</v>
       </c>
       <c r="P268" t="n">
-        <v>4591</v>
+        <v>4584</v>
       </c>
       <c r="Q268" t="n">
-        <v>4551</v>
+        <v>4556</v>
       </c>
       <c r="R268" t="n">
-        <v>4504</v>
+        <v>4530</v>
       </c>
       <c r="S268" t="n">
-        <v>4465</v>
+        <v>4505</v>
       </c>
       <c r="T268" t="n">
-        <v>4438</v>
+        <v>4502</v>
       </c>
       <c r="U268" t="n">
-        <v>4496</v>
+        <v>4563</v>
       </c>
       <c r="V268" t="n">
-        <v>4801</v>
+        <v>4852</v>
       </c>
       <c r="W268" t="n">
-        <v>5102</v>
+        <v>5125</v>
       </c>
       <c r="X268" t="n">
-        <v>4971</v>
+        <v>4983</v>
       </c>
       <c r="Y268" t="n">
-        <v>4724</v>
+        <v>4719</v>
       </c>
       <c r="Z268" t="n">
-        <v>4461</v>
+        <v>4439</v>
       </c>
       <c r="AA268" t="n">
-        <v>4198</v>
+        <v>4157</v>
       </c>
     </row>
     <row r="269">
@@ -22735,76 +22735,76 @@
         <v>30</v>
       </c>
       <c r="D269" t="n">
-        <v>3808</v>
+        <v>3823</v>
       </c>
       <c r="E269" t="n">
-        <v>3667</v>
+        <v>3582</v>
       </c>
       <c r="F269" t="n">
-        <v>3597</v>
+        <v>3466</v>
       </c>
       <c r="G269" t="n">
-        <v>3565</v>
+        <v>3416</v>
       </c>
       <c r="H269" t="n">
-        <v>3589</v>
+        <v>3441</v>
       </c>
       <c r="I269" t="n">
-        <v>3700</v>
+        <v>3557</v>
       </c>
       <c r="J269" t="n">
-        <v>4123</v>
+        <v>4007</v>
       </c>
       <c r="K269" t="n">
-        <v>4475</v>
+        <v>4388</v>
       </c>
       <c r="L269" t="n">
-        <v>4751</v>
+        <v>4673</v>
       </c>
       <c r="M269" t="n">
-        <v>4828</v>
+        <v>4734</v>
       </c>
       <c r="N269" t="n">
-        <v>4693</v>
+        <v>4641</v>
       </c>
       <c r="O269" t="n">
-        <v>4633</v>
+        <v>4597</v>
       </c>
       <c r="P269" t="n">
-        <v>4573</v>
+        <v>4555</v>
       </c>
       <c r="Q269" t="n">
-        <v>4532</v>
+        <v>4527</v>
       </c>
       <c r="R269" t="n">
-        <v>4485</v>
+        <v>4501</v>
       </c>
       <c r="S269" t="n">
-        <v>4446</v>
+        <v>4476</v>
       </c>
       <c r="T269" t="n">
-        <v>4419</v>
+        <v>4473</v>
       </c>
       <c r="U269" t="n">
-        <v>4470</v>
+        <v>4526</v>
       </c>
       <c r="V269" t="n">
-        <v>4740</v>
+        <v>4780</v>
       </c>
       <c r="W269" t="n">
-        <v>5006</v>
+        <v>5020</v>
       </c>
       <c r="X269" t="n">
-        <v>4880</v>
+        <v>4884</v>
       </c>
       <c r="Y269" t="n">
-        <v>4644</v>
+        <v>4631</v>
       </c>
       <c r="Z269" t="n">
-        <v>4391</v>
+        <v>4362</v>
       </c>
       <c r="AA269" t="n">
-        <v>4139</v>
+        <v>4093</v>
       </c>
     </row>
     <row r="270">
@@ -22818,76 +22818,159 @@
         <v>31</v>
       </c>
       <c r="D270" t="n">
-        <v>3791</v>
+        <v>3809</v>
       </c>
       <c r="E270" t="n">
-        <v>3634</v>
+        <v>3542</v>
       </c>
       <c r="F270" t="n">
-        <v>3552</v>
+        <v>3397</v>
       </c>
       <c r="G270" t="n">
-        <v>3501</v>
+        <v>3348</v>
       </c>
       <c r="H270" t="n">
-        <v>3495</v>
+        <v>3350</v>
       </c>
       <c r="I270" t="n">
-        <v>3547</v>
+        <v>3393</v>
       </c>
       <c r="J270" t="n">
-        <v>3701</v>
+        <v>3596</v>
       </c>
       <c r="K270" t="n">
-        <v>3967</v>
+        <v>3881</v>
       </c>
       <c r="L270" t="n">
-        <v>4305</v>
+        <v>4248</v>
       </c>
       <c r="M270" t="n">
-        <v>4498</v>
+        <v>4409</v>
       </c>
       <c r="N270" t="n">
-        <v>4498</v>
+        <v>4407</v>
       </c>
       <c r="O270" t="n">
-        <v>4400</v>
+        <v>4378</v>
       </c>
       <c r="P270" t="n">
-        <v>4303</v>
+        <v>4345</v>
       </c>
       <c r="Q270" t="n">
-        <v>4282</v>
+        <v>4285</v>
       </c>
       <c r="R270" t="n">
-        <v>4241</v>
+        <v>4271</v>
       </c>
       <c r="S270" t="n">
-        <v>4176</v>
+        <v>4234</v>
       </c>
       <c r="T270" t="n">
-        <v>4208</v>
+        <v>4249</v>
       </c>
       <c r="U270" t="n">
-        <v>4378</v>
+        <v>4415</v>
       </c>
       <c r="V270" t="n">
-        <v>4618</v>
+        <v>4645</v>
       </c>
       <c r="W270" t="n">
-        <v>4798</v>
+        <v>4816</v>
       </c>
       <c r="X270" t="n">
-        <v>4641</v>
+        <v>4637</v>
       </c>
       <c r="Y270" t="n">
-        <v>4414</v>
+        <v>4386</v>
       </c>
       <c r="Z270" t="n">
-        <v>4195</v>
+        <v>4126</v>
       </c>
       <c r="AA270" t="n">
-        <v>4033</v>
+        <v>3989</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B271" t="n">
+        <v>11</v>
+      </c>
+      <c r="C271" t="n">
+        <v>1</v>
+      </c>
+      <c r="D271" t="n">
+        <v>3736</v>
+      </c>
+      <c r="E271" t="n">
+        <v>3515</v>
+      </c>
+      <c r="F271" t="n">
+        <v>3373</v>
+      </c>
+      <c r="G271" t="n">
+        <v>3302</v>
+      </c>
+      <c r="H271" t="n">
+        <v>3283</v>
+      </c>
+      <c r="I271" t="n">
+        <v>3327</v>
+      </c>
+      <c r="J271" t="n">
+        <v>3486</v>
+      </c>
+      <c r="K271" t="n">
+        <v>3672</v>
+      </c>
+      <c r="L271" t="n">
+        <v>4011</v>
+      </c>
+      <c r="M271" t="n">
+        <v>4249</v>
+      </c>
+      <c r="N271" t="n">
+        <v>4357</v>
+      </c>
+      <c r="O271" t="n">
+        <v>4384</v>
+      </c>
+      <c r="P271" t="n">
+        <v>4369</v>
+      </c>
+      <c r="Q271" t="n">
+        <v>4304</v>
+      </c>
+      <c r="R271" t="n">
+        <v>4286</v>
+      </c>
+      <c r="S271" t="n">
+        <v>4277</v>
+      </c>
+      <c r="T271" t="n">
+        <v>4297</v>
+      </c>
+      <c r="U271" t="n">
+        <v>4456</v>
+      </c>
+      <c r="V271" t="n">
+        <v>4716</v>
+      </c>
+      <c r="W271" t="n">
+        <v>5016</v>
+      </c>
+      <c r="X271" t="n">
+        <v>4900</v>
+      </c>
+      <c r="Y271" t="n">
+        <v>4640</v>
+      </c>
+      <c r="Z271" t="n">
+        <v>4329</v>
+      </c>
+      <c r="AA271" t="n">
+        <v>4064</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA271"/>
+  <dimension ref="A1:AA272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22569,76 +22569,76 @@
         <v>28</v>
       </c>
       <c r="D267" t="n">
-        <v>3859</v>
+        <v>3639</v>
       </c>
       <c r="E267" t="n">
-        <v>3622</v>
+        <v>3489</v>
       </c>
       <c r="F267" t="n">
-        <v>3509</v>
+        <v>3417</v>
       </c>
       <c r="G267" t="n">
-        <v>3460</v>
+        <v>3385</v>
       </c>
       <c r="H267" t="n">
-        <v>3485</v>
+        <v>3405</v>
       </c>
       <c r="I267" t="n">
-        <v>3605</v>
+        <v>3516</v>
       </c>
       <c r="J267" t="n">
-        <v>4064</v>
+        <v>3940</v>
       </c>
       <c r="K267" t="n">
-        <v>4454</v>
+        <v>4309</v>
       </c>
       <c r="L267" t="n">
-        <v>4746</v>
+        <v>4587</v>
       </c>
       <c r="M267" t="n">
-        <v>4809</v>
+        <v>4664</v>
       </c>
       <c r="N267" t="n">
-        <v>4716</v>
+        <v>4558</v>
       </c>
       <c r="O267" t="n">
-        <v>4673</v>
+        <v>4494</v>
       </c>
       <c r="P267" t="n">
-        <v>4631</v>
+        <v>4419</v>
       </c>
       <c r="Q267" t="n">
-        <v>4604</v>
+        <v>4422</v>
       </c>
       <c r="R267" t="n">
-        <v>4578</v>
+        <v>4382</v>
       </c>
       <c r="S267" t="n">
-        <v>4553</v>
+        <v>4336</v>
       </c>
       <c r="T267" t="n">
-        <v>4550</v>
+        <v>4320</v>
       </c>
       <c r="U267" t="n">
-        <v>4610</v>
+        <v>4372</v>
       </c>
       <c r="V267" t="n">
-        <v>4895</v>
+        <v>4627</v>
       </c>
       <c r="W267" t="n">
-        <v>5165</v>
+        <v>4864</v>
       </c>
       <c r="X267" t="n">
-        <v>5021</v>
+        <v>4723</v>
       </c>
       <c r="Y267" t="n">
-        <v>4753</v>
+        <v>4476</v>
       </c>
       <c r="Z267" t="n">
-        <v>4470</v>
+        <v>4214</v>
       </c>
       <c r="AA267" t="n">
-        <v>4185</v>
+        <v>3963</v>
       </c>
     </row>
     <row r="268">
@@ -22652,76 +22652,76 @@
         <v>29</v>
       </c>
       <c r="D268" t="n">
-        <v>3837</v>
+        <v>3590</v>
       </c>
       <c r="E268" t="n">
-        <v>3597</v>
+        <v>3434</v>
       </c>
       <c r="F268" t="n">
-        <v>3483</v>
+        <v>3359</v>
       </c>
       <c r="G268" t="n">
-        <v>3433</v>
+        <v>3325</v>
       </c>
       <c r="H268" t="n">
-        <v>3458</v>
+        <v>3345</v>
       </c>
       <c r="I268" t="n">
-        <v>3575</v>
+        <v>3452</v>
       </c>
       <c r="J268" t="n">
-        <v>4029</v>
+        <v>3863</v>
       </c>
       <c r="K268" t="n">
-        <v>4413</v>
+        <v>4220</v>
       </c>
       <c r="L268" t="n">
-        <v>4701</v>
+        <v>4488</v>
       </c>
       <c r="M268" t="n">
-        <v>4763</v>
+        <v>4563</v>
       </c>
       <c r="N268" t="n">
-        <v>4669</v>
+        <v>4456</v>
       </c>
       <c r="O268" t="n">
-        <v>4626</v>
+        <v>4391</v>
       </c>
       <c r="P268" t="n">
-        <v>4584</v>
+        <v>4316</v>
       </c>
       <c r="Q268" t="n">
-        <v>4556</v>
+        <v>4319</v>
       </c>
       <c r="R268" t="n">
-        <v>4530</v>
+        <v>4278</v>
       </c>
       <c r="S268" t="n">
-        <v>4505</v>
+        <v>4232</v>
       </c>
       <c r="T268" t="n">
-        <v>4502</v>
+        <v>4215</v>
       </c>
       <c r="U268" t="n">
-        <v>4563</v>
+        <v>4269</v>
       </c>
       <c r="V268" t="n">
-        <v>4852</v>
+        <v>4532</v>
       </c>
       <c r="W268" t="n">
-        <v>5125</v>
+        <v>4776</v>
       </c>
       <c r="X268" t="n">
-        <v>4983</v>
+        <v>4640</v>
       </c>
       <c r="Y268" t="n">
-        <v>4719</v>
+        <v>4400</v>
       </c>
       <c r="Z268" t="n">
-        <v>4439</v>
+        <v>4147</v>
       </c>
       <c r="AA268" t="n">
-        <v>4157</v>
+        <v>3904</v>
       </c>
     </row>
     <row r="269">
@@ -22735,76 +22735,76 @@
         <v>30</v>
       </c>
       <c r="D269" t="n">
+        <v>3563</v>
+      </c>
+      <c r="E269" t="n">
+        <v>3404</v>
+      </c>
+      <c r="F269" t="n">
+        <v>3327</v>
+      </c>
+      <c r="G269" t="n">
+        <v>3292</v>
+      </c>
+      <c r="H269" t="n">
+        <v>3311</v>
+      </c>
+      <c r="I269" t="n">
+        <v>3417</v>
+      </c>
+      <c r="J269" t="n">
+        <v>3820</v>
+      </c>
+      <c r="K269" t="n">
+        <v>4171</v>
+      </c>
+      <c r="L269" t="n">
+        <v>4434</v>
+      </c>
+      <c r="M269" t="n">
+        <v>4508</v>
+      </c>
+      <c r="N269" t="n">
+        <v>4400</v>
+      </c>
+      <c r="O269" t="n">
+        <v>4335</v>
+      </c>
+      <c r="P269" t="n">
+        <v>4259</v>
+      </c>
+      <c r="Q269" t="n">
+        <v>4262</v>
+      </c>
+      <c r="R269" t="n">
+        <v>4221</v>
+      </c>
+      <c r="S269" t="n">
+        <v>4174</v>
+      </c>
+      <c r="T269" t="n">
+        <v>4158</v>
+      </c>
+      <c r="U269" t="n">
+        <v>4204</v>
+      </c>
+      <c r="V269" t="n">
+        <v>4435</v>
+      </c>
+      <c r="W269" t="n">
+        <v>4648</v>
+      </c>
+      <c r="X269" t="n">
+        <v>4519</v>
+      </c>
+      <c r="Y269" t="n">
+        <v>4292</v>
+      </c>
+      <c r="Z269" t="n">
+        <v>4052</v>
+      </c>
+      <c r="AA269" t="n">
         <v>3823</v>
-      </c>
-      <c r="E269" t="n">
-        <v>3582</v>
-      </c>
-      <c r="F269" t="n">
-        <v>3466</v>
-      </c>
-      <c r="G269" t="n">
-        <v>3416</v>
-      </c>
-      <c r="H269" t="n">
-        <v>3441</v>
-      </c>
-      <c r="I269" t="n">
-        <v>3557</v>
-      </c>
-      <c r="J269" t="n">
-        <v>4007</v>
-      </c>
-      <c r="K269" t="n">
-        <v>4388</v>
-      </c>
-      <c r="L269" t="n">
-        <v>4673</v>
-      </c>
-      <c r="M269" t="n">
-        <v>4734</v>
-      </c>
-      <c r="N269" t="n">
-        <v>4641</v>
-      </c>
-      <c r="O269" t="n">
-        <v>4597</v>
-      </c>
-      <c r="P269" t="n">
-        <v>4555</v>
-      </c>
-      <c r="Q269" t="n">
-        <v>4527</v>
-      </c>
-      <c r="R269" t="n">
-        <v>4501</v>
-      </c>
-      <c r="S269" t="n">
-        <v>4476</v>
-      </c>
-      <c r="T269" t="n">
-        <v>4473</v>
-      </c>
-      <c r="U269" t="n">
-        <v>4526</v>
-      </c>
-      <c r="V269" t="n">
-        <v>4780</v>
-      </c>
-      <c r="W269" t="n">
-        <v>5020</v>
-      </c>
-      <c r="X269" t="n">
-        <v>4884</v>
-      </c>
-      <c r="Y269" t="n">
-        <v>4631</v>
-      </c>
-      <c r="Z269" t="n">
-        <v>4362</v>
-      </c>
-      <c r="AA269" t="n">
-        <v>4093</v>
       </c>
     </row>
     <row r="270">
@@ -22818,76 +22818,76 @@
         <v>31</v>
       </c>
       <c r="D270" t="n">
-        <v>3809</v>
+        <v>3553</v>
       </c>
       <c r="E270" t="n">
-        <v>3542</v>
+        <v>3373</v>
       </c>
       <c r="F270" t="n">
-        <v>3397</v>
+        <v>3282</v>
       </c>
       <c r="G270" t="n">
-        <v>3348</v>
+        <v>3244</v>
       </c>
       <c r="H270" t="n">
-        <v>3350</v>
+        <v>3230</v>
       </c>
       <c r="I270" t="n">
-        <v>3393</v>
+        <v>3273</v>
       </c>
       <c r="J270" t="n">
-        <v>3596</v>
+        <v>3442</v>
       </c>
       <c r="K270" t="n">
-        <v>3881</v>
+        <v>3679</v>
       </c>
       <c r="L270" t="n">
-        <v>4248</v>
+        <v>4003</v>
       </c>
       <c r="M270" t="n">
-        <v>4409</v>
+        <v>4191</v>
       </c>
       <c r="N270" t="n">
-        <v>4407</v>
+        <v>4171</v>
       </c>
       <c r="O270" t="n">
-        <v>4378</v>
+        <v>4107</v>
       </c>
       <c r="P270" t="n">
-        <v>4345</v>
+        <v>4047</v>
       </c>
       <c r="Q270" t="n">
-        <v>4285</v>
+        <v>4017</v>
       </c>
       <c r="R270" t="n">
-        <v>4271</v>
+        <v>3975</v>
       </c>
       <c r="S270" t="n">
-        <v>4234</v>
+        <v>3928</v>
       </c>
       <c r="T270" t="n">
-        <v>4249</v>
+        <v>3944</v>
       </c>
       <c r="U270" t="n">
-        <v>4415</v>
+        <v>4082</v>
       </c>
       <c r="V270" t="n">
-        <v>4645</v>
+        <v>4297</v>
       </c>
       <c r="W270" t="n">
-        <v>4816</v>
+        <v>4452</v>
       </c>
       <c r="X270" t="n">
-        <v>4637</v>
+        <v>4304</v>
       </c>
       <c r="Y270" t="n">
-        <v>4386</v>
+        <v>4086</v>
       </c>
       <c r="Z270" t="n">
-        <v>4126</v>
+        <v>3883</v>
       </c>
       <c r="AA270" t="n">
-        <v>3989</v>
+        <v>3725</v>
       </c>
     </row>
     <row r="271">
@@ -22901,76 +22901,159 @@
         <v>1</v>
       </c>
       <c r="D271" t="n">
-        <v>3736</v>
+        <v>3541</v>
       </c>
       <c r="E271" t="n">
-        <v>3515</v>
+        <v>3382</v>
       </c>
       <c r="F271" t="n">
-        <v>3373</v>
+        <v>3283</v>
       </c>
       <c r="G271" t="n">
-        <v>3302</v>
+        <v>3228</v>
       </c>
       <c r="H271" t="n">
-        <v>3283</v>
+        <v>3233</v>
       </c>
       <c r="I271" t="n">
-        <v>3327</v>
+        <v>3304</v>
       </c>
       <c r="J271" t="n">
-        <v>3486</v>
+        <v>3488</v>
       </c>
       <c r="K271" t="n">
-        <v>3672</v>
+        <v>3686</v>
       </c>
       <c r="L271" t="n">
-        <v>4011</v>
+        <v>3928</v>
       </c>
       <c r="M271" t="n">
-        <v>4249</v>
+        <v>4089</v>
       </c>
       <c r="N271" t="n">
-        <v>4357</v>
+        <v>4145</v>
       </c>
       <c r="O271" t="n">
-        <v>4384</v>
+        <v>4218</v>
       </c>
       <c r="P271" t="n">
-        <v>4369</v>
+        <v>4186</v>
       </c>
       <c r="Q271" t="n">
-        <v>4304</v>
+        <v>4130</v>
       </c>
       <c r="R271" t="n">
-        <v>4286</v>
+        <v>4017</v>
       </c>
       <c r="S271" t="n">
-        <v>4277</v>
+        <v>4046</v>
       </c>
       <c r="T271" t="n">
-        <v>4297</v>
+        <v>4216</v>
       </c>
       <c r="U271" t="n">
-        <v>4456</v>
+        <v>4474</v>
       </c>
       <c r="V271" t="n">
-        <v>4716</v>
+        <v>4659</v>
       </c>
       <c r="W271" t="n">
-        <v>5016</v>
+        <v>4701</v>
       </c>
       <c r="X271" t="n">
-        <v>4900</v>
+        <v>4719</v>
       </c>
       <c r="Y271" t="n">
-        <v>4640</v>
+        <v>4443</v>
       </c>
       <c r="Z271" t="n">
-        <v>4329</v>
+        <v>4135</v>
       </c>
       <c r="AA271" t="n">
-        <v>4064</v>
+        <v>3867</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B272" t="n">
+        <v>11</v>
+      </c>
+      <c r="C272" t="n">
+        <v>2</v>
+      </c>
+      <c r="D272" t="n">
+        <v>3618</v>
+      </c>
+      <c r="E272" t="n">
+        <v>3459</v>
+      </c>
+      <c r="F272" t="n">
+        <v>3379</v>
+      </c>
+      <c r="G272" t="n">
+        <v>3339</v>
+      </c>
+      <c r="H272" t="n">
+        <v>3357</v>
+      </c>
+      <c r="I272" t="n">
+        <v>3500</v>
+      </c>
+      <c r="J272" t="n">
+        <v>4014</v>
+      </c>
+      <c r="K272" t="n">
+        <v>4423</v>
+      </c>
+      <c r="L272" t="n">
+        <v>4714</v>
+      </c>
+      <c r="M272" t="n">
+        <v>4736</v>
+      </c>
+      <c r="N272" t="n">
+        <v>4608</v>
+      </c>
+      <c r="O272" t="n">
+        <v>4547</v>
+      </c>
+      <c r="P272" t="n">
+        <v>4474</v>
+      </c>
+      <c r="Q272" t="n">
+        <v>4487</v>
+      </c>
+      <c r="R272" t="n">
+        <v>4465</v>
+      </c>
+      <c r="S272" t="n">
+        <v>4412</v>
+      </c>
+      <c r="T272" t="n">
+        <v>4392</v>
+      </c>
+      <c r="U272" t="n">
+        <v>4427</v>
+      </c>
+      <c r="V272" t="n">
+        <v>4661</v>
+      </c>
+      <c r="W272" t="n">
+        <v>4974</v>
+      </c>
+      <c r="X272" t="n">
+        <v>4867</v>
+      </c>
+      <c r="Y272" t="n">
+        <v>4599</v>
+      </c>
+      <c r="Z272" t="n">
+        <v>4303</v>
+      </c>
+      <c r="AA272" t="n">
+        <v>4067</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA272"/>
+  <dimension ref="A1:AA273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22652,76 +22652,76 @@
         <v>29</v>
       </c>
       <c r="D268" t="n">
-        <v>3590</v>
+        <v>3620</v>
       </c>
       <c r="E268" t="n">
-        <v>3434</v>
+        <v>3509</v>
       </c>
       <c r="F268" t="n">
-        <v>3359</v>
+        <v>3448</v>
       </c>
       <c r="G268" t="n">
-        <v>3325</v>
+        <v>3422</v>
       </c>
       <c r="H268" t="n">
-        <v>3345</v>
+        <v>3453</v>
       </c>
       <c r="I268" t="n">
-        <v>3452</v>
+        <v>3592</v>
       </c>
       <c r="J268" t="n">
-        <v>3863</v>
+        <v>4122</v>
       </c>
       <c r="K268" t="n">
-        <v>4220</v>
+        <v>4584</v>
       </c>
       <c r="L268" t="n">
-        <v>4488</v>
+        <v>4934</v>
       </c>
       <c r="M268" t="n">
-        <v>4563</v>
+        <v>5023</v>
       </c>
       <c r="N268" t="n">
-        <v>4456</v>
+        <v>4990</v>
       </c>
       <c r="O268" t="n">
-        <v>4391</v>
+        <v>4970</v>
       </c>
       <c r="P268" t="n">
-        <v>4316</v>
+        <v>4947</v>
       </c>
       <c r="Q268" t="n">
-        <v>4319</v>
+        <v>4942</v>
       </c>
       <c r="R268" t="n">
-        <v>4278</v>
+        <v>4925</v>
       </c>
       <c r="S268" t="n">
-        <v>4232</v>
+        <v>4914</v>
       </c>
       <c r="T268" t="n">
-        <v>4215</v>
+        <v>4913</v>
       </c>
       <c r="U268" t="n">
-        <v>4269</v>
+        <v>4948</v>
       </c>
       <c r="V268" t="n">
-        <v>4532</v>
+        <v>5128</v>
       </c>
       <c r="W268" t="n">
-        <v>4776</v>
+        <v>5296</v>
       </c>
       <c r="X268" t="n">
-        <v>4640</v>
+        <v>5106</v>
       </c>
       <c r="Y268" t="n">
-        <v>4400</v>
+        <v>4754</v>
       </c>
       <c r="Z268" t="n">
-        <v>4147</v>
+        <v>4372</v>
       </c>
       <c r="AA268" t="n">
-        <v>3904</v>
+        <v>4017</v>
       </c>
     </row>
     <row r="269">
@@ -22735,76 +22735,76 @@
         <v>30</v>
       </c>
       <c r="D269" t="n">
-        <v>3563</v>
+        <v>3592</v>
       </c>
       <c r="E269" t="n">
-        <v>3404</v>
+        <v>3478</v>
       </c>
       <c r="F269" t="n">
-        <v>3327</v>
+        <v>3414</v>
       </c>
       <c r="G269" t="n">
-        <v>3292</v>
+        <v>3388</v>
       </c>
       <c r="H269" t="n">
-        <v>3311</v>
+        <v>3418</v>
       </c>
       <c r="I269" t="n">
-        <v>3417</v>
+        <v>3555</v>
       </c>
       <c r="J269" t="n">
-        <v>3820</v>
+        <v>4077</v>
       </c>
       <c r="K269" t="n">
-        <v>4171</v>
+        <v>4532</v>
       </c>
       <c r="L269" t="n">
-        <v>4434</v>
+        <v>4877</v>
       </c>
       <c r="M269" t="n">
-        <v>4508</v>
+        <v>4965</v>
       </c>
       <c r="N269" t="n">
-        <v>4400</v>
+        <v>4932</v>
       </c>
       <c r="O269" t="n">
-        <v>4335</v>
+        <v>4911</v>
       </c>
       <c r="P269" t="n">
-        <v>4259</v>
+        <v>4887</v>
       </c>
       <c r="Q269" t="n">
-        <v>4262</v>
+        <v>4882</v>
       </c>
       <c r="R269" t="n">
-        <v>4221</v>
+        <v>4865</v>
       </c>
       <c r="S269" t="n">
-        <v>4174</v>
+        <v>4854</v>
       </c>
       <c r="T269" t="n">
-        <v>4158</v>
+        <v>4853</v>
       </c>
       <c r="U269" t="n">
-        <v>4204</v>
+        <v>4881</v>
       </c>
       <c r="V269" t="n">
-        <v>4435</v>
+        <v>5029</v>
       </c>
       <c r="W269" t="n">
-        <v>4648</v>
+        <v>5166</v>
       </c>
       <c r="X269" t="n">
-        <v>4519</v>
+        <v>4982</v>
       </c>
       <c r="Y269" t="n">
-        <v>4292</v>
+        <v>4644</v>
       </c>
       <c r="Z269" t="n">
-        <v>4052</v>
+        <v>4277</v>
       </c>
       <c r="AA269" t="n">
-        <v>3823</v>
+        <v>3935</v>
       </c>
     </row>
     <row r="270">
@@ -22818,76 +22818,76 @@
         <v>31</v>
       </c>
       <c r="D270" t="n">
-        <v>3553</v>
+        <v>3573</v>
       </c>
       <c r="E270" t="n">
+        <v>3429</v>
+      </c>
+      <c r="F270" t="n">
+        <v>3356</v>
+      </c>
+      <c r="G270" t="n">
+        <v>3325</v>
+      </c>
+      <c r="H270" t="n">
+        <v>3314</v>
+      </c>
+      <c r="I270" t="n">
         <v>3373</v>
       </c>
-      <c r="F270" t="n">
-        <v>3282</v>
-      </c>
-      <c r="G270" t="n">
-        <v>3244</v>
-      </c>
-      <c r="H270" t="n">
-        <v>3230</v>
-      </c>
-      <c r="I270" t="n">
-        <v>3273</v>
-      </c>
       <c r="J270" t="n">
-        <v>3442</v>
+        <v>3605</v>
       </c>
       <c r="K270" t="n">
-        <v>3679</v>
+        <v>3929</v>
       </c>
       <c r="L270" t="n">
-        <v>4003</v>
+        <v>4371</v>
       </c>
       <c r="M270" t="n">
-        <v>4191</v>
+        <v>4629</v>
       </c>
       <c r="N270" t="n">
-        <v>4171</v>
+        <v>4627</v>
       </c>
       <c r="O270" t="n">
-        <v>4107</v>
+        <v>4621</v>
       </c>
       <c r="P270" t="n">
-        <v>4047</v>
+        <v>4616</v>
       </c>
       <c r="Q270" t="n">
-        <v>4017</v>
+        <v>4613</v>
       </c>
       <c r="R270" t="n">
-        <v>3975</v>
+        <v>4609</v>
       </c>
       <c r="S270" t="n">
-        <v>3928</v>
+        <v>4605</v>
       </c>
       <c r="T270" t="n">
-        <v>3944</v>
+        <v>4615</v>
       </c>
       <c r="U270" t="n">
-        <v>4082</v>
+        <v>4707</v>
       </c>
       <c r="V270" t="n">
-        <v>4297</v>
+        <v>4850</v>
       </c>
       <c r="W270" t="n">
-        <v>4452</v>
+        <v>4953</v>
       </c>
       <c r="X270" t="n">
-        <v>4304</v>
+        <v>4723</v>
       </c>
       <c r="Y270" t="n">
-        <v>4086</v>
+        <v>4386</v>
       </c>
       <c r="Z270" t="n">
-        <v>3883</v>
+        <v>4071</v>
       </c>
       <c r="AA270" t="n">
-        <v>3725</v>
+        <v>3826</v>
       </c>
     </row>
     <row r="271">
@@ -22901,76 +22901,76 @@
         <v>1</v>
       </c>
       <c r="D271" t="n">
-        <v>3541</v>
+        <v>3572</v>
       </c>
       <c r="E271" t="n">
-        <v>3382</v>
+        <v>3447</v>
       </c>
       <c r="F271" t="n">
-        <v>3283</v>
+        <v>3376</v>
       </c>
       <c r="G271" t="n">
-        <v>3228</v>
+        <v>3327</v>
       </c>
       <c r="H271" t="n">
-        <v>3233</v>
+        <v>3322</v>
       </c>
       <c r="I271" t="n">
-        <v>3304</v>
+        <v>3417</v>
       </c>
       <c r="J271" t="n">
-        <v>3488</v>
+        <v>3653</v>
       </c>
       <c r="K271" t="n">
-        <v>3686</v>
+        <v>3913</v>
       </c>
       <c r="L271" t="n">
-        <v>3928</v>
+        <v>4269</v>
       </c>
       <c r="M271" t="n">
-        <v>4089</v>
+        <v>4539</v>
       </c>
       <c r="N271" t="n">
-        <v>4145</v>
+        <v>4635</v>
       </c>
       <c r="O271" t="n">
-        <v>4218</v>
+        <v>4665</v>
       </c>
       <c r="P271" t="n">
-        <v>4186</v>
+        <v>4690</v>
       </c>
       <c r="Q271" t="n">
-        <v>4130</v>
+        <v>4697</v>
       </c>
       <c r="R271" t="n">
-        <v>4017</v>
+        <v>4701</v>
       </c>
       <c r="S271" t="n">
-        <v>4046</v>
+        <v>4735</v>
       </c>
       <c r="T271" t="n">
-        <v>4216</v>
+        <v>4806</v>
       </c>
       <c r="U271" t="n">
-        <v>4474</v>
+        <v>4978</v>
       </c>
       <c r="V271" t="n">
-        <v>4659</v>
+        <v>5155</v>
       </c>
       <c r="W271" t="n">
-        <v>4701</v>
+        <v>5233</v>
       </c>
       <c r="X271" t="n">
-        <v>4719</v>
+        <v>5030</v>
       </c>
       <c r="Y271" t="n">
-        <v>4443</v>
+        <v>4693</v>
       </c>
       <c r="Z271" t="n">
-        <v>4135</v>
+        <v>4324</v>
       </c>
       <c r="AA271" t="n">
-        <v>3867</v>
+        <v>3980</v>
       </c>
     </row>
     <row r="272">
@@ -22984,76 +22984,159 @@
         <v>2</v>
       </c>
       <c r="D272" t="n">
-        <v>3618</v>
+        <v>3681</v>
       </c>
       <c r="E272" t="n">
-        <v>3459</v>
+        <v>3550</v>
       </c>
       <c r="F272" t="n">
-        <v>3379</v>
+        <v>3492</v>
       </c>
       <c r="G272" t="n">
-        <v>3339</v>
+        <v>3466</v>
       </c>
       <c r="H272" t="n">
-        <v>3357</v>
+        <v>3498</v>
       </c>
       <c r="I272" t="n">
-        <v>3500</v>
+        <v>3667</v>
       </c>
       <c r="J272" t="n">
-        <v>4014</v>
+        <v>4232</v>
       </c>
       <c r="K272" t="n">
-        <v>4423</v>
+        <v>4733</v>
       </c>
       <c r="L272" t="n">
-        <v>4714</v>
+        <v>5100</v>
       </c>
       <c r="M272" t="n">
-        <v>4736</v>
+        <v>5215</v>
       </c>
       <c r="N272" t="n">
-        <v>4608</v>
+        <v>5161</v>
       </c>
       <c r="O272" t="n">
-        <v>4547</v>
+        <v>5156</v>
       </c>
       <c r="P272" t="n">
-        <v>4474</v>
+        <v>5126</v>
       </c>
       <c r="Q272" t="n">
-        <v>4487</v>
+        <v>5149</v>
       </c>
       <c r="R272" t="n">
-        <v>4465</v>
+        <v>5138</v>
       </c>
       <c r="S272" t="n">
-        <v>4412</v>
+        <v>5119</v>
       </c>
       <c r="T272" t="n">
-        <v>4392</v>
+        <v>5110</v>
       </c>
       <c r="U272" t="n">
-        <v>4427</v>
+        <v>5203</v>
       </c>
       <c r="V272" t="n">
-        <v>4661</v>
+        <v>5404</v>
       </c>
       <c r="W272" t="n">
-        <v>4974</v>
+        <v>5523</v>
       </c>
       <c r="X272" t="n">
-        <v>4867</v>
+        <v>5296</v>
       </c>
       <c r="Y272" t="n">
-        <v>4599</v>
+        <v>4933</v>
       </c>
       <c r="Z272" t="n">
-        <v>4303</v>
+        <v>4557</v>
       </c>
       <c r="AA272" t="n">
-        <v>4067</v>
+        <v>4215</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B273" t="n">
+        <v>11</v>
+      </c>
+      <c r="C273" t="n">
+        <v>3</v>
+      </c>
+      <c r="D273" t="n">
+        <v>3760</v>
+      </c>
+      <c r="E273" t="n">
+        <v>3653</v>
+      </c>
+      <c r="F273" t="n">
+        <v>3593</v>
+      </c>
+      <c r="G273" t="n">
+        <v>3568</v>
+      </c>
+      <c r="H273" t="n">
+        <v>3600</v>
+      </c>
+      <c r="I273" t="n">
+        <v>3745</v>
+      </c>
+      <c r="J273" t="n">
+        <v>4297</v>
+      </c>
+      <c r="K273" t="n">
+        <v>4779</v>
+      </c>
+      <c r="L273" t="n">
+        <v>5144</v>
+      </c>
+      <c r="M273" t="n">
+        <v>5237</v>
+      </c>
+      <c r="N273" t="n">
+        <v>5206</v>
+      </c>
+      <c r="O273" t="n">
+        <v>5187</v>
+      </c>
+      <c r="P273" t="n">
+        <v>5165</v>
+      </c>
+      <c r="Q273" t="n">
+        <v>5161</v>
+      </c>
+      <c r="R273" t="n">
+        <v>5146</v>
+      </c>
+      <c r="S273" t="n">
+        <v>5135</v>
+      </c>
+      <c r="T273" t="n">
+        <v>5134</v>
+      </c>
+      <c r="U273" t="n">
+        <v>5171</v>
+      </c>
+      <c r="V273" t="n">
+        <v>5367</v>
+      </c>
+      <c r="W273" t="n">
+        <v>5549</v>
+      </c>
+      <c r="X273" t="n">
+        <v>5354</v>
+      </c>
+      <c r="Y273" t="n">
+        <v>4994</v>
+      </c>
+      <c r="Z273" t="n">
+        <v>4604</v>
+      </c>
+      <c r="AA273" t="n">
+        <v>4241</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA273"/>
+  <dimension ref="A1:AA274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22735,76 +22735,76 @@
         <v>30</v>
       </c>
       <c r="D269" t="n">
-        <v>3592</v>
+        <v>3765</v>
       </c>
       <c r="E269" t="n">
-        <v>3478</v>
+        <v>3590</v>
       </c>
       <c r="F269" t="n">
-        <v>3414</v>
+        <v>3502</v>
       </c>
       <c r="G269" t="n">
-        <v>3388</v>
+        <v>3468</v>
       </c>
       <c r="H269" t="n">
-        <v>3418</v>
+        <v>3501</v>
       </c>
       <c r="I269" t="n">
-        <v>3555</v>
+        <v>3637</v>
       </c>
       <c r="J269" t="n">
-        <v>4077</v>
+        <v>4117</v>
       </c>
       <c r="K269" t="n">
-        <v>4532</v>
+        <v>4541</v>
       </c>
       <c r="L269" t="n">
-        <v>4877</v>
+        <v>4861</v>
       </c>
       <c r="M269" t="n">
-        <v>4965</v>
+        <v>4946</v>
       </c>
       <c r="N269" t="n">
-        <v>4932</v>
+        <v>4928</v>
       </c>
       <c r="O269" t="n">
-        <v>4911</v>
+        <v>4918</v>
       </c>
       <c r="P269" t="n">
+        <v>4903</v>
+      </c>
+      <c r="Q269" t="n">
+        <v>4903</v>
+      </c>
+      <c r="R269" t="n">
+        <v>4894</v>
+      </c>
+      <c r="S269" t="n">
         <v>4887</v>
       </c>
-      <c r="Q269" t="n">
-        <v>4882</v>
-      </c>
-      <c r="R269" t="n">
-        <v>4865</v>
-      </c>
-      <c r="S269" t="n">
-        <v>4854</v>
-      </c>
       <c r="T269" t="n">
-        <v>4853</v>
+        <v>4890</v>
       </c>
       <c r="U269" t="n">
-        <v>4881</v>
+        <v>4961</v>
       </c>
       <c r="V269" t="n">
-        <v>5029</v>
+        <v>5198</v>
       </c>
       <c r="W269" t="n">
-        <v>5166</v>
+        <v>5377</v>
       </c>
       <c r="X269" t="n">
-        <v>4982</v>
+        <v>5188</v>
       </c>
       <c r="Y269" t="n">
-        <v>4644</v>
+        <v>4857</v>
       </c>
       <c r="Z269" t="n">
-        <v>4277</v>
+        <v>4501</v>
       </c>
       <c r="AA269" t="n">
-        <v>3935</v>
+        <v>4154</v>
       </c>
     </row>
     <row r="270">
@@ -22818,76 +22818,76 @@
         <v>31</v>
       </c>
       <c r="D270" t="n">
-        <v>3573</v>
+        <v>3738</v>
       </c>
       <c r="E270" t="n">
-        <v>3429</v>
+        <v>3533</v>
       </c>
       <c r="F270" t="n">
-        <v>3356</v>
+        <v>3431</v>
       </c>
       <c r="G270" t="n">
-        <v>3325</v>
+        <v>3409</v>
       </c>
       <c r="H270" t="n">
-        <v>3314</v>
+        <v>3385</v>
       </c>
       <c r="I270" t="n">
-        <v>3373</v>
+        <v>3430</v>
       </c>
       <c r="J270" t="n">
-        <v>3605</v>
+        <v>3673</v>
       </c>
       <c r="K270" t="n">
-        <v>3929</v>
+        <v>3946</v>
       </c>
       <c r="L270" t="n">
-        <v>4371</v>
+        <v>4354</v>
       </c>
       <c r="M270" t="n">
+        <v>4596</v>
+      </c>
+      <c r="N270" t="n">
+        <v>4600</v>
+      </c>
+      <c r="O270" t="n">
+        <v>4606</v>
+      </c>
+      <c r="P270" t="n">
+        <v>4611</v>
+      </c>
+      <c r="Q270" t="n">
+        <v>4615</v>
+      </c>
+      <c r="R270" t="n">
+        <v>4620</v>
+      </c>
+      <c r="S270" t="n">
+        <v>4625</v>
+      </c>
+      <c r="T270" t="n">
         <v>4629</v>
       </c>
-      <c r="N270" t="n">
-        <v>4627</v>
-      </c>
-      <c r="O270" t="n">
-        <v>4621</v>
-      </c>
-      <c r="P270" t="n">
-        <v>4616</v>
-      </c>
-      <c r="Q270" t="n">
-        <v>4613</v>
-      </c>
-      <c r="R270" t="n">
-        <v>4609</v>
-      </c>
-      <c r="S270" t="n">
-        <v>4605</v>
-      </c>
-      <c r="T270" t="n">
-        <v>4615</v>
-      </c>
       <c r="U270" t="n">
-        <v>4707</v>
+        <v>4765</v>
       </c>
       <c r="V270" t="n">
-        <v>4850</v>
+        <v>4992</v>
       </c>
       <c r="W270" t="n">
-        <v>4953</v>
+        <v>5152</v>
       </c>
       <c r="X270" t="n">
-        <v>4723</v>
+        <v>4926</v>
       </c>
       <c r="Y270" t="n">
-        <v>4386</v>
+        <v>4589</v>
       </c>
       <c r="Z270" t="n">
-        <v>4071</v>
+        <v>4286</v>
       </c>
       <c r="AA270" t="n">
-        <v>3826</v>
+        <v>4036</v>
       </c>
     </row>
     <row r="271">
@@ -22901,76 +22901,76 @@
         <v>1</v>
       </c>
       <c r="D271" t="n">
-        <v>3572</v>
+        <v>3736</v>
       </c>
       <c r="E271" t="n">
-        <v>3447</v>
+        <v>3563</v>
       </c>
       <c r="F271" t="n">
-        <v>3376</v>
+        <v>3467</v>
       </c>
       <c r="G271" t="n">
-        <v>3327</v>
+        <v>3399</v>
       </c>
       <c r="H271" t="n">
-        <v>3322</v>
+        <v>3391</v>
       </c>
       <c r="I271" t="n">
-        <v>3417</v>
+        <v>3479</v>
       </c>
       <c r="J271" t="n">
-        <v>3653</v>
+        <v>3697</v>
       </c>
       <c r="K271" t="n">
-        <v>3913</v>
+        <v>3937</v>
       </c>
       <c r="L271" t="n">
-        <v>4269</v>
+        <v>4265</v>
       </c>
       <c r="M271" t="n">
-        <v>4539</v>
+        <v>4514</v>
       </c>
       <c r="N271" t="n">
-        <v>4635</v>
+        <v>4603</v>
       </c>
       <c r="O271" t="n">
-        <v>4665</v>
+        <v>4630</v>
       </c>
       <c r="P271" t="n">
-        <v>4690</v>
+        <v>4692</v>
       </c>
       <c r="Q271" t="n">
-        <v>4697</v>
+        <v>4710</v>
       </c>
       <c r="R271" t="n">
-        <v>4701</v>
+        <v>4720</v>
       </c>
       <c r="S271" t="n">
-        <v>4735</v>
+        <v>4765</v>
       </c>
       <c r="T271" t="n">
-        <v>4806</v>
+        <v>4860</v>
       </c>
       <c r="U271" t="n">
-        <v>4978</v>
+        <v>5090</v>
       </c>
       <c r="V271" t="n">
-        <v>5155</v>
+        <v>5326</v>
       </c>
       <c r="W271" t="n">
-        <v>5233</v>
+        <v>5430</v>
       </c>
       <c r="X271" t="n">
-        <v>5030</v>
+        <v>5228</v>
       </c>
       <c r="Y271" t="n">
-        <v>4693</v>
+        <v>4894</v>
       </c>
       <c r="Z271" t="n">
-        <v>4324</v>
+        <v>4529</v>
       </c>
       <c r="AA271" t="n">
-        <v>3980</v>
+        <v>4188</v>
       </c>
     </row>
     <row r="272">
@@ -22984,76 +22984,76 @@
         <v>2</v>
       </c>
       <c r="D272" t="n">
-        <v>3681</v>
+        <v>3869</v>
       </c>
       <c r="E272" t="n">
-        <v>3550</v>
+        <v>3682</v>
       </c>
       <c r="F272" t="n">
-        <v>3492</v>
+        <v>3599</v>
       </c>
       <c r="G272" t="n">
-        <v>3466</v>
+        <v>3562</v>
       </c>
       <c r="H272" t="n">
-        <v>3498</v>
+        <v>3592</v>
       </c>
       <c r="I272" t="n">
-        <v>3667</v>
+        <v>3751</v>
       </c>
       <c r="J272" t="n">
-        <v>4232</v>
+        <v>4281</v>
       </c>
       <c r="K272" t="n">
-        <v>4733</v>
+        <v>4752</v>
       </c>
       <c r="L272" t="n">
-        <v>5100</v>
+        <v>5097</v>
       </c>
       <c r="M272" t="n">
-        <v>5215</v>
+        <v>5205</v>
       </c>
       <c r="N272" t="n">
-        <v>5161</v>
+        <v>5179</v>
       </c>
       <c r="O272" t="n">
-        <v>5156</v>
+        <v>5177</v>
       </c>
       <c r="P272" t="n">
-        <v>5126</v>
+        <v>5163</v>
       </c>
       <c r="Q272" t="n">
-        <v>5149</v>
+        <v>5174</v>
       </c>
       <c r="R272" t="n">
-        <v>5138</v>
+        <v>5168</v>
       </c>
       <c r="S272" t="n">
-        <v>5119</v>
+        <v>5159</v>
       </c>
       <c r="T272" t="n">
-        <v>5110</v>
+        <v>5155</v>
       </c>
       <c r="U272" t="n">
-        <v>5203</v>
+        <v>5289</v>
       </c>
       <c r="V272" t="n">
-        <v>5404</v>
+        <v>5577</v>
       </c>
       <c r="W272" t="n">
+        <v>5748</v>
+      </c>
+      <c r="X272" t="n">
         <v>5523</v>
       </c>
-      <c r="X272" t="n">
-        <v>5296</v>
-      </c>
       <c r="Y272" t="n">
-        <v>4933</v>
+        <v>5163</v>
       </c>
       <c r="Z272" t="n">
-        <v>4557</v>
+        <v>4790</v>
       </c>
       <c r="AA272" t="n">
-        <v>4215</v>
+        <v>4451</v>
       </c>
     </row>
     <row r="273">
@@ -23067,76 +23067,159 @@
         <v>3</v>
       </c>
       <c r="D273" t="n">
-        <v>3760</v>
+        <v>4001</v>
       </c>
       <c r="E273" t="n">
-        <v>3653</v>
+        <v>3835</v>
       </c>
       <c r="F273" t="n">
-        <v>3593</v>
+        <v>3751</v>
       </c>
       <c r="G273" t="n">
-        <v>3568</v>
+        <v>3719</v>
       </c>
       <c r="H273" t="n">
-        <v>3600</v>
+        <v>3753</v>
       </c>
       <c r="I273" t="n">
-        <v>3745</v>
+        <v>3897</v>
       </c>
       <c r="J273" t="n">
-        <v>4297</v>
+        <v>4403</v>
       </c>
       <c r="K273" t="n">
-        <v>4779</v>
+        <v>4850</v>
       </c>
       <c r="L273" t="n">
-        <v>5144</v>
+        <v>5188</v>
       </c>
       <c r="M273" t="n">
-        <v>5237</v>
+        <v>5278</v>
       </c>
       <c r="N273" t="n">
-        <v>5206</v>
+        <v>5260</v>
       </c>
       <c r="O273" t="n">
-        <v>5187</v>
+        <v>5250</v>
       </c>
       <c r="P273" t="n">
-        <v>5165</v>
+        <v>5236</v>
       </c>
       <c r="Q273" t="n">
-        <v>5161</v>
+        <v>5236</v>
       </c>
       <c r="R273" t="n">
-        <v>5146</v>
+        <v>5227</v>
       </c>
       <c r="S273" t="n">
-        <v>5135</v>
+        <v>5221</v>
       </c>
       <c r="T273" t="n">
-        <v>5134</v>
+        <v>5225</v>
       </c>
       <c r="U273" t="n">
-        <v>5171</v>
+        <v>5312</v>
       </c>
       <c r="V273" t="n">
-        <v>5367</v>
+        <v>5609</v>
       </c>
       <c r="W273" t="n">
-        <v>5549</v>
+        <v>5832</v>
       </c>
       <c r="X273" t="n">
-        <v>5354</v>
+        <v>5632</v>
       </c>
       <c r="Y273" t="n">
-        <v>4994</v>
+        <v>5281</v>
       </c>
       <c r="Z273" t="n">
-        <v>4604</v>
+        <v>4903</v>
       </c>
       <c r="AA273" t="n">
-        <v>4241</v>
+        <v>4534</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B274" t="n">
+        <v>11</v>
+      </c>
+      <c r="C274" t="n">
+        <v>4</v>
+      </c>
+      <c r="D274" t="n">
+        <v>4039</v>
+      </c>
+      <c r="E274" t="n">
+        <v>3873</v>
+      </c>
+      <c r="F274" t="n">
+        <v>3790</v>
+      </c>
+      <c r="G274" t="n">
+        <v>3758</v>
+      </c>
+      <c r="H274" t="n">
+        <v>3793</v>
+      </c>
+      <c r="I274" t="n">
+        <v>3936</v>
+      </c>
+      <c r="J274" t="n">
+        <v>4442</v>
+      </c>
+      <c r="K274" t="n">
+        <v>4888</v>
+      </c>
+      <c r="L274" t="n">
+        <v>5225</v>
+      </c>
+      <c r="M274" t="n">
+        <v>5314</v>
+      </c>
+      <c r="N274" t="n">
+        <v>5296</v>
+      </c>
+      <c r="O274" t="n">
+        <v>5285</v>
+      </c>
+      <c r="P274" t="n">
+        <v>5270</v>
+      </c>
+      <c r="Q274" t="n">
+        <v>5269</v>
+      </c>
+      <c r="R274" t="n">
+        <v>5260</v>
+      </c>
+      <c r="S274" t="n">
+        <v>5253</v>
+      </c>
+      <c r="T274" t="n">
+        <v>5257</v>
+      </c>
+      <c r="U274" t="n">
+        <v>5347</v>
+      </c>
+      <c r="V274" t="n">
+        <v>5648</v>
+      </c>
+      <c r="W274" t="n">
+        <v>5875</v>
+      </c>
+      <c r="X274" t="n">
+        <v>5675</v>
+      </c>
+      <c r="Y274" t="n">
+        <v>5323</v>
+      </c>
+      <c r="Z274" t="n">
+        <v>4945</v>
+      </c>
+      <c r="AA274" t="n">
+        <v>4576</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA274"/>
+  <dimension ref="A1:AA275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22818,76 +22818,76 @@
         <v>31</v>
       </c>
       <c r="D270" t="n">
-        <v>3738</v>
+        <v>3900</v>
       </c>
       <c r="E270" t="n">
-        <v>3533</v>
+        <v>3745</v>
       </c>
       <c r="F270" t="n">
-        <v>3431</v>
+        <v>3668</v>
       </c>
       <c r="G270" t="n">
-        <v>3409</v>
+        <v>3652</v>
       </c>
       <c r="H270" t="n">
-        <v>3385</v>
+        <v>3634</v>
       </c>
       <c r="I270" t="n">
-        <v>3430</v>
+        <v>3675</v>
       </c>
       <c r="J270" t="n">
-        <v>3673</v>
+        <v>3897</v>
       </c>
       <c r="K270" t="n">
-        <v>3946</v>
+        <v>4146</v>
       </c>
       <c r="L270" t="n">
-        <v>4354</v>
+        <v>4517</v>
       </c>
       <c r="M270" t="n">
-        <v>4596</v>
+        <v>4738</v>
       </c>
       <c r="N270" t="n">
-        <v>4600</v>
+        <v>4716</v>
       </c>
       <c r="O270" t="n">
-        <v>4606</v>
+        <v>4683</v>
       </c>
       <c r="P270" t="n">
-        <v>4611</v>
+        <v>4653</v>
       </c>
       <c r="Q270" t="n">
-        <v>4615</v>
+        <v>4629</v>
       </c>
       <c r="R270" t="n">
-        <v>4620</v>
+        <v>4598</v>
       </c>
       <c r="S270" t="n">
-        <v>4625</v>
+        <v>4571</v>
       </c>
       <c r="T270" t="n">
-        <v>4629</v>
+        <v>4575</v>
       </c>
       <c r="U270" t="n">
-        <v>4765</v>
+        <v>4690</v>
       </c>
       <c r="V270" t="n">
-        <v>4992</v>
+        <v>4883</v>
       </c>
       <c r="W270" t="n">
-        <v>5152</v>
+        <v>5019</v>
       </c>
       <c r="X270" t="n">
-        <v>4926</v>
+        <v>4824</v>
       </c>
       <c r="Y270" t="n">
-        <v>4589</v>
+        <v>4533</v>
       </c>
       <c r="Z270" t="n">
-        <v>4286</v>
+        <v>4271</v>
       </c>
       <c r="AA270" t="n">
-        <v>4036</v>
+        <v>4055</v>
       </c>
     </row>
     <row r="271">
@@ -22901,76 +22901,76 @@
         <v>1</v>
       </c>
       <c r="D271" t="n">
-        <v>3736</v>
+        <v>3876</v>
       </c>
       <c r="E271" t="n">
-        <v>3563</v>
+        <v>3744</v>
       </c>
       <c r="F271" t="n">
-        <v>3467</v>
+        <v>3682</v>
       </c>
       <c r="G271" t="n">
-        <v>3399</v>
+        <v>3620</v>
       </c>
       <c r="H271" t="n">
-        <v>3391</v>
+        <v>3620</v>
       </c>
       <c r="I271" t="n">
-        <v>3479</v>
+        <v>3742</v>
       </c>
       <c r="J271" t="n">
-        <v>3697</v>
+        <v>3982</v>
       </c>
       <c r="K271" t="n">
-        <v>3937</v>
+        <v>4234</v>
       </c>
       <c r="L271" t="n">
-        <v>4265</v>
+        <v>4477</v>
       </c>
       <c r="M271" t="n">
-        <v>4514</v>
+        <v>4687</v>
       </c>
       <c r="N271" t="n">
-        <v>4603</v>
+        <v>4733</v>
       </c>
       <c r="O271" t="n">
-        <v>4630</v>
+        <v>4755</v>
       </c>
       <c r="P271" t="n">
-        <v>4692</v>
+        <v>4651</v>
       </c>
       <c r="Q271" t="n">
-        <v>4710</v>
+        <v>4651</v>
       </c>
       <c r="R271" t="n">
+        <v>4651</v>
+      </c>
+      <c r="S271" t="n">
+        <v>4731</v>
+      </c>
+      <c r="T271" t="n">
+        <v>4866</v>
+      </c>
+      <c r="U271" t="n">
+        <v>5104</v>
+      </c>
+      <c r="V271" t="n">
+        <v>5273</v>
+      </c>
+      <c r="W271" t="n">
+        <v>5193</v>
+      </c>
+      <c r="X271" t="n">
+        <v>4986</v>
+      </c>
+      <c r="Y271" t="n">
         <v>4720</v>
       </c>
-      <c r="S271" t="n">
-        <v>4765</v>
-      </c>
-      <c r="T271" t="n">
-        <v>4860</v>
-      </c>
-      <c r="U271" t="n">
-        <v>5090</v>
-      </c>
-      <c r="V271" t="n">
-        <v>5326</v>
-      </c>
-      <c r="W271" t="n">
-        <v>5430</v>
-      </c>
-      <c r="X271" t="n">
-        <v>5228</v>
-      </c>
-      <c r="Y271" t="n">
-        <v>4894</v>
-      </c>
       <c r="Z271" t="n">
-        <v>4529</v>
+        <v>4457</v>
       </c>
       <c r="AA271" t="n">
-        <v>4188</v>
+        <v>4184</v>
       </c>
     </row>
     <row r="272">
@@ -22984,76 +22984,76 @@
         <v>2</v>
       </c>
       <c r="D272" t="n">
-        <v>3869</v>
+        <v>3929</v>
       </c>
       <c r="E272" t="n">
-        <v>3682</v>
+        <v>3793</v>
       </c>
       <c r="F272" t="n">
-        <v>3599</v>
+        <v>3733</v>
       </c>
       <c r="G272" t="n">
-        <v>3562</v>
+        <v>3706</v>
       </c>
       <c r="H272" t="n">
-        <v>3592</v>
+        <v>3734</v>
       </c>
       <c r="I272" t="n">
-        <v>3751</v>
+        <v>3884</v>
       </c>
       <c r="J272" t="n">
-        <v>4281</v>
+        <v>4382</v>
       </c>
       <c r="K272" t="n">
-        <v>4752</v>
+        <v>4825</v>
       </c>
       <c r="L272" t="n">
-        <v>5097</v>
+        <v>5150</v>
       </c>
       <c r="M272" t="n">
-        <v>5205</v>
+        <v>5251</v>
       </c>
       <c r="N272" t="n">
-        <v>5179</v>
+        <v>5123</v>
       </c>
       <c r="O272" t="n">
-        <v>5177</v>
+        <v>5112</v>
       </c>
       <c r="P272" t="n">
-        <v>5163</v>
+        <v>5040</v>
       </c>
       <c r="Q272" t="n">
-        <v>5174</v>
+        <v>5094</v>
       </c>
       <c r="R272" t="n">
-        <v>5168</v>
+        <v>5068</v>
       </c>
       <c r="S272" t="n">
-        <v>5159</v>
+        <v>5022</v>
       </c>
       <c r="T272" t="n">
-        <v>5155</v>
+        <v>5001</v>
       </c>
       <c r="U272" t="n">
-        <v>5289</v>
+        <v>5113</v>
       </c>
       <c r="V272" t="n">
-        <v>5577</v>
+        <v>5357</v>
       </c>
       <c r="W272" t="n">
-        <v>5748</v>
+        <v>5501</v>
       </c>
       <c r="X272" t="n">
-        <v>5523</v>
+        <v>5303</v>
       </c>
       <c r="Y272" t="n">
-        <v>5163</v>
+        <v>4985</v>
       </c>
       <c r="Z272" t="n">
-        <v>4790</v>
+        <v>4656</v>
       </c>
       <c r="AA272" t="n">
-        <v>4451</v>
+        <v>4358</v>
       </c>
     </row>
     <row r="273">
@@ -23067,76 +23067,76 @@
         <v>3</v>
       </c>
       <c r="D273" t="n">
-        <v>4001</v>
+        <v>4049</v>
       </c>
       <c r="E273" t="n">
-        <v>3835</v>
+        <v>3927</v>
       </c>
       <c r="F273" t="n">
-        <v>3751</v>
+        <v>3871</v>
       </c>
       <c r="G273" t="n">
-        <v>3719</v>
+        <v>3851</v>
       </c>
       <c r="H273" t="n">
-        <v>3753</v>
+        <v>3874</v>
       </c>
       <c r="I273" t="n">
-        <v>3897</v>
+        <v>4002</v>
       </c>
       <c r="J273" t="n">
-        <v>4403</v>
+        <v>4475</v>
       </c>
       <c r="K273" t="n">
-        <v>4850</v>
+        <v>4899</v>
       </c>
       <c r="L273" t="n">
-        <v>5188</v>
+        <v>5222</v>
       </c>
       <c r="M273" t="n">
-        <v>5278</v>
+        <v>5313</v>
       </c>
       <c r="N273" t="n">
-        <v>5260</v>
+        <v>5231</v>
       </c>
       <c r="O273" t="n">
-        <v>5250</v>
+        <v>5187</v>
       </c>
       <c r="P273" t="n">
-        <v>5236</v>
+        <v>5122</v>
       </c>
       <c r="Q273" t="n">
-        <v>5236</v>
+        <v>5115</v>
       </c>
       <c r="R273" t="n">
-        <v>5227</v>
+        <v>5078</v>
       </c>
       <c r="S273" t="n">
-        <v>5221</v>
+        <v>5057</v>
       </c>
       <c r="T273" t="n">
-        <v>5225</v>
+        <v>5069</v>
       </c>
       <c r="U273" t="n">
-        <v>5312</v>
+        <v>5163</v>
       </c>
       <c r="V273" t="n">
-        <v>5609</v>
+        <v>5412</v>
       </c>
       <c r="W273" t="n">
-        <v>5832</v>
+        <v>5573</v>
       </c>
       <c r="X273" t="n">
-        <v>5632</v>
+        <v>5390</v>
       </c>
       <c r="Y273" t="n">
-        <v>5281</v>
+        <v>5081</v>
       </c>
       <c r="Z273" t="n">
-        <v>4903</v>
+        <v>4753</v>
       </c>
       <c r="AA273" t="n">
-        <v>4534</v>
+        <v>4428</v>
       </c>
     </row>
     <row r="274">
@@ -23150,76 +23150,159 @@
         <v>4</v>
       </c>
       <c r="D274" t="n">
-        <v>4039</v>
+        <v>4122</v>
       </c>
       <c r="E274" t="n">
-        <v>3873</v>
+        <v>4002</v>
       </c>
       <c r="F274" t="n">
-        <v>3790</v>
+        <v>3947</v>
       </c>
       <c r="G274" t="n">
-        <v>3758</v>
+        <v>3927</v>
       </c>
       <c r="H274" t="n">
-        <v>3793</v>
+        <v>3950</v>
       </c>
       <c r="I274" t="n">
-        <v>3936</v>
+        <v>4077</v>
       </c>
       <c r="J274" t="n">
-        <v>4442</v>
+        <v>4548</v>
       </c>
       <c r="K274" t="n">
-        <v>4888</v>
+        <v>4971</v>
       </c>
       <c r="L274" t="n">
-        <v>5225</v>
+        <v>5292</v>
       </c>
       <c r="M274" t="n">
-        <v>5314</v>
+        <v>5383</v>
       </c>
       <c r="N274" t="n">
-        <v>5296</v>
+        <v>5300</v>
       </c>
       <c r="O274" t="n">
-        <v>5285</v>
+        <v>5254</v>
       </c>
       <c r="P274" t="n">
-        <v>5270</v>
+        <v>5187</v>
       </c>
       <c r="Q274" t="n">
-        <v>5269</v>
+        <v>5180</v>
       </c>
       <c r="R274" t="n">
-        <v>5260</v>
+        <v>5141</v>
       </c>
       <c r="S274" t="n">
-        <v>5253</v>
+        <v>5120</v>
       </c>
       <c r="T274" t="n">
-        <v>5257</v>
+        <v>5132</v>
       </c>
       <c r="U274" t="n">
-        <v>5347</v>
+        <v>5230</v>
       </c>
       <c r="V274" t="n">
-        <v>5648</v>
+        <v>5488</v>
       </c>
       <c r="W274" t="n">
-        <v>5875</v>
+        <v>5654</v>
       </c>
       <c r="X274" t="n">
-        <v>5675</v>
+        <v>5471</v>
       </c>
       <c r="Y274" t="n">
-        <v>5323</v>
+        <v>5162</v>
       </c>
       <c r="Z274" t="n">
-        <v>4945</v>
+        <v>4833</v>
       </c>
       <c r="AA274" t="n">
-        <v>4576</v>
+        <v>4509</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B275" t="n">
+        <v>11</v>
+      </c>
+      <c r="C275" t="n">
+        <v>5</v>
+      </c>
+      <c r="D275" t="n">
+        <v>4173</v>
+      </c>
+      <c r="E275" t="n">
+        <v>4055</v>
+      </c>
+      <c r="F275" t="n">
+        <v>4001</v>
+      </c>
+      <c r="G275" t="n">
+        <v>3981</v>
+      </c>
+      <c r="H275" t="n">
+        <v>4004</v>
+      </c>
+      <c r="I275" t="n">
+        <v>4131</v>
+      </c>
+      <c r="J275" t="n">
+        <v>4601</v>
+      </c>
+      <c r="K275" t="n">
+        <v>5022</v>
+      </c>
+      <c r="L275" t="n">
+        <v>5343</v>
+      </c>
+      <c r="M275" t="n">
+        <v>5434</v>
+      </c>
+      <c r="N275" t="n">
+        <v>5348</v>
+      </c>
+      <c r="O275" t="n">
+        <v>5301</v>
+      </c>
+      <c r="P275" t="n">
+        <v>5233</v>
+      </c>
+      <c r="Q275" t="n">
+        <v>5226</v>
+      </c>
+      <c r="R275" t="n">
+        <v>5187</v>
+      </c>
+      <c r="S275" t="n">
+        <v>5165</v>
+      </c>
+      <c r="T275" t="n">
+        <v>5178</v>
+      </c>
+      <c r="U275" t="n">
+        <v>5278</v>
+      </c>
+      <c r="V275" t="n">
+        <v>5542</v>
+      </c>
+      <c r="W275" t="n">
+        <v>5712</v>
+      </c>
+      <c r="X275" t="n">
+        <v>5529</v>
+      </c>
+      <c r="Y275" t="n">
+        <v>5220</v>
+      </c>
+      <c r="Z275" t="n">
+        <v>4891</v>
+      </c>
+      <c r="AA275" t="n">
+        <v>4566</v>
       </c>
     </row>
   </sheetData>

--- a/data/plexos_load_master.xlsx
+++ b/data/plexos_load_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA275"/>
+  <dimension ref="A1:AA276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22901,76 +22901,76 @@
         <v>1</v>
       </c>
       <c r="D271" t="n">
-        <v>3876</v>
+        <v>3904</v>
       </c>
       <c r="E271" t="n">
-        <v>3744</v>
+        <v>3764</v>
       </c>
       <c r="F271" t="n">
-        <v>3682</v>
+        <v>3698</v>
       </c>
       <c r="G271" t="n">
-        <v>3620</v>
+        <v>3631</v>
       </c>
       <c r="H271" t="n">
-        <v>3620</v>
+        <v>3632</v>
       </c>
       <c r="I271" t="n">
-        <v>3742</v>
+        <v>3770</v>
       </c>
       <c r="J271" t="n">
-        <v>3982</v>
+        <v>4042</v>
       </c>
       <c r="K271" t="n">
-        <v>4234</v>
+        <v>4328</v>
       </c>
       <c r="L271" t="n">
-        <v>4477</v>
+        <v>4604</v>
       </c>
       <c r="M271" t="n">
-        <v>4687</v>
+        <v>4842</v>
       </c>
       <c r="N271" t="n">
-        <v>4733</v>
+        <v>4894</v>
       </c>
       <c r="O271" t="n">
-        <v>4755</v>
+        <v>4919</v>
       </c>
       <c r="P271" t="n">
-        <v>4651</v>
+        <v>4888</v>
       </c>
       <c r="Q271" t="n">
-        <v>4651</v>
+        <v>4888</v>
       </c>
       <c r="R271" t="n">
-        <v>4651</v>
+        <v>4888</v>
       </c>
       <c r="S271" t="n">
-        <v>4731</v>
+        <v>4953</v>
       </c>
       <c r="T271" t="n">
-        <v>4866</v>
+        <v>5062</v>
       </c>
       <c r="U271" t="n">
-        <v>5104</v>
+        <v>5255</v>
       </c>
       <c r="V271" t="n">
-        <v>5273</v>
+        <v>5391</v>
       </c>
       <c r="W271" t="n">
-        <v>5193</v>
+        <v>5310</v>
       </c>
       <c r="X271" t="n">
-        <v>4986</v>
+        <v>5101</v>
       </c>
       <c r="Y271" t="n">
-        <v>4720</v>
+        <v>4832</v>
       </c>
       <c r="Z271" t="n">
-        <v>4457</v>
+        <v>4566</v>
       </c>
       <c r="AA271" t="n">
-        <v>4184</v>
+        <v>4290</v>
       </c>
     </row>
     <row r="272">
@@ -22984,76 +22984,76 @@
         <v>2</v>
       </c>
       <c r="D272" t="n">
-        <v>3929</v>
+        <v>3928</v>
       </c>
       <c r="E272" t="n">
-        <v>3793</v>
+        <v>3765</v>
       </c>
       <c r="F272" t="n">
-        <v>3733</v>
+        <v>3708</v>
       </c>
       <c r="G272" t="n">
-        <v>3706</v>
+        <v>3687</v>
       </c>
       <c r="H272" t="n">
-        <v>3734</v>
+        <v>3722</v>
       </c>
       <c r="I272" t="n">
-        <v>3884</v>
+        <v>3863</v>
       </c>
       <c r="J272" t="n">
-        <v>4382</v>
+        <v>4292</v>
       </c>
       <c r="K272" t="n">
-        <v>4825</v>
+        <v>4723</v>
       </c>
       <c r="L272" t="n">
-        <v>5150</v>
+        <v>5049</v>
       </c>
       <c r="M272" t="n">
-        <v>5251</v>
+        <v>5224</v>
       </c>
       <c r="N272" t="n">
-        <v>5123</v>
+        <v>5236</v>
       </c>
       <c r="O272" t="n">
-        <v>5112</v>
+        <v>5319</v>
       </c>
       <c r="P272" t="n">
-        <v>5040</v>
+        <v>5328</v>
       </c>
       <c r="Q272" t="n">
-        <v>5094</v>
+        <v>5391</v>
       </c>
       <c r="R272" t="n">
-        <v>5068</v>
+        <v>5213</v>
       </c>
       <c r="S272" t="n">
-        <v>5022</v>
+        <v>5227</v>
       </c>
       <c r="T272" t="n">
-        <v>5001</v>
+        <v>5228</v>
       </c>
       <c r="U272" t="n">
-        <v>5113</v>
+        <v>5399</v>
       </c>
       <c r="V272" t="n">
-        <v>5357</v>
+        <v>5587</v>
       </c>
       <c r="W272" t="n">
-        <v>5501</v>
+        <v>5490</v>
       </c>
       <c r="X272" t="n">
-        <v>5303</v>
+        <v>5257</v>
       </c>
       <c r="Y272" t="n">
-        <v>4985</v>
+        <v>4979</v>
       </c>
       <c r="Z272" t="n">
-        <v>4656</v>
+        <v>4708</v>
       </c>
       <c r="AA272" t="n">
-        <v>4358</v>
+        <v>4431</v>
       </c>
     </row>
     <row r="273">
@@ -23067,76 +23067,76 @@
         <v>3</v>
       </c>
       <c r="D273" t="n">
-        <v>4049</v>
+        <v>3986</v>
       </c>
       <c r="E273" t="n">
-        <v>3927</v>
+        <v>3847</v>
       </c>
       <c r="F273" t="n">
-        <v>3871</v>
+        <v>3789</v>
       </c>
       <c r="G273" t="n">
-        <v>3851</v>
+        <v>3767</v>
       </c>
       <c r="H273" t="n">
-        <v>3874</v>
+        <v>3786</v>
       </c>
       <c r="I273" t="n">
-        <v>4002</v>
+        <v>3921</v>
       </c>
       <c r="J273" t="n">
-        <v>4475</v>
+        <v>4448</v>
       </c>
       <c r="K273" t="n">
-        <v>4899</v>
+        <v>4916</v>
       </c>
       <c r="L273" t="n">
-        <v>5222</v>
+        <v>5279</v>
       </c>
       <c r="M273" t="n">
-        <v>5313</v>
+        <v>5393</v>
       </c>
       <c r="N273" t="n">
-        <v>5231</v>
+        <v>5335</v>
       </c>
       <c r="O273" t="n">
-        <v>5187</v>
+        <v>5303</v>
       </c>
       <c r="P273" t="n">
-        <v>5122</v>
+        <v>5258</v>
       </c>
       <c r="Q273" t="n">
-        <v>5115</v>
+        <v>5256</v>
       </c>
       <c r="R273" t="n">
-        <v>5078</v>
+        <v>5227</v>
       </c>
       <c r="S273" t="n">
-        <v>5057</v>
+        <v>5215</v>
       </c>
       <c r="T273" t="n">
-        <v>5069</v>
+        <v>5226</v>
       </c>
       <c r="U273" t="n">
-        <v>5163</v>
+        <v>5304</v>
       </c>
       <c r="V273" t="n">
-        <v>5412</v>
+        <v>5486</v>
       </c>
       <c r="W273" t="n">
-        <v>5573</v>
+        <v>5589</v>
       </c>
       <c r="X273" t="n">
-        <v>5390</v>
+        <v>5401</v>
       </c>
       <c r="Y273" t="n">
-        <v>5081</v>
+        <v>5086</v>
       </c>
       <c r="Z273" t="n">
-        <v>4753</v>
+        <v>4758</v>
       </c>
       <c r="AA273" t="n">
-        <v>4428</v>
+        <v>4433</v>
       </c>
     </row>
     <row r="274">
@@ -23150,76 +23150,76 @@
         <v>4</v>
       </c>
       <c r="D274" t="n">
-        <v>4122</v>
+        <v>4050</v>
       </c>
       <c r="E274" t="n">
-        <v>4002</v>
+        <v>3913</v>
       </c>
       <c r="F274" t="n">
-        <v>3947</v>
+        <v>3856</v>
       </c>
       <c r="G274" t="n">
-        <v>3927</v>
+        <v>3834</v>
       </c>
       <c r="H274" t="n">
-        <v>3950</v>
+        <v>3853</v>
       </c>
       <c r="I274" t="n">
-        <v>4077</v>
+        <v>3988</v>
       </c>
       <c r="J274" t="n">
-        <v>4548</v>
+        <v>4513</v>
       </c>
       <c r="K274" t="n">
-        <v>4971</v>
+        <v>4980</v>
       </c>
       <c r="L274" t="n">
-        <v>5292</v>
+        <v>5342</v>
       </c>
       <c r="M274" t="n">
-        <v>5383</v>
+        <v>5455</v>
       </c>
       <c r="N274" t="n">
-        <v>5300</v>
+        <v>5395</v>
       </c>
       <c r="O274" t="n">
-        <v>5254</v>
+        <v>5362</v>
       </c>
       <c r="P274" t="n">
-        <v>5187</v>
+        <v>5316</v>
       </c>
       <c r="Q274" t="n">
-        <v>5180</v>
+        <v>5314</v>
       </c>
       <c r="R274" t="n">
-        <v>5141</v>
+        <v>5284</v>
       </c>
       <c r="S274" t="n">
-        <v>5120</v>
+        <v>5271</v>
       </c>
       <c r="T274" t="n">
-        <v>5132</v>
+        <v>5283</v>
       </c>
       <c r="U274" t="n">
-        <v>5230</v>
+        <v>5364</v>
       </c>
       <c r="V274" t="n">
-        <v>5488</v>
+        <v>5553</v>
       </c>
       <c r="W274" t="n">
-        <v>5654</v>
+        <v>5661</v>
       </c>
       <c r="X274" t="n">
-        <v>5471</v>
+        <v>5473</v>
       </c>
       <c r="Y274" t="n">
-        <v>5162</v>
+        <v>5158</v>
       </c>
       <c r="Z274" t="n">
-        <v>4833</v>
+        <v>4829</v>
       </c>
       <c r="AA274" t="n">
-        <v>4509</v>
+        <v>4504</v>
       </c>
     </row>
     <row r="275">
@@ -23233,76 +23233,159 @@
         <v>5</v>
       </c>
       <c r="D275" t="n">
-        <v>4173</v>
+        <v>4166</v>
       </c>
       <c r="E275" t="n">
-        <v>4055</v>
+        <v>4032</v>
       </c>
       <c r="F275" t="n">
-        <v>4001</v>
+        <v>3977</v>
       </c>
       <c r="G275" t="n">
-        <v>3981</v>
+        <v>3955</v>
       </c>
       <c r="H275" t="n">
-        <v>4004</v>
+        <v>3974</v>
       </c>
       <c r="I275" t="n">
-        <v>4131</v>
+        <v>4108</v>
       </c>
       <c r="J275" t="n">
-        <v>4601</v>
+        <v>4631</v>
       </c>
       <c r="K275" t="n">
-        <v>5022</v>
+        <v>5095</v>
       </c>
       <c r="L275" t="n">
-        <v>5343</v>
+        <v>5455</v>
       </c>
       <c r="M275" t="n">
-        <v>5434</v>
+        <v>5568</v>
       </c>
       <c r="N275" t="n">
-        <v>5348</v>
+        <v>5504</v>
       </c>
       <c r="O275" t="n">
-        <v>5301</v>
+        <v>5469</v>
       </c>
       <c r="P275" t="n">
-        <v>5233</v>
+        <v>5419</v>
       </c>
       <c r="Q275" t="n">
-        <v>5226</v>
+        <v>5417</v>
       </c>
       <c r="R275" t="n">
-        <v>5187</v>
+        <v>5385</v>
       </c>
       <c r="S275" t="n">
-        <v>5165</v>
+        <v>5371</v>
       </c>
       <c r="T275" t="n">
-        <v>5178</v>
+        <v>5384</v>
       </c>
       <c r="U275" t="n">
-        <v>5278</v>
+        <v>5472</v>
       </c>
       <c r="V275" t="n">
-        <v>5542</v>
+        <v>5675</v>
       </c>
       <c r="W275" t="n">
-        <v>5712</v>
+        <v>5790</v>
       </c>
       <c r="X275" t="n">
-        <v>5529</v>
+        <v>5602</v>
       </c>
       <c r="Y275" t="n">
-        <v>5220</v>
+        <v>5287</v>
       </c>
       <c r="Z275" t="n">
-        <v>4891</v>
+        <v>4958</v>
       </c>
       <c r="AA275" t="n">
-        <v>4566</v>
+        <v>4632</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B276" t="n">
+        <v>11</v>
+      </c>
+      <c r="C276" t="n">
+        <v>6</v>
+      </c>
+      <c r="D276" t="n">
+        <v>4251</v>
+      </c>
+      <c r="E276" t="n">
+        <v>4119</v>
+      </c>
+      <c r="F276" t="n">
+        <v>4065</v>
+      </c>
+      <c r="G276" t="n">
+        <v>4044</v>
+      </c>
+      <c r="H276" t="n">
+        <v>4063</v>
+      </c>
+      <c r="I276" t="n">
+        <v>4196</v>
+      </c>
+      <c r="J276" t="n">
+        <v>4716</v>
+      </c>
+      <c r="K276" t="n">
+        <v>5179</v>
+      </c>
+      <c r="L276" t="n">
+        <v>5538</v>
+      </c>
+      <c r="M276" t="n">
+        <v>5650</v>
+      </c>
+      <c r="N276" t="n">
+        <v>5583</v>
+      </c>
+      <c r="O276" t="n">
+        <v>5546</v>
+      </c>
+      <c r="P276" t="n">
+        <v>5495</v>
+      </c>
+      <c r="Q276" t="n">
+        <v>5493</v>
+      </c>
+      <c r="R276" t="n">
+        <v>5459</v>
+      </c>
+      <c r="S276" t="n">
+        <v>5445</v>
+      </c>
+      <c r="T276" t="n">
+        <v>5456</v>
+      </c>
+      <c r="U276" t="n">
+        <v>5531</v>
+      </c>
+      <c r="V276" t="n">
+        <v>5706</v>
+      </c>
+      <c r="W276" t="n">
+        <v>5805</v>
+      </c>
+      <c r="X276" t="n">
+        <v>5622</v>
+      </c>
+      <c r="Y276" t="n">
+        <v>5315</v>
+      </c>
+      <c r="Z276" t="n">
+        <v>4995</v>
+      </c>
+      <c r="AA276" t="n">
+        <v>4677</v>
       </c>
     </row>
   </sheetData>
